--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC8E901-5EDB-4E9F-B8E9-D11753F9C635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672732F1-95CE-471A-9A0E-90CE6C9C00BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,12 +108,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="644">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 28/09/2026 10:11 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 28/09/2026 10:49 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -299,7 +299,7 @@
     <t>Dias de carga a descarga (lead time)</t>
   </si>
   <si>
-    <t>Regla de Gonzalo: lo que carga lunes a miercoles entra en la semana; viernes y sabado entra lunes o martes. Bolivia 6 dias. OJO Paraguay: 3 es optimista, la mediana real es 4 (fila 44): la mitad de los camiones PY cargados un martes descargan domingo/lunes. Se deja 3 para que coincida con el simulador web y el WhatsApp; cambiar a 4 si Gonzalo quiere planificar con el real.</t>
+    <t>Brasil 3: regla de Gonzalo (lo que carga lunes a miercoles entra en la semana; viernes y sabado entra lunes o martes). Paraguay 4: mediana observada en Aloha, decidido por Gonzalo el 28/09/2026 ("paraguay vamos a 4 dias"): un camion PY cargado el martes descarga el sabado y entra en la semana; el del miercoles ya no. Bolivia 6. Los tres valores vienen de plan_compras.json y son los mismos del simulador web y del WhatsApp.</t>
   </si>
   <si>
     <t>Cajas por camion (tipico)</t>
@@ -653,15 +653,21 @@
     <t>OTIF (1 = descargo a tiempo)</t>
   </si>
   <si>
+    <t>Paraguay AS</t>
+  </si>
+  <si>
+    <t>MARSO EMPRENDIMIENTOS S.R.L.</t>
+  </si>
+  <si>
+    <t>Aloha</t>
+  </si>
+  <si>
+    <t>Aloha: Solicitado</t>
+  </si>
+  <si>
     <t>Bolivia</t>
   </si>
   <si>
-    <t>Aloha</t>
-  </si>
-  <si>
-    <t>Aloha: Solicitado</t>
-  </si>
-  <si>
     <t>Cassio Hauck</t>
   </si>
   <si>
@@ -671,9 +677,6 @@
     <t>FG</t>
   </si>
   <si>
-    <t>Paraguay AS</t>
-  </si>
-  <si>
     <t>Dictado</t>
   </si>
   <si>
@@ -791,7 +794,7 @@
     <t>STOCK PROYECTADO</t>
   </si>
   <si>
-    <t>Fecha limite de carga</t>
+    <t>Fecha limite de carga (el lead time mas largo BR/PY)</t>
   </si>
   <si>
     <t>CAMIONES A CARGAR</t>
@@ -839,7 +842,7 @@
     <t>Camiones a cargar</t>
   </si>
   <si>
-    <t>Cargar hasta</t>
+    <t>Cargar hasta (por origen)</t>
   </si>
   <si>
     <t>Origen sugerido</t>
@@ -3790,12 +3793,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45">
@@ -3803,31 +3806,31 @@
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>169</v>
@@ -3844,7 +3847,7 @@
       </c>
       <c r="C6" s="7">
         <f>Proyeccion!E6</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="D6" s="7">
         <f>Demanda!H7</f>
@@ -3864,7 +3867,7 @@
       </c>
       <c r="H6" s="7">
         <f ca="1">Proyeccion!L6</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="I6" s="7" t="str">
         <f t="shared" ref="I6:I18" si="3">IF(CapFisica="","",CapFisica)</f>
@@ -3910,7 +3913,7 @@
       </c>
       <c r="H7" s="7">
         <f ca="1">Proyeccion!L7</f>
-        <v>22918</v>
+        <v>22898</v>
       </c>
       <c r="I7" s="7" t="str">
         <f t="shared" si="3"/>
@@ -3956,7 +3959,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>22810</v>
+        <v>22790</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4002,7 +4005,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>22774</v>
+        <v>22754</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4048,7 +4051,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>22738</v>
+        <v>22718</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4094,7 +4097,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>22802</v>
+        <v>22782</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4140,7 +4143,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>22866</v>
+        <v>22846</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4186,7 +4189,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>22930</v>
+        <v>22910</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4232,7 +4235,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>22994</v>
+        <v>22974</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4278,7 +4281,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>23058</v>
+        <v>23038</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4324,7 +4327,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>23122</v>
+        <v>23102</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4370,7 +4373,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>23186</v>
+        <v>23166</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4416,7 +4419,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>23250</v>
+        <v>23230</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4433,7 +4436,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -4466,184 +4469,184 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B5" s="12">
         <f>ConteoTotal</f>
         <v>26972</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
       <c r="A6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B6" s="23">
         <f>ConteoTotal/(INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))/DiasVenta)</f>
         <v>10.114500000000001</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B7" s="12">
         <f ca="1">IFERROR(INDEX(PrStock,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
-        <v>22918</v>
+        <v>22898</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B8" s="24">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B9" s="24">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B10" s="23">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.0505882352941178</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B11" s="24">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B12" s="24">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B13" s="23">
         <f>ConteoTotal/INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))</f>
         <v>1.6857500000000001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B14" s="12">
         <f>ConteoBR*CostoBR+ConteoPY*CostoPY+ConteoBO*CostoBO</f>
         <v>196107.57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30">
       <c r="A15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B15" s="12">
         <f ca="1">SUM(CgPipeline)</f>
-        <v>5934</v>
+        <v>6914</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B16" s="25">
         <f>PrecioBR_BRL-(CepeaKg*KgCaja+ServiciosCaja)</f>
         <v>-7.0899999999999963</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B17" s="26">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="PY")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"PY",Proveedores!D5:D60),"")</f>
         <v>0.48076923076923078</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B18" s="26">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="BR")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"BR",Proveedores!D5:D60),"")</f>
@@ -4655,31 +4658,31 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B19" s="23">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>12.5</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30">
       <c r="A20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B20" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
         <v>0.6047502310814612</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B21" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B22" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4703,206 +4706,206 @@
     </row>
     <row r="23" spans="1:3" ht="30">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>355060.63999999978</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B24" s="24">
         <f>COUNTIFS(CgEstado,"Supuesto*",CgCuenta,1)</f>
         <v>103</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B25" s="27">
         <f>IFERROR(AVERAGE(Proveedores!R5:R60),"")</f>
         <v>-9.5789473684210517E-4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
       <c r="A26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B26" s="26" t="str">
         <f>IFERROR(AVERAGE(CgOTIF),"sin descargas reales todavia")</f>
         <v>sin descargas reales todavia</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B27" s="24">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" s="28" t="str">
         <f>IFERROR(SUMPRODUCT((Demanda!O6:O18&lt;&gt;"")*ABS(Demanda!P6:P18))/COUNTIF(Demanda!O6:O18,"&lt;&gt;"),"sin venta real cargada")</f>
         <v>sin venta real cargada</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30">
       <c r="A30" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="45">
       <c r="A31" s="29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45">
       <c r="A32" s="29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45">
       <c r="A33" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30">
       <c r="A34" s="29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30">
       <c r="A35" s="29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="30">
       <c r="A36" s="29" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="45">
       <c r="A37" s="29" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45">
       <c r="A38" s="29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30">
       <c r="A39" s="29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30">
       <c r="A40" s="29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30">
       <c r="A41" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4934,12 +4937,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="90">
@@ -4947,64 +4950,64 @@
         <v>164</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -5012,10 +5015,10 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -5039,10 +5042,10 @@
         <v>1008</v>
       </c>
       <c r="K5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M5" s="10">
         <v>37.75</v>
@@ -5059,19 +5062,19 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R5" s="32">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="S5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T5" s="21">
         <v>1.2</v>
       </c>
       <c r="U5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -5079,10 +5082,10 @@
         <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -5106,10 +5109,10 @@
         <v>1008</v>
       </c>
       <c r="K6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M6" s="10">
         <v>37</v>
@@ -5126,19 +5129,19 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R6" s="32">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="S6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T6" s="21">
         <v>1.6</v>
       </c>
       <c r="U6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -5146,10 +5149,10 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -5173,10 +5176,10 @@
         <v>936</v>
       </c>
       <c r="K7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M7" s="10">
         <v>38.64</v>
@@ -5193,19 +5196,19 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R7" s="32">
         <v>-1.4E-3</v>
       </c>
       <c r="S7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T7" s="21">
         <v>2.5</v>
       </c>
       <c r="U7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -5213,10 +5216,10 @@
         <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5240,10 +5243,10 @@
         <v>1008</v>
       </c>
       <c r="K8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M8" s="10">
         <v>41.63</v>
@@ -5260,19 +5263,19 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R8" s="32">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T8" s="21">
         <v>0.6</v>
       </c>
       <c r="U8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -5280,10 +5283,10 @@
         <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -5307,10 +5310,10 @@
         <v>1008</v>
       </c>
       <c r="K9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M9" s="10">
         <v>40.74</v>
@@ -5327,19 +5330,19 @@
         <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R9" s="32">
         <v>-7.7999999999999996E-3</v>
       </c>
       <c r="S9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T9" s="21">
         <v>0.4</v>
       </c>
       <c r="U9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -5347,10 +5350,10 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -5374,10 +5377,10 @@
         <v>1008</v>
       </c>
       <c r="K10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M10" s="10">
         <v>40.65</v>
@@ -5394,19 +5397,19 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R10" s="32">
         <v>-4.0000000000000002E-4</v>
       </c>
       <c r="S10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T10" s="21">
         <v>1</v>
       </c>
       <c r="U10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -5414,10 +5417,10 @@
         <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -5441,10 +5444,10 @@
         <v>1008</v>
       </c>
       <c r="K11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M11" s="10">
         <v>42.33</v>
@@ -5467,7 +5470,7 @@
         <v>3</v>
       </c>
       <c r="U11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -5475,10 +5478,10 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -5502,10 +5505,10 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M12" s="10">
         <v>42.16</v>
@@ -5522,19 +5525,19 @@
         <v>3</v>
       </c>
       <c r="Q12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R12" s="32">
         <v>-1E-4</v>
       </c>
       <c r="S12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T12" s="21">
         <v>0.4</v>
       </c>
       <c r="U12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -5542,10 +5545,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -5569,10 +5572,10 @@
         <v>1008</v>
       </c>
       <c r="K13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M13" s="10">
         <v>37.64</v>
@@ -5589,7 +5592,7 @@
         <v>3</v>
       </c>
       <c r="U13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -5597,10 +5600,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -5624,10 +5627,10 @@
         <v>1008</v>
       </c>
       <c r="K14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M14" s="10">
         <v>37.799999999999997</v>
@@ -5644,7 +5647,7 @@
         <v>3</v>
       </c>
       <c r="U14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -5652,10 +5655,10 @@
         <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -5679,10 +5682,10 @@
         <v>1008</v>
       </c>
       <c r="K15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M15" s="10">
         <v>41.14</v>
@@ -5699,19 +5702,19 @@
         <v>3</v>
       </c>
       <c r="Q15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R15" s="32">
         <v>-1.8E-3</v>
       </c>
       <c r="S15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="T15" s="21">
         <v>0.3</v>
       </c>
       <c r="U15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -5719,10 +5722,10 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -5746,10 +5749,10 @@
         <v>980</v>
       </c>
       <c r="K16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
@@ -5760,22 +5763,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="R16" s="32">
         <v>-1E-3</v>
       </c>
       <c r="S16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T16" s="21">
         <v>2</v>
       </c>
       <c r="U16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -5783,10 +5786,10 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -5810,10 +5813,10 @@
         <v>980</v>
       </c>
       <c r="K17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="0"/>
@@ -5824,22 +5827,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R17" s="32">
         <v>-3.8999999999999998E-3</v>
       </c>
       <c r="S17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T17" s="21">
         <v>1.8</v>
       </c>
       <c r="U17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -5847,10 +5850,10 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D18">
         <v>12</v>
@@ -5874,10 +5877,10 @@
         <v>980</v>
       </c>
       <c r="K18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
@@ -5888,22 +5891,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R18" s="32">
         <v>1E-4</v>
       </c>
       <c r="S18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T18" s="21">
         <v>0.6</v>
       </c>
       <c r="U18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -5911,10 +5914,10 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -5938,10 +5941,10 @@
         <v>980</v>
       </c>
       <c r="K19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="0"/>
@@ -5952,22 +5955,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="R19" s="32">
         <v>-1.5E-3</v>
       </c>
       <c r="S19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T19" s="21">
         <v>0.5</v>
       </c>
       <c r="U19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -5975,10 +5978,10 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -6002,10 +6005,10 @@
         <v>1050</v>
       </c>
       <c r="K20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="0"/>
@@ -6016,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q20" t="s">
         <v>3</v>
@@ -6025,7 +6028,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -6033,10 +6036,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -6060,10 +6063,10 @@
         <v>1050</v>
       </c>
       <c r="K21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="0"/>
@@ -6074,7 +6077,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q21" t="s">
         <v>3</v>
@@ -6083,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="U21" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -6091,10 +6094,10 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -6118,7 +6121,7 @@
         <v>3</v>
       </c>
       <c r="L22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="0"/>
@@ -6129,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q22" t="s">
         <v>3</v>
@@ -6138,7 +6141,7 @@
         <v>3</v>
       </c>
       <c r="U22" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -6146,10 +6149,10 @@
         <v>58</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D23" s="33">
         <v>0</v>
@@ -6165,7 +6168,7 @@
         <v>982</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L23" s="33"/>
       <c r="M23" s="35">
@@ -6180,20 +6183,20 @@
         <v>0</v>
       </c>
       <c r="P23" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R23" s="36">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="S23" s="33" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="T23" s="33"/>
       <c r="U23" s="33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -6201,10 +6204,10 @@
         <v>58</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D24" s="33">
         <v>0</v>
@@ -6220,7 +6223,7 @@
         <v>976</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L24" s="33"/>
       <c r="M24" s="35">
@@ -6235,20 +6238,20 @@
         <v>0</v>
       </c>
       <c r="P24" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R24" s="36">
         <v>-8.0000000000000004E-4</v>
       </c>
       <c r="S24" s="33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T24" s="33"/>
       <c r="U24" s="33" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -6256,10 +6259,10 @@
         <v>58</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D25" s="33">
         <v>0</v>
@@ -6275,7 +6278,7 @@
         <v>1008</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L25" s="33"/>
       <c r="M25" s="35">
@@ -6290,20 +6293,20 @@
         <v>0</v>
       </c>
       <c r="P25" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R25" s="36">
         <v>0</v>
       </c>
       <c r="S25" s="33" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="T25" s="33"/>
       <c r="U25" s="33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -6311,10 +6314,10 @@
         <v>58</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D26" s="33">
         <v>0</v>
@@ -6330,7 +6333,7 @@
         <v>996</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L26" s="33"/>
       <c r="M26" s="33"/>
@@ -6343,20 +6346,20 @@
         <v>0</v>
       </c>
       <c r="P26" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="R26" s="36">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="S26" s="33" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T26" s="33"/>
       <c r="U26" s="33" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -6364,10 +6367,10 @@
         <v>59</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D27" s="33">
         <v>0</v>
@@ -6383,7 +6386,7 @@
         <v>972</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -6396,20 +6399,20 @@
         <v>0</v>
       </c>
       <c r="P27" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R27" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="S27" s="33" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="T27" s="33"/>
       <c r="U27" s="33" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -6417,10 +6420,10 @@
         <v>59</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D28" s="33">
         <v>0</v>
@@ -6449,20 +6452,20 @@
         <v>0</v>
       </c>
       <c r="P28" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R28" s="36">
         <v>-1.4E-3</v>
       </c>
       <c r="S28" s="33" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T28" s="33"/>
       <c r="U28" s="33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -6470,10 +6473,10 @@
         <v>59</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D29" s="33">
         <v>0</v>
@@ -6502,25 +6505,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="R29" s="36">
         <v>-1E-3</v>
       </c>
       <c r="S29" s="33" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T29" s="33"/>
       <c r="U29" s="33" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -6551,34 +6554,34 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30">
       <c r="A4" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B5" s="17">
         <v>0.18</v>
@@ -6590,12 +6593,12 @@
         <v>8600</v>
       </c>
       <c r="E5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B6" s="17">
         <v>9.5000000000000001E-2</v>
@@ -6607,12 +6610,12 @@
         <v>4200</v>
       </c>
       <c r="E6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B7" s="17">
         <v>6.9000000000000006E-2</v>
@@ -6629,7 +6632,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B8" s="17">
         <v>6.3E-2</v>
@@ -6646,7 +6649,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B9" s="17">
         <v>5.1999999999999998E-2</v>
@@ -6663,7 +6666,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B10" s="17">
         <v>4.7E-2</v>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B11" s="17">
         <v>4.2000000000000003E-2</v>
@@ -6692,12 +6695,12 @@
         <v>2100</v>
       </c>
       <c r="E11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B12" s="17">
         <v>0.04</v>
@@ -6709,12 +6712,12 @@
         <v>1750</v>
       </c>
       <c r="E12" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B13" s="17">
         <v>3.6999999999999998E-2</v>
@@ -6731,7 +6734,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B14" s="17">
         <v>3.5000000000000003E-2</v>
@@ -6748,7 +6751,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B15" s="17">
         <v>3.4000000000000002E-2</v>
@@ -6765,7 +6768,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B16" s="17">
         <v>3.1E-2</v>
@@ -6782,7 +6785,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B17" s="17">
         <v>0.03</v>
@@ -6799,18 +6802,18 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B18" s="17">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B19" s="17">
         <v>2.5999999999999999E-2</v>
@@ -6821,18 +6824,18 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B20" s="17">
         <v>2.4E-2</v>
       </c>
       <c r="E20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B21" s="17">
         <v>2.3E-2</v>
@@ -6843,7 +6846,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B22" s="17">
         <v>2.1000000000000001E-2</v>
@@ -6854,7 +6857,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B23" s="17">
         <v>1.7999999999999999E-2</v>
@@ -6865,7 +6868,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -6884,164 +6887,164 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30">
       <c r="A17" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30">
       <c r="A18" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30">
       <c r="A20" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>3</v>
@@ -7049,138 +7052,138 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -7220,12 +7223,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7233,140 +7236,140 @@
         <v>163</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45">
       <c r="A5" s="37" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30">
       <c r="A6" s="37" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45">
       <c r="A7" s="37" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30">
       <c r="A8" s="37" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30">
       <c r="A9" s="37" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30">
       <c r="A10" s="37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30">
       <c r="A11" s="37" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -7518,7 +7521,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9">
         <v>6</v>
@@ -9027,43 +9030,43 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" ref="C5:C68" si="1">IF(B5="","",TEXT(B5,"ddd"))</f>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>181</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="G5" s="8">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" ref="H5:H68" si="2">IF(B5="","",IF(G5&lt;&gt;"",G5,IFERROR(INDEX(CajasOrigen,MATCH(D5,Origenes,0)),CajasProm)))</f>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5">
         <f t="shared" ref="K5:K68" si="3">IF(B5="","",IFERROR(INDEX(Lags,MATCH(D5,Origenes,0)),LagBR)+IF(J5&lt;&gt;"",0,AtrasoDias))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5">
         <f t="shared" ref="L5:L68" si="4">IF(B5="","",IF(J5&lt;&gt;"",J5,B5+K5))</f>
-        <v>46296</v>
+        <v>46292</v>
       </c>
       <c r="M5" s="5">
         <f t="shared" ref="M5:M68" si="5">IF(L5="","",L5-WEEKDAY(L5,2)+1)</f>
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="N5">
         <f t="shared" ref="N5:N68" si="6">IF(L5="","",IF(L5&gt;FechaConteo,1,0)*IF(I5="Supuesto",SupPY,IF(I5="Supuesto BR",SupBR,1)))</f>
@@ -9071,18 +9074,18 @@
       </c>
       <c r="O5" s="10">
         <f t="shared" ref="O5:O68" si="7">IF(D5="","",IFERROR(INDEX(CostoOrigen,MATCH(D5,Origenes,0)),0))</f>
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="P5" s="7">
         <f t="shared" ref="P5:P68" si="8">IF(H5="","",H5*O5)</f>
-        <v>11340</v>
+        <v>6860</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" ref="R5:R68" si="9">IF(B5="","",IF(J5&lt;&gt;"",J5,B5+IFERROR(INDEX(LagsP90,MATCH(D5,Origenes,0)),K5)))</f>
-        <v>46298</v>
+        <v>46293</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" ref="S5:S68" si="10">IF(R5="","",R5-WEEKDAY(R5,2)+1)</f>
@@ -9090,7 +9093,7 @@
       </c>
       <c r="T5" s="7">
         <f t="shared" ref="T5:T68" ca="1" si="11">IF(B5="","",IF(AND(B5&lt;=FechaHoy,J5="",I5&lt;&gt;"Supuesto",I5&lt;&gt;"Simulado"),H5,0))</f>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" ref="U5:U68" si="12">IF(J5="","",IF(J5-B5&lt;=K5+1,1,0))</f>
@@ -9110,32 +9113,32 @@
         <v>vie</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="8">
-        <v>936</v>
+        <v>1050</v>
       </c>
       <c r="H6" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1050</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" si="4"/>
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" si="5"/>
@@ -9147,18 +9150,18 @@
       </c>
       <c r="O6" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>11340</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="9"/>
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="10"/>
@@ -9166,7 +9169,7 @@
       </c>
       <c r="T6" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>936</v>
+        <v>1050</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="12"/>
@@ -9189,20 +9192,20 @@
         <v>58</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="G7" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7">
@@ -9227,10 +9230,10 @@
       </c>
       <c r="P7" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="9"/>
@@ -9242,7 +9245,7 @@
       </c>
       <c r="T7" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="12"/>
@@ -9255,30 +9258,30 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>187</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="G8" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8">
@@ -9287,7 +9290,7 @@
       </c>
       <c r="L8" s="5">
         <f t="shared" si="4"/>
-        <v>46296</v>
+        <v>46293</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" si="5"/>
@@ -9299,18 +9302,18 @@
       </c>
       <c r="O8" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="9"/>
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="10"/>
@@ -9318,7 +9321,7 @@
       </c>
       <c r="T8" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="12"/>
@@ -9341,7 +9344,7 @@
         <v>59</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>3</v>
@@ -9354,16 +9357,16 @@
         <v>980</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="4"/>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="5"/>
@@ -9382,7 +9385,7 @@
         <v>6860</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="9"/>
@@ -9417,7 +9420,7 @@
         <v>59</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>3</v>
@@ -9430,16 +9433,16 @@
         <v>980</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="4"/>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" si="5"/>
@@ -9458,7 +9461,7 @@
         <v>6860</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="9"/>
@@ -9483,35 +9486,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>lun</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>195</v>
+        <v>3</v>
       </c>
       <c r="G11" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="4"/>
@@ -9527,26 +9530,26 @@
       </c>
       <c r="O11" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="9"/>
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="T11" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="12"/>
@@ -9566,23 +9569,23 @@
         <v>mar</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="G12" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12">
@@ -9603,22 +9606,22 @@
       </c>
       <c r="O12" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>197</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="9"/>
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="10"/>
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="T12" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -9635,35 +9638,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>mar</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>199</v>
+        <v>3</v>
       </c>
       <c r="G13" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="4"/>
@@ -9679,22 +9682,22 @@
       </c>
       <c r="O13" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="9"/>
-        <v>46301</v>
+        <v>46299</v>
       </c>
       <c r="S13" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="T13" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -9721,10 +9724,10 @@
         <v>58</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G14" s="8">
         <v>1008</v>
@@ -9734,7 +9737,7 @@
         <v>1008</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14">
@@ -9762,7 +9765,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="9"/>
@@ -9797,10 +9800,10 @@
         <v>58</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="G15" s="8">
         <v>1008</v>
@@ -9810,7 +9813,7 @@
         <v>1008</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15">
@@ -9838,7 +9841,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="9"/>
@@ -9863,20 +9866,20 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G16" s="8">
         <v>1008</v>
@@ -9886,7 +9889,7 @@
         <v>1008</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16">
@@ -9895,11 +9898,11 @@
       </c>
       <c r="L16" s="5">
         <f t="shared" si="4"/>
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="M16" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="N16">
         <f t="shared" si="6"/>
@@ -9918,7 +9921,7 @@
       </c>
       <c r="R16" s="5">
         <f t="shared" si="9"/>
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="S16" s="5">
         <f t="shared" si="10"/>
@@ -9949,20 +9952,20 @@
         <v>58</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G17" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17">
@@ -9987,10 +9990,10 @@
       </c>
       <c r="P17" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R17" s="5">
         <f t="shared" si="9"/>
@@ -10025,20 +10028,20 @@
         <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G18" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18">
@@ -10063,10 +10066,10 @@
       </c>
       <c r="P18" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R18" s="5">
         <f t="shared" si="9"/>
@@ -10101,10 +10104,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G19" s="8">
         <v>1008</v>
@@ -10114,7 +10117,7 @@
         <v>1008</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19">
@@ -10142,7 +10145,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="9"/>
@@ -10177,10 +10180,10 @@
         <v>58</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G20" s="8">
         <v>1008</v>
@@ -10190,7 +10193,7 @@
         <v>1008</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20">
@@ -10218,7 +10221,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R20" s="5">
         <f t="shared" si="9"/>
@@ -10253,10 +10256,10 @@
         <v>58</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G21" s="8">
         <v>1008</v>
@@ -10266,7 +10269,7 @@
         <v>1008</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21">
@@ -10294,7 +10297,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R21" s="5">
         <f t="shared" si="9"/>
@@ -10332,7 +10335,7 @@
         <v>210</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G22" s="8">
         <v>1008</v>
@@ -10342,7 +10345,7 @@
         <v>1008</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22">
@@ -10370,7 +10373,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R22" s="5">
         <f t="shared" si="9"/>
@@ -10405,10 +10408,10 @@
         <v>58</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G23" s="8">
         <v>1008</v>
@@ -10418,7 +10421,7 @@
         <v>1008</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23">
@@ -10446,7 +10449,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R23" s="5">
         <f t="shared" si="9"/>
@@ -10471,30 +10474,30 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="G24" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H24" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24">
@@ -10503,7 +10506,7 @@
       </c>
       <c r="L24" s="5">
         <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="M24" s="5">
         <f t="shared" si="5"/>
@@ -10515,18 +10518,18 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P24" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="R24" s="5">
         <f t="shared" si="9"/>
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="S24" s="5">
         <f t="shared" si="10"/>
@@ -10557,7 +10560,7 @@
         <v>59</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>3</v>
@@ -10570,16 +10573,16 @@
         <v>980</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M25" s="5">
         <f t="shared" si="5"/>
@@ -10598,7 +10601,7 @@
         <v>6860</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" si="9"/>
@@ -10633,7 +10636,7 @@
         <v>59</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>3</v>
@@ -10646,16 +10649,16 @@
         <v>980</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M26" s="5">
         <f t="shared" si="5"/>
@@ -10674,7 +10677,7 @@
         <v>6860</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="9"/>
@@ -10709,7 +10712,7 @@
         <v>59</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>3</v>
@@ -10722,16 +10725,16 @@
         <v>980</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M27" s="5">
         <f t="shared" si="5"/>
@@ -10750,7 +10753,7 @@
         <v>6860</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R27" s="5">
         <f t="shared" si="9"/>
@@ -10785,7 +10788,7 @@
         <v>59</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>3</v>
@@ -10798,16 +10801,16 @@
         <v>980</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M28" s="5">
         <f t="shared" si="5"/>
@@ -10826,7 +10829,7 @@
         <v>6860</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="9"/>
@@ -10851,43 +10854,43 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G29" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H29" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="M29" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N29">
         <f t="shared" si="6"/>
@@ -10895,22 +10898,22 @@
       </c>
       <c r="O29" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="S29" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="T29" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -10937,7 +10940,7 @@
         <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>3</v>
@@ -10950,7 +10953,7 @@
         <v>1008</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30">
@@ -10978,7 +10981,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
@@ -11013,7 +11016,7 @@
         <v>58</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>3</v>
@@ -11026,7 +11029,7 @@
         <v>1008</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31">
@@ -11054,7 +11057,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="9"/>
@@ -11089,7 +11092,7 @@
         <v>58</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>3</v>
@@ -11102,7 +11105,7 @@
         <v>1008</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32">
@@ -11130,7 +11133,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
@@ -11165,7 +11168,7 @@
         <v>58</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>3</v>
@@ -11178,7 +11181,7 @@
         <v>1008</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33">
@@ -11206,7 +11209,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="9"/>
@@ -11241,7 +11244,7 @@
         <v>58</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>3</v>
@@ -11254,7 +11257,7 @@
         <v>1008</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34">
@@ -11282,7 +11285,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
@@ -11317,7 +11320,7 @@
         <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>3</v>
@@ -11330,7 +11333,7 @@
         <v>1008</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35">
@@ -11358,7 +11361,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
@@ -11393,7 +11396,7 @@
         <v>58</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>3</v>
@@ -11406,7 +11409,7 @@
         <v>1008</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36">
@@ -11434,7 +11437,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R36" s="5">
         <f t="shared" si="9"/>
@@ -11459,30 +11462,30 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G37" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37">
@@ -11491,7 +11494,7 @@
       </c>
       <c r="L37" s="5">
         <f t="shared" si="4"/>
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="M37" s="5">
         <f t="shared" si="5"/>
@@ -11503,18 +11506,18 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P37" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="S37" s="5">
         <f t="shared" si="10"/>
@@ -11545,7 +11548,7 @@
         <v>59</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>3</v>
@@ -11558,16 +11561,16 @@
         <v>980</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="4"/>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M38" s="5">
         <f t="shared" si="5"/>
@@ -11586,7 +11589,7 @@
         <v>6860</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="9"/>
@@ -11621,7 +11624,7 @@
         <v>59</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>3</v>
@@ -11634,16 +11637,16 @@
         <v>980</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J39" s="6"/>
       <c r="K39">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="4"/>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M39" s="5">
         <f t="shared" si="5"/>
@@ -11662,7 +11665,7 @@
         <v>6860</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R39" s="5">
         <f t="shared" si="9"/>
@@ -11697,7 +11700,7 @@
         <v>59</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>3</v>
@@ -11710,16 +11713,16 @@
         <v>980</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="4"/>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M40" s="5">
         <f t="shared" si="5"/>
@@ -11738,7 +11741,7 @@
         <v>6860</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
@@ -11773,7 +11776,7 @@
         <v>59</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>3</v>
@@ -11786,16 +11789,16 @@
         <v>980</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="4"/>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="5"/>
@@ -11814,7 +11817,7 @@
         <v>6860</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
@@ -11839,43 +11842,43 @@
         <v>38</v>
       </c>
       <c r="B42" s="6">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G42" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H42" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="M42" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="N42">
         <f t="shared" si="6"/>
@@ -11883,22 +11886,22 @@
       </c>
       <c r="O42" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P42" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="S42" s="5">
         <f t="shared" si="10"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="T42" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -11925,7 +11928,7 @@
         <v>58</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>3</v>
@@ -11938,7 +11941,7 @@
         <v>1008</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43">
@@ -11966,7 +11969,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R43" s="5">
         <f t="shared" si="9"/>
@@ -12001,7 +12004,7 @@
         <v>58</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>3</v>
@@ -12014,7 +12017,7 @@
         <v>1008</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44">
@@ -12042,7 +12045,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R44" s="5">
         <f t="shared" si="9"/>
@@ -12077,7 +12080,7 @@
         <v>58</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>3</v>
@@ -12090,7 +12093,7 @@
         <v>1008</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45">
@@ -12118,7 +12121,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R45" s="5">
         <f t="shared" si="9"/>
@@ -12153,7 +12156,7 @@
         <v>58</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>3</v>
@@ -12166,7 +12169,7 @@
         <v>1008</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46">
@@ -12194,7 +12197,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="9"/>
@@ -12229,7 +12232,7 @@
         <v>58</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
@@ -12242,7 +12245,7 @@
         <v>1008</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47">
@@ -12270,7 +12273,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
@@ -12305,7 +12308,7 @@
         <v>58</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
@@ -12318,7 +12321,7 @@
         <v>1008</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
@@ -12346,7 +12349,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
@@ -12381,7 +12384,7 @@
         <v>58</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>3</v>
@@ -12394,7 +12397,7 @@
         <v>1008</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49">
@@ -12422,7 +12425,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R49" s="5">
         <f t="shared" si="9"/>
@@ -12447,30 +12450,30 @@
         <v>46</v>
       </c>
       <c r="B50" s="6">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G50" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H50" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50">
@@ -12479,7 +12482,7 @@
       </c>
       <c r="L50" s="5">
         <f t="shared" si="4"/>
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="M50" s="5">
         <f t="shared" si="5"/>
@@ -12491,18 +12494,18 @@
       </c>
       <c r="O50" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P50" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="R50" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="S50" s="5">
         <f t="shared" si="10"/>
@@ -12533,7 +12536,7 @@
         <v>59</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>3</v>
@@ -12546,16 +12549,16 @@
         <v>980</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" s="5">
         <f t="shared" si="4"/>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="M51" s="5">
         <f t="shared" si="5"/>
@@ -12574,7 +12577,7 @@
         <v>6860</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R51" s="5">
         <f t="shared" si="9"/>
@@ -12609,7 +12612,7 @@
         <v>59</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>3</v>
@@ -12622,16 +12625,16 @@
         <v>980</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="4"/>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="M52" s="5">
         <f t="shared" si="5"/>
@@ -12650,7 +12653,7 @@
         <v>6860</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R52" s="5">
         <f t="shared" si="9"/>
@@ -12685,7 +12688,7 @@
         <v>59</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>3</v>
@@ -12698,16 +12701,16 @@
         <v>980</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53" s="5">
         <f t="shared" si="4"/>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="M53" s="5">
         <f t="shared" si="5"/>
@@ -12726,7 +12729,7 @@
         <v>6860</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R53" s="5">
         <f t="shared" si="9"/>
@@ -12761,7 +12764,7 @@
         <v>59</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>3</v>
@@ -12774,16 +12777,16 @@
         <v>980</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" si="4"/>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="M54" s="5">
         <f t="shared" si="5"/>
@@ -12802,7 +12805,7 @@
         <v>6860</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="9"/>
@@ -12827,43 +12830,43 @@
         <v>51</v>
       </c>
       <c r="B55" s="6">
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G55" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H55" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="5">
         <f t="shared" si="4"/>
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="M55" s="5">
         <f t="shared" si="5"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="N55">
         <f t="shared" si="6"/>
@@ -12871,22 +12874,22 @@
       </c>
       <c r="O55" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P55" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R55" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46319</v>
       </c>
       <c r="S55" s="5">
         <f t="shared" si="10"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="T55" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12913,7 +12916,7 @@
         <v>58</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>3</v>
@@ -12926,7 +12929,7 @@
         <v>1008</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56">
@@ -12954,7 +12957,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="9"/>
@@ -12989,7 +12992,7 @@
         <v>58</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>3</v>
@@ -13002,7 +13005,7 @@
         <v>1008</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57">
@@ -13030,7 +13033,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R57" s="5">
         <f t="shared" si="9"/>
@@ -13065,7 +13068,7 @@
         <v>58</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>3</v>
@@ -13078,7 +13081,7 @@
         <v>1008</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58">
@@ -13106,7 +13109,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="9"/>
@@ -13141,7 +13144,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>3</v>
@@ -13154,7 +13157,7 @@
         <v>1008</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59">
@@ -13182,7 +13185,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R59" s="5">
         <f t="shared" si="9"/>
@@ -13217,7 +13220,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>3</v>
@@ -13230,7 +13233,7 @@
         <v>1008</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60">
@@ -13258,7 +13261,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R60" s="5">
         <f t="shared" si="9"/>
@@ -13293,7 +13296,7 @@
         <v>58</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>3</v>
@@ -13306,7 +13309,7 @@
         <v>1008</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61">
@@ -13334,7 +13337,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="9"/>
@@ -13369,7 +13372,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
@@ -13382,7 +13385,7 @@
         <v>1008</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
@@ -13410,7 +13413,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
@@ -13435,7 +13438,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="6">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="1"/>
@@ -13445,7 +13448,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>3</v>
@@ -13458,7 +13461,7 @@
         <v>1008</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63">
@@ -13467,11 +13470,11 @@
       </c>
       <c r="L63" s="5">
         <f t="shared" si="4"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="M63" s="5">
         <f t="shared" si="5"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="N63">
         <f t="shared" si="6"/>
@@ -13486,15 +13489,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R63" s="5">
         <f t="shared" si="9"/>
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="S63" s="5">
         <f t="shared" si="10"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="T63" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13521,7 +13524,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>3</v>
@@ -13534,7 +13537,7 @@
         <v>1008</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64">
@@ -13562,7 +13565,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q64" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R64" s="5">
         <f t="shared" si="9"/>
@@ -13597,7 +13600,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>3</v>
@@ -13610,7 +13613,7 @@
         <v>1008</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65">
@@ -13638,7 +13641,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R65" s="5">
         <f t="shared" si="9"/>
@@ -13673,7 +13676,7 @@
         <v>58</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>3</v>
@@ -13686,7 +13689,7 @@
         <v>1008</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66">
@@ -13714,7 +13717,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R66" s="5">
         <f t="shared" si="9"/>
@@ -13749,7 +13752,7 @@
         <v>58</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>3</v>
@@ -13762,7 +13765,7 @@
         <v>1008</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67">
@@ -13790,7 +13793,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R67" s="5">
         <f t="shared" si="9"/>
@@ -13825,7 +13828,7 @@
         <v>58</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>3</v>
@@ -13838,7 +13841,7 @@
         <v>1008</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68">
@@ -13866,7 +13869,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R68" s="5">
         <f t="shared" si="9"/>
@@ -13901,7 +13904,7 @@
         <v>58</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>3</v>
@@ -13914,7 +13917,7 @@
         <v>1008</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69">
@@ -13942,7 +13945,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R69" s="5">
         <f t="shared" ref="R69:R132" si="22">IF(B69="","",IF(J69&lt;&gt;"",J69,B69+IFERROR(INDEX(LagsP90,MATCH(D69,Origenes,0)),K69)))</f>
@@ -13977,7 +13980,7 @@
         <v>58</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>3</v>
@@ -13990,7 +13993,7 @@
         <v>1008</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70">
@@ -14018,7 +14021,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
@@ -14043,7 +14046,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="6">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="14"/>
@@ -14053,7 +14056,7 @@
         <v>58</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>3</v>
@@ -14066,7 +14069,7 @@
         <v>1008</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71">
@@ -14075,11 +14078,11 @@
       </c>
       <c r="L71" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="M71" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="N71">
         <f t="shared" si="19"/>
@@ -14094,15 +14097,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R71" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="S71" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="T71" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -14129,7 +14132,7 @@
         <v>58</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>3</v>
@@ -14142,7 +14145,7 @@
         <v>1008</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72">
@@ -14170,7 +14173,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R72" s="5">
         <f t="shared" si="22"/>
@@ -14205,7 +14208,7 @@
         <v>58</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>3</v>
@@ -14218,7 +14221,7 @@
         <v>1008</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73">
@@ -14246,7 +14249,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R73" s="5">
         <f t="shared" si="22"/>
@@ -14281,7 +14284,7 @@
         <v>58</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>3</v>
@@ -14294,7 +14297,7 @@
         <v>1008</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74">
@@ -14322,7 +14325,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R74" s="5">
         <f t="shared" si="22"/>
@@ -14357,7 +14360,7 @@
         <v>58</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>3</v>
@@ -14370,7 +14373,7 @@
         <v>1008</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75">
@@ -14398,7 +14401,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R75" s="5">
         <f t="shared" si="22"/>
@@ -14433,7 +14436,7 @@
         <v>58</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>3</v>
@@ -14446,7 +14449,7 @@
         <v>1008</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76">
@@ -14474,7 +14477,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R76" s="5">
         <f t="shared" si="22"/>
@@ -14509,7 +14512,7 @@
         <v>58</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>3</v>
@@ -14522,7 +14525,7 @@
         <v>1008</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77">
@@ -14550,7 +14553,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q77" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R77" s="5">
         <f t="shared" si="22"/>
@@ -14585,7 +14588,7 @@
         <v>58</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>3</v>
@@ -14598,7 +14601,7 @@
         <v>1008</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78">
@@ -14626,7 +14629,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
@@ -14651,7 +14654,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="6">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="14"/>
@@ -14661,7 +14664,7 @@
         <v>58</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>3</v>
@@ -14674,7 +14677,7 @@
         <v>1008</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79">
@@ -14683,11 +14686,11 @@
       </c>
       <c r="L79" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="M79" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="N79">
         <f t="shared" si="19"/>
@@ -14702,15 +14705,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R79" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="S79" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="T79" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -14737,7 +14740,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>3</v>
@@ -14750,7 +14753,7 @@
         <v>1008</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80">
@@ -14778,7 +14781,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R80" s="5">
         <f t="shared" si="22"/>
@@ -14813,7 +14816,7 @@
         <v>58</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>3</v>
@@ -14826,7 +14829,7 @@
         <v>1008</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81">
@@ -14854,7 +14857,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R81" s="5">
         <f t="shared" si="22"/>
@@ -14889,7 +14892,7 @@
         <v>58</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>3</v>
@@ -14902,7 +14905,7 @@
         <v>1008</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82">
@@ -14930,7 +14933,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R82" s="5">
         <f t="shared" si="22"/>
@@ -14965,7 +14968,7 @@
         <v>58</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>3</v>
@@ -14978,7 +14981,7 @@
         <v>1008</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83">
@@ -15006,7 +15009,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q83" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R83" s="5">
         <f t="shared" si="22"/>
@@ -15041,7 +15044,7 @@
         <v>58</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>3</v>
@@ -15054,7 +15057,7 @@
         <v>1008</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84">
@@ -15082,7 +15085,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R84" s="5">
         <f t="shared" si="22"/>
@@ -15117,7 +15120,7 @@
         <v>58</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>3</v>
@@ -15130,7 +15133,7 @@
         <v>1008</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85">
@@ -15158,7 +15161,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R85" s="5">
         <f t="shared" si="22"/>
@@ -15193,7 +15196,7 @@
         <v>58</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>3</v>
@@ -15206,7 +15209,7 @@
         <v>1008</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86">
@@ -15234,7 +15237,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
@@ -15259,7 +15262,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="6">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="14"/>
@@ -15269,7 +15272,7 @@
         <v>58</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>3</v>
@@ -15282,7 +15285,7 @@
         <v>1008</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87">
@@ -15291,11 +15294,11 @@
       </c>
       <c r="L87" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="M87" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="N87">
         <f t="shared" si="19"/>
@@ -15310,15 +15313,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R87" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="S87" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="T87" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15345,7 +15348,7 @@
         <v>58</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>3</v>
@@ -15358,7 +15361,7 @@
         <v>1008</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88">
@@ -15386,7 +15389,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q88" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R88" s="5">
         <f t="shared" si="22"/>
@@ -15421,7 +15424,7 @@
         <v>58</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>3</v>
@@ -15434,7 +15437,7 @@
         <v>1008</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89">
@@ -15462,7 +15465,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q89" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R89" s="5">
         <f t="shared" si="22"/>
@@ -15497,7 +15500,7 @@
         <v>58</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>3</v>
@@ -15510,7 +15513,7 @@
         <v>1008</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90">
@@ -15538,7 +15541,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q90" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R90" s="5">
         <f t="shared" si="22"/>
@@ -15573,7 +15576,7 @@
         <v>58</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>3</v>
@@ -15586,7 +15589,7 @@
         <v>1008</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91">
@@ -15614,7 +15617,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R91" s="5">
         <f t="shared" si="22"/>
@@ -15649,7 +15652,7 @@
         <v>58</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>3</v>
@@ -15662,7 +15665,7 @@
         <v>1008</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92">
@@ -15690,7 +15693,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R92" s="5">
         <f t="shared" si="22"/>
@@ -15725,7 +15728,7 @@
         <v>58</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>3</v>
@@ -15738,7 +15741,7 @@
         <v>1008</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93">
@@ -15766,7 +15769,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q93" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R93" s="5">
         <f t="shared" si="22"/>
@@ -15801,7 +15804,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>3</v>
@@ -15814,7 +15817,7 @@
         <v>1008</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94">
@@ -15842,7 +15845,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
@@ -15867,7 +15870,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="6">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="14"/>
@@ -15877,7 +15880,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>3</v>
@@ -15890,7 +15893,7 @@
         <v>1008</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95">
@@ -15899,11 +15902,11 @@
       </c>
       <c r="L95" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="M95" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="N95">
         <f t="shared" si="19"/>
@@ -15918,15 +15921,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R95" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46352</v>
       </c>
       <c r="S95" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="T95" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15953,7 +15956,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>3</v>
@@ -15966,7 +15969,7 @@
         <v>1008</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96">
@@ -15994,7 +15997,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q96" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R96" s="5">
         <f t="shared" si="22"/>
@@ -16029,7 +16032,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>3</v>
@@ -16042,7 +16045,7 @@
         <v>1008</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97">
@@ -16070,7 +16073,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R97" s="5">
         <f t="shared" si="22"/>
@@ -16105,7 +16108,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>3</v>
@@ -16118,7 +16121,7 @@
         <v>1008</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98">
@@ -16146,7 +16149,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R98" s="5">
         <f t="shared" si="22"/>
@@ -16181,7 +16184,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>3</v>
@@ -16194,7 +16197,7 @@
         <v>1008</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99">
@@ -16222,7 +16225,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q99" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R99" s="5">
         <f t="shared" si="22"/>
@@ -16257,7 +16260,7 @@
         <v>58</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>3</v>
@@ -16270,7 +16273,7 @@
         <v>1008</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100">
@@ -16298,7 +16301,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q100" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R100" s="5">
         <f t="shared" si="22"/>
@@ -16333,7 +16336,7 @@
         <v>58</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>3</v>
@@ -16346,7 +16349,7 @@
         <v>1008</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101">
@@ -16374,7 +16377,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R101" s="5">
         <f t="shared" si="22"/>
@@ -16409,7 +16412,7 @@
         <v>58</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>3</v>
@@ -16422,7 +16425,7 @@
         <v>1008</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102">
@@ -16450,7 +16453,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q102" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
@@ -16475,7 +16478,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="6">
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="14"/>
@@ -16485,7 +16488,7 @@
         <v>58</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>3</v>
@@ -16498,7 +16501,7 @@
         <v>1008</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103">
@@ -16507,11 +16510,11 @@
       </c>
       <c r="L103" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="M103" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="N103">
         <f t="shared" si="19"/>
@@ -16526,15 +16529,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R103" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46359</v>
       </c>
       <c r="S103" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="T103" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16561,7 +16564,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>3</v>
@@ -16574,7 +16577,7 @@
         <v>1008</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104">
@@ -16602,7 +16605,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q104" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R104" s="5">
         <f t="shared" si="22"/>
@@ -16637,7 +16640,7 @@
         <v>58</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>3</v>
@@ -16650,7 +16653,7 @@
         <v>1008</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105">
@@ -16678,7 +16681,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R105" s="5">
         <f t="shared" si="22"/>
@@ -16713,7 +16716,7 @@
         <v>58</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
@@ -16726,7 +16729,7 @@
         <v>1008</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106">
@@ -16754,7 +16757,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q106" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R106" s="5">
         <f t="shared" si="22"/>
@@ -16789,7 +16792,7 @@
         <v>58</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>3</v>
@@ -16802,7 +16805,7 @@
         <v>1008</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107">
@@ -16830,7 +16833,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R107" s="5">
         <f t="shared" si="22"/>
@@ -16865,7 +16868,7 @@
         <v>58</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>3</v>
@@ -16878,7 +16881,7 @@
         <v>1008</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108">
@@ -16906,7 +16909,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q108" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R108" s="5">
         <f t="shared" si="22"/>
@@ -16941,7 +16944,7 @@
         <v>58</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>3</v>
@@ -16954,7 +16957,7 @@
         <v>1008</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109">
@@ -16982,7 +16985,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R109" s="5">
         <f t="shared" si="22"/>
@@ -17017,7 +17020,7 @@
         <v>58</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>3</v>
@@ -17030,7 +17033,7 @@
         <v>1008</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110">
@@ -17058,7 +17061,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q110" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
@@ -17083,7 +17086,7 @@
         <v>107</v>
       </c>
       <c r="B111" s="6">
-        <v>46367</v>
+        <v>46360</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="14"/>
@@ -17093,7 +17096,7 @@
         <v>58</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>3</v>
@@ -17106,7 +17109,7 @@
         <v>1008</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111">
@@ -17115,11 +17118,11 @@
       </c>
       <c r="L111" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="M111" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="N111">
         <f t="shared" si="19"/>
@@ -17134,15 +17137,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q111" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R111" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46366</v>
       </c>
       <c r="S111" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="T111" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17169,7 +17172,7 @@
         <v>58</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>3</v>
@@ -17182,7 +17185,7 @@
         <v>1008</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112">
@@ -17210,7 +17213,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q112" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R112" s="5">
         <f t="shared" si="22"/>
@@ -17245,7 +17248,7 @@
         <v>58</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>3</v>
@@ -17258,7 +17261,7 @@
         <v>1008</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113">
@@ -17286,7 +17289,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q113" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R113" s="5">
         <f t="shared" si="22"/>
@@ -17321,7 +17324,7 @@
         <v>58</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>3</v>
@@ -17334,7 +17337,7 @@
         <v>1008</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114">
@@ -17362,7 +17365,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q114" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R114" s="5">
         <f t="shared" si="22"/>
@@ -17397,7 +17400,7 @@
         <v>58</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>3</v>
@@ -17410,7 +17413,7 @@
         <v>1008</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115">
@@ -17438,7 +17441,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R115" s="5">
         <f t="shared" si="22"/>
@@ -17473,7 +17476,7 @@
         <v>58</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>3</v>
@@ -17486,7 +17489,7 @@
         <v>1008</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116">
@@ -17514,7 +17517,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q116" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R116" s="5">
         <f t="shared" si="22"/>
@@ -17549,7 +17552,7 @@
         <v>58</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>3</v>
@@ -17562,7 +17565,7 @@
         <v>1008</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117">
@@ -17590,7 +17593,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R117" s="5">
         <f t="shared" si="22"/>
@@ -17625,7 +17628,7 @@
         <v>58</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>3</v>
@@ -17638,7 +17641,7 @@
         <v>1008</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118">
@@ -17666,7 +17669,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q118" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
@@ -17691,7 +17694,7 @@
         <v>115</v>
       </c>
       <c r="B119" s="6">
-        <v>46374</v>
+        <v>46367</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="14"/>
@@ -17701,7 +17704,7 @@
         <v>58</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>3</v>
@@ -17714,7 +17717,7 @@
         <v>1008</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119">
@@ -17723,11 +17726,11 @@
       </c>
       <c r="L119" s="5">
         <f t="shared" si="17"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="M119" s="5">
         <f t="shared" si="18"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="N119">
         <f t="shared" si="19"/>
@@ -17742,15 +17745,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R119" s="5">
         <f t="shared" si="22"/>
-        <v>46380</v>
+        <v>46373</v>
       </c>
       <c r="S119" s="5">
         <f t="shared" si="23"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="T119" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17777,7 +17780,7 @@
         <v>58</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>3</v>
@@ -17790,7 +17793,7 @@
         <v>1008</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120">
@@ -17818,7 +17821,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q120" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R120" s="5">
         <f t="shared" si="22"/>
@@ -17853,7 +17856,7 @@
         <v>58</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>3</v>
@@ -17866,7 +17869,7 @@
         <v>1008</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121">
@@ -17894,7 +17897,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R121" s="5">
         <f t="shared" si="22"/>
@@ -17929,7 +17932,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>3</v>
@@ -17942,7 +17945,7 @@
         <v>1008</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122">
@@ -17970,7 +17973,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q122" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R122" s="5">
         <f t="shared" si="22"/>
@@ -18005,7 +18008,7 @@
         <v>58</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>3</v>
@@ -18018,7 +18021,7 @@
         <v>1008</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123">
@@ -18046,7 +18049,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q123" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R123" s="5">
         <f t="shared" si="22"/>
@@ -18081,7 +18084,7 @@
         <v>58</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>3</v>
@@ -18094,7 +18097,7 @@
         <v>1008</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124">
@@ -18122,7 +18125,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q124" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R124" s="5">
         <f t="shared" si="22"/>
@@ -18157,7 +18160,7 @@
         <v>58</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>3</v>
@@ -18170,7 +18173,7 @@
         <v>1008</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125">
@@ -18198,7 +18201,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R125" s="5">
         <f t="shared" si="22"/>
@@ -18233,7 +18236,7 @@
         <v>58</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>3</v>
@@ -18246,7 +18249,7 @@
         <v>1008</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126">
@@ -18274,7 +18277,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q126" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
@@ -18294,61 +18297,75 @@
       </c>
     </row>
     <row r="127" spans="1:21">
-      <c r="A127" t="str">
+      <c r="A127">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="B127" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="B127" s="6">
+        <v>46374</v>
+      </c>
       <c r="C127" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="7" t="str">
+        <v>vie</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G127" s="8">
+        <v>1008</v>
+      </c>
+      <c r="H127" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I127" s="9"/>
+        <v>1008</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>216</v>
+      </c>
       <c r="J127" s="6"/>
-      <c r="K127" t="str">
+      <c r="K127">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L127" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L127" s="5">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="M127" s="5" t="str">
+        <v>46377</v>
+      </c>
+      <c r="M127" s="5">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N127" t="str">
+        <v>46377</v>
+      </c>
+      <c r="N127">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="O127" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O127" s="10">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="P127" s="7" t="str">
+        <v>7.09</v>
+      </c>
+      <c r="P127" s="7">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Q127" s="9"/>
-      <c r="R127" s="5" t="str">
+        <v>7146.72</v>
+      </c>
+      <c r="Q127" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="R127" s="5">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="S127" s="5" t="str">
+        <v>46380</v>
+      </c>
+      <c r="S127" s="5">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="T127" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v/>
+        <v>46377</v>
+      </c>
+      <c r="T127" s="7">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
       </c>
       <c r="U127" t="str">
         <f t="shared" si="25"/>
@@ -29135,77 +29152,77 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="75">
       <c r="A5" s="11" t="s">
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>169</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -29223,11 +29240,11 @@
       </c>
       <c r="D6" s="7">
         <f t="shared" ref="D6:D18" si="1">COUNTIFS(CgSemana,A6,CgCuenta,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" ref="E6:E18" si="2">SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="F6" s="7">
         <f>ROUND(Demanda!H6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
@@ -29235,7 +29252,7 @@
       </c>
       <c r="G6" s="7">
         <f t="shared" ref="G6:G18" si="3">C6+E6-F6</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="H6" s="7">
         <f>0</f>
@@ -29243,11 +29260,11 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ref="I6:I18" si="4">G6+H6</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="J6" s="20">
-        <f t="shared" ref="J6:J18" si="5">B6-LagBR-AtrasoDias</f>
-        <v>46288</v>
+        <f t="shared" ref="J6:J18" si="5">B6-MAX(LagBR,LagPY)-AtrasoDias</f>
+        <v>46287</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" ref="K6:K18" ca="1" si="6">IF(AND(I6&lt;MinimoSabado,J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-I6)/CajasProm,0),0)</f>
@@ -29255,11 +29272,11 @@
       </c>
       <c r="L6" s="7">
         <f t="shared" ref="L6:L18" ca="1" si="7">I6+K6*CajasProm</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="M6" s="21">
         <f ca="1">IF(Demanda!H7=0,"",L6/(Demanda!H7/DiasVenta))</f>
-        <v>10.114500000000001</v>
+        <v>10.482000000000001</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" ref="N6:N18" ca="1" si="8">IF(I6&lt;0,"FALTA",IF(K6&gt;0,"CARGAR "&amp;K6,IF(I6&lt;MinimoSabado,"BAJO MINIMO (limite pasado)",IF(AND(M6&lt;&gt;"",M6&gt;VidaVerde),"EXCESO (merma)","OK"))))</f>
@@ -29275,11 +29292,11 @@
       </c>
       <c r="Q6" s="7">
         <f>ConteoPY+SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
-        <v>13673</v>
+        <v>14653</v>
       </c>
       <c r="R6" s="21">
         <f>IF(Demanda!M7=0,"",Q6/(Demanda!M7/DiasVenta))</f>
-        <v>13.013642131979694</v>
+        <v>13.946383248730964</v>
       </c>
       <c r="S6" s="7">
         <f>ConteoBO+SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
@@ -29305,7 +29322,7 @@
       </c>
       <c r="C7" s="7">
         <f t="shared" ref="C7:C18" si="10">G6</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="1"/>
@@ -29321,7 +29338,7 @@
       </c>
       <c r="G7" s="7">
         <f t="shared" si="3"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="H7" s="7">
         <f ca="1">SUM($K$6:K6)*CajasProm</f>
@@ -29329,27 +29346,27 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="J7" s="20">
         <f t="shared" si="5"/>
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22918</v>
+        <v>22898</v>
       </c>
       <c r="M7" s="21">
         <f ca="1">IF(Demanda!H8=0,"",L7/(Demanda!H8/DiasVenta))</f>
-        <v>8.0887058823529401</v>
+        <v>8.0816470588235294</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="O7" s="7">
         <f>O6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L7,0)</f>
@@ -29361,11 +29378,11 @@
       </c>
       <c r="Q7" s="7">
         <f>Q6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M7,0)</f>
-        <v>11289</v>
+        <v>12269</v>
       </c>
       <c r="R7" s="21">
         <f>IF(Demanda!M8=0,"",Q7/(Demanda!M8/DiasVenta))</f>
-        <v>10.375919117647058</v>
+        <v>11.276654411764707</v>
       </c>
       <c r="S7" s="7">
         <f>S6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N7,0)</f>
@@ -29391,7 +29408,7 @@
       </c>
       <c r="C8" s="7">
         <f t="shared" si="10"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
@@ -29407,19 +29424,19 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>17810</v>
+        <v>18790</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18810</v>
+        <v>18790</v>
       </c>
       <c r="J8" s="20">
         <f t="shared" si="5"/>
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29427,11 +29444,11 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22810</v>
+        <v>22790</v>
       </c>
       <c r="M8" s="21">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.0505882352941178</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29447,11 +29464,11 @@
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
-        <v>9661</v>
+        <v>10641</v>
       </c>
       <c r="R8" s="21">
         <f>IF(Demanda!M9=0,"",Q8/(Demanda!M9/DiasVenta))</f>
-        <v>8.8795955882352935</v>
+        <v>9.780330882352942</v>
       </c>
       <c r="S8" s="7">
         <f>S7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N8,0)</f>
@@ -29477,7 +29494,7 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>17810</v>
+        <v>18790</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
@@ -29493,19 +29510,19 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>13774</v>
+        <v>14754</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18774</v>
+        <v>18754</v>
       </c>
       <c r="J9" s="20">
         <f t="shared" si="5"/>
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29513,11 +29530,11 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22774</v>
+        <v>22754</v>
       </c>
       <c r="M9" s="21">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>8.0378823529411765</v>
+        <v>8.030823529411764</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29533,11 +29550,11 @@
       </c>
       <c r="Q9" s="7">
         <f>Q8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M9,0)</f>
-        <v>8033</v>
+        <v>9013</v>
       </c>
       <c r="R9" s="21">
         <f>IF(Demanda!M10=0,"",Q9/(Demanda!M10/DiasVenta))</f>
-        <v>7.383272058823529</v>
+        <v>8.2840073529411757</v>
       </c>
       <c r="S9" s="7">
         <f>S8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N9,0)</f>
@@ -29563,7 +29580,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>13774</v>
+        <v>14754</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -29579,19 +29596,19 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>9738</v>
+        <v>10718</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18738</v>
+        <v>18718</v>
       </c>
       <c r="J10" s="20">
         <f t="shared" si="5"/>
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29599,11 +29616,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22738</v>
+        <v>22718</v>
       </c>
       <c r="M10" s="21">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>8.0251764705882351</v>
+        <v>8.0181176470588227</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29619,11 +29636,11 @@
       </c>
       <c r="Q10" s="7">
         <f>Q9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M10,0)</f>
-        <v>6405</v>
+        <v>7385</v>
       </c>
       <c r="R10" s="21">
         <f>IF(Demanda!M11=0,"",Q10/(Demanda!M11/DiasVenta))</f>
-        <v>5.8869485294117645</v>
+        <v>6.7876838235294121</v>
       </c>
       <c r="S10" s="7">
         <f>S9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N10,0)</f>
@@ -29649,7 +29666,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>9738</v>
+        <v>10718</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -29665,19 +29682,19 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>802</v>
+        <v>1782</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13802</v>
+        <v>13782</v>
       </c>
       <c r="J11" s="20">
         <f t="shared" si="5"/>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29685,11 +29702,11 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22802</v>
+        <v>22782</v>
       </c>
       <c r="M11" s="21">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>8.0477647058823525</v>
+        <v>8.04070588235294</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29705,11 +29722,11 @@
       </c>
       <c r="Q11" s="7">
         <f>Q10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M11,0)</f>
-        <v>-123</v>
+        <v>857</v>
       </c>
       <c r="R11" s="21">
         <f>IF(Demanda!M12=0,"",Q11/(Demanda!M12/DiasVenta))</f>
-        <v>-0.11305147058823529</v>
+        <v>0.7876838235294118</v>
       </c>
       <c r="S11" s="7">
         <f>S10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N11,0)</f>
@@ -29735,7 +29752,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>802</v>
+        <v>1782</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -29751,19 +29768,19 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-8134</v>
+        <v>-7154</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13866</v>
+        <v>13846</v>
       </c>
       <c r="J12" s="20">
         <f t="shared" si="5"/>
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29771,11 +29788,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22866</v>
+        <v>22846</v>
       </c>
       <c r="M12" s="21">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.0703529411764698</v>
+        <v>8.0632941176470592</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29791,11 +29808,11 @@
       </c>
       <c r="Q12" s="7">
         <f>Q11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M12,0)</f>
-        <v>-6651</v>
+        <v>-5671</v>
       </c>
       <c r="R12" s="21">
         <f>IF(Demanda!M13=0,"",Q12/(Demanda!M13/DiasVenta))</f>
-        <v>-6.1130514705882355</v>
+        <v>-5.2123161764705879</v>
       </c>
       <c r="S12" s="7">
         <f>S11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N12,0)</f>
@@ -29821,7 +29838,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-8134</v>
+        <v>-7154</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -29837,19 +29854,19 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-17070</v>
+        <v>-16090</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
-        <v>31000</v>
+        <v>30000</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13930</v>
+        <v>13910</v>
       </c>
       <c r="J13" s="20">
         <f t="shared" si="5"/>
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="K13" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29857,11 +29874,11 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22930</v>
+        <v>22910</v>
       </c>
       <c r="M13" s="21">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.0929411764705872</v>
+        <v>8.0858823529411765</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29877,11 +29894,11 @@
       </c>
       <c r="Q13" s="7">
         <f>Q12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M13,0)</f>
-        <v>-13179</v>
+        <v>-12199</v>
       </c>
       <c r="R13" s="21">
         <f>IF(Demanda!M14=0,"",Q13/(Demanda!M14/DiasVenta))</f>
-        <v>-12.113051470588236</v>
+        <v>-11.212316176470589</v>
       </c>
       <c r="S13" s="7">
         <f>S12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N13,0)</f>
@@ -29907,7 +29924,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-17070</v>
+        <v>-16090</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -29923,19 +29940,19 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-26006</v>
+        <v>-25026</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13994</v>
+        <v>13974</v>
       </c>
       <c r="J14" s="20">
         <f t="shared" si="5"/>
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="K14" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -29943,11 +29960,11 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22994</v>
+        <v>22974</v>
       </c>
       <c r="M14" s="21">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.1155294117647063</v>
+        <v>8.1084705882352939</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -29963,11 +29980,11 @@
       </c>
       <c r="Q14" s="7">
         <f>Q13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M14,0)</f>
-        <v>-19707</v>
+        <v>-18727</v>
       </c>
       <c r="R14" s="21">
         <f>IF(Demanda!M15=0,"",Q14/(Demanda!M15/DiasVenta))</f>
-        <v>-18.113051470588236</v>
+        <v>-17.212316176470587</v>
       </c>
       <c r="S14" s="7">
         <f>S13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N14,0)</f>
@@ -29993,7 +30010,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-26006</v>
+        <v>-25026</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -30009,19 +30026,19 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-34942</v>
+        <v>-33962</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>49000</v>
+        <v>48000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14058</v>
+        <v>14038</v>
       </c>
       <c r="J15" s="20">
         <f t="shared" si="5"/>
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="K15" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -30029,11 +30046,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23058</v>
+        <v>23038</v>
       </c>
       <c r="M15" s="21">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.1381176470588237</v>
+        <v>8.1310588235294112</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30049,11 +30066,11 @@
       </c>
       <c r="Q15" s="7">
         <f>Q14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M15,0)</f>
-        <v>-26235</v>
+        <v>-25255</v>
       </c>
       <c r="R15" s="21">
         <f>IF(Demanda!M16=0,"",Q15/(Demanda!M16/DiasVenta))</f>
-        <v>-24.113051470588236</v>
+        <v>-23.212316176470587</v>
       </c>
       <c r="S15" s="7">
         <f>S14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N15,0)</f>
@@ -30079,7 +30096,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-34942</v>
+        <v>-33962</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -30095,19 +30112,19 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-43878</v>
+        <v>-42898</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>58000</v>
+        <v>57000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14122</v>
+        <v>14102</v>
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="K16" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -30115,11 +30132,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23122</v>
+        <v>23102</v>
       </c>
       <c r="M16" s="21">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.160705882352941</v>
+        <v>8.1536470588235286</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30135,11 +30152,11 @@
       </c>
       <c r="Q16" s="7">
         <f>Q15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M16,0)</f>
-        <v>-32763</v>
+        <v>-31783</v>
       </c>
       <c r="R16" s="21">
         <f>IF(Demanda!M17=0,"",Q16/(Demanda!M17/DiasVenta))</f>
-        <v>-30.113051470588236</v>
+        <v>-29.212316176470587</v>
       </c>
       <c r="S16" s="7">
         <f>S15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N16,0)</f>
@@ -30165,7 +30182,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-43878</v>
+        <v>-42898</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -30181,19 +30198,19 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-52814</v>
+        <v>-51834</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>67000</v>
+        <v>66000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14186</v>
+        <v>14166</v>
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>46365</v>
+        <v>46364</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -30201,11 +30218,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23186</v>
+        <v>23166</v>
       </c>
       <c r="M17" s="21">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.1832941176470584</v>
+        <v>8.1762352941176459</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30221,11 +30238,11 @@
       </c>
       <c r="Q17" s="7">
         <f>Q16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M17,0)</f>
-        <v>-39291</v>
+        <v>-38311</v>
       </c>
       <c r="R17" s="21">
         <f>IF(Demanda!M18=0,"",Q17/(Demanda!M18/DiasVenta))</f>
-        <v>-36.113051470588232</v>
+        <v>-35.212316176470587</v>
       </c>
       <c r="S17" s="7">
         <f>S16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N17,0)</f>
@@ -30251,7 +30268,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-52814</v>
+        <v>-51834</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -30267,19 +30284,19 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-61750</v>
+        <v>-60770</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>76000</v>
+        <v>75000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14250</v>
+        <v>14230</v>
       </c>
       <c r="J18" s="20">
         <f t="shared" si="5"/>
-        <v>46372</v>
+        <v>46371</v>
       </c>
       <c r="K18" s="3">
         <f t="shared" ca="1" si="6"/>
@@ -30287,11 +30304,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23250</v>
+        <v>23230</v>
       </c>
       <c r="M18" s="21">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.2058823529411757</v>
+        <v>8.1988235294117651</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30307,11 +30324,11 @@
       </c>
       <c r="Q18" s="7">
         <f>Q17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M18,0)</f>
-        <v>-45819</v>
+        <v>-44839</v>
       </c>
       <c r="R18" s="21">
         <f>IF(Demanda!M18=0,"",Q18/(Demanda!M18/DiasVenta))</f>
-        <v>-42.113051470588232</v>
+        <v>-41.212316176470587</v>
       </c>
       <c r="S18" s="7">
         <f>S17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N18,0)</f>
@@ -30408,41 +30425,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45">
       <c r="A5" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>169</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -30458,8 +30475,8 @@
         <f ca="1">IF(A6="","",Proyeccion!K6)</f>
         <v/>
       </c>
-      <c r="D6" s="20" t="str">
-        <f ca="1">IF(A6="","",Proyeccion!J6)</f>
+      <c r="D6" t="str">
+        <f ca="1">IF(A6="","","BR "&amp;TEXT(Proyeccion!B6-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B6-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B6-LagBO-AtrasoDias,"ddd dd/mm"))</f>
         <v/>
       </c>
       <c r="E6" t="str">
@@ -30479,7 +30496,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <f ca="1">IF(A6="","","Sab "&amp;TEXT(A6,"dd/mm")&amp;": "&amp;FIXED(B6,0)&amp;" cajas - descargan "&amp;Proyeccion!D6&amp;" - vende "&amp;FIXED(Proyeccion!F6,0)&amp;IF(C6&gt;0," -&gt; cargar "&amp;C6&amp;" mas hasta el "&amp;TEXT(D6,"dd/mm")&amp;" ("&amp;E6&amp;")"," -&gt; ok"))</f>
+        <f ca="1">IF(A6="","","Sab "&amp;TEXT(A6,"dd/mm")&amp;": "&amp;FIXED(B6,0)&amp;" cajas - descargan "&amp;Proyeccion!D6&amp;" - vende "&amp;FIXED(Proyeccion!F6,0)&amp;IF(C6&gt;0," -&gt; cargar "&amp;C6&amp;" mas hasta el "&amp;TEXT(Proyeccion!J6,"dd/mm")&amp;" ("&amp;E6&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B6-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
         <v/>
       </c>
     </row>
@@ -30490,19 +30507,19 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">IF(A7="","",Proyeccion!I7)</f>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="C7" s="3">
         <f ca="1">IF(A7="","",Proyeccion!K7)</f>
-        <v>1</v>
-      </c>
-      <c r="D7" s="20">
-        <f ca="1">IF(A7="","",Proyeccion!J7)</f>
-        <v>46295</v>
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <f ca="1">IF(A7="","","BR "&amp;TEXT(Proyeccion!B7-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B7-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B7-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 30/09 · PY mar 29/09 · BO dom 27/09</v>
       </c>
       <c r="E7" t="str">
         <f ca="1">IF(A7="","",IF(C7&gt;0,Proyeccion!U7,"-"))</f>
-        <v>Brasil</v>
+        <v>-</v>
       </c>
       <c r="F7" t="str">
         <f ca="1">IF(A7="","","PY mie "&amp;TEXT(Proyeccion!A7-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A7-4,"dd/mm"))</f>
@@ -30510,15 +30527,15 @@
       </c>
       <c r="G7" s="21">
         <f ca="1">IF(A7="","",Proyeccion!M7)</f>
-        <v>8.0887058823529401</v>
+        <v>8.0816470588235294</v>
       </c>
       <c r="H7" t="str">
         <f ca="1">IF(A7="","",Proyeccion!N7)</f>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="I7" t="str">
-        <f ca="1">IF(A7="","","Sab "&amp;TEXT(A7,"dd/mm")&amp;": "&amp;FIXED(B7,0)&amp;" cajas - descargan "&amp;Proyeccion!D7&amp;" - vende "&amp;FIXED(Proyeccion!F7,0)&amp;IF(C7&gt;0," -&gt; cargar "&amp;C7&amp;" mas hasta el "&amp;TEXT(D7,"dd/mm")&amp;" ("&amp;E7&amp;")"," -&gt; ok"))</f>
-        <v>Sab 03/10: 21.918 cajas - descargan 11 - vende 16.000 -&gt; cargar 1 mas hasta el 30/09 (Brasil)</v>
+        <f ca="1">IF(A7="","","Sab "&amp;TEXT(A7,"dd/mm")&amp;": "&amp;FIXED(B7,0)&amp;" cajas - descargan "&amp;Proyeccion!D7&amp;" - vende "&amp;FIXED(Proyeccion!F7,0)&amp;IF(C7&gt;0," -&gt; cargar "&amp;C7&amp;" mas hasta el "&amp;TEXT(Proyeccion!J7,"dd/mm")&amp;" ("&amp;E7&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B7-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 03/10: 22.898 cajas - descargan 11 - vende 16.000 -&gt; ok</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -30528,15 +30545,15 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>18810</v>
+        <v>18790</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
         <v>4</v>
       </c>
-      <c r="D8" s="20">
-        <f ca="1">IF(A8="","",Proyeccion!J8)</f>
-        <v>46302</v>
+      <c r="D8" t="str">
+        <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 07/10 · PY mar 06/10 · BO dom 04/10</v>
       </c>
       <c r="E8" t="str">
         <f ca="1">IF(A8="","",IF(C8&gt;0,Proyeccion!U8,"-"))</f>
@@ -30548,15 +30565,15 @@
       </c>
       <c r="G8" s="21">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.0505882352941178</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
         <v>CARGAR 4</v>
       </c>
       <c r="I8" t="str">
-        <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(D8,"dd/mm")&amp;" ("&amp;E8&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 18.810 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 07/10 (Bolivia)</v>
+        <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 10/10: 18.790 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 06/10 (Bolivia; BR hasta el 07/10)</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -30566,15 +30583,15 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>18774</v>
+        <v>18754</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
         <v>4</v>
       </c>
-      <c r="D9" s="20">
-        <f ca="1">IF(A9="","",Proyeccion!J9)</f>
-        <v>46309</v>
+      <c r="D9" t="str">
+        <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 14/10 · PY mar 13/10 · BO dom 11/10</v>
       </c>
       <c r="E9" t="str">
         <f ca="1">IF(A9="","",IF(C9&gt;0,Proyeccion!U9,"-"))</f>
@@ -30586,15 +30603,15 @@
       </c>
       <c r="G9" s="21">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>8.0378823529411765</v>
+        <v>8.030823529411764</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
         <v>CARGAR 4</v>
       </c>
       <c r="I9" t="str">
-        <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(D9,"dd/mm")&amp;" ("&amp;E9&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 18.774 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 14/10 (Bolivia)</v>
+        <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 17/10: 18.754 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -30604,15 +30621,15 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>18738</v>
+        <v>18718</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
         <v>4</v>
       </c>
-      <c r="D10" s="20">
-        <f ca="1">IF(A10="","",Proyeccion!J10)</f>
-        <v>46316</v>
+      <c r="D10" t="str">
+        <f ca="1">IF(A10="","","BR "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B10-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B10-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 21/10 · PY mar 20/10 · BO dom 18/10</v>
       </c>
       <c r="E10" t="str">
         <f ca="1">IF(A10="","",IF(C10&gt;0,Proyeccion!U10,"-"))</f>
@@ -30624,15 +30641,15 @@
       </c>
       <c r="G10" s="21">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>8.0251764705882351</v>
+        <v>8.0181176470588227</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
         <v>CARGAR 4</v>
       </c>
       <c r="I10" t="str">
-        <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(D10,"dd/mm")&amp;" ("&amp;E10&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 18.738 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 21/10 (Bolivia)</v>
+        <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 24/10: 18.718 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -30642,15 +30659,15 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>13802</v>
+        <v>13782</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
         <v>9</v>
       </c>
-      <c r="D11" s="20">
-        <f ca="1">IF(A11="","",Proyeccion!J11)</f>
-        <v>46323</v>
+      <c r="D11" t="str">
+        <f ca="1">IF(A11="","","BR "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B11-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B11-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 28/10 · PY mar 27/10 · BO dom 25/10</v>
       </c>
       <c r="E11" t="str">
         <f ca="1">IF(A11="","",IF(C11&gt;0,Proyeccion!U11,"-"))</f>
@@ -30662,15 +30679,15 @@
       </c>
       <c r="G11" s="21">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>8.0477647058823525</v>
+        <v>8.04070588235294</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I11" t="str">
-        <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(D11,"dd/mm")&amp;" ("&amp;E11&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 13.802 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 28/10 (Bolivia)</v>
+        <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 31/10: 13.782 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -30680,15 +30697,15 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>13866</v>
+        <v>13846</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
         <v>9</v>
       </c>
-      <c r="D12" s="20">
-        <f ca="1">IF(A12="","",Proyeccion!J12)</f>
-        <v>46330</v>
+      <c r="D12" t="str">
+        <f ca="1">IF(A12="","","BR "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B12-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B12-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 04/11 · PY mar 03/11 · BO dom 01/11</v>
       </c>
       <c r="E12" t="str">
         <f ca="1">IF(A12="","",IF(C12&gt;0,Proyeccion!U12,"-"))</f>
@@ -30700,15 +30717,15 @@
       </c>
       <c r="G12" s="21">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.0703529411764698</v>
+        <v>8.0632941176470592</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I12" t="str">
-        <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(D12,"dd/mm")&amp;" ("&amp;E12&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 13.866 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 04/11 (Bolivia)</v>
+        <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 07/11: 13.846 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -30718,15 +30735,15 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>13930</v>
+        <v>13910</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
         <v>9</v>
       </c>
-      <c r="D13" s="20">
-        <f ca="1">IF(A13="","",Proyeccion!J13)</f>
-        <v>46337</v>
+      <c r="D13" t="str">
+        <f ca="1">IF(A13="","","BR "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B13-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B13-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 11/11 · PY mar 10/11 · BO dom 08/11</v>
       </c>
       <c r="E13" t="str">
         <f ca="1">IF(A13="","",IF(C13&gt;0,Proyeccion!U13,"-"))</f>
@@ -30738,15 +30755,15 @@
       </c>
       <c r="G13" s="21">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.0929411764705872</v>
+        <v>8.0858823529411765</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I13" t="str">
-        <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(D13,"dd/mm")&amp;" ("&amp;E13&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 13.930 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 11/11 (Bolivia)</v>
+        <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 14/11: 13.910 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -30756,15 +30773,15 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>13994</v>
+        <v>13974</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
         <v>9</v>
       </c>
-      <c r="D14" s="20">
-        <f ca="1">IF(A14="","",Proyeccion!J14)</f>
-        <v>46344</v>
+      <c r="D14" t="str">
+        <f ca="1">IF(A14="","","BR "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B14-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B14-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 18/11 · PY mar 17/11 · BO dom 15/11</v>
       </c>
       <c r="E14" t="str">
         <f ca="1">IF(A14="","",IF(C14&gt;0,Proyeccion!U14,"-"))</f>
@@ -30776,15 +30793,15 @@
       </c>
       <c r="G14" s="21">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.1155294117647063</v>
+        <v>8.1084705882352939</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I14" t="str">
-        <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(D14,"dd/mm")&amp;" ("&amp;E14&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 13.994 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 18/11 (Bolivia)</v>
+        <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 21/11: 13.974 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -30794,15 +30811,15 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>14058</v>
+        <v>14038</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
         <v>9</v>
       </c>
-      <c r="D15" s="20">
-        <f ca="1">IF(A15="","",Proyeccion!J15)</f>
-        <v>46351</v>
+      <c r="D15" t="str">
+        <f ca="1">IF(A15="","","BR "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B15-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B15-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 25/11 · PY mar 24/11 · BO dom 22/11</v>
       </c>
       <c r="E15" t="str">
         <f ca="1">IF(A15="","",IF(C15&gt;0,Proyeccion!U15,"-"))</f>
@@ -30814,15 +30831,15 @@
       </c>
       <c r="G15" s="21">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.1381176470588237</v>
+        <v>8.1310588235294112</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I15" t="str">
-        <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(D15,"dd/mm")&amp;" ("&amp;E15&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 14.058 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 25/11 (Bolivia)</v>
+        <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 28/11: 14.038 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -30832,15 +30849,15 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>14122</v>
+        <v>14102</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
         <v>9</v>
       </c>
-      <c r="D16" s="20">
-        <f ca="1">IF(A16="","",Proyeccion!J16)</f>
-        <v>46358</v>
+      <c r="D16" t="str">
+        <f ca="1">IF(A16="","","BR "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B16-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B16-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 02/12 · PY mar 01/12 · BO dom 29/11</v>
       </c>
       <c r="E16" t="str">
         <f ca="1">IF(A16="","",IF(C16&gt;0,Proyeccion!U16,"-"))</f>
@@ -30852,15 +30869,15 @@
       </c>
       <c r="G16" s="21">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.160705882352941</v>
+        <v>8.1536470588235286</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I16" t="str">
-        <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(D16,"dd/mm")&amp;" ("&amp;E16&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 14.122 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 02/12 (Bolivia)</v>
+        <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 05/12: 14.102 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -30870,15 +30887,15 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>14186</v>
+        <v>14166</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
         <v>9</v>
       </c>
-      <c r="D17" s="20">
-        <f ca="1">IF(A17="","",Proyeccion!J17)</f>
-        <v>46365</v>
+      <c r="D17" t="str">
+        <f ca="1">IF(A17="","","BR "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B17-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B17-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 09/12 · PY mar 08/12 · BO dom 06/12</v>
       </c>
       <c r="E17" t="str">
         <f ca="1">IF(A17="","",IF(C17&gt;0,Proyeccion!U17,"-"))</f>
@@ -30890,15 +30907,15 @@
       </c>
       <c r="G17" s="21">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.1832941176470584</v>
+        <v>8.1762352941176459</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I17" t="str">
-        <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(D17,"dd/mm")&amp;" ("&amp;E17&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 14.186 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 09/12 (Bolivia)</v>
+        <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 12/12: 14.166 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -30908,15 +30925,15 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>14250</v>
+        <v>14230</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
         <v>9</v>
       </c>
-      <c r="D18" s="20">
-        <f ca="1">IF(A18="","",Proyeccion!J18)</f>
-        <v>46372</v>
+      <c r="D18" t="str">
+        <f ca="1">IF(A18="","","BR "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B18-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B18-LagBO-AtrasoDias,"ddd dd/mm"))</f>
+        <v>BR mié 16/12 · PY mar 15/12 · BO dom 13/12</v>
       </c>
       <c r="E18" t="str">
         <f ca="1">IF(A18="","",IF(C18&gt;0,Proyeccion!U18,"-"))</f>
@@ -30928,25 +30945,25 @@
       </c>
       <c r="G18" s="21">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.2058823529411757</v>
+        <v>8.1988235294117651</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
         <v>CARGAR 9</v>
       </c>
       <c r="I18" t="str">
-        <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(D18,"dd/mm")&amp;" ("&amp;E18&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 14.250 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 16/12 (Bolivia)</v>
+        <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
+        <v>Sab 19/12: 14.230 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -30983,12 +31000,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -31006,21 +31023,21 @@
         <v>164</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B6" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -31041,15 +31058,15 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B7" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>11289</v>
+        <v>12269</v>
       </c>
       <c r="C7" s="21">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>10.375919117647058</v>
+        <v>11.276654411764707</v>
       </c>
       <c r="D7" t="str">
         <f ca="1">IF(B7="","",IF(B7&lt;0,"FALTA",IF(C7&lt;2,"CRITICO",IF(C7&lt;CoberturaObjetivo,"JUSTO",IF(C7&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -31062,7 +31079,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B8" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -31083,23 +31100,23 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B9" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="C9" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>8.0887058823529401</v>
+        <v>8.0816470588235294</v>
       </c>
       <c r="D9" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="E9" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 1 camion(es) mas hasta el mié 30/09 para cerrar en 22.500</v>
+        <v>ok, cierra sobre 22.500</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -31117,21 +31134,21 @@
         <v>164</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31152,15 +31169,15 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>9661</v>
+        <v>10641</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.8795955882352935</v>
+        <v>9.780330882352942</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(B14="","",IF(B14&lt;0,"FALTA",IF(C14&lt;2,"CRITICO",IF(C14&lt;CoberturaObjetivo,"JUSTO",IF(C14&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -31173,7 +31190,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B15" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31194,15 +31211,15 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="39" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>18810</v>
+        <v>18790</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.0505882352941178</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31210,7 +31227,7 @@
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 4 camion(es) mas hasta el mié 07/10 para cerrar en 22.500</v>
+        <v>cargar 4 camion(es) mas hasta el mar 06/10 para cerrar en 22.500</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -31228,21 +31245,21 @@
         <v>164</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31263,15 +31280,15 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>8033</v>
+        <v>9013</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>7.383272058823529</v>
+        <v>8.2840073529411757</v>
       </c>
       <c r="D21" t="str">
         <f ca="1">IF(B21="","",IF(B21&lt;0,"FALTA",IF(C21&lt;2,"CRITICO",IF(C21&lt;CoberturaObjetivo,"JUSTO",IF(C21&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -31284,7 +31301,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B22" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31305,15 +31322,15 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>18774</v>
+        <v>18754</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>8.0378823529411765</v>
+        <v>8.030823529411764</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31321,12 +31338,12 @@
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 4 camion(es) mas hasta el mié 14/10 para cerrar en 22.500</v>
+        <v>cargar 4 camion(es) mas hasta el mar 13/10 para cerrar en 22.500</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -31376,7 +31393,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="44" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (4.032 menos que el plan) y el 10/10 en 22.810 (plan: 18.810).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 22.790 (plan: 18.790).</v>
       </c>
       <c r="B30" s="45"/>
       <c r="C30" s="45"/>
@@ -31406,7 +31423,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="44" t="str">
         <f ca="1">"Verde en transito (cargado y sin descargar): "&amp;FIXED(SUM(CgPipeline),0)&amp;" cajas."</f>
-        <v>Verde en transito (cargado y sin descargar): 5.934 cajas.</v>
+        <v>Verde en transito (cargado y sin descargar): 6.914 cajas.</v>
       </c>
       <c r="B33" s="45"/>
       <c r="C33" s="45"/>
@@ -31492,12 +31509,12 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="45">
@@ -31505,49 +31522,49 @@
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -31561,7 +31578,7 @@
       </c>
       <c r="C6" s="7">
         <f>Proyeccion!E6</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="D6" s="7">
         <f>Proyeccion!F6</f>
@@ -31569,7 +31586,7 @@
       </c>
       <c r="E6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*0.9,0)</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="F6">
         <f ca="1">IF(AND(E6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-E6)/CajasProm,0),0)</f>
@@ -31577,7 +31594,7 @@
       </c>
       <c r="G6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*1,0)</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="H6">
         <f ca="1">IF(AND(G6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-G6)/CajasProm,0),0)</f>
@@ -31585,7 +31602,7 @@
       </c>
       <c r="I6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*1.1,0)</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="J6">
         <f ca="1">IF(AND(I6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-I6)/CajasProm,0),0)</f>
@@ -31605,15 +31622,15 @@
       </c>
       <c r="N6" s="7">
         <f t="shared" ref="N6:N18" ca="1" si="1">G6-IF(A6&gt;=FechaHoy-WEEKDAY(FechaHoy,2)+8,3*CajasPY,0)</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" ref="O6:O18" ca="1" si="2">G6-IF(A6&gt;=FechaHoy-WEEKDAY(FechaHoy,2)+8,1000,0)</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P18" ca="1" si="3">G6-SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+8),CgSemana,"&lt;="&amp;MIN(A6,FechaHoy-WEEKDAY(FechaHoy,2)+15))</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -31635,7 +31652,7 @@
       </c>
       <c r="E7" s="7">
         <f t="shared" ref="E7:E18" ca="1" si="4">(E6+F6*CajasProm)+C7-ROUND(D7*0.9,0)</f>
-        <v>23518</v>
+        <v>24498</v>
       </c>
       <c r="F7">
         <f ca="1">IF(AND(E7&lt;MinimoSabado,Proyeccion!J7&gt;=FechaHoy),ROUNDUP((MinimoSabado-E7)/CajasProm,0),0)</f>
@@ -31643,43 +31660,43 @@
       </c>
       <c r="G7" s="7">
         <f t="shared" ref="G7:G18" ca="1" si="5">(G6+H6*CajasProm)+C7-ROUND(D7*1,0)</f>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="H7">
         <f ca="1">IF(AND(G7&lt;MinimoSabado,Proyeccion!J7&gt;=FechaHoy),ROUNDUP((MinimoSabado-G7)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ref="I7:I18" ca="1" si="6">(I6+J6*CajasProm)+C7-ROUND(D7*1.1,0)</f>
-        <v>20318</v>
+        <v>21298</v>
       </c>
       <c r="J7">
         <f ca="1">IF(AND(I7&lt;MinimoSabado,Proyeccion!J7&gt;=FechaHoy),ROUNDUP((MinimoSabado-I7)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" si="0"/>
-        <v>6914</v>
+        <v>7894</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" ref="L7:L18" ca="1" si="7">(L6+M6*CajasProm)+K7-D7</f>
-        <v>17886</v>
+        <v>18866</v>
       </c>
       <c r="M7">
         <f ca="1">IF(AND(L7&lt;MinimoSabado,Proyeccion!J7&gt;=FechaHoy),ROUNDUP((MinimoSabado-L7)/CajasProm,0),0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="O7" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>21918</v>
+        <v>22898</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -31701,15 +31718,15 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>21110</v>
+        <v>22090</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18810</v>
+        <v>18790</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
@@ -31717,11 +31734,11 @@
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>17510</v>
+        <v>17490</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -31729,7 +31746,7 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22810</v>
+        <v>22790</v>
       </c>
       <c r="M8">
         <f ca="1">IF(AND(L8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-L8)/CajasProm,0),0)</f>
@@ -31737,15 +31754,15 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15870</v>
+        <v>15850</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17810</v>
+        <v>17790</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18810</v>
+        <v>18790</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -31767,7 +31784,7 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>20774</v>
+        <v>20754</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
@@ -31775,7 +31792,7 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18774</v>
+        <v>18754</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
@@ -31783,11 +31800,11 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16774</v>
+        <v>17754</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
@@ -31795,7 +31812,7 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18774</v>
+        <v>18754</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -31803,15 +31820,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15834</v>
+        <v>15814</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17774</v>
+        <v>17754</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18774</v>
+        <v>18754</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -31833,7 +31850,7 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>20438</v>
+        <v>20418</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
@@ -31841,7 +31858,7 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18738</v>
+        <v>18718</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
@@ -31849,7 +31866,7 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>17038</v>
+        <v>17018</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
@@ -31861,7 +31878,7 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18738</v>
+        <v>18718</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
@@ -31869,15 +31886,15 @@
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15798</v>
+        <v>15778</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17738</v>
+        <v>17718</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18738</v>
+        <v>18718</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -31899,7 +31916,7 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16202</v>
+        <v>16182</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
@@ -31907,7 +31924,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13802</v>
+        <v>13782</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
@@ -31915,7 +31932,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12402</v>
+        <v>12382</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
@@ -31927,7 +31944,7 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13802</v>
+        <v>13782</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
@@ -31935,15 +31952,15 @@
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10862</v>
+        <v>10842</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12802</v>
+        <v>12782</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13802</v>
+        <v>13782</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -31965,7 +31982,7 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15966</v>
+        <v>15946</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -31973,7 +31990,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13866</v>
+        <v>13846</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -31981,7 +31998,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12766</v>
+        <v>12746</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
@@ -31993,7 +32010,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13866</v>
+        <v>13846</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -32001,15 +32018,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10926</v>
+        <v>10906</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12866</v>
+        <v>12846</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13866</v>
+        <v>13846</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -32031,7 +32048,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15730</v>
+        <v>15710</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -32039,7 +32056,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13930</v>
+        <v>13910</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
@@ -32047,7 +32064,7 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12130</v>
+        <v>12110</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
@@ -32059,7 +32076,7 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13930</v>
+        <v>13910</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
@@ -32067,15 +32084,15 @@
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10990</v>
+        <v>10970</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12930</v>
+        <v>12910</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13930</v>
+        <v>13910</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -32097,7 +32114,7 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15494</v>
+        <v>15474</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
@@ -32105,7 +32122,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13994</v>
+        <v>13974</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
@@ -32113,7 +32130,7 @@
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12494</v>
+        <v>12474</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -32125,7 +32142,7 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13994</v>
+        <v>13974</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
@@ -32133,15 +32150,15 @@
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11054</v>
+        <v>11034</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12994</v>
+        <v>12974</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13994</v>
+        <v>13974</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -32163,7 +32180,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16258</v>
+        <v>16238</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -32171,7 +32188,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14058</v>
+        <v>14038</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -32179,7 +32196,7 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12858</v>
+        <v>12838</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -32191,7 +32208,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14058</v>
+        <v>14038</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -32199,15 +32216,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11118</v>
+        <v>11098</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13058</v>
+        <v>13038</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14058</v>
+        <v>14038</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -32229,7 +32246,7 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16022</v>
+        <v>16002</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
@@ -32237,7 +32254,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14122</v>
+        <v>14102</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -32245,7 +32262,7 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12222</v>
+        <v>12202</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
@@ -32257,7 +32274,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14122</v>
+        <v>14102</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -32265,15 +32282,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11182</v>
+        <v>11162</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13122</v>
+        <v>13102</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14122</v>
+        <v>14102</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -32295,7 +32312,7 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15786</v>
+        <v>15766</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
@@ -32303,7 +32320,7 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14186</v>
+        <v>14166</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -32311,7 +32328,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12586</v>
+        <v>12566</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -32323,7 +32340,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14186</v>
+        <v>14166</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -32331,15 +32348,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11246</v>
+        <v>11226</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13186</v>
+        <v>13166</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14186</v>
+        <v>14166</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -32361,7 +32378,7 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15550</v>
+        <v>15530</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
@@ -32369,7 +32386,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14250</v>
+        <v>14230</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -32377,7 +32394,7 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>11950</v>
+        <v>11930</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
@@ -32389,7 +32406,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14250</v>
+        <v>14230</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -32397,20 +32414,20 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11310</v>
+        <v>11290</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13250</v>
+        <v>13230</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14250</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672732F1-95CE-471A-9A0E-90CE6C9C00BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ABC897-9AC8-4224-AF5B-9B89D6A02A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,12 +108,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="645">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 28/09/2026 10:49 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 28/09/2026 11:01 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -662,10 +662,13 @@
     <t>Aloha</t>
   </si>
   <si>
+    <t>descarga real confirmada por Gonzalo 28/09/2026 ("domingo 27/09 si descarga"): despues del conteo del sabado 26, suma a la semana del 28/09</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
     <t>Aloha: Solicitado</t>
-  </si>
-  <si>
-    <t>Bolivia</t>
   </si>
   <si>
     <t>Cassio Hauck</t>
@@ -3793,12 +3796,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45">
@@ -3806,31 +3809,31 @@
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>169</v>
@@ -4436,7 +4439,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -4469,184 +4472,184 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B5" s="12">
         <f>ConteoTotal</f>
         <v>26972</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B6" s="23">
         <f>ConteoTotal/(INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))/DiasVenta)</f>
         <v>10.114500000000001</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B7" s="12">
         <f ca="1">IFERROR(INDEX(PrStock,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>22898</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B8" s="24">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B9" s="24">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30">
       <c r="A10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B10" s="23">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>8.0435294117647054</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B11" s="24">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B12" s="24">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B13" s="23">
         <f>ConteoTotal/INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))</f>
         <v>1.6857500000000001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B14" s="12">
         <f>ConteoBR*CostoBR+ConteoPY*CostoPY+ConteoBO*CostoBO</f>
         <v>196107.57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B15" s="12">
         <f ca="1">SUM(CgPipeline)</f>
-        <v>6914</v>
+        <v>5934</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="25">
         <f>PrecioBR_BRL-(CepeaKg*KgCaja+ServiciosCaja)</f>
         <v>-7.0899999999999963</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B17" s="26">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="PY")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"PY",Proveedores!D5:D60),"")</f>
         <v>0.48076923076923078</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B18" s="26">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="BR")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"BR",Proveedores!D5:D60),"")</f>
@@ -4658,31 +4661,31 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B19" s="23">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>12.5</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B20" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
         <v>0.6047502310814612</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B21" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4694,7 +4697,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B22" s="26">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4706,206 +4709,206 @@
     </row>
     <row r="23" spans="1:3" ht="30">
       <c r="A23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>355060.63999999978</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B24" s="24">
         <f>COUNTIFS(CgEstado,"Supuesto*",CgCuenta,1)</f>
         <v>103</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B25" s="27">
         <f>IFERROR(AVERAGE(Proveedores!R5:R60),"")</f>
         <v>-9.5789473684210517E-4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
       <c r="A26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B26" s="26" t="str">
+        <v>312</v>
+      </c>
+      <c r="B26" s="26">
         <f>IFERROR(AVERAGE(CgOTIF),"sin descargas reales todavia")</f>
-        <v>sin descargas reales todavia</v>
+        <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B27" s="24">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
         <v>16</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B28" s="28" t="str">
         <f>IFERROR(SUMPRODUCT((Demanda!O6:O18&lt;&gt;"")*ABS(Demanda!P6:P18))/COUNTIF(Demanda!O6:O18,"&lt;&gt;"),"sin venta real cargada")</f>
         <v>sin venta real cargada</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30">
       <c r="A30" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="45">
       <c r="A31" s="29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45">
       <c r="A32" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45">
       <c r="A33" s="29" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30">
       <c r="A34" s="29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30">
       <c r="A35" s="29" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="30">
       <c r="A36" s="29" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="45">
       <c r="A37" s="29" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45">
       <c r="A38" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30">
       <c r="A39" s="29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30">
       <c r="A40" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30">
       <c r="A41" s="29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -4937,12 +4940,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="90">
@@ -4950,64 +4953,64 @@
         <v>164</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -5015,10 +5018,10 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -5042,10 +5045,10 @@
         <v>1008</v>
       </c>
       <c r="K5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M5" s="10">
         <v>37.75</v>
@@ -5062,19 +5065,19 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R5" s="32">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="S5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T5" s="21">
         <v>1.2</v>
       </c>
       <c r="U5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -5082,10 +5085,10 @@
         <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -5109,10 +5112,10 @@
         <v>1008</v>
       </c>
       <c r="K6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M6" s="10">
         <v>37</v>
@@ -5129,19 +5132,19 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="R6" s="32">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="S6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T6" s="21">
         <v>1.6</v>
       </c>
       <c r="U6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -5149,10 +5152,10 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -5176,10 +5179,10 @@
         <v>936</v>
       </c>
       <c r="K7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M7" s="10">
         <v>38.64</v>
@@ -5196,19 +5199,19 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R7" s="32">
         <v>-1.4E-3</v>
       </c>
       <c r="S7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="T7" s="21">
         <v>2.5</v>
       </c>
       <c r="U7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -5216,10 +5219,10 @@
         <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5243,10 +5246,10 @@
         <v>1008</v>
       </c>
       <c r="K8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M8" s="10">
         <v>41.63</v>
@@ -5263,19 +5266,19 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R8" s="32">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T8" s="21">
         <v>0.6</v>
       </c>
       <c r="U8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -5283,10 +5286,10 @@
         <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -5310,10 +5313,10 @@
         <v>1008</v>
       </c>
       <c r="K9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M9" s="10">
         <v>40.74</v>
@@ -5330,19 +5333,19 @@
         <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="R9" s="32">
         <v>-7.7999999999999996E-3</v>
       </c>
       <c r="S9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="T9" s="21">
         <v>0.4</v>
       </c>
       <c r="U9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -5350,10 +5353,10 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -5377,10 +5380,10 @@
         <v>1008</v>
       </c>
       <c r="K10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M10" s="10">
         <v>40.65</v>
@@ -5397,19 +5400,19 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R10" s="32">
         <v>-4.0000000000000002E-4</v>
       </c>
       <c r="S10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="T10" s="21">
         <v>1</v>
       </c>
       <c r="U10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -5417,10 +5420,10 @@
         <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -5444,10 +5447,10 @@
         <v>1008</v>
       </c>
       <c r="K11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M11" s="10">
         <v>42.33</v>
@@ -5470,7 +5473,7 @@
         <v>3</v>
       </c>
       <c r="U11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -5478,10 +5481,10 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -5505,10 +5508,10 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M12" s="10">
         <v>42.16</v>
@@ -5525,19 +5528,19 @@
         <v>3</v>
       </c>
       <c r="Q12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R12" s="32">
         <v>-1E-4</v>
       </c>
       <c r="S12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T12" s="21">
         <v>0.4</v>
       </c>
       <c r="U12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -5545,10 +5548,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -5572,10 +5575,10 @@
         <v>1008</v>
       </c>
       <c r="K13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M13" s="10">
         <v>37.64</v>
@@ -5592,7 +5595,7 @@
         <v>3</v>
       </c>
       <c r="U13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -5600,10 +5603,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -5627,10 +5630,10 @@
         <v>1008</v>
       </c>
       <c r="K14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M14" s="10">
         <v>37.799999999999997</v>
@@ -5647,7 +5650,7 @@
         <v>3</v>
       </c>
       <c r="U14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -5655,10 +5658,10 @@
         <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -5682,10 +5685,10 @@
         <v>1008</v>
       </c>
       <c r="K15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M15" s="10">
         <v>41.14</v>
@@ -5702,19 +5705,19 @@
         <v>3</v>
       </c>
       <c r="Q15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R15" s="32">
         <v>-1.8E-3</v>
       </c>
       <c r="S15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="T15" s="21">
         <v>0.3</v>
       </c>
       <c r="U15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -5722,10 +5725,10 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -5749,10 +5752,10 @@
         <v>980</v>
       </c>
       <c r="K16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
@@ -5763,22 +5766,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="R16" s="32">
         <v>-1E-3</v>
       </c>
       <c r="S16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T16" s="21">
         <v>2</v>
       </c>
       <c r="U16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -5813,10 +5816,10 @@
         <v>980</v>
       </c>
       <c r="K17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="0"/>
@@ -5827,22 +5830,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R17" s="32">
         <v>-3.8999999999999998E-3</v>
       </c>
       <c r="S17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T17" s="21">
         <v>1.8</v>
       </c>
       <c r="U17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -5850,10 +5853,10 @@
         <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D18">
         <v>12</v>
@@ -5877,10 +5880,10 @@
         <v>980</v>
       </c>
       <c r="K18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
@@ -5891,22 +5894,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R18" s="32">
         <v>1E-4</v>
       </c>
       <c r="S18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="T18" s="21">
         <v>0.6</v>
       </c>
       <c r="U18" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -5914,10 +5917,10 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -5941,10 +5944,10 @@
         <v>980</v>
       </c>
       <c r="K19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="0"/>
@@ -5955,22 +5958,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R19" s="32">
         <v>-1.5E-3</v>
       </c>
       <c r="S19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="T19" s="21">
         <v>0.5</v>
       </c>
       <c r="U19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -5978,7 +5981,7 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>185</v>
@@ -6005,10 +6008,10 @@
         <v>1050</v>
       </c>
       <c r="K20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="0"/>
@@ -6019,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q20" t="s">
         <v>3</v>
@@ -6028,7 +6031,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -6036,7 +6039,7 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>185</v>
@@ -6063,10 +6066,10 @@
         <v>1050</v>
       </c>
       <c r="K21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="0"/>
@@ -6077,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q21" t="s">
         <v>3</v>
@@ -6121,7 +6124,7 @@
         <v>3</v>
       </c>
       <c r="L22" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="0"/>
@@ -6132,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q22" t="s">
         <v>3</v>
@@ -6141,7 +6144,7 @@
         <v>3</v>
       </c>
       <c r="U22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -6149,10 +6152,10 @@
         <v>58</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D23" s="33">
         <v>0</v>
@@ -6168,7 +6171,7 @@
         <v>982</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L23" s="33"/>
       <c r="M23" s="35">
@@ -6183,20 +6186,20 @@
         <v>0</v>
       </c>
       <c r="P23" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R23" s="36">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="S23" s="33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="T23" s="33"/>
       <c r="U23" s="33" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -6204,10 +6207,10 @@
         <v>58</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D24" s="33">
         <v>0</v>
@@ -6223,7 +6226,7 @@
         <v>976</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L24" s="33"/>
       <c r="M24" s="35">
@@ -6238,20 +6241,20 @@
         <v>0</v>
       </c>
       <c r="P24" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R24" s="36">
         <v>-8.0000000000000004E-4</v>
       </c>
       <c r="S24" s="33" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T24" s="33"/>
       <c r="U24" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -6259,10 +6262,10 @@
         <v>58</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D25" s="33">
         <v>0</v>
@@ -6278,7 +6281,7 @@
         <v>1008</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L25" s="33"/>
       <c r="M25" s="35">
@@ -6293,20 +6296,20 @@
         <v>0</v>
       </c>
       <c r="P25" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R25" s="36">
         <v>0</v>
       </c>
       <c r="S25" s="33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="T25" s="33"/>
       <c r="U25" s="33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -6314,10 +6317,10 @@
         <v>58</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D26" s="33">
         <v>0</v>
@@ -6333,7 +6336,7 @@
         <v>996</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L26" s="33"/>
       <c r="M26" s="33"/>
@@ -6346,20 +6349,20 @@
         <v>0</v>
       </c>
       <c r="P26" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R26" s="36">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="S26" s="33" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T26" s="33"/>
       <c r="U26" s="33" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -6367,10 +6370,10 @@
         <v>59</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D27" s="33">
         <v>0</v>
@@ -6386,7 +6389,7 @@
         <v>972</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -6399,20 +6402,20 @@
         <v>0</v>
       </c>
       <c r="P27" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R27" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="S27" s="33" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="T27" s="33"/>
       <c r="U27" s="33" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -6420,10 +6423,10 @@
         <v>59</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D28" s="33">
         <v>0</v>
@@ -6452,20 +6455,20 @@
         <v>0</v>
       </c>
       <c r="P28" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="R28" s="36">
         <v>-1.4E-3</v>
       </c>
       <c r="S28" s="33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="T28" s="33"/>
       <c r="U28" s="33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -6473,10 +6476,10 @@
         <v>59</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D29" s="33">
         <v>0</v>
@@ -6505,25 +6508,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="R29" s="36">
         <v>-1E-3</v>
       </c>
       <c r="S29" s="33" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="T29" s="33"/>
       <c r="U29" s="33" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -6554,34 +6557,34 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30">
       <c r="A4" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B5" s="17">
         <v>0.18</v>
@@ -6593,12 +6596,12 @@
         <v>8600</v>
       </c>
       <c r="E5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B6" s="17">
         <v>9.5000000000000001E-2</v>
@@ -6610,12 +6613,12 @@
         <v>4200</v>
       </c>
       <c r="E6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B7" s="17">
         <v>6.9000000000000006E-2</v>
@@ -6632,7 +6635,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B8" s="17">
         <v>6.3E-2</v>
@@ -6649,7 +6652,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B9" s="17">
         <v>5.1999999999999998E-2</v>
@@ -6666,7 +6669,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B10" s="17">
         <v>4.7E-2</v>
@@ -6683,7 +6686,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B11" s="17">
         <v>4.2000000000000003E-2</v>
@@ -6695,12 +6698,12 @@
         <v>2100</v>
       </c>
       <c r="E11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B12" s="17">
         <v>0.04</v>
@@ -6712,12 +6715,12 @@
         <v>1750</v>
       </c>
       <c r="E12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B13" s="17">
         <v>3.6999999999999998E-2</v>
@@ -6734,7 +6737,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B14" s="17">
         <v>3.5000000000000003E-2</v>
@@ -6751,7 +6754,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B15" s="17">
         <v>3.4000000000000002E-2</v>
@@ -6768,7 +6771,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B16" s="17">
         <v>3.1E-2</v>
@@ -6785,7 +6788,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B17" s="17">
         <v>0.03</v>
@@ -6802,18 +6805,18 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B18" s="17">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B19" s="17">
         <v>2.5999999999999999E-2</v>
@@ -6824,18 +6827,18 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B20" s="17">
         <v>2.4E-2</v>
       </c>
       <c r="E20" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B21" s="17">
         <v>2.3E-2</v>
@@ -6846,7 +6849,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B22" s="17">
         <v>2.1000000000000001E-2</v>
@@ -6857,7 +6860,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B23" s="17">
         <v>1.7999999999999999E-2</v>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6887,164 +6890,164 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30">
       <c r="A17" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30">
       <c r="A18" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30">
       <c r="A20" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>3</v>
@@ -7052,138 +7055,138 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -7223,12 +7226,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7236,140 +7239,140 @@
         <v>163</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45">
       <c r="A5" s="37" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30">
       <c r="A6" s="37" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45">
       <c r="A7" s="37" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30">
       <c r="A8" s="37" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30">
       <c r="A9" s="37" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30">
       <c r="A10" s="37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30">
       <c r="A11" s="37" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -9055,7 +9058,9 @@
       <c r="I5" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="J5" s="6"/>
+      <c r="J5" s="6">
+        <v>46292</v>
+      </c>
       <c r="K5">
         <f t="shared" ref="K5:K68" si="3">IF(B5="","",IFERROR(INDEX(Lags,MATCH(D5,Origenes,0)),LagBR)+IF(J5&lt;&gt;"",0,AtrasoDias))</f>
         <v>4</v>
@@ -9085,19 +9090,19 @@
       </c>
       <c r="R5" s="5">
         <f t="shared" ref="R5:R68" si="9">IF(B5="","",IF(J5&lt;&gt;"",J5,B5+IFERROR(INDEX(LagsP90,MATCH(D5,Origenes,0)),K5)))</f>
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" ref="S5:S68" si="10">IF(R5="","",R5-WEEKDAY(R5,2)+1)</f>
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="T5" s="7">
         <f t="shared" ref="T5:T68" ca="1" si="11">IF(B5="","",IF(AND(B5&lt;=FechaHoy,J5="",I5&lt;&gt;"Supuesto",I5&lt;&gt;"Simulado"),H5,0))</f>
-        <v>980</v>
-      </c>
-      <c r="U5" t="str">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <f t="shared" ref="U5:U68" si="12">IF(J5="","",IF(J5-B5&lt;=K5+1,1,0))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -9157,7 +9162,7 @@
         <v>11340</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="9"/>
@@ -9192,7 +9197,7 @@
         <v>58</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>3</v>
@@ -9233,7 +9238,7 @@
         <v>6636.24</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="9"/>
@@ -9268,10 +9273,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" s="8">
         <v>1008</v>
@@ -9309,7 +9314,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="9"/>
@@ -9357,7 +9362,7 @@
         <v>980</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9">
@@ -9385,7 +9390,7 @@
         <v>6860</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="9"/>
@@ -9420,7 +9425,7 @@
         <v>59</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>3</v>
@@ -9433,7 +9438,7 @@
         <v>980</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10">
@@ -9461,7 +9466,7 @@
         <v>6860</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="9"/>
@@ -9496,7 +9501,7 @@
         <v>59</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>3</v>
@@ -9509,7 +9514,7 @@
         <v>980</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11">
@@ -9537,7 +9542,7 @@
         <v>6860</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="9"/>
@@ -9572,10 +9577,10 @@
         <v>58</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G12" s="8">
         <v>1008</v>
@@ -9585,7 +9590,7 @@
         <v>1008</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12">
@@ -9613,7 +9618,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="9"/>
@@ -9648,7 +9653,7 @@
         <v>59</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>3</v>
@@ -9661,7 +9666,7 @@
         <v>980</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13">
@@ -9689,7 +9694,7 @@
         <v>6860</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="9"/>
@@ -9724,10 +9729,10 @@
         <v>58</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G14" s="8">
         <v>1008</v>
@@ -9737,7 +9742,7 @@
         <v>1008</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14">
@@ -9765,7 +9770,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="9"/>
@@ -9800,10 +9805,10 @@
         <v>58</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G15" s="8">
         <v>1008</v>
@@ -9813,7 +9818,7 @@
         <v>1008</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15">
@@ -9841,7 +9846,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="9"/>
@@ -9876,10 +9881,10 @@
         <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G16" s="8">
         <v>1008</v>
@@ -9889,7 +9894,7 @@
         <v>1008</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16">
@@ -9917,7 +9922,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R16" s="5">
         <f t="shared" si="9"/>
@@ -9952,10 +9957,10 @@
         <v>58</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G17" s="8">
         <v>1008</v>
@@ -9965,7 +9970,7 @@
         <v>1008</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17">
@@ -9993,7 +9998,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R17" s="5">
         <f t="shared" si="9"/>
@@ -10028,10 +10033,10 @@
         <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G18" s="8">
         <v>936</v>
@@ -10041,7 +10046,7 @@
         <v>936</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18">
@@ -10069,7 +10074,7 @@
         <v>6636.24</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R18" s="5">
         <f t="shared" si="9"/>
@@ -10104,10 +10109,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G19" s="8">
         <v>1008</v>
@@ -10117,7 +10122,7 @@
         <v>1008</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19">
@@ -10145,7 +10150,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="9"/>
@@ -10180,10 +10185,10 @@
         <v>58</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G20" s="8">
         <v>1008</v>
@@ -10193,7 +10198,7 @@
         <v>1008</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20">
@@ -10221,7 +10226,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R20" s="5">
         <f t="shared" si="9"/>
@@ -10256,10 +10261,10 @@
         <v>58</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G21" s="8">
         <v>1008</v>
@@ -10269,7 +10274,7 @@
         <v>1008</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21">
@@ -10297,7 +10302,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R21" s="5">
         <f t="shared" si="9"/>
@@ -10332,10 +10337,10 @@
         <v>58</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G22" s="8">
         <v>1008</v>
@@ -10345,7 +10350,7 @@
         <v>1008</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22">
@@ -10373,7 +10378,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R22" s="5">
         <f t="shared" si="9"/>
@@ -10408,10 +10413,10 @@
         <v>58</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G23" s="8">
         <v>1008</v>
@@ -10421,7 +10426,7 @@
         <v>1008</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23">
@@ -10449,7 +10454,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R23" s="5">
         <f t="shared" si="9"/>
@@ -10484,10 +10489,10 @@
         <v>58</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G24" s="8">
         <v>1008</v>
@@ -10497,7 +10502,7 @@
         <v>1008</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24">
@@ -10525,7 +10530,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R24" s="5">
         <f t="shared" si="9"/>
@@ -10560,7 +10565,7 @@
         <v>59</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>3</v>
@@ -10573,7 +10578,7 @@
         <v>980</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25">
@@ -10601,7 +10606,7 @@
         <v>6860</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" si="9"/>
@@ -10636,7 +10641,7 @@
         <v>59</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>3</v>
@@ -10649,7 +10654,7 @@
         <v>980</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26">
@@ -10677,7 +10682,7 @@
         <v>6860</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="9"/>
@@ -10712,7 +10717,7 @@
         <v>59</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>3</v>
@@ -10725,7 +10730,7 @@
         <v>980</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27">
@@ -10753,7 +10758,7 @@
         <v>6860</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R27" s="5">
         <f t="shared" si="9"/>
@@ -10788,7 +10793,7 @@
         <v>59</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>3</v>
@@ -10801,7 +10806,7 @@
         <v>980</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28">
@@ -10829,7 +10834,7 @@
         <v>6860</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="9"/>
@@ -10864,7 +10869,7 @@
         <v>59</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>3</v>
@@ -10877,7 +10882,7 @@
         <v>980</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29">
@@ -10905,7 +10910,7 @@
         <v>6860</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="9"/>
@@ -10940,7 +10945,7 @@
         <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>3</v>
@@ -10953,7 +10958,7 @@
         <v>1008</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30">
@@ -10981,7 +10986,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
@@ -11016,7 +11021,7 @@
         <v>58</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>3</v>
@@ -11029,7 +11034,7 @@
         <v>1008</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31">
@@ -11057,7 +11062,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="9"/>
@@ -11092,7 +11097,7 @@
         <v>58</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>3</v>
@@ -11105,7 +11110,7 @@
         <v>1008</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32">
@@ -11133,7 +11138,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
@@ -11168,7 +11173,7 @@
         <v>58</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>3</v>
@@ -11181,7 +11186,7 @@
         <v>1008</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33">
@@ -11209,7 +11214,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="9"/>
@@ -11244,7 +11249,7 @@
         <v>58</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>3</v>
@@ -11257,7 +11262,7 @@
         <v>1008</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34">
@@ -11285,7 +11290,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
@@ -11320,7 +11325,7 @@
         <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>3</v>
@@ -11333,7 +11338,7 @@
         <v>1008</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35">
@@ -11361,7 +11366,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
@@ -11396,7 +11401,7 @@
         <v>58</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>3</v>
@@ -11409,7 +11414,7 @@
         <v>1008</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36">
@@ -11437,7 +11442,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R36" s="5">
         <f t="shared" si="9"/>
@@ -11472,7 +11477,7 @@
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>3</v>
@@ -11485,7 +11490,7 @@
         <v>1008</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37">
@@ -11513,7 +11518,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
@@ -11548,7 +11553,7 @@
         <v>59</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>3</v>
@@ -11561,7 +11566,7 @@
         <v>980</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38">
@@ -11589,7 +11594,7 @@
         <v>6860</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="9"/>
@@ -11624,7 +11629,7 @@
         <v>59</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>3</v>
@@ -11637,7 +11642,7 @@
         <v>980</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J39" s="6"/>
       <c r="K39">
@@ -11665,7 +11670,7 @@
         <v>6860</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R39" s="5">
         <f t="shared" si="9"/>
@@ -11700,7 +11705,7 @@
         <v>59</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>3</v>
@@ -11713,7 +11718,7 @@
         <v>980</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40">
@@ -11741,7 +11746,7 @@
         <v>6860</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
@@ -11776,7 +11781,7 @@
         <v>59</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>3</v>
@@ -11789,7 +11794,7 @@
         <v>980</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41">
@@ -11817,7 +11822,7 @@
         <v>6860</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
@@ -11852,7 +11857,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>3</v>
@@ -11865,7 +11870,7 @@
         <v>980</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42">
@@ -11893,7 +11898,7 @@
         <v>6860</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="9"/>
@@ -11928,7 +11933,7 @@
         <v>58</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>3</v>
@@ -11941,7 +11946,7 @@
         <v>1008</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43">
@@ -11969,7 +11974,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R43" s="5">
         <f t="shared" si="9"/>
@@ -12004,7 +12009,7 @@
         <v>58</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>3</v>
@@ -12017,7 +12022,7 @@
         <v>1008</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44">
@@ -12045,7 +12050,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R44" s="5">
         <f t="shared" si="9"/>
@@ -12080,7 +12085,7 @@
         <v>58</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>3</v>
@@ -12093,7 +12098,7 @@
         <v>1008</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45">
@@ -12121,7 +12126,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R45" s="5">
         <f t="shared" si="9"/>
@@ -12156,7 +12161,7 @@
         <v>58</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>3</v>
@@ -12169,7 +12174,7 @@
         <v>1008</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46">
@@ -12197,7 +12202,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="9"/>
@@ -12232,7 +12237,7 @@
         <v>58</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
@@ -12245,7 +12250,7 @@
         <v>1008</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47">
@@ -12273,7 +12278,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
@@ -12308,7 +12313,7 @@
         <v>58</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
@@ -12321,7 +12326,7 @@
         <v>1008</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
@@ -12349,7 +12354,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
@@ -12384,7 +12389,7 @@
         <v>58</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>3</v>
@@ -12397,7 +12402,7 @@
         <v>1008</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49">
@@ -12425,7 +12430,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R49" s="5">
         <f t="shared" si="9"/>
@@ -12460,7 +12465,7 @@
         <v>58</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>3</v>
@@ -12473,7 +12478,7 @@
         <v>1008</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50">
@@ -12501,7 +12506,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R50" s="5">
         <f t="shared" si="9"/>
@@ -12536,7 +12541,7 @@
         <v>59</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>3</v>
@@ -12549,7 +12554,7 @@
         <v>980</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51">
@@ -12577,7 +12582,7 @@
         <v>6860</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R51" s="5">
         <f t="shared" si="9"/>
@@ -12612,7 +12617,7 @@
         <v>59</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>3</v>
@@ -12625,7 +12630,7 @@
         <v>980</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52">
@@ -12653,7 +12658,7 @@
         <v>6860</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R52" s="5">
         <f t="shared" si="9"/>
@@ -12688,7 +12693,7 @@
         <v>59</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>3</v>
@@ -12701,7 +12706,7 @@
         <v>980</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53">
@@ -12729,7 +12734,7 @@
         <v>6860</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R53" s="5">
         <f t="shared" si="9"/>
@@ -12764,7 +12769,7 @@
         <v>59</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>3</v>
@@ -12777,7 +12782,7 @@
         <v>980</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54">
@@ -12805,7 +12810,7 @@
         <v>6860</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="9"/>
@@ -12840,7 +12845,7 @@
         <v>59</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>3</v>
@@ -12853,7 +12858,7 @@
         <v>980</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55">
@@ -12881,7 +12886,7 @@
         <v>6860</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R55" s="5">
         <f t="shared" si="9"/>
@@ -12916,7 +12921,7 @@
         <v>58</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>3</v>
@@ -12929,7 +12934,7 @@
         <v>1008</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56">
@@ -12957,7 +12962,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="9"/>
@@ -12992,7 +12997,7 @@
         <v>58</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>3</v>
@@ -13005,7 +13010,7 @@
         <v>1008</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57">
@@ -13033,7 +13038,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R57" s="5">
         <f t="shared" si="9"/>
@@ -13068,7 +13073,7 @@
         <v>58</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>3</v>
@@ -13081,7 +13086,7 @@
         <v>1008</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58">
@@ -13109,7 +13114,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="9"/>
@@ -13144,7 +13149,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>3</v>
@@ -13157,7 +13162,7 @@
         <v>1008</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59">
@@ -13185,7 +13190,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R59" s="5">
         <f t="shared" si="9"/>
@@ -13220,7 +13225,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>3</v>
@@ -13233,7 +13238,7 @@
         <v>1008</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60">
@@ -13261,7 +13266,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R60" s="5">
         <f t="shared" si="9"/>
@@ -13296,7 +13301,7 @@
         <v>58</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>3</v>
@@ -13309,7 +13314,7 @@
         <v>1008</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61">
@@ -13337,7 +13342,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="9"/>
@@ -13372,7 +13377,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
@@ -13385,7 +13390,7 @@
         <v>1008</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
@@ -13413,7 +13418,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
@@ -13448,7 +13453,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>3</v>
@@ -13461,7 +13466,7 @@
         <v>1008</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63">
@@ -13489,7 +13494,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R63" s="5">
         <f t="shared" si="9"/>
@@ -13524,7 +13529,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>3</v>
@@ -13537,7 +13542,7 @@
         <v>1008</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64">
@@ -13565,7 +13570,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q64" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R64" s="5">
         <f t="shared" si="9"/>
@@ -13600,7 +13605,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>3</v>
@@ -13613,7 +13618,7 @@
         <v>1008</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65">
@@ -13641,7 +13646,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R65" s="5">
         <f t="shared" si="9"/>
@@ -13676,7 +13681,7 @@
         <v>58</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>3</v>
@@ -13689,7 +13694,7 @@
         <v>1008</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66">
@@ -13717,7 +13722,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R66" s="5">
         <f t="shared" si="9"/>
@@ -13752,7 +13757,7 @@
         <v>58</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>3</v>
@@ -13765,7 +13770,7 @@
         <v>1008</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67">
@@ -13793,7 +13798,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R67" s="5">
         <f t="shared" si="9"/>
@@ -13828,7 +13833,7 @@
         <v>58</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>3</v>
@@ -13841,7 +13846,7 @@
         <v>1008</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68">
@@ -13869,7 +13874,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R68" s="5">
         <f t="shared" si="9"/>
@@ -13904,7 +13909,7 @@
         <v>58</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>3</v>
@@ -13917,7 +13922,7 @@
         <v>1008</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69">
@@ -13945,7 +13950,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R69" s="5">
         <f t="shared" ref="R69:R132" si="22">IF(B69="","",IF(J69&lt;&gt;"",J69,B69+IFERROR(INDEX(LagsP90,MATCH(D69,Origenes,0)),K69)))</f>
@@ -13980,7 +13985,7 @@
         <v>58</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>3</v>
@@ -13993,7 +13998,7 @@
         <v>1008</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70">
@@ -14021,7 +14026,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
@@ -14056,7 +14061,7 @@
         <v>58</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>3</v>
@@ -14069,7 +14074,7 @@
         <v>1008</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71">
@@ -14097,7 +14102,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R71" s="5">
         <f t="shared" si="22"/>
@@ -14132,7 +14137,7 @@
         <v>58</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>3</v>
@@ -14145,7 +14150,7 @@
         <v>1008</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72">
@@ -14173,7 +14178,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R72" s="5">
         <f t="shared" si="22"/>
@@ -14208,7 +14213,7 @@
         <v>58</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>3</v>
@@ -14221,7 +14226,7 @@
         <v>1008</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73">
@@ -14249,7 +14254,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R73" s="5">
         <f t="shared" si="22"/>
@@ -14284,7 +14289,7 @@
         <v>58</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>3</v>
@@ -14297,7 +14302,7 @@
         <v>1008</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74">
@@ -14325,7 +14330,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R74" s="5">
         <f t="shared" si="22"/>
@@ -14360,7 +14365,7 @@
         <v>58</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>3</v>
@@ -14373,7 +14378,7 @@
         <v>1008</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75">
@@ -14401,7 +14406,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R75" s="5">
         <f t="shared" si="22"/>
@@ -14436,7 +14441,7 @@
         <v>58</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>3</v>
@@ -14449,7 +14454,7 @@
         <v>1008</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76">
@@ -14477,7 +14482,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R76" s="5">
         <f t="shared" si="22"/>
@@ -14512,7 +14517,7 @@
         <v>58</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>3</v>
@@ -14525,7 +14530,7 @@
         <v>1008</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77">
@@ -14553,7 +14558,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q77" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R77" s="5">
         <f t="shared" si="22"/>
@@ -14588,7 +14593,7 @@
         <v>58</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>3</v>
@@ -14601,7 +14606,7 @@
         <v>1008</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78">
@@ -14629,7 +14634,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
@@ -14664,7 +14669,7 @@
         <v>58</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>3</v>
@@ -14677,7 +14682,7 @@
         <v>1008</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79">
@@ -14705,7 +14710,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R79" s="5">
         <f t="shared" si="22"/>
@@ -14740,7 +14745,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>3</v>
@@ -14753,7 +14758,7 @@
         <v>1008</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80">
@@ -14781,7 +14786,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R80" s="5">
         <f t="shared" si="22"/>
@@ -14816,7 +14821,7 @@
         <v>58</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>3</v>
@@ -14829,7 +14834,7 @@
         <v>1008</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81">
@@ -14857,7 +14862,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R81" s="5">
         <f t="shared" si="22"/>
@@ -14892,7 +14897,7 @@
         <v>58</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>3</v>
@@ -14905,7 +14910,7 @@
         <v>1008</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82">
@@ -14933,7 +14938,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R82" s="5">
         <f t="shared" si="22"/>
@@ -14968,7 +14973,7 @@
         <v>58</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>3</v>
@@ -14981,7 +14986,7 @@
         <v>1008</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83">
@@ -15009,7 +15014,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q83" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R83" s="5">
         <f t="shared" si="22"/>
@@ -15044,7 +15049,7 @@
         <v>58</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>3</v>
@@ -15057,7 +15062,7 @@
         <v>1008</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84">
@@ -15085,7 +15090,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R84" s="5">
         <f t="shared" si="22"/>
@@ -15120,7 +15125,7 @@
         <v>58</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>3</v>
@@ -15133,7 +15138,7 @@
         <v>1008</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85">
@@ -15161,7 +15166,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R85" s="5">
         <f t="shared" si="22"/>
@@ -15196,7 +15201,7 @@
         <v>58</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>3</v>
@@ -15209,7 +15214,7 @@
         <v>1008</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86">
@@ -15237,7 +15242,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
@@ -15272,7 +15277,7 @@
         <v>58</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>3</v>
@@ -15285,7 +15290,7 @@
         <v>1008</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87">
@@ -15313,7 +15318,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R87" s="5">
         <f t="shared" si="22"/>
@@ -15348,7 +15353,7 @@
         <v>58</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>3</v>
@@ -15361,7 +15366,7 @@
         <v>1008</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88">
@@ -15389,7 +15394,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q88" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R88" s="5">
         <f t="shared" si="22"/>
@@ -15424,7 +15429,7 @@
         <v>58</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>3</v>
@@ -15437,7 +15442,7 @@
         <v>1008</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89">
@@ -15465,7 +15470,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q89" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R89" s="5">
         <f t="shared" si="22"/>
@@ -15500,7 +15505,7 @@
         <v>58</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>3</v>
@@ -15513,7 +15518,7 @@
         <v>1008</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90">
@@ -15541,7 +15546,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q90" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R90" s="5">
         <f t="shared" si="22"/>
@@ -15576,7 +15581,7 @@
         <v>58</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>3</v>
@@ -15589,7 +15594,7 @@
         <v>1008</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91">
@@ -15617,7 +15622,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R91" s="5">
         <f t="shared" si="22"/>
@@ -15652,7 +15657,7 @@
         <v>58</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>3</v>
@@ -15665,7 +15670,7 @@
         <v>1008</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92">
@@ -15693,7 +15698,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R92" s="5">
         <f t="shared" si="22"/>
@@ -15728,7 +15733,7 @@
         <v>58</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>3</v>
@@ -15741,7 +15746,7 @@
         <v>1008</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93">
@@ -15769,7 +15774,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q93" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R93" s="5">
         <f t="shared" si="22"/>
@@ -15804,7 +15809,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>3</v>
@@ -15817,7 +15822,7 @@
         <v>1008</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94">
@@ -15845,7 +15850,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
@@ -15880,7 +15885,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>3</v>
@@ -15893,7 +15898,7 @@
         <v>1008</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95">
@@ -15921,7 +15926,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R95" s="5">
         <f t="shared" si="22"/>
@@ -15956,7 +15961,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>3</v>
@@ -15969,7 +15974,7 @@
         <v>1008</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96">
@@ -15997,7 +16002,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q96" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R96" s="5">
         <f t="shared" si="22"/>
@@ -16032,7 +16037,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>3</v>
@@ -16045,7 +16050,7 @@
         <v>1008</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97">
@@ -16073,7 +16078,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R97" s="5">
         <f t="shared" si="22"/>
@@ -16108,7 +16113,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>3</v>
@@ -16121,7 +16126,7 @@
         <v>1008</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98">
@@ -16149,7 +16154,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R98" s="5">
         <f t="shared" si="22"/>
@@ -16184,7 +16189,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>3</v>
@@ -16197,7 +16202,7 @@
         <v>1008</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99">
@@ -16225,7 +16230,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q99" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R99" s="5">
         <f t="shared" si="22"/>
@@ -16260,7 +16265,7 @@
         <v>58</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>3</v>
@@ -16273,7 +16278,7 @@
         <v>1008</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100">
@@ -16301,7 +16306,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q100" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R100" s="5">
         <f t="shared" si="22"/>
@@ -16336,7 +16341,7 @@
         <v>58</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>3</v>
@@ -16349,7 +16354,7 @@
         <v>1008</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101">
@@ -16377,7 +16382,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R101" s="5">
         <f t="shared" si="22"/>
@@ -16412,7 +16417,7 @@
         <v>58</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>3</v>
@@ -16425,7 +16430,7 @@
         <v>1008</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102">
@@ -16453,7 +16458,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q102" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
@@ -16488,7 +16493,7 @@
         <v>58</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>3</v>
@@ -16501,7 +16506,7 @@
         <v>1008</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103">
@@ -16529,7 +16534,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R103" s="5">
         <f t="shared" si="22"/>
@@ -16564,7 +16569,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>3</v>
@@ -16577,7 +16582,7 @@
         <v>1008</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104">
@@ -16605,7 +16610,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q104" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R104" s="5">
         <f t="shared" si="22"/>
@@ -16640,7 +16645,7 @@
         <v>58</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>3</v>
@@ -16653,7 +16658,7 @@
         <v>1008</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105">
@@ -16681,7 +16686,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q105" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R105" s="5">
         <f t="shared" si="22"/>
@@ -16716,7 +16721,7 @@
         <v>58</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
@@ -16729,7 +16734,7 @@
         <v>1008</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106">
@@ -16757,7 +16762,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q106" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R106" s="5">
         <f t="shared" si="22"/>
@@ -16792,7 +16797,7 @@
         <v>58</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>3</v>
@@ -16805,7 +16810,7 @@
         <v>1008</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107">
@@ -16833,7 +16838,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q107" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R107" s="5">
         <f t="shared" si="22"/>
@@ -16868,7 +16873,7 @@
         <v>58</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>3</v>
@@ -16881,7 +16886,7 @@
         <v>1008</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108">
@@ -16909,7 +16914,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q108" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R108" s="5">
         <f t="shared" si="22"/>
@@ -16944,7 +16949,7 @@
         <v>58</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>3</v>
@@ -16957,7 +16962,7 @@
         <v>1008</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109">
@@ -16985,7 +16990,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q109" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R109" s="5">
         <f t="shared" si="22"/>
@@ -17020,7 +17025,7 @@
         <v>58</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>3</v>
@@ -17033,7 +17038,7 @@
         <v>1008</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110">
@@ -17061,7 +17066,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q110" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
@@ -17096,7 +17101,7 @@
         <v>58</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>3</v>
@@ -17109,7 +17114,7 @@
         <v>1008</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111">
@@ -17137,7 +17142,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q111" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R111" s="5">
         <f t="shared" si="22"/>
@@ -17172,7 +17177,7 @@
         <v>58</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>3</v>
@@ -17185,7 +17190,7 @@
         <v>1008</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112">
@@ -17213,7 +17218,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q112" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R112" s="5">
         <f t="shared" si="22"/>
@@ -17248,7 +17253,7 @@
         <v>58</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>3</v>
@@ -17261,7 +17266,7 @@
         <v>1008</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113">
@@ -17289,7 +17294,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q113" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R113" s="5">
         <f t="shared" si="22"/>
@@ -17324,7 +17329,7 @@
         <v>58</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>3</v>
@@ -17337,7 +17342,7 @@
         <v>1008</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114">
@@ -17365,7 +17370,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q114" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R114" s="5">
         <f t="shared" si="22"/>
@@ -17400,7 +17405,7 @@
         <v>58</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>3</v>
@@ -17413,7 +17418,7 @@
         <v>1008</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115">
@@ -17441,7 +17446,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R115" s="5">
         <f t="shared" si="22"/>
@@ -17476,7 +17481,7 @@
         <v>58</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>3</v>
@@ -17489,7 +17494,7 @@
         <v>1008</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116">
@@ -17517,7 +17522,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q116" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R116" s="5">
         <f t="shared" si="22"/>
@@ -17552,7 +17557,7 @@
         <v>58</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>3</v>
@@ -17565,7 +17570,7 @@
         <v>1008</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117">
@@ -17593,7 +17598,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q117" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R117" s="5">
         <f t="shared" si="22"/>
@@ -17628,7 +17633,7 @@
         <v>58</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>3</v>
@@ -17641,7 +17646,7 @@
         <v>1008</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118">
@@ -17669,7 +17674,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q118" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
@@ -17704,7 +17709,7 @@
         <v>58</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>3</v>
@@ -17717,7 +17722,7 @@
         <v>1008</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119">
@@ -17745,7 +17750,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q119" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R119" s="5">
         <f t="shared" si="22"/>
@@ -17780,7 +17785,7 @@
         <v>58</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>3</v>
@@ -17793,7 +17798,7 @@
         <v>1008</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120">
@@ -17821,7 +17826,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q120" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R120" s="5">
         <f t="shared" si="22"/>
@@ -17856,7 +17861,7 @@
         <v>58</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>3</v>
@@ -17869,7 +17874,7 @@
         <v>1008</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121">
@@ -17897,7 +17902,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q121" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R121" s="5">
         <f t="shared" si="22"/>
@@ -17932,7 +17937,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>3</v>
@@ -17945,7 +17950,7 @@
         <v>1008</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122">
@@ -17973,7 +17978,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q122" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R122" s="5">
         <f t="shared" si="22"/>
@@ -18008,7 +18013,7 @@
         <v>58</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>3</v>
@@ -18021,7 +18026,7 @@
         <v>1008</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123">
@@ -18049,7 +18054,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q123" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R123" s="5">
         <f t="shared" si="22"/>
@@ -18084,7 +18089,7 @@
         <v>58</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>3</v>
@@ -18097,7 +18102,7 @@
         <v>1008</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124">
@@ -18125,7 +18130,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q124" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R124" s="5">
         <f t="shared" si="22"/>
@@ -18160,7 +18165,7 @@
         <v>58</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>3</v>
@@ -18173,7 +18178,7 @@
         <v>1008</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125">
@@ -18201,7 +18206,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q125" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R125" s="5">
         <f t="shared" si="22"/>
@@ -18236,7 +18241,7 @@
         <v>58</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>3</v>
@@ -18249,7 +18254,7 @@
         <v>1008</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126">
@@ -18277,7 +18282,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q126" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
@@ -18312,7 +18317,7 @@
         <v>58</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>3</v>
@@ -18325,7 +18330,7 @@
         <v>1008</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J127" s="6"/>
       <c r="K127">
@@ -18353,7 +18358,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q127" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R127" s="5">
         <f t="shared" si="22"/>
@@ -29152,12 +29157,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="75">
@@ -29165,64 +29170,64 @@
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>169</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -30425,41 +30430,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45">
       <c r="A5" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>169</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -30958,12 +30963,12 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -31000,12 +31005,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -31023,21 +31028,21 @@
         <v>164</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B6" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -31058,7 +31063,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B7" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -31100,7 +31105,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B9" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -31134,21 +31139,21 @@
         <v>164</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31169,7 +31174,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31211,7 +31216,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="39" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -31245,21 +31250,21 @@
         <v>164</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>169</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31280,7 +31285,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31322,7 +31327,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -31343,7 +31348,7 @@
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -31423,7 +31428,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="44" t="str">
         <f ca="1">"Verde en transito (cargado y sin descargar): "&amp;FIXED(SUM(CgPipeline),0)&amp;" cajas."</f>
-        <v>Verde en transito (cargado y sin descargar): 6.914 cajas.</v>
+        <v>Verde en transito (cargado y sin descargar): 5.934 cajas.</v>
       </c>
       <c r="B33" s="45"/>
       <c r="C33" s="45"/>
@@ -31509,12 +31514,12 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="45">
@@ -31522,49 +31527,49 @@
         <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -31610,11 +31615,11 @@
       </c>
       <c r="K6" s="7">
         <f t="shared" ref="K6:K18" si="0">SUMIFS(CgCajas,CgSemanaP90,A6,CgCuenta,1)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="L6" s="7">
         <f>ConteoTotal+K6-D6</f>
-        <v>26972</v>
+        <v>27952</v>
       </c>
       <c r="M6">
         <f ca="1">IF(AND(L6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-L6)/CajasProm,0),0)</f>
@@ -31676,7 +31681,7 @@
       </c>
       <c r="K7" s="7">
         <f t="shared" si="0"/>
-        <v>7894</v>
+        <v>6914</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" ref="L7:L18" ca="1" si="7">(L6+M6*CajasProm)+K7-D7</f>
@@ -32427,7 +32432,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F55DFD4-0008-42D6-9667-93576920F21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B5A0B3-74E7-4B60-AF2D-52250EAD9DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="678">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 30/09/2026 17:20 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 30/09/2026 17:24 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>18840</v>
+        <v>17904</v>
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>22614</v>
+        <v>22678</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>22578</v>
+        <v>22642</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>22642</v>
+        <v>22706</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>22706</v>
+        <v>22770</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>22770</v>
+        <v>22834</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>22834</v>
+        <v>22898</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>22898</v>
+        <v>22962</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>22962</v>
+        <v>23026</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>23026</v>
+        <v>23090</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>23090</v>
+        <v>23154</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.1907058823529404</v>
+        <v>8.1194117647058821</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>303</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>307</v>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>13.5</v>
+        <v>13.25</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>320</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.61492559579308548</v>
+        <v>0.60808502562156008</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>322</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.36549434975571549</v>
+        <v>0.37198709432529892</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>1.9580054451199046E-2</v>
+        <v>1.9927880053141014E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>382339.83999999973</v>
+        <v>375703.59999999974</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>326</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B27" s="25">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>334</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="s">
         <v>3</v>
@@ -11820,17 +11820,17 @@
         <v>58</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G28" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H28" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>199</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="P28" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q28" s="9" t="s">
         <v>225</v>
@@ -11896,10 +11896,10 @@
         <v>58</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G29" s="8">
         <v>1008</v>
@@ -11969,20 +11969,20 @@
         <v>mar</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="G30" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H30" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>199</v>
@@ -11990,11 +11990,11 @@
       <c r="J30" s="6"/>
       <c r="K30">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="4"/>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="M30" s="5">
         <f t="shared" si="5"/>
@@ -12006,22 +12006,22 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="S30" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="T30" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12048,7 +12048,7 @@
         <v>59</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>3</v>
@@ -12089,7 +12089,7 @@
         <v>6860</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="9"/>
@@ -12114,27 +12114,27 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>mié</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="G32" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H32" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>199</v>
@@ -12142,7 +12142,7 @@
       <c r="J32" s="6"/>
       <c r="K32">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="4"/>
@@ -12158,22 +12158,22 @@
       </c>
       <c r="O32" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P32" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="S32" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="T32" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12200,10 +12200,10 @@
         <v>58</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G33" s="8">
         <v>1008</v>
@@ -12273,20 +12273,20 @@
         <v>mié</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="G34" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>199</v>
@@ -12294,11 +12294,11 @@
       <c r="J34" s="6"/>
       <c r="K34">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="4"/>
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M34" s="5">
         <f t="shared" si="5"/>
@@ -12310,18 +12310,18 @@
       </c>
       <c r="O34" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P34" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="S34" s="5">
         <f t="shared" si="10"/>
@@ -12342,27 +12342,27 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>vie</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="G35" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H35" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>199</v>
@@ -12370,15 +12370,15 @@
       <c r="J35" s="6"/>
       <c r="K35">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="4"/>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M35" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="N35">
         <f t="shared" si="6"/>
@@ -12386,18 +12386,18 @@
       </c>
       <c r="O35" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P35" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="S35" s="5">
         <f t="shared" si="10"/>
@@ -12428,10 +12428,10 @@
         <v>58</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G36" s="8">
         <v>1008</v>
@@ -12504,10 +12504,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G37" s="8">
         <v>1008</v>
@@ -12580,10 +12580,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G38" s="8">
         <v>1008</v>
@@ -12656,7 +12656,7 @@
         <v>58</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>206</v>
@@ -12722,27 +12722,27 @@
         <v>36</v>
       </c>
       <c r="B40" s="6">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>sáb</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G40" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>199</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L40" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="M40" s="5">
         <f t="shared" si="5"/>
@@ -12770,14 +12770,14 @@
       </c>
       <c r="P40" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="S40" s="5">
         <f t="shared" si="10"/>
@@ -12798,39 +12798,39 @@
         <v>37</v>
       </c>
       <c r="B41" s="6">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="1"/>
-        <v>sáb</v>
+        <v>lun</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>218</v>
+        <v>3</v>
       </c>
       <c r="G41" s="8">
-        <v>936</v>
+        <v>980</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>980</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="4"/>
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="5"/>
@@ -12842,18 +12842,18 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P41" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>6860</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="S41" s="5">
         <f t="shared" si="10"/>
@@ -13178,43 +13178,43 @@
         <v>42</v>
       </c>
       <c r="B46" s="6">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H46" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="4"/>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="M46" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="N46">
         <f t="shared" si="6"/>
@@ -13222,22 +13222,22 @@
       </c>
       <c r="O46" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="S46" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="T46" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13786,39 +13786,39 @@
         <v>50</v>
       </c>
       <c r="B54" s="6">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G54" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H54" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M54" s="5">
         <f t="shared" si="5"/>
@@ -13830,18 +13830,18 @@
       </c>
       <c r="O54" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P54" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="S54" s="5">
         <f t="shared" si="10"/>
@@ -14166,43 +14166,43 @@
         <v>55</v>
       </c>
       <c r="B59" s="6">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H59" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" s="5">
         <f t="shared" si="4"/>
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="M59" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="N59">
         <f t="shared" si="6"/>
@@ -14210,22 +14210,22 @@
       </c>
       <c r="O59" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P59" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="R59" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46324</v>
       </c>
       <c r="S59" s="5">
         <f t="shared" si="10"/>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="T59" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14774,7 +14774,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="6">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="1"/>
@@ -14806,11 +14806,11 @@
       </c>
       <c r="L67" s="5">
         <f t="shared" si="4"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="M67" s="5">
         <f t="shared" si="5"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="N67">
         <f t="shared" si="6"/>
@@ -14829,11 +14829,11 @@
       </c>
       <c r="R67" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46331</v>
       </c>
       <c r="S67" s="5">
         <f t="shared" si="10"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="T67" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -15382,7 +15382,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="6">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="14"/>
@@ -15414,11 +15414,11 @@
       </c>
       <c r="L75" s="5">
         <f t="shared" si="17"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="M75" s="5">
         <f t="shared" si="18"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="N75">
         <f t="shared" si="19"/>
@@ -15437,11 +15437,11 @@
       </c>
       <c r="R75" s="5">
         <f t="shared" si="22"/>
-        <v>46331</v>
+        <v>46338</v>
       </c>
       <c r="S75" s="5">
         <f t="shared" si="23"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="T75" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15990,7 +15990,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="6">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="14"/>
@@ -16022,11 +16022,11 @@
       </c>
       <c r="L83" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="M83" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="N83">
         <f t="shared" si="19"/>
@@ -16045,11 +16045,11 @@
       </c>
       <c r="R83" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46345</v>
       </c>
       <c r="S83" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="T83" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16598,7 +16598,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="6">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="14"/>
@@ -16630,11 +16630,11 @@
       </c>
       <c r="L91" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="M91" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="N91">
         <f t="shared" si="19"/>
@@ -16653,11 +16653,11 @@
       </c>
       <c r="R91" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46352</v>
       </c>
       <c r="S91" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="T91" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17206,7 +17206,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="6">
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="14"/>
@@ -17238,11 +17238,11 @@
       </c>
       <c r="L99" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="M99" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="N99">
         <f t="shared" si="19"/>
@@ -17261,11 +17261,11 @@
       </c>
       <c r="R99" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46359</v>
       </c>
       <c r="S99" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="T99" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17814,7 +17814,7 @@
         <v>103</v>
       </c>
       <c r="B107" s="6">
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="14"/>
@@ -17846,11 +17846,11 @@
       </c>
       <c r="L107" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="M107" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="N107">
         <f t="shared" si="19"/>
@@ -17869,11 +17869,11 @@
       </c>
       <c r="R107" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46366</v>
       </c>
       <c r="S107" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="T107" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18422,7 +18422,7 @@
         <v>111</v>
       </c>
       <c r="B115" s="6">
-        <v>46360</v>
+        <v>46367</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="14"/>
@@ -18454,11 +18454,11 @@
       </c>
       <c r="L115" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="M115" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="N115">
         <f t="shared" si="19"/>
@@ -18477,11 +18477,11 @@
       </c>
       <c r="R115" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46373</v>
       </c>
       <c r="S115" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="T115" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19030,7 +19030,7 @@
         <v>119</v>
       </c>
       <c r="B123" s="6">
-        <v>46367</v>
+        <v>46374</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="14"/>
@@ -19062,11 +19062,11 @@
       </c>
       <c r="L123" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="M123" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="N123">
         <f t="shared" si="19"/>
@@ -19085,11 +19085,11 @@
       </c>
       <c r="R123" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46380</v>
       </c>
       <c r="S123" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="T123" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19633,75 +19633,61 @@
       </c>
     </row>
     <row r="131" spans="1:21">
-      <c r="A131">
+      <c r="A131" t="str">
         <f t="shared" si="13"/>
-        <v>127</v>
-      </c>
-      <c r="B131" s="6">
-        <v>46374</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B131" s="6"/>
       <c r="C131" t="str">
         <f t="shared" si="14"/>
-        <v>vie</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E131" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G131" s="8">
-        <v>1008</v>
-      </c>
-      <c r="H131" s="7">
+        <v/>
+      </c>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>1008</v>
-      </c>
-      <c r="I131" s="9" t="s">
-        <v>237</v>
-      </c>
+        <v/>
+      </c>
+      <c r="I131" s="9"/>
       <c r="J131" s="6"/>
-      <c r="K131">
+      <c r="K131" t="str">
         <f t="shared" si="16"/>
-        <v>3</v>
-      </c>
-      <c r="L131" s="5">
+        <v/>
+      </c>
+      <c r="L131" s="5" t="str">
         <f t="shared" si="17"/>
-        <v>46377</v>
-      </c>
-      <c r="M131" s="5">
+        <v/>
+      </c>
+      <c r="M131" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>46377</v>
-      </c>
-      <c r="N131">
+        <v/>
+      </c>
+      <c r="N131" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O131" s="10">
+        <v/>
+      </c>
+      <c r="O131" s="10" t="str">
         <f t="shared" si="20"/>
-        <v>7.09</v>
-      </c>
-      <c r="P131" s="7">
+        <v/>
+      </c>
+      <c r="P131" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>7146.72</v>
-      </c>
-      <c r="Q131" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="R131" s="5">
+        <v/>
+      </c>
+      <c r="Q131" s="9"/>
+      <c r="R131" s="5" t="str">
         <f t="shared" si="22"/>
-        <v>46380</v>
-      </c>
-      <c r="S131" s="5">
+        <v/>
+      </c>
+      <c r="S131" s="5" t="str">
         <f t="shared" si="23"/>
-        <v>46377</v>
-      </c>
-      <c r="T131" s="7">
-        <f t="shared" ca="1" si="24"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="T131" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="U131" t="str">
         <f t="shared" si="25"/>
@@ -30500,11 +30486,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="2"/>
-        <v>18840</v>
+        <v>17904</v>
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
@@ -30512,7 +30498,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30520,7 +30506,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30532,11 +30518,11 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.7310588235294109</v>
+        <v>8.4007058823529412</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30544,11 +30530,11 @@
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
-        <v>11460</v>
+        <v>10524</v>
       </c>
       <c r="P8" s="22">
         <f>IF(Demanda!L9=0,"",O8/(Demanda!L9/DiasVenta))</f>
-        <v>6.555439031366193</v>
+        <v>6.0200209743540851</v>
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
@@ -30582,7 +30568,7 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
@@ -30598,7 +30584,7 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
@@ -30606,7 +30592,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30614,27 +30600,27 @@
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22614</v>
+        <v>22678</v>
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>7.9814117647058822</v>
+        <v>8.0039999999999996</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 4</v>
+        <v>CARGAR 5</v>
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
-        <v>6947</v>
+        <v>6011</v>
       </c>
       <c r="P9" s="22">
         <f>IF(Demanda!L10=0,"",O9/(Demanda!L10/DiasVenta))</f>
-        <v>3.9738773953665745</v>
+        <v>3.4384593383544666</v>
       </c>
       <c r="Q9" s="7">
         <f>Q8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M9,0)</f>
@@ -30668,7 +30654,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -30684,15 +30670,15 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>14578</v>
+        <v>13642</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18578</v>
+        <v>18642</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30704,11 +30690,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22578</v>
+        <v>22642</v>
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>7.9687058823529409</v>
+        <v>7.9912941176470582</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30716,11 +30702,11 @@
       </c>
       <c r="O10" s="7">
         <f>O9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L10,0)</f>
-        <v>4522</v>
+        <v>3586</v>
       </c>
       <c r="P10" s="22">
         <f>IF(Demanda!L11=0,"",O10/(Demanda!L11/DiasVenta))</f>
-        <v>2.586709886547812</v>
+        <v>2.0512918295357041</v>
       </c>
       <c r="Q10" s="7">
         <f>Q9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M10,0)</f>
@@ -30754,7 +30740,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>14578</v>
+        <v>13642</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -30770,15 +30756,15 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>5642</v>
+        <v>4706</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13642</v>
+        <v>13706</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30790,11 +30776,11 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22642</v>
+        <v>22706</v>
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>7.9912941176470582</v>
+        <v>8.0138823529411756</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30802,11 +30788,11 @@
       </c>
       <c r="O11" s="7">
         <f>O10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L11,0)</f>
-        <v>2097</v>
+        <v>1161</v>
       </c>
       <c r="P11" s="22">
         <f>IF(Demanda!L12=0,"",O11/(Demanda!L12/DiasVenta))</f>
-        <v>1.1995423777290495</v>
+        <v>0.6641243207169415</v>
       </c>
       <c r="Q11" s="7">
         <f>Q10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M11,0)</f>
@@ -30840,7 +30826,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>5642</v>
+        <v>4706</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30856,15 +30842,15 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-3294</v>
+        <v>-4230</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13706</v>
+        <v>13770</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30876,11 +30862,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22706</v>
+        <v>22770</v>
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.0138823529411756</v>
+        <v>8.0364705882352929</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30888,11 +30874,11 @@
       </c>
       <c r="O12" s="7">
         <f>O11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L12,0)</f>
-        <v>-328</v>
+        <v>-1264</v>
       </c>
       <c r="P12" s="22">
         <f>IF(Demanda!L13=0,"",O12/(Demanda!L13/DiasVenta))</f>
-        <v>-0.18762513108971302</v>
+        <v>-0.72304318810182089</v>
       </c>
       <c r="Q12" s="7">
         <f>Q11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M12,0)</f>
@@ -30926,7 +30912,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-3294</v>
+        <v>-4230</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30942,15 +30928,15 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-12230</v>
+        <v>-13166</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13770</v>
+        <v>13834</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -30962,11 +30948,11 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22770</v>
+        <v>22834</v>
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.0364705882352929</v>
+        <v>8.0590588235294121</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30974,11 +30960,11 @@
       </c>
       <c r="O13" s="7">
         <f>O12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L13,0)</f>
-        <v>-2753</v>
+        <v>-3689</v>
       </c>
       <c r="P13" s="22">
         <f>IF(Demanda!L14=0,"",O13/(Demanda!L14/DiasVenta))</f>
-        <v>-1.5747926399084755</v>
+        <v>-2.1102106969205834</v>
       </c>
       <c r="Q13" s="7">
         <f>Q12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M13,0)</f>
@@ -31012,7 +30998,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-12230</v>
+        <v>-13166</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31028,15 +31014,15 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-21166</v>
+        <v>-22102</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13834</v>
+        <v>13898</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31048,11 +31034,11 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22834</v>
+        <v>22898</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.0590588235294121</v>
+        <v>8.0816470588235294</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31060,11 +31046,11 @@
       </c>
       <c r="O14" s="7">
         <f>O13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L14,0)</f>
-        <v>-5178</v>
+        <v>-6114</v>
       </c>
       <c r="P14" s="22">
         <f>IF(Demanda!L15=0,"",O14/(Demanda!L15/DiasVenta))</f>
-        <v>-2.961960148727238</v>
+        <v>-3.4973782057393459</v>
       </c>
       <c r="Q14" s="7">
         <f>Q13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M14,0)</f>
@@ -31098,7 +31084,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-21166</v>
+        <v>-22102</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31114,15 +31100,15 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-30102</v>
+        <v>-31038</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>44000</v>
+        <v>45000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13898</v>
+        <v>13962</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31134,11 +31120,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22898</v>
+        <v>22962</v>
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.0816470588235294</v>
+        <v>8.1042352941176468</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31146,11 +31132,11 @@
       </c>
       <c r="O15" s="7">
         <f>O14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L15,0)</f>
-        <v>-7603</v>
+        <v>-8539</v>
       </c>
       <c r="P15" s="22">
         <f>IF(Demanda!L16=0,"",O15/(Demanda!L16/DiasVenta))</f>
-        <v>-4.3491276575460001</v>
+        <v>-4.8845457145581079</v>
       </c>
       <c r="Q15" s="7">
         <f>Q14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M15,0)</f>
@@ -31184,7 +31170,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-30102</v>
+        <v>-31038</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31200,15 +31186,15 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-39038</v>
+        <v>-39974</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>53000</v>
+        <v>54000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13962</v>
+        <v>14026</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31220,11 +31206,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22962</v>
+        <v>23026</v>
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.1042352941176468</v>
+        <v>8.1268235294117641</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31232,11 +31218,11 @@
       </c>
       <c r="O16" s="7">
         <f>O15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L16,0)</f>
-        <v>-10028</v>
+        <v>-10964</v>
       </c>
       <c r="P16" s="22">
         <f>IF(Demanda!L17=0,"",O16/(Demanda!L17/DiasVenta))</f>
-        <v>-5.736295166364763</v>
+        <v>-6.2717132233768709</v>
       </c>
       <c r="Q16" s="7">
         <f>Q15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M16,0)</f>
@@ -31270,7 +31256,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-39038</v>
+        <v>-39974</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31286,15 +31272,15 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-47974</v>
+        <v>-48910</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14026</v>
+        <v>14090</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31306,11 +31292,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23026</v>
+        <v>23090</v>
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.1268235294117641</v>
+        <v>8.1494117647058815</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31318,11 +31304,11 @@
       </c>
       <c r="O17" s="7">
         <f>O16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L17,0)</f>
-        <v>-12453</v>
+        <v>-13389</v>
       </c>
       <c r="P17" s="22">
         <f>IF(Demanda!L18=0,"",O17/(Demanda!L18/DiasVenta))</f>
-        <v>-7.1234626751835251</v>
+        <v>-7.6588807321956329</v>
       </c>
       <c r="Q17" s="7">
         <f>Q16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M17,0)</f>
@@ -31356,7 +31342,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-47974</v>
+        <v>-48910</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31372,15 +31358,15 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-56910</v>
+        <v>-57846</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>71000</v>
+        <v>72000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14090</v>
+        <v>14154</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31392,11 +31378,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23090</v>
+        <v>23154</v>
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.1494117647058815</v>
+        <v>8.1719999999999988</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31404,11 +31390,11 @@
       </c>
       <c r="O18" s="7">
         <f>O17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L18,0)</f>
-        <v>-14878</v>
+        <v>-15814</v>
       </c>
       <c r="P18" s="22">
         <f>IF(Demanda!L18=0,"",O18/(Demanda!L18/DiasVenta))</f>
-        <v>-8.510630184002288</v>
+        <v>-9.046048241014395</v>
       </c>
       <c r="Q18" s="7">
         <f>Q17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M18,0)</f>
@@ -31634,7 +31620,7 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
@@ -31654,7 +31640,7 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.7310588235294109</v>
+        <v>8.4007058823529412</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
@@ -31662,7 +31648,7 @@
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 24.738 cajas - descargan 19 - vende 17.000 -&gt; ok</v>
+        <v>Sab 10/10: 23.802 cajas - descargan 18 - vende 17.000 -&gt; ok</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31672,11 +31658,11 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="str">
         <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31692,15 +31678,15 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>7.9814117647058822</v>
+        <v>8.0039999999999996</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
-        <v>CARGAR 4</v>
+        <v>CARGAR 5</v>
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 18.614 cajas - descargan 11 - vende 17.000 -&gt; cargar 4 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 17.678 cajas - descargan 11 - vende 17.000 -&gt; cargar 5 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31710,7 +31696,7 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>18578</v>
+        <v>18642</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
@@ -31730,7 +31716,7 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>7.9687058823529409</v>
+        <v>7.9912941176470582</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
@@ -31738,7 +31724,7 @@
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 18.578 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 18.642 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31748,7 +31734,7 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>13642</v>
+        <v>13706</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
@@ -31768,7 +31754,7 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>7.9912941176470582</v>
+        <v>8.0138823529411756</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
@@ -31776,7 +31762,7 @@
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 13.642 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 13.706 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31786,7 +31772,7 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>13706</v>
+        <v>13770</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
@@ -31806,7 +31792,7 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.0138823529411756</v>
+        <v>8.0364705882352929</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
@@ -31814,7 +31800,7 @@
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 13.706 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 13.770 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31824,7 +31810,7 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>13770</v>
+        <v>13834</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
@@ -31844,7 +31830,7 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.0364705882352929</v>
+        <v>8.0590588235294121</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
@@ -31852,7 +31838,7 @@
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 13.770 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 13.834 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31862,7 +31848,7 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>13834</v>
+        <v>13898</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
@@ -31882,7 +31868,7 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.0590588235294121</v>
+        <v>8.0816470588235294</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
@@ -31890,7 +31876,7 @@
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 13.834 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 13.898 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31900,7 +31886,7 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>13898</v>
+        <v>13962</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
@@ -31920,7 +31906,7 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.0816470588235294</v>
+        <v>8.1042352941176468</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
@@ -31928,7 +31914,7 @@
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 13.898 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 13.962 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31938,7 +31924,7 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>13962</v>
+        <v>14026</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
@@ -31958,7 +31944,7 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.1042352941176468</v>
+        <v>8.1268235294117641</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
@@ -31966,7 +31952,7 @@
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 13.962 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 14.026 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -31976,7 +31962,7 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>14026</v>
+        <v>14090</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
@@ -31996,7 +31982,7 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.1268235294117641</v>
+        <v>8.1494117647058815</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
@@ -32004,7 +31990,7 @@
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 14.026 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 14.090 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32014,7 +32000,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>14090</v>
+        <v>14154</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
@@ -32034,7 +32020,7 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.1494117647058815</v>
+        <v>8.1719999999999988</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
@@ -32042,7 +32028,7 @@
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 14.090 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 14.154 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -32267,11 +32253,11 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>11460</v>
+        <v>10524</v>
       </c>
       <c r="C13" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>6.555439031366193</v>
+        <v>6.0200209743540851</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(B13="","",IF(B13&lt;0,"FALTA",IF(C13&lt;2,"CRITICO",IF(C13&lt;CoberturaObjetivo,"JUSTO",IF(C13&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32330,11 +32316,11 @@
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.7310588235294109</v>
+        <v>8.4007058823529412</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32378,11 +32364,11 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>6947</v>
+        <v>6011</v>
       </c>
       <c r="C20" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>3.9738773953665745</v>
+        <v>3.4384593383544666</v>
       </c>
       <c r="D20" t="str">
         <f ca="1">IF(B20="","",IF(B20&lt;0,"FALTA",IF(C20&lt;2,"CRITICO",IF(C20&lt;CoberturaObjetivo,"JUSTO",IF(C20&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32441,19 +32427,19 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>7.9814117647058822</v>
+        <v>8.0039999999999996</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>CARGAR 4</v>
+        <v>CARGAR 5</v>
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 4 camion(es) mas hasta el mar 13/10 para cerrar en 22.500</v>
+        <v>cargar 5 camion(es) mas hasta el mar 13/10 para cerrar en 22.500</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
@@ -32498,7 +32484,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="45" t="str">
         <f>"Dictados que Aloha aun no tiene: "&amp;COUNTIFS(CgEstado,"Dictado",CgCuenta,1)&amp;" camiones. Pasan a Aloha cuando se cargan en el sistema."</f>
-        <v>Dictados que Aloha aun no tiene: 33 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
+        <v>Dictados que Aloha aun no tiene: 32 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
       </c>
       <c r="B29" s="46"/>
       <c r="C29" s="46"/>
@@ -32508,7 +32494,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 18.790 (plan: 24.738).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 18.790 (plan: 23.802).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32825,7 +32811,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>18840</v>
+        <v>17904</v>
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
@@ -32833,7 +32819,7 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>28038</v>
+        <v>27102</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32841,7 +32827,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
@@ -32849,7 +32835,7 @@
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>21438</v>
+        <v>20502</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
@@ -32869,15 +32855,15 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>21798</v>
+        <v>20862</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>23738</v>
+        <v>22802</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>24738</v>
+        <v>23802</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -32899,7 +32885,7 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>23614</v>
+        <v>22678</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
@@ -32907,43 +32893,43 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18614</v>
+        <v>17678</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>15614</v>
+        <v>14678</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>16824</v>
+        <v>15888</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22614</v>
+        <v>21678</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15674</v>
+        <v>14738</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17614</v>
+        <v>16678</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18614</v>
+        <v>17678</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -32965,15 +32951,15 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>21278</v>
+        <v>20342</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18578</v>
+        <v>18642</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
@@ -32981,7 +32967,7 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16878</v>
+        <v>16942</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
@@ -32993,7 +32979,7 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18578</v>
+        <v>18642</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
@@ -33001,15 +32987,15 @@
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15638</v>
+        <v>15702</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17578</v>
+        <v>17642</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18578</v>
+        <v>18642</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33031,7 +33017,7 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16042</v>
+        <v>16106</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
@@ -33039,7 +33025,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13642</v>
+        <v>13706</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
@@ -33047,7 +33033,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12242</v>
+        <v>12306</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
@@ -33059,7 +33045,7 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13642</v>
+        <v>13706</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
@@ -33067,15 +33053,15 @@
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10702</v>
+        <v>10766</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12642</v>
+        <v>12706</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13642</v>
+        <v>13706</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33097,7 +33083,7 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15806</v>
+        <v>15870</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -33105,7 +33091,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13706</v>
+        <v>13770</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -33113,7 +33099,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12606</v>
+        <v>12670</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
@@ -33125,7 +33111,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13706</v>
+        <v>13770</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -33133,15 +33119,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10766</v>
+        <v>10830</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12706</v>
+        <v>12770</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13706</v>
+        <v>13770</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33163,7 +33149,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15570</v>
+        <v>15634</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -33171,7 +33157,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13770</v>
+        <v>13834</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
@@ -33179,7 +33165,7 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>11970</v>
+        <v>12034</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
@@ -33191,7 +33177,7 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13770</v>
+        <v>13834</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
@@ -33199,15 +33185,15 @@
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10830</v>
+        <v>10894</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12770</v>
+        <v>12834</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13770</v>
+        <v>13834</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33229,7 +33215,7 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15334</v>
+        <v>15398</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
@@ -33237,7 +33223,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13834</v>
+        <v>13898</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
@@ -33245,7 +33231,7 @@
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12334</v>
+        <v>12398</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -33257,7 +33243,7 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13834</v>
+        <v>13898</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
@@ -33265,15 +33251,15 @@
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10894</v>
+        <v>10958</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12834</v>
+        <v>12898</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13834</v>
+        <v>13898</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33295,7 +33281,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16098</v>
+        <v>16162</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -33303,7 +33289,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13898</v>
+        <v>13962</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -33311,7 +33297,7 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12698</v>
+        <v>12762</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -33323,7 +33309,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13898</v>
+        <v>13962</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -33331,15 +33317,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10958</v>
+        <v>11022</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12898</v>
+        <v>12962</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13898</v>
+        <v>13962</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33361,7 +33347,7 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15862</v>
+        <v>15926</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
@@ -33369,7 +33355,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13962</v>
+        <v>14026</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -33377,7 +33363,7 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12062</v>
+        <v>12126</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
@@ -33389,7 +33375,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13962</v>
+        <v>14026</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -33397,15 +33383,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11022</v>
+        <v>11086</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12962</v>
+        <v>13026</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13962</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33427,7 +33413,7 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15626</v>
+        <v>15690</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
@@ -33435,7 +33421,7 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14026</v>
+        <v>14090</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -33443,7 +33429,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12426</v>
+        <v>12490</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -33455,7 +33441,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14026</v>
+        <v>14090</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -33463,15 +33449,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11086</v>
+        <v>11150</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13026</v>
+        <v>13090</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14026</v>
+        <v>14090</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33493,7 +33479,7 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15390</v>
+        <v>15454</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
@@ -33501,7 +33487,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14090</v>
+        <v>14154</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -33509,7 +33495,7 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12790</v>
+        <v>12854</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
@@ -33521,7 +33507,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14090</v>
+        <v>14154</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -33529,15 +33515,15 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11150</v>
+        <v>11214</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13090</v>
+        <v>13154</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14090</v>
+        <v>14154</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B5A0B3-74E7-4B60-AF2D-52250EAD9DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36283C1A-FBB3-4A4B-8CB7-9A1043A13AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="679">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 30/09/2026 17:24 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 12:30 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -790,6 +790,9 @@
     <t>nota 30/09: tersa; transportista supuesto = semana anterior</t>
   </si>
   <si>
+    <t>nota 01/10: tersa; transportista supuesto = semana anterior</t>
+  </si>
+  <si>
     <t>nota 30/09: Diego 2, martes</t>
   </si>
   <si>
@@ -799,784 +802,784 @@
     <t>nota 30/09: cuarta; transportista supuesto = semana anterior</t>
   </si>
   <si>
+    <t>nota 01/10: cuarta (antes martes, sacada el 30/09); transportista supuesto</t>
+  </si>
+  <si>
+    <t>nota 30/09: sexta; transportista supuesto = semana anterior</t>
+  </si>
+  <si>
+    <t>nota 30/09: sabado (descarga martes 13, suma a la semana siguiente); transportista supuesto = semana anterior</t>
+  </si>
+  <si>
+    <t>Paraguay (supuesto)</t>
+  </si>
+  <si>
+    <t>Supuesto</t>
+  </si>
+  <si>
+    <t>supuesto: 5 camiones PY por semana, cargan dom-lun-mar (Gonzalo 27/09)</t>
+  </si>
+  <si>
+    <t>Brasil (supuesto)</t>
+  </si>
+  <si>
+    <t>Supuesto BR</t>
+  </si>
+  <si>
+    <t>supuesto: 8 camiones BR los viernes, ritmo habitual (Gonzalo 28/09); se apaga en Parametros &gt; SupBR</t>
+  </si>
+  <si>
+    <t>Proyeccion de stock al cierre de cada sabado</t>
+  </si>
+  <si>
+    <t>Stock final = stock inicial + cajas que descargan en la semana - venta. Los camiones a cargar se arrastran: "Stock proyectado" ya incluye los pedidos de las semanas anteriores. La primera semana (la del conteo) va prorrateada por los dias que quedan.</t>
+  </si>
+  <si>
+    <t>Stock inicial</t>
+  </si>
+  <si>
+    <t>Camiones que descargan</t>
+  </si>
+  <si>
+    <t>Cajas que descargan</t>
+  </si>
+  <si>
+    <t>Venta</t>
+  </si>
+  <si>
+    <t>Stock final (sin pedidos)</t>
+  </si>
+  <si>
+    <t>Pedidos anteriores (cajas)</t>
+  </si>
+  <si>
+    <t>STOCK PROYECTADO</t>
+  </si>
+  <si>
+    <t>Fecha limite de carga (el lead time mas largo BR/PY)</t>
+  </si>
+  <si>
+    <t>CAMIONES A CARGAR</t>
+  </si>
+  <si>
+    <t>Stock con pedido</t>
+  </si>
+  <si>
+    <t>Dias de cobertura</t>
+  </si>
+  <si>
+    <t>BR stock</t>
+  </si>
+  <si>
+    <t>BR dias</t>
+  </si>
+  <si>
+    <t>PY stock</t>
+  </si>
+  <si>
+    <t>PY dias</t>
+  </si>
+  <si>
+    <t>BO stock</t>
+  </si>
+  <si>
+    <t>BO dias</t>
+  </si>
+  <si>
+    <t>Origen mas justo</t>
+  </si>
+  <si>
+    <t>Que cargar</t>
+  </si>
+  <si>
+    <t>Solo las semanas cuyo limite de carga todavia no paso. Camiones ADEMAS de lo dictado y de los supuestos. El origen sugerido es el que queda con menos dias de venta al cierre (Proyeccion).</t>
+  </si>
+  <si>
+    <t>Sabado de cierre</t>
+  </si>
+  <si>
+    <t>Stock proyectado (con pedidos anteriores)</t>
+  </si>
+  <si>
+    <t>Camiones a cargar</t>
+  </si>
+  <si>
+    <t>Cargar hasta (por origen)</t>
+  </si>
+  <si>
+    <t>Origen sugerido</t>
+  </si>
+  <si>
+    <t>Pedido cierra (PY mie / BR jue)</t>
+  </si>
+  <si>
+    <t>Cobertura al cierre (dias)</t>
+  </si>
+  <si>
+    <t>Renglon para WhatsApp</t>
+  </si>
+  <si>
+    <t>Como leerlo: "cargar N mas hasta el mie" = camiones que hay que agregar a lo ya dictado para cerrar ese sabado en el minimo; lo que cargue despues del limite descarga la semana siguiente. Los faltantes de una semana se arrastran a la siguiente (Proyeccion, columna "Pedidos anteriores").</t>
+  </si>
+  <si>
+    <t>Hay SUPUESTOS de los dos origenes en Cargas: 5 camiones de Paraguay por semana (Estado = Supuesto) y 8 de Brasil los viernes en las semanas posteriores a la ultima dictada (Estado = Supuesto BR). Con ellos, "cargar N mas" es lo que falta ADEMAS del ritmo habitual; para ver toda la necesidad como en el WhatsApp, poner SupBR = 0 en Parametros. Cuando se dictan los reales, reemplazarlos.</t>
+  </si>
+  <si>
+    <t>Escenarios de venta lado a lado</t>
+  </si>
+  <si>
+    <t>Misma proyeccion con la venta usada x 0,9 / x 1,0 / x 1,1 (ademas del escenario elegido en Parametros). Cada escenario arrastra sus propios camiones a cargar. Para atraso en frontera: Parametros &gt; Atraso extra.</t>
+  </si>
+  <si>
+    <t>Venta base</t>
+  </si>
+  <si>
+    <t>Stock -10%</t>
+  </si>
+  <si>
+    <t>A cargar -10%</t>
+  </si>
+  <si>
+    <t>Stock base</t>
+  </si>
+  <si>
+    <t>A cargar base</t>
+  </si>
+  <si>
+    <t>Stock +10%</t>
+  </si>
+  <si>
+    <t>A cargar +10%</t>
+  </si>
+  <si>
+    <t>Cajas si frontera a P90</t>
+  </si>
+  <si>
+    <t>Stock frontera P90</t>
+  </si>
+  <si>
+    <t>A cargar P90</t>
+  </si>
+  <si>
+    <t>Stock sin HF 1 semana (-3 PY)</t>
+  </si>
+  <si>
+    <t>Stock 1 camion rechazado (-1.000)</t>
+  </si>
+  <si>
+    <t>Stock sin Bolivia 2 sem</t>
+  </si>
+  <si>
+    <t>Lectura: si con -10% igual hay que cargar, el pedido es firme; si solo hace falta con +10%, es un pedido "por las dudas" que conviene decidir el miercoles con la venta real de la semana. "Frontera a P90": todos los camiones sin descarga real tardan lo que tarda el peor 10% (Parametros fila 45). Los shocks (sin HF, camion rechazado, sin Bolivia) se aplican desde la semana proxima sobre el stock base.</t>
+  </si>
+  <si>
+    <t>KPIs del plan</t>
+  </si>
+  <si>
+    <t>Los de arriba salen de la planilla. Abajo, la referencia de como lo miden las multinacionales de fruta y que equivale en Almar.</t>
+  </si>
+  <si>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Como se calcula / lectura</t>
+  </si>
+  <si>
+    <t>Stock al conteo (cajas)</t>
+  </si>
+  <si>
+    <t>Parametros: conteo por camara, BR + PY + BO. Ecuador no entra (va por otro canal).</t>
+  </si>
+  <si>
+    <t>Dias de cobertura al conteo</t>
+  </si>
+  <si>
+    <t>Stock / venta diaria de la semana siguiente al conteo. Multinacionales: "days on hand" o DOS.</t>
+  </si>
+  <si>
+    <t>Semana actual: stock proyectado al sabado</t>
+  </si>
+  <si>
+    <t>Proyeccion, fila de la semana de hoy, con los pedidos ya contados.</t>
+  </si>
+  <si>
+    <t>Semana actual: camiones a cargar</t>
+  </si>
+  <si>
+    <t>Lo que falta cargar antes del limite de esta semana.</t>
+  </si>
+  <si>
+    <t>Semana proxima: camiones a cargar</t>
+  </si>
+  <si>
+    <t>El numero que hay que tener el miercoles (PY) y el jueves (BR).</t>
+  </si>
+  <si>
+    <t>Cobertura promedio proximas 4 semanas (dias)</t>
+  </si>
+  <si>
+    <t>Promedio de "Dias de cobertura" de Proyeccion. Objetivo: Parametros &gt; cobertura objetivo.</t>
+  </si>
+  <si>
+    <t>Semanas que piden cargar (prox. 4 sem)</t>
+  </si>
+  <si>
+    <t>Semanas de las proximas 4 que cierran abajo del minimo sin camiones extra. Mas alla de 2-3 semanas es normal que pidan, porque todavia no hay cargas dictadas.</t>
+  </si>
+  <si>
+    <t>Camiones a cargar prox. 4 sem (ademas de lo dictado)</t>
+  </si>
+  <si>
+    <t>Suma de "Camiones a cargar" de Proyeccion en las proximas 4 semanas.</t>
+  </si>
+  <si>
+    <t>Rotacion: semanas de stock al conteo</t>
+  </si>
+  <si>
+    <t>Stock / venta semanal. Referencia en fresco: 1 a 2 semanas de stock (26-52 vueltas al ano). Almar al 26/09: 1,6 semanas, dentro del rango pero en el borde alto.</t>
+  </si>
+  <si>
+    <t>Valor del stock al conteo (USD)</t>
+  </si>
+  <si>
+    <t>Cajas por origen x USD/caja usado (Parametros). Capital de trabajo inmovilizado en camara.</t>
+  </si>
+  <si>
+    <t>Verde en transito (cajas cargadas y no descargadas, Aloha)</t>
+  </si>
+  <si>
+    <t>Pipeline: camiones ya cargados que todavia no descargaron (Cargas, columna "Pipeline"). Con el export de Aloha al dia es lo que viene en camino.</t>
+  </si>
+  <si>
+    <t>Brasil: precio pagado vs Cepea + servicios (R$/caja)</t>
+  </si>
+  <si>
+    <t>Negativo = Almar paga por debajo de la referencia Cepea x 22 kg + R$ 18 de servicios.</t>
+  </si>
+  <si>
+    <t>Concentracion Paraguay: % camiones del mayor productor (8 sem)</t>
+  </si>
+  <si>
+    <t>Riesgo de dependencia: HF sola fue el 54% de los camiones PY de 2026. Multinacionales: 20-30% del programa en proveedores de contingencia precalificados (hoja MercadoPY).</t>
+  </si>
+  <si>
+    <t>Concentracion Brasil: % camiones del mayor productor (8 sem)</t>
+  </si>
+  <si>
+    <t>Camiones que descargan por semana, prox. 4 sem (promedio)</t>
+  </si>
+  <si>
+    <t>Aloha + dictados + supuestos.</t>
+  </si>
+  <si>
+    <t>Mix descargas prox. 4 sem: Brasil</t>
+  </si>
+  <si>
+    <t>Cajas por origen sobre el total de las proximas 4 semanas. Diversificacion de origen = menos riesgo (frontera, clima, TR4).</t>
+  </si>
+  <si>
+    <t>Mix descargas prox. 4 sem: Paraguay</t>
+  </si>
+  <si>
+    <t>Mix descargas prox. 4 sem: Bolivia</t>
+  </si>
+  <si>
+    <t>Costo estimado de compra prox. 4 sem (USD)</t>
+  </si>
+  <si>
+    <t>Cajas que descargan x USD/caja usado (Parametros: precio de compra real si esta cargado, si no la referencia de aduana 2026).</t>
+  </si>
+  <si>
+    <t>Camiones supuestos en el horizonte (PY + BR)</t>
+  </si>
+  <si>
+    <t>Cuantos de los camiones contados todavia son supuestos (5 PY por semana; 8 BR los viernes mas alla de lo dictado). Cuanto mas bajo, mas firme el plan. Se apagan en Parametros (SupPY / SupBR).</t>
+  </si>
+  <si>
+    <t>Faltante promedio de los proveedores (MIC - descargado, Aloha 2024-26)</t>
+  </si>
+  <si>
+    <t>Fill rate del proveedor: positivo = descargo menos de lo declarado; negativo = descargo de mas. Por productor en Proveedores.</t>
+  </si>
+  <si>
+    <t>OTIF: camiones que descargaron dentro del lead time + 1 dia</t>
+  </si>
+  <si>
+    <t>Sobre los camiones con descarga real cargada en Cargas (columna Descarga real). Se llena solo a medida que se anotan descargas.</t>
+  </si>
+  <si>
+    <t>Camiones dictados que Aloha aun no tiene</t>
+  </si>
+  <si>
+    <t>Pasan a Aloha cuando se cargan en el sistema.</t>
+  </si>
+  <si>
+    <t>Exactitud del pronostico (MAPE, semanas con venta real)</t>
+  </si>
+  <si>
+    <t>Promedio del desvio absoluto entre venta real (ERP) y venta usada. Multinacionales: forecast accuracy semanal; &lt;10% es bueno para fruta.</t>
+  </si>
+  <si>
+    <t>REFERENCIA MULTINACIONAL (S&amp;OP de fruta fresca)</t>
+  </si>
+  <si>
+    <t>Practica</t>
+  </si>
+  <si>
+    <t>Equivalente en Almar / esta planilla</t>
+  </si>
+  <si>
+    <t>Cadencia S&amp;OP</t>
+  </si>
+  <si>
+    <t>Reunion semanal (15-30 min) de demanda, abastecimiento y riesgos, con KPIs de merma y exactitud del pronostico.</t>
+  </si>
+  <si>
+    <t>El WhatsApp del miercoles 12:00 (pedidos) y del viernes 19:00 (cierre): Cepea, clima, stock proyectado y camiones que faltan. Esta planilla es el soporte para probar antes de dictar.</t>
+  </si>
+  <si>
+    <t>Un solo plan de demanda</t>
+  </si>
+  <si>
+    <t>Un numero de venta por semana acordado entre ventas y compras, con estacionalidad (dia de la semana, semana del mes) y venta real para medir el desvio.</t>
+  </si>
+  <si>
+    <t>Hoja Demanda: venta plan + factor por semana del mes + venta manual + venta real ERP + desvio.</t>
+  </si>
+  <si>
+    <t>Proyeccion de inventario</t>
+  </si>
+  <si>
+    <t>Stock inicial + recepciones - demanda = stock final, por semana, contra un stock de seguridad explicito; recomendacion de pedido con fecha limite por lead time.</t>
+  </si>
+  <si>
+    <t>Hoja Proyeccion: cierre del sabado, minimo 22.500, camiones a cargar y fecha limite (sabado - lead time).</t>
+  </si>
+  <si>
+    <t>Stock de seguridad dinamico (perecederos)</t>
+  </si>
+  <si>
+    <t>Sube y baja con la venta (mas antes del fin de semana / comienzo de mes), acotado por la vida util: mas stock = mas merma.</t>
+  </si>
+  <si>
+    <t>Minimo en cajas (22.500) o por dias de venta (7): Parametros. La cobertura objetivo pinta la proyeccion.</t>
+  </si>
+  <si>
+    <t>Dias de cobertura (DOS / days on hand)</t>
+  </si>
+  <si>
+    <t>Indicador central: stock / venta diaria. Objetivo por categoria; fruta fresca 5-10 dias segun madurez.</t>
+  </si>
+  <si>
+    <t>Columnas "Dias de cobertura" (total y por origen). Almar: 7 dias = fruta que todavia no maduro (gas + camara).</t>
+  </si>
+  <si>
+    <t>Lead time y ciclo de pedido por dia de la semana</t>
+  </si>
+  <si>
+    <t>Cada origen con su lead time y su dia de corte; el sistema avisa antes del corte si la cobertura no llega.</t>
+  </si>
+  <si>
+    <t>Lead time por origen (3/3/6), lead time real por productor (Proveedores), corte PY miercoles / BR jueves, "Cargar hasta" por semana.</t>
+  </si>
+  <si>
+    <t>Capacidad de maduracion</t>
+  </si>
+  <si>
+    <t>Camaras de maduracion planificadas por volumen semanal (regla: una camara de 20 pallets por cada 20 pallets extra por semana, hasta ~140 pallets/sem).</t>
+  </si>
+  <si>
+    <t>Pendiente: cargar capacidad de camaras (ZAC / Coronel Raiz) como tope de recepcion semanal. FechaHoy el limite es el minimo, no el maximo.</t>
+  </si>
+  <si>
+    <t>Costo total puesto en destino</t>
+  </si>
+  <si>
+    <t>Precio en origen + empaque + flete + aduana + maduracion + merma esperada por carril/proveedor.</t>
+  </si>
+  <si>
+    <t>Parametros: Cepea x 22 + servicios, precio pagado Almar, TC; KPI de costo de las proximas 4 semanas. Falta: flete internacional, aduana y merma por productor (calidad).</t>
+  </si>
+  <si>
+    <t>Diversificacion de origen y proveedores</t>
+  </si>
+  <si>
+    <t>20-30% del programa en proveedores de contingencia precalificados; varios origenes, puertos y transportistas.</t>
+  </si>
+  <si>
+    <t>Tres origenes (BR / PY / BO), 17 productores BR, 4 PY, 2 BO; el mix por origen esta en KPIs. Proveedores: capacidad semanal por productor.</t>
+  </si>
+  <si>
+    <t>Scorecard de proveedores</t>
+  </si>
+  <si>
+    <t>OTIF por carril, reclamos, dias en verde / color de llegada, tiempo de correccion.</t>
+  </si>
+  <si>
+    <t>Proveedores: lead time real, regularidad (camiones por semana), precio. Calidad y vida verde: index_calidad (necesita 15 lotes con fecha de rompio).</t>
+  </si>
+  <si>
+    <t>Merma / shrink</t>
+  </si>
+  <si>
+    <t>2-10% del costo puesto en destino segun cadena de frio y madurez; se mide y se descuenta del plan.</t>
+  </si>
+  <si>
+    <t>Sin dato en el plan. Sugerencia: registrar cajas descartadas por semana en la hoja Demanda (columna nueva) y restarlas del stock.</t>
+  </si>
+  <si>
+    <t>Proveedores: capacidad y comportamiento real</t>
+  </si>
+  <si>
+    <t>Camiones desde el 02/08/2026 segun el Plan de Cargas de Aloha (8 semanas). Capacidad semanal = maximo observado (editable). Precio 2026 = promedio pagado por caja (cargas 2026.xlsx).</t>
+  </si>
+  <si>
+    <t>Productor (Aloha)</t>
+  </si>
+  <si>
+    <t>Nombre en cargas dictadas</t>
+  </si>
+  <si>
+    <t>Camiones (8 sem)</t>
+  </si>
+  <si>
+    <t>Semanas con carga</t>
+  </si>
+  <si>
+    <t>Prom camiones/sem</t>
+  </si>
+  <si>
+    <t>Pico: max camiones en una semana</t>
+  </si>
+  <si>
+    <t>CAPACIDAD semanal (prom. de las 2 mejores semanas)</t>
+  </si>
+  <si>
+    <t>Lead time real (dias)</t>
+  </si>
+  <si>
+    <t>Cajas/camion</t>
+  </si>
+  <si>
+    <t>Transportista habitual</t>
+  </si>
+  <si>
+    <t>Dias de carga habituales</t>
+  </si>
+  <si>
+    <t>Precio prom 2026 (R$/caja)</t>
+  </si>
+  <si>
+    <t>Camiones esta semana (Cargas)</t>
+  </si>
+  <si>
+    <t>Camiones semana proxima (Cargas)</t>
+  </si>
+  <si>
+    <t>Camiones 2024/2025/2026 (Aloha)</t>
+  </si>
+  <si>
+    <t>Faltante % (MIC - descargado)</t>
+  </si>
+  <si>
+    <t>Ultima carga (Aloha 24/09)</t>
+  </si>
+  <si>
+    <t>Cupo aprox/sem 2026</t>
+  </si>
+  <si>
+    <t>Situacion</t>
+  </si>
+  <si>
+    <t>FG (11) / Chabat (1)</t>
+  </si>
+  <si>
+    <t>vie 6, mie 4, mar 1</t>
+  </si>
+  <si>
+    <t>47/76/46</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>Amaro (8) / FG (4)</t>
+  </si>
+  <si>
+    <t>vie 5, mar 4, sab 2</t>
+  </si>
+  <si>
+    <t>17/164/61</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>AXT (6) / Chabat (3)</t>
+  </si>
+  <si>
+    <t>vie 6, mie 2, mar 2</t>
+  </si>
+  <si>
+    <t>13/88/96</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>el mas regular de Brasil</t>
+  </si>
+  <si>
+    <t>Osnildo Stein</t>
+  </si>
+  <si>
+    <t>Chabat (5) / FG (2)</t>
+  </si>
+  <si>
+    <t>vie 5, mie 1, mar 1</t>
+  </si>
+  <si>
+    <t>0/0/22</t>
+  </si>
+  <si>
+    <t>nuevo 2026</t>
+  </si>
+  <si>
+    <t>Ivo Zimerman</t>
+  </si>
+  <si>
+    <t>FG (4) / Chabat (2)</t>
+  </si>
+  <si>
+    <t>mie 2, vie 2, mar 1</t>
+  </si>
+  <si>
+    <t>0/0/16</t>
+  </si>
+  <si>
+    <t>FG (5)</t>
+  </si>
+  <si>
+    <t>jue 1, mar 1, mie 1</t>
+  </si>
+  <si>
+    <t>39/70/37</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>Josemar Provesi</t>
+  </si>
+  <si>
+    <t>FG (2) / Chabat (1)</t>
+  </si>
+  <si>
+    <t>vie 2, sab 1, mie 1</t>
+  </si>
+  <si>
+    <t>Marconi Kons</t>
+  </si>
+  <si>
+    <t>FG (2) / Amaro (1)</t>
+  </si>
+  <si>
+    <t>vie 2, sab 1</t>
+  </si>
+  <si>
+    <t>0/0/14</t>
+  </si>
+  <si>
+    <t>camion chico (834 cajas promedio historico)</t>
+  </si>
+  <si>
+    <t>Furlani</t>
+  </si>
+  <si>
+    <t>Amaro (1) / Chabat (1)</t>
+  </si>
+  <si>
+    <t>mie 1, vie 1</t>
+  </si>
+  <si>
+    <t>Shapo</t>
+  </si>
+  <si>
+    <t>Chabat (1) / FG (1)</t>
+  </si>
+  <si>
+    <t>vie 2</t>
+  </si>
+  <si>
+    <t>Wagner Schveitzer</t>
+  </si>
+  <si>
+    <t>Wagner</t>
+  </si>
+  <si>
+    <t>Amaro (1)</t>
+  </si>
+  <si>
+    <t>vie 1</t>
+  </si>
+  <si>
+    <t>0/0/11</t>
+  </si>
+  <si>
+    <t>14/08/2026</t>
+  </si>
+  <si>
+    <t>Paraguay HF</t>
+  </si>
+  <si>
+    <t>Mega Logistica (22) / G.S.C.S. PARAGUAY TTES. (3)</t>
+  </si>
+  <si>
+    <t>dom 12, lun 8, mar 2</t>
+  </si>
+  <si>
+    <t>Paraguay carga domingo-lunes-martes y entra en la semana.</t>
+  </si>
+  <si>
+    <t>39/16/76</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>54% de los camiones PY de 2026: dependencia alta</t>
+  </si>
+  <si>
+    <t>MARSO EMPRENDIMIENTOS S.R.L. (10)</t>
+  </si>
+  <si>
+    <t>lun 5, mar 5, mie 1</t>
+  </si>
+  <si>
+    <t>nuevo desde 11/08/2026 (Alvarito)</t>
+  </si>
+  <si>
+    <t>G.S.C.S. PARAGUAY TTES. (6) / Lider Express (4)</t>
+  </si>
+  <si>
+    <t>lun 5, mar 5, dom 1</t>
+  </si>
+  <si>
+    <t>84/16/22</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>Jauser (3)</t>
+  </si>
+  <si>
+    <t>dom 1, lun 1, mar 1</t>
+  </si>
+  <si>
+    <t>40/13/20</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>transportista historico Compass</t>
+  </si>
+  <si>
+    <t>Banexfrut</t>
+  </si>
+  <si>
+    <t>Surcentral (5)</t>
+  </si>
+  <si>
+    <t>vie 3, lun 2</t>
+  </si>
+  <si>
+    <t>Bolivia: 6-9 dias reales de carga a descarga; 1 camion por semana en promedio.</t>
+  </si>
+  <si>
+    <t>Bolivia: 1 camion por semana aprox, 6-9 dias de viaje</t>
+  </si>
+  <si>
+    <t>Befrut</t>
+  </si>
+  <si>
+    <t>Sintercargas (3)</t>
+  </si>
+  <si>
+    <t>mie 2, lun 1</t>
+  </si>
+  <si>
+    <t>Bolivia (sin productor en Aloha)</t>
+  </si>
+  <si>
+    <t>Valdemar</t>
+  </si>
+  <si>
+    <t>Sin cargas en las ultimas 8 semanas: alternativa si falla un habitual.</t>
+  </si>
+  <si>
+    <t>81/133/33</t>
+  </si>
+  <si>
+    <t>25/04/2026</t>
+  </si>
+  <si>
+    <t>inactivo desde abril 2026; fue el 2do de 2025</t>
+  </si>
+  <si>
+    <t>Jhony Viera</t>
+  </si>
+  <si>
+    <t>Jony</t>
+  </si>
+  <si>
+    <t>64/120/26</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>inactivo desde marzo 2026</t>
+  </si>
+  <si>
+    <t>Jorge Marangoni</t>
+  </si>
+  <si>
+    <t>Marangoni</t>
+  </si>
+  <si>
+    <t>0/0/21</t>
+  </si>
+  <si>
+    <t>24/07/2026</t>
+  </si>
+  <si>
+    <t>sin cargas desde julio; TT 4 dias</t>
+  </si>
+  <si>
+    <t>Banana Combinada</t>
+  </si>
+  <si>
+    <t>0/10/14</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>sin cargas desde junio; TT 4 dias</t>
+  </si>
+  <si>
     <t>Paraguay GM</t>
-  </si>
-  <si>
-    <t>nota 30/09: Guido 1, miercoles (con 4 dias descarga domingo 11: suma a la semana siguiente)</t>
-  </si>
-  <si>
-    <t>nota 30/09: sexta; transportista supuesto = semana anterior</t>
-  </si>
-  <si>
-    <t>nota 30/09: sabado (descarga martes 13, suma a la semana siguiente); transportista supuesto = semana anterior</t>
-  </si>
-  <si>
-    <t>Paraguay (supuesto)</t>
-  </si>
-  <si>
-    <t>Supuesto</t>
-  </si>
-  <si>
-    <t>supuesto: 5 camiones PY por semana, cargan dom-lun-mar (Gonzalo 27/09)</t>
-  </si>
-  <si>
-    <t>Brasil (supuesto)</t>
-  </si>
-  <si>
-    <t>Supuesto BR</t>
-  </si>
-  <si>
-    <t>supuesto: 8 camiones BR los viernes, ritmo habitual (Gonzalo 28/09); se apaga en Parametros &gt; SupBR</t>
-  </si>
-  <si>
-    <t>Proyeccion de stock al cierre de cada sabado</t>
-  </si>
-  <si>
-    <t>Stock final = stock inicial + cajas que descargan en la semana - venta. Los camiones a cargar se arrastran: "Stock proyectado" ya incluye los pedidos de las semanas anteriores. La primera semana (la del conteo) va prorrateada por los dias que quedan.</t>
-  </si>
-  <si>
-    <t>Stock inicial</t>
-  </si>
-  <si>
-    <t>Camiones que descargan</t>
-  </si>
-  <si>
-    <t>Cajas que descargan</t>
-  </si>
-  <si>
-    <t>Venta</t>
-  </si>
-  <si>
-    <t>Stock final (sin pedidos)</t>
-  </si>
-  <si>
-    <t>Pedidos anteriores (cajas)</t>
-  </si>
-  <si>
-    <t>STOCK PROYECTADO</t>
-  </si>
-  <si>
-    <t>Fecha limite de carga (el lead time mas largo BR/PY)</t>
-  </si>
-  <si>
-    <t>CAMIONES A CARGAR</t>
-  </si>
-  <si>
-    <t>Stock con pedido</t>
-  </si>
-  <si>
-    <t>Dias de cobertura</t>
-  </si>
-  <si>
-    <t>BR stock</t>
-  </si>
-  <si>
-    <t>BR dias</t>
-  </si>
-  <si>
-    <t>PY stock</t>
-  </si>
-  <si>
-    <t>PY dias</t>
-  </si>
-  <si>
-    <t>BO stock</t>
-  </si>
-  <si>
-    <t>BO dias</t>
-  </si>
-  <si>
-    <t>Origen mas justo</t>
-  </si>
-  <si>
-    <t>Que cargar</t>
-  </si>
-  <si>
-    <t>Solo las semanas cuyo limite de carga todavia no paso. Camiones ADEMAS de lo dictado y de los supuestos. El origen sugerido es el que queda con menos dias de venta al cierre (Proyeccion).</t>
-  </si>
-  <si>
-    <t>Sabado de cierre</t>
-  </si>
-  <si>
-    <t>Stock proyectado (con pedidos anteriores)</t>
-  </si>
-  <si>
-    <t>Camiones a cargar</t>
-  </si>
-  <si>
-    <t>Cargar hasta (por origen)</t>
-  </si>
-  <si>
-    <t>Origen sugerido</t>
-  </si>
-  <si>
-    <t>Pedido cierra (PY mie / BR jue)</t>
-  </si>
-  <si>
-    <t>Cobertura al cierre (dias)</t>
-  </si>
-  <si>
-    <t>Renglon para WhatsApp</t>
-  </si>
-  <si>
-    <t>Como leerlo: "cargar N mas hasta el mie" = camiones que hay que agregar a lo ya dictado para cerrar ese sabado en el minimo; lo que cargue despues del limite descarga la semana siguiente. Los faltantes de una semana se arrastran a la siguiente (Proyeccion, columna "Pedidos anteriores").</t>
-  </si>
-  <si>
-    <t>Hay SUPUESTOS de los dos origenes en Cargas: 5 camiones de Paraguay por semana (Estado = Supuesto) y 8 de Brasil los viernes en las semanas posteriores a la ultima dictada (Estado = Supuesto BR). Con ellos, "cargar N mas" es lo que falta ADEMAS del ritmo habitual; para ver toda la necesidad como en el WhatsApp, poner SupBR = 0 en Parametros. Cuando se dictan los reales, reemplazarlos.</t>
-  </si>
-  <si>
-    <t>Escenarios de venta lado a lado</t>
-  </si>
-  <si>
-    <t>Misma proyeccion con la venta usada x 0,9 / x 1,0 / x 1,1 (ademas del escenario elegido en Parametros). Cada escenario arrastra sus propios camiones a cargar. Para atraso en frontera: Parametros &gt; Atraso extra.</t>
-  </si>
-  <si>
-    <t>Venta base</t>
-  </si>
-  <si>
-    <t>Stock -10%</t>
-  </si>
-  <si>
-    <t>A cargar -10%</t>
-  </si>
-  <si>
-    <t>Stock base</t>
-  </si>
-  <si>
-    <t>A cargar base</t>
-  </si>
-  <si>
-    <t>Stock +10%</t>
-  </si>
-  <si>
-    <t>A cargar +10%</t>
-  </si>
-  <si>
-    <t>Cajas si frontera a P90</t>
-  </si>
-  <si>
-    <t>Stock frontera P90</t>
-  </si>
-  <si>
-    <t>A cargar P90</t>
-  </si>
-  <si>
-    <t>Stock sin HF 1 semana (-3 PY)</t>
-  </si>
-  <si>
-    <t>Stock 1 camion rechazado (-1.000)</t>
-  </si>
-  <si>
-    <t>Stock sin Bolivia 2 sem</t>
-  </si>
-  <si>
-    <t>Lectura: si con -10% igual hay que cargar, el pedido es firme; si solo hace falta con +10%, es un pedido "por las dudas" que conviene decidir el miercoles con la venta real de la semana. "Frontera a P90": todos los camiones sin descarga real tardan lo que tarda el peor 10% (Parametros fila 45). Los shocks (sin HF, camion rechazado, sin Bolivia) se aplican desde la semana proxima sobre el stock base.</t>
-  </si>
-  <si>
-    <t>KPIs del plan</t>
-  </si>
-  <si>
-    <t>Los de arriba salen de la planilla. Abajo, la referencia de como lo miden las multinacionales de fruta y que equivale en Almar.</t>
-  </si>
-  <si>
-    <t>Indicador</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Como se calcula / lectura</t>
-  </si>
-  <si>
-    <t>Stock al conteo (cajas)</t>
-  </si>
-  <si>
-    <t>Parametros: conteo por camara, BR + PY + BO. Ecuador no entra (va por otro canal).</t>
-  </si>
-  <si>
-    <t>Dias de cobertura al conteo</t>
-  </si>
-  <si>
-    <t>Stock / venta diaria de la semana siguiente al conteo. Multinacionales: "days on hand" o DOS.</t>
-  </si>
-  <si>
-    <t>Semana actual: stock proyectado al sabado</t>
-  </si>
-  <si>
-    <t>Proyeccion, fila de la semana de hoy, con los pedidos ya contados.</t>
-  </si>
-  <si>
-    <t>Semana actual: camiones a cargar</t>
-  </si>
-  <si>
-    <t>Lo que falta cargar antes del limite de esta semana.</t>
-  </si>
-  <si>
-    <t>Semana proxima: camiones a cargar</t>
-  </si>
-  <si>
-    <t>El numero que hay que tener el miercoles (PY) y el jueves (BR).</t>
-  </si>
-  <si>
-    <t>Cobertura promedio proximas 4 semanas (dias)</t>
-  </si>
-  <si>
-    <t>Promedio de "Dias de cobertura" de Proyeccion. Objetivo: Parametros &gt; cobertura objetivo.</t>
-  </si>
-  <si>
-    <t>Semanas que piden cargar (prox. 4 sem)</t>
-  </si>
-  <si>
-    <t>Semanas de las proximas 4 que cierran abajo del minimo sin camiones extra. Mas alla de 2-3 semanas es normal que pidan, porque todavia no hay cargas dictadas.</t>
-  </si>
-  <si>
-    <t>Camiones a cargar prox. 4 sem (ademas de lo dictado)</t>
-  </si>
-  <si>
-    <t>Suma de "Camiones a cargar" de Proyeccion en las proximas 4 semanas.</t>
-  </si>
-  <si>
-    <t>Rotacion: semanas de stock al conteo</t>
-  </si>
-  <si>
-    <t>Stock / venta semanal. Referencia en fresco: 1 a 2 semanas de stock (26-52 vueltas al ano). Almar al 26/09: 1,6 semanas, dentro del rango pero en el borde alto.</t>
-  </si>
-  <si>
-    <t>Valor del stock al conteo (USD)</t>
-  </si>
-  <si>
-    <t>Cajas por origen x USD/caja usado (Parametros). Capital de trabajo inmovilizado en camara.</t>
-  </si>
-  <si>
-    <t>Verde en transito (cajas cargadas y no descargadas, Aloha)</t>
-  </si>
-  <si>
-    <t>Pipeline: camiones ya cargados que todavia no descargaron (Cargas, columna "Pipeline"). Con el export de Aloha al dia es lo que viene en camino.</t>
-  </si>
-  <si>
-    <t>Brasil: precio pagado vs Cepea + servicios (R$/caja)</t>
-  </si>
-  <si>
-    <t>Negativo = Almar paga por debajo de la referencia Cepea x 22 kg + R$ 18 de servicios.</t>
-  </si>
-  <si>
-    <t>Concentracion Paraguay: % camiones del mayor productor (8 sem)</t>
-  </si>
-  <si>
-    <t>Riesgo de dependencia: HF sola fue el 54% de los camiones PY de 2026. Multinacionales: 20-30% del programa en proveedores de contingencia precalificados (hoja MercadoPY).</t>
-  </si>
-  <si>
-    <t>Concentracion Brasil: % camiones del mayor productor (8 sem)</t>
-  </si>
-  <si>
-    <t>Camiones que descargan por semana, prox. 4 sem (promedio)</t>
-  </si>
-  <si>
-    <t>Aloha + dictados + supuestos.</t>
-  </si>
-  <si>
-    <t>Mix descargas prox. 4 sem: Brasil</t>
-  </si>
-  <si>
-    <t>Cajas por origen sobre el total de las proximas 4 semanas. Diversificacion de origen = menos riesgo (frontera, clima, TR4).</t>
-  </si>
-  <si>
-    <t>Mix descargas prox. 4 sem: Paraguay</t>
-  </si>
-  <si>
-    <t>Mix descargas prox. 4 sem: Bolivia</t>
-  </si>
-  <si>
-    <t>Costo estimado de compra prox. 4 sem (USD)</t>
-  </si>
-  <si>
-    <t>Cajas que descargan x USD/caja usado (Parametros: precio de compra real si esta cargado, si no la referencia de aduana 2026).</t>
-  </si>
-  <si>
-    <t>Camiones supuestos en el horizonte (PY + BR)</t>
-  </si>
-  <si>
-    <t>Cuantos de los camiones contados todavia son supuestos (5 PY por semana; 8 BR los viernes mas alla de lo dictado). Cuanto mas bajo, mas firme el plan. Se apagan en Parametros (SupPY / SupBR).</t>
-  </si>
-  <si>
-    <t>Faltante promedio de los proveedores (MIC - descargado, Aloha 2024-26)</t>
-  </si>
-  <si>
-    <t>Fill rate del proveedor: positivo = descargo menos de lo declarado; negativo = descargo de mas. Por productor en Proveedores.</t>
-  </si>
-  <si>
-    <t>OTIF: camiones que descargaron dentro del lead time + 1 dia</t>
-  </si>
-  <si>
-    <t>Sobre los camiones con descarga real cargada en Cargas (columna Descarga real). Se llena solo a medida que se anotan descargas.</t>
-  </si>
-  <si>
-    <t>Camiones dictados que Aloha aun no tiene</t>
-  </si>
-  <si>
-    <t>Pasan a Aloha cuando se cargan en el sistema.</t>
-  </si>
-  <si>
-    <t>Exactitud del pronostico (MAPE, semanas con venta real)</t>
-  </si>
-  <si>
-    <t>Promedio del desvio absoluto entre venta real (ERP) y venta usada. Multinacionales: forecast accuracy semanal; &lt;10% es bueno para fruta.</t>
-  </si>
-  <si>
-    <t>REFERENCIA MULTINACIONAL (S&amp;OP de fruta fresca)</t>
-  </si>
-  <si>
-    <t>Practica</t>
-  </si>
-  <si>
-    <t>Equivalente en Almar / esta planilla</t>
-  </si>
-  <si>
-    <t>Cadencia S&amp;OP</t>
-  </si>
-  <si>
-    <t>Reunion semanal (15-30 min) de demanda, abastecimiento y riesgos, con KPIs de merma y exactitud del pronostico.</t>
-  </si>
-  <si>
-    <t>El WhatsApp del miercoles 12:00 (pedidos) y del viernes 19:00 (cierre): Cepea, clima, stock proyectado y camiones que faltan. Esta planilla es el soporte para probar antes de dictar.</t>
-  </si>
-  <si>
-    <t>Un solo plan de demanda</t>
-  </si>
-  <si>
-    <t>Un numero de venta por semana acordado entre ventas y compras, con estacionalidad (dia de la semana, semana del mes) y venta real para medir el desvio.</t>
-  </si>
-  <si>
-    <t>Hoja Demanda: venta plan + factor por semana del mes + venta manual + venta real ERP + desvio.</t>
-  </si>
-  <si>
-    <t>Proyeccion de inventario</t>
-  </si>
-  <si>
-    <t>Stock inicial + recepciones - demanda = stock final, por semana, contra un stock de seguridad explicito; recomendacion de pedido con fecha limite por lead time.</t>
-  </si>
-  <si>
-    <t>Hoja Proyeccion: cierre del sabado, minimo 22.500, camiones a cargar y fecha limite (sabado - lead time).</t>
-  </si>
-  <si>
-    <t>Stock de seguridad dinamico (perecederos)</t>
-  </si>
-  <si>
-    <t>Sube y baja con la venta (mas antes del fin de semana / comienzo de mes), acotado por la vida util: mas stock = mas merma.</t>
-  </si>
-  <si>
-    <t>Minimo en cajas (22.500) o por dias de venta (7): Parametros. La cobertura objetivo pinta la proyeccion.</t>
-  </si>
-  <si>
-    <t>Dias de cobertura (DOS / days on hand)</t>
-  </si>
-  <si>
-    <t>Indicador central: stock / venta diaria. Objetivo por categoria; fruta fresca 5-10 dias segun madurez.</t>
-  </si>
-  <si>
-    <t>Columnas "Dias de cobertura" (total y por origen). Almar: 7 dias = fruta que todavia no maduro (gas + camara).</t>
-  </si>
-  <si>
-    <t>Lead time y ciclo de pedido por dia de la semana</t>
-  </si>
-  <si>
-    <t>Cada origen con su lead time y su dia de corte; el sistema avisa antes del corte si la cobertura no llega.</t>
-  </si>
-  <si>
-    <t>Lead time por origen (3/3/6), lead time real por productor (Proveedores), corte PY miercoles / BR jueves, "Cargar hasta" por semana.</t>
-  </si>
-  <si>
-    <t>Capacidad de maduracion</t>
-  </si>
-  <si>
-    <t>Camaras de maduracion planificadas por volumen semanal (regla: una camara de 20 pallets por cada 20 pallets extra por semana, hasta ~140 pallets/sem).</t>
-  </si>
-  <si>
-    <t>Pendiente: cargar capacidad de camaras (ZAC / Coronel Raiz) como tope de recepcion semanal. FechaHoy el limite es el minimo, no el maximo.</t>
-  </si>
-  <si>
-    <t>Costo total puesto en destino</t>
-  </si>
-  <si>
-    <t>Precio en origen + empaque + flete + aduana + maduracion + merma esperada por carril/proveedor.</t>
-  </si>
-  <si>
-    <t>Parametros: Cepea x 22 + servicios, precio pagado Almar, TC; KPI de costo de las proximas 4 semanas. Falta: flete internacional, aduana y merma por productor (calidad).</t>
-  </si>
-  <si>
-    <t>Diversificacion de origen y proveedores</t>
-  </si>
-  <si>
-    <t>20-30% del programa en proveedores de contingencia precalificados; varios origenes, puertos y transportistas.</t>
-  </si>
-  <si>
-    <t>Tres origenes (BR / PY / BO), 17 productores BR, 4 PY, 2 BO; el mix por origen esta en KPIs. Proveedores: capacidad semanal por productor.</t>
-  </si>
-  <si>
-    <t>Scorecard de proveedores</t>
-  </si>
-  <si>
-    <t>OTIF por carril, reclamos, dias en verde / color de llegada, tiempo de correccion.</t>
-  </si>
-  <si>
-    <t>Proveedores: lead time real, regularidad (camiones por semana), precio. Calidad y vida verde: index_calidad (necesita 15 lotes con fecha de rompio).</t>
-  </si>
-  <si>
-    <t>Merma / shrink</t>
-  </si>
-  <si>
-    <t>2-10% del costo puesto en destino segun cadena de frio y madurez; se mide y se descuenta del plan.</t>
-  </si>
-  <si>
-    <t>Sin dato en el plan. Sugerencia: registrar cajas descartadas por semana en la hoja Demanda (columna nueva) y restarlas del stock.</t>
-  </si>
-  <si>
-    <t>Proveedores: capacidad y comportamiento real</t>
-  </si>
-  <si>
-    <t>Camiones desde el 02/08/2026 segun el Plan de Cargas de Aloha (8 semanas). Capacidad semanal = maximo observado (editable). Precio 2026 = promedio pagado por caja (cargas 2026.xlsx).</t>
-  </si>
-  <si>
-    <t>Productor (Aloha)</t>
-  </si>
-  <si>
-    <t>Nombre en cargas dictadas</t>
-  </si>
-  <si>
-    <t>Camiones (8 sem)</t>
-  </si>
-  <si>
-    <t>Semanas con carga</t>
-  </si>
-  <si>
-    <t>Prom camiones/sem</t>
-  </si>
-  <si>
-    <t>Pico: max camiones en una semana</t>
-  </si>
-  <si>
-    <t>CAPACIDAD semanal (prom. de las 2 mejores semanas)</t>
-  </si>
-  <si>
-    <t>Lead time real (dias)</t>
-  </si>
-  <si>
-    <t>Cajas/camion</t>
-  </si>
-  <si>
-    <t>Transportista habitual</t>
-  </si>
-  <si>
-    <t>Dias de carga habituales</t>
-  </si>
-  <si>
-    <t>Precio prom 2026 (R$/caja)</t>
-  </si>
-  <si>
-    <t>Camiones esta semana (Cargas)</t>
-  </si>
-  <si>
-    <t>Camiones semana proxima (Cargas)</t>
-  </si>
-  <si>
-    <t>Camiones 2024/2025/2026 (Aloha)</t>
-  </si>
-  <si>
-    <t>Faltante % (MIC - descargado)</t>
-  </si>
-  <si>
-    <t>Ultima carga (Aloha 24/09)</t>
-  </si>
-  <si>
-    <t>Cupo aprox/sem 2026</t>
-  </si>
-  <si>
-    <t>Situacion</t>
-  </si>
-  <si>
-    <t>FG (11) / Chabat (1)</t>
-  </si>
-  <si>
-    <t>vie 6, mie 4, mar 1</t>
-  </si>
-  <si>
-    <t>47/76/46</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>activo</t>
-  </si>
-  <si>
-    <t>Fischer</t>
-  </si>
-  <si>
-    <t>Amaro (8) / FG (4)</t>
-  </si>
-  <si>
-    <t>vie 5, mar 4, sab 2</t>
-  </si>
-  <si>
-    <t>17/164/61</t>
-  </si>
-  <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
-    <t>AXT (6) / Chabat (3)</t>
-  </si>
-  <si>
-    <t>vie 6, mie 2, mar 2</t>
-  </si>
-  <si>
-    <t>13/88/96</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>el mas regular de Brasil</t>
-  </si>
-  <si>
-    <t>Osnildo Stein</t>
-  </si>
-  <si>
-    <t>Chabat (5) / FG (2)</t>
-  </si>
-  <si>
-    <t>vie 5, mie 1, mar 1</t>
-  </si>
-  <si>
-    <t>0/0/22</t>
-  </si>
-  <si>
-    <t>nuevo 2026</t>
-  </si>
-  <si>
-    <t>Ivo Zimerman</t>
-  </si>
-  <si>
-    <t>FG (4) / Chabat (2)</t>
-  </si>
-  <si>
-    <t>mie 2, vie 2, mar 1</t>
-  </si>
-  <si>
-    <t>0/0/16</t>
-  </si>
-  <si>
-    <t>FG (5)</t>
-  </si>
-  <si>
-    <t>jue 1, mar 1, mie 1</t>
-  </si>
-  <si>
-    <t>39/70/37</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>Josemar Provesi</t>
-  </si>
-  <si>
-    <t>FG (2) / Chabat (1)</t>
-  </si>
-  <si>
-    <t>vie 2, sab 1, mie 1</t>
-  </si>
-  <si>
-    <t>Marconi Kons</t>
-  </si>
-  <si>
-    <t>FG (2) / Amaro (1)</t>
-  </si>
-  <si>
-    <t>vie 2, sab 1</t>
-  </si>
-  <si>
-    <t>0/0/14</t>
-  </si>
-  <si>
-    <t>camion chico (834 cajas promedio historico)</t>
-  </si>
-  <si>
-    <t>Furlani</t>
-  </si>
-  <si>
-    <t>Amaro (1) / Chabat (1)</t>
-  </si>
-  <si>
-    <t>mie 1, vie 1</t>
-  </si>
-  <si>
-    <t>Shapo</t>
-  </si>
-  <si>
-    <t>Chabat (1) / FG (1)</t>
-  </si>
-  <si>
-    <t>vie 2</t>
-  </si>
-  <si>
-    <t>Wagner Schveitzer</t>
-  </si>
-  <si>
-    <t>Wagner</t>
-  </si>
-  <si>
-    <t>Amaro (1)</t>
-  </si>
-  <si>
-    <t>vie 1</t>
-  </si>
-  <si>
-    <t>0/0/11</t>
-  </si>
-  <si>
-    <t>14/08/2026</t>
-  </si>
-  <si>
-    <t>Paraguay HF</t>
-  </si>
-  <si>
-    <t>Mega Logistica (22) / G.S.C.S. PARAGUAY TTES. (3)</t>
-  </si>
-  <si>
-    <t>dom 12, lun 8, mar 2</t>
-  </si>
-  <si>
-    <t>Paraguay carga domingo-lunes-martes y entra en la semana.</t>
-  </si>
-  <si>
-    <t>39/16/76</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>54% de los camiones PY de 2026: dependencia alta</t>
-  </si>
-  <si>
-    <t>MARSO EMPRENDIMIENTOS S.R.L. (10)</t>
-  </si>
-  <si>
-    <t>lun 5, mar 5, mie 1</t>
-  </si>
-  <si>
-    <t>nuevo desde 11/08/2026 (Alvarito)</t>
-  </si>
-  <si>
-    <t>G.S.C.S. PARAGUAY TTES. (6) / Lider Express (4)</t>
-  </si>
-  <si>
-    <t>lun 5, mar 5, dom 1</t>
-  </si>
-  <si>
-    <t>84/16/22</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>Jauser (3)</t>
-  </si>
-  <si>
-    <t>dom 1, lun 1, mar 1</t>
-  </si>
-  <si>
-    <t>40/13/20</t>
-  </si>
-  <si>
-    <t>14/09/2026</t>
-  </si>
-  <si>
-    <t>transportista historico Compass</t>
-  </si>
-  <si>
-    <t>Banexfrut</t>
-  </si>
-  <si>
-    <t>Surcentral (5)</t>
-  </si>
-  <si>
-    <t>vie 3, lun 2</t>
-  </si>
-  <si>
-    <t>Bolivia: 6-9 dias reales de carga a descarga; 1 camion por semana en promedio.</t>
-  </si>
-  <si>
-    <t>Bolivia: 1 camion por semana aprox, 6-9 dias de viaje</t>
-  </si>
-  <si>
-    <t>Befrut</t>
-  </si>
-  <si>
-    <t>Sintercargas (3)</t>
-  </si>
-  <si>
-    <t>mie 2, lun 1</t>
-  </si>
-  <si>
-    <t>Bolivia (sin productor en Aloha)</t>
-  </si>
-  <si>
-    <t>Valdemar</t>
-  </si>
-  <si>
-    <t>Sin cargas en las ultimas 8 semanas: alternativa si falla un habitual.</t>
-  </si>
-  <si>
-    <t>81/133/33</t>
-  </si>
-  <si>
-    <t>25/04/2026</t>
-  </si>
-  <si>
-    <t>inactivo desde abril 2026; fue el 2do de 2025</t>
-  </si>
-  <si>
-    <t>Jhony Viera</t>
-  </si>
-  <si>
-    <t>Jony</t>
-  </si>
-  <si>
-    <t>64/120/26</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>inactivo desde marzo 2026</t>
-  </si>
-  <si>
-    <t>Jorge Marangoni</t>
-  </si>
-  <si>
-    <t>Marangoni</t>
-  </si>
-  <si>
-    <t>0/0/21</t>
-  </si>
-  <si>
-    <t>24/07/2026</t>
-  </si>
-  <si>
-    <t>sin cargas desde julio; TT 4 dias</t>
-  </si>
-  <si>
-    <t>Banana Combinada</t>
-  </si>
-  <si>
-    <t>0/10/14</t>
-  </si>
-  <si>
-    <t>26/06/2026</t>
-  </si>
-  <si>
-    <t>sin cargas desde junio; TT 4 dias</t>
   </si>
   <si>
     <t>Guido / Servi Fel</t>
@@ -3901,12 +3904,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45">
@@ -3920,25 +3923,25 @@
         <v>243</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>178</v>
@@ -4047,7 +4050,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>17904</v>
+        <v>18868</v>
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
@@ -4067,7 +4070,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4093,7 +4096,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>10876</v>
+        <v>9868</v>
       </c>
       <c r="D9" s="7">
         <f>Demanda!H10</f>
@@ -4113,7 +4116,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>22678</v>
+        <v>22634</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4159,7 +4162,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>22642</v>
+        <v>22598</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4205,7 +4208,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>22706</v>
+        <v>22662</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4251,7 +4254,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>22770</v>
+        <v>22726</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4297,7 +4300,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>22834</v>
+        <v>22790</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4343,7 +4346,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>22898</v>
+        <v>22854</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4389,7 +4392,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>22962</v>
+        <v>22918</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4435,7 +4438,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>23026</v>
+        <v>22982</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4481,7 +4484,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>23090</v>
+        <v>23046</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4527,7 +4530,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>23154</v>
+        <v>23110</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4544,7 +4547,7 @@
     </row>
     <row r="20" spans="1:12" ht="63.95" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -4676,7 +4679,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.1194117647058821</v>
+        <v>8.1967058823529406</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>303</v>
@@ -4796,7 +4799,7 @@
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.60808502562156008</v>
+        <v>0.62637237396953238</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>322</v>
@@ -4808,7 +4811,7 @@
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.37198709432529892</v>
+        <v>0.35368309083311172</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4820,7 +4823,7 @@
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>1.9927880053141014E-2</v>
+        <v>1.9944535197355926E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4832,7 +4835,7 @@
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>375703.59999999974</v>
+        <v>375479.83999999973</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>326</v>
@@ -5312,7 +5315,7 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="s">
         <v>3</v>
@@ -5580,7 +5583,7 @@
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="s">
         <v>3</v>
@@ -6489,10 +6492,10 @@
         <v>59</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>229</v>
+        <v>489</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D27" s="33">
         <v>0</v>
@@ -6508,7 +6511,7 @@
         <v>972</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -6518,23 +6521,23 @@
       </c>
       <c r="O27" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="33" t="s">
         <v>471</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R27" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="S27" s="33" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T27" s="33"/>
       <c r="U27" s="33" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -6542,10 +6545,10 @@
         <v>59</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D28" s="33">
         <v>0</v>
@@ -6577,17 +6580,17 @@
         <v>471</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R28" s="36">
         <v>-1.4E-3</v>
       </c>
       <c r="S28" s="33" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T28" s="33"/>
       <c r="U28" s="33" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -6595,10 +6598,10 @@
         <v>59</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D29" s="33">
         <v>0</v>
@@ -6630,22 +6633,22 @@
         <v>471</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="R29" s="36">
         <v>-1E-3</v>
       </c>
       <c r="S29" s="33" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="T29" s="33"/>
       <c r="U29" s="33" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="48.95" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
@@ -6691,40 +6694,40 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21">
       <c r="A1" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30">
       <c r="A4" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C5" s="18">
         <v>0.18</v>
@@ -6736,15 +6739,15 @@
         <v>8600</v>
       </c>
       <c r="F5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C6" s="18">
         <v>9.5000000000000001E-2</v>
@@ -6756,12 +6759,12 @@
         <v>4200</v>
       </c>
       <c r="F6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -6781,7 +6784,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -6801,7 +6804,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -6821,7 +6824,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -6836,15 +6839,15 @@
         <v>2250</v>
       </c>
       <c r="F10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="18">
         <v>4.2000000000000003E-2</v>
@@ -6856,15 +6859,15 @@
         <v>2100</v>
       </c>
       <c r="F11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C12" s="18">
         <v>0.04</v>
@@ -6876,12 +6879,12 @@
         <v>1750</v>
       </c>
       <c r="F12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -6901,7 +6904,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -6921,7 +6924,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -6941,7 +6944,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -6961,7 +6964,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -6981,24 +6984,24 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C18" s="18">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C19" s="18">
         <v>2.5999999999999999E-2</v>
@@ -7009,7 +7012,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -7018,12 +7021,12 @@
         <v>2.4E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -7037,7 +7040,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -7051,7 +7054,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -7065,7 +7068,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -7080,21 +7083,21 @@
         <v>940</v>
       </c>
       <c r="F24" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45">
       <c r="A26" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>61</v>
@@ -7102,10 +7105,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B27" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C27" s="18">
         <v>0.22</v>
@@ -7114,15 +7117,15 @@
         <v>10350</v>
       </c>
       <c r="E27" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B28" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C28" s="18">
         <v>0.121</v>
@@ -7131,15 +7134,15 @@
         <v>4200</v>
       </c>
       <c r="E28" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B29" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C29" s="18">
         <v>7.0999999999999994E-2</v>
@@ -7148,15 +7151,15 @@
         <v>2100</v>
       </c>
       <c r="E29" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B30" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C30" s="18">
         <v>6.9000000000000006E-2</v>
@@ -7170,10 +7173,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B31" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C31" s="18">
         <v>6.3E-2</v>
@@ -7187,10 +7190,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B32" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C32" s="18">
         <v>5.1999999999999998E-2</v>
@@ -7204,10 +7207,10 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B33" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C33" s="18">
         <v>4.7E-2</v>
@@ -7221,10 +7224,10 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B34" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C34" s="18">
         <v>3.6999999999999998E-2</v>
@@ -7238,10 +7241,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B35" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C35" s="18">
         <v>3.5000000000000003E-2</v>
@@ -7255,10 +7258,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B36" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C36" s="18">
         <v>3.4000000000000002E-2</v>
@@ -7272,10 +7275,10 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B37" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C37" s="18">
         <v>3.1E-2</v>
@@ -7289,10 +7292,10 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B38" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C38" s="18">
         <v>0.03</v>
@@ -7306,10 +7309,10 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B39" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C39" s="18">
         <v>2.4E-2</v>
@@ -7320,10 +7323,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B40" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C40" s="18">
         <v>2.3E-2</v>
@@ -7334,10 +7337,10 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B41" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C41" s="18">
         <v>2.1000000000000001E-2</v>
@@ -7348,10 +7351,10 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B42" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C42" s="18">
         <v>1.7999999999999999E-2</v>
@@ -7362,10 +7365,10 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C43" s="18">
         <v>8.9999999999999993E-3</v>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="45" spans="1:12" ht="63.95" customHeight="1">
       <c r="A45" s="44" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
@@ -7412,79 +7415,79 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7492,84 +7495,84 @@
         <v>234</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30">
       <c r="A17" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30">
       <c r="A18" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30">
       <c r="A20" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>3</v>
@@ -7577,138 +7580,138 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -7749,12 +7752,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21">
       <c r="A1" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -7762,101 +7765,101 @@
         <v>172</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45">
       <c r="A5" s="37" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30">
       <c r="A6" s="37" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="45">
       <c r="A7" s="37" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30">
       <c r="A8" s="37" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30">
       <c r="A9" s="37" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30">
@@ -7864,38 +7867,38 @@
         <v>160</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30">
       <c r="A11" s="37" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48.95" customHeight="1">
       <c r="A13" s="44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -7956,7 +7959,7 @@
       </c>
       <c r="B4" s="5">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
@@ -11896,7 +11899,7 @@
         <v>58</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>210</v>
@@ -11937,7 +11940,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="9"/>
@@ -11969,20 +11972,20 @@
         <v>mar</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="G30" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H30" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>199</v>
@@ -11990,11 +11993,11 @@
       <c r="J30" s="6"/>
       <c r="K30">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="4"/>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="M30" s="5">
         <f t="shared" si="5"/>
@@ -12006,22 +12009,22 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="S30" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="T30" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12048,7 +12051,7 @@
         <v>59</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>3</v>
@@ -12114,27 +12117,27 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>mar</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="G32" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H32" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>199</v>
@@ -12142,7 +12145,7 @@
       <c r="J32" s="6"/>
       <c r="K32">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="4"/>
@@ -12158,22 +12161,22 @@
       </c>
       <c r="O32" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P32" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q32" s="9" t="s">
         <v>228</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="S32" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="T32" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12200,10 +12203,10 @@
         <v>58</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G33" s="8">
         <v>1008</v>
@@ -12241,7 +12244,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="9"/>
@@ -12273,20 +12276,20 @@
         <v>mié</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="G34" s="8">
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>199</v>
@@ -12294,11 +12297,11 @@
       <c r="J34" s="6"/>
       <c r="K34">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="4"/>
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="M34" s="5">
         <f t="shared" si="5"/>
@@ -12310,18 +12313,18 @@
       </c>
       <c r="O34" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P34" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>6636.24</v>
       </c>
       <c r="Q34" s="9" t="s">
         <v>230</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="S34" s="5">
         <f t="shared" si="10"/>
@@ -12342,20 +12345,20 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G35" s="8">
         <v>1008</v>
@@ -12374,11 +12377,11 @@
       </c>
       <c r="L35" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="M35" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N35">
         <f t="shared" si="6"/>
@@ -12393,11 +12396,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="S35" s="5">
         <f t="shared" si="10"/>
@@ -30486,11 +30489,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="2"/>
-        <v>17904</v>
+        <v>18868</v>
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
@@ -30498,7 +30501,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30506,7 +30509,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30518,11 +30521,11 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.4007058823529412</v>
+        <v>8.7409411764705869</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30530,19 +30533,19 @@
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
-        <v>10524</v>
+        <v>12468</v>
       </c>
       <c r="P8" s="22">
         <f>IF(Demanda!L9=0,"",O8/(Demanda!L9/DiasVenta))</f>
-        <v>6.0200209743540851</v>
+        <v>7.1320430927638476</v>
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
-        <v>12845</v>
+        <v>11865</v>
       </c>
       <c r="R8" s="22">
         <f>IF(Demanda!M9=0,"",Q8/(Demanda!M9/DiasVenta))</f>
-        <v>14.53054298642534</v>
+        <v>13.421945701357465</v>
       </c>
       <c r="S8" s="7">
         <f>S7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N8,0)</f>
@@ -30568,15 +30571,15 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="2"/>
-        <v>10876</v>
+        <v>9868</v>
       </c>
       <c r="F9" s="7">
         <f>ROUND(Demanda!H9,0)</f>
@@ -30584,7 +30587,7 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
@@ -30592,7 +30595,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30604,11 +30607,11 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22678</v>
+        <v>22634</v>
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>8.0039999999999996</v>
+        <v>7.9884705882352938</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30616,19 +30619,19 @@
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
-        <v>6011</v>
+        <v>6947</v>
       </c>
       <c r="P9" s="22">
         <f>IF(Demanda!L10=0,"",O9/(Demanda!L10/DiasVenta))</f>
-        <v>3.4384593383544666</v>
+        <v>3.9738773953665745</v>
       </c>
       <c r="Q9" s="7">
         <f>Q8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M9,0)</f>
-        <v>12441</v>
+        <v>11461</v>
       </c>
       <c r="R9" s="22">
         <f>IF(Demanda!M10=0,"",Q9/(Demanda!M10/DiasVenta))</f>
-        <v>14.073529411764707</v>
+        <v>12.964932126696832</v>
       </c>
       <c r="S9" s="7">
         <f>S8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N9,0)</f>
@@ -30654,7 +30657,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -30670,7 +30673,7 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>13642</v>
+        <v>13598</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
@@ -30678,7 +30681,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18642</v>
+        <v>18598</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30690,11 +30693,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22642</v>
+        <v>22598</v>
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>7.9912941176470582</v>
+        <v>7.9757647058823524</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30702,19 +30705,19 @@
       </c>
       <c r="O10" s="7">
         <f>O9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L10,0)</f>
-        <v>3586</v>
+        <v>4522</v>
       </c>
       <c r="P10" s="22">
         <f>IF(Demanda!L11=0,"",O10/(Demanda!L11/DiasVenta))</f>
-        <v>2.0512918295357041</v>
+        <v>2.586709886547812</v>
       </c>
       <c r="Q10" s="7">
         <f>Q9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M10,0)</f>
-        <v>12037</v>
+        <v>11057</v>
       </c>
       <c r="R10" s="22">
         <f>IF(Demanda!M11=0,"",Q10/(Demanda!M11/DiasVenta))</f>
-        <v>13.616515837104073</v>
+        <v>12.5079185520362</v>
       </c>
       <c r="S10" s="7">
         <f>S9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N10,0)</f>
@@ -30740,7 +30743,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>13642</v>
+        <v>13598</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -30756,7 +30759,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>4706</v>
+        <v>4662</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
@@ -30764,7 +30767,7 @@
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13706</v>
+        <v>13662</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30776,11 +30779,11 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22706</v>
+        <v>22662</v>
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>8.0138823529411756</v>
+        <v>7.9983529411764698</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30788,19 +30791,19 @@
       </c>
       <c r="O11" s="7">
         <f>O10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L11,0)</f>
-        <v>1161</v>
+        <v>2097</v>
       </c>
       <c r="P11" s="22">
         <f>IF(Demanda!L12=0,"",O11/(Demanda!L12/DiasVenta))</f>
-        <v>0.6641243207169415</v>
+        <v>1.1995423777290495</v>
       </c>
       <c r="Q11" s="7">
         <f>Q10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M11,0)</f>
-        <v>6733</v>
+        <v>5753</v>
       </c>
       <c r="R11" s="22">
         <f>IF(Demanda!M12=0,"",Q11/(Demanda!M12/DiasVenta))</f>
-        <v>7.616515837104072</v>
+        <v>6.5079185520361991</v>
       </c>
       <c r="S11" s="7">
         <f>S10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N11,0)</f>
@@ -30826,7 +30829,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>4706</v>
+        <v>4662</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30842,7 +30845,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-4230</v>
+        <v>-4274</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
@@ -30850,7 +30853,7 @@
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30862,11 +30865,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22770</v>
+        <v>22726</v>
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.0364705882352929</v>
+        <v>8.020941176470588</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30874,19 +30877,19 @@
       </c>
       <c r="O12" s="7">
         <f>O11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L12,0)</f>
-        <v>-1264</v>
+        <v>-328</v>
       </c>
       <c r="P12" s="22">
         <f>IF(Demanda!L13=0,"",O12/(Demanda!L13/DiasVenta))</f>
-        <v>-0.72304318810182089</v>
+        <v>-0.18762513108971302</v>
       </c>
       <c r="Q12" s="7">
         <f>Q11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M12,0)</f>
-        <v>1429</v>
+        <v>449</v>
       </c>
       <c r="R12" s="22">
         <f>IF(Demanda!M13=0,"",Q12/(Demanda!M13/DiasVenta))</f>
-        <v>1.6165158371040724</v>
+        <v>0.50791855203619907</v>
       </c>
       <c r="S12" s="7">
         <f>S11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N12,0)</f>
@@ -30912,7 +30915,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-4230</v>
+        <v>-4274</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30928,7 +30931,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-13166</v>
+        <v>-13210</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
@@ -30936,7 +30939,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13834</v>
+        <v>13790</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -30948,11 +30951,11 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22834</v>
+        <v>22790</v>
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.0590588235294121</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30960,19 +30963,19 @@
       </c>
       <c r="O13" s="7">
         <f>O12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L13,0)</f>
-        <v>-3689</v>
+        <v>-2753</v>
       </c>
       <c r="P13" s="22">
         <f>IF(Demanda!L14=0,"",O13/(Demanda!L14/DiasVenta))</f>
-        <v>-2.1102106969205834</v>
+        <v>-1.5747926399084755</v>
       </c>
       <c r="Q13" s="7">
         <f>Q12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M13,0)</f>
-        <v>-3875</v>
+        <v>-4855</v>
       </c>
       <c r="R13" s="22">
         <f>IF(Demanda!M14=0,"",Q13/(Demanda!M14/DiasVenta))</f>
-        <v>-4.383484162895928</v>
+        <v>-5.4920814479638009</v>
       </c>
       <c r="S13" s="7">
         <f>S12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N13,0)</f>
@@ -30998,7 +31001,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-13166</v>
+        <v>-13210</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31014,7 +31017,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-22102</v>
+        <v>-22146</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
@@ -31022,7 +31025,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13898</v>
+        <v>13854</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31034,11 +31037,11 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22898</v>
+        <v>22854</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.0816470588235294</v>
+        <v>8.0661176470588227</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31046,19 +31049,19 @@
       </c>
       <c r="O14" s="7">
         <f>O13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L14,0)</f>
-        <v>-6114</v>
+        <v>-5178</v>
       </c>
       <c r="P14" s="22">
         <f>IF(Demanda!L15=0,"",O14/(Demanda!L15/DiasVenta))</f>
-        <v>-3.4973782057393459</v>
+        <v>-2.961960148727238</v>
       </c>
       <c r="Q14" s="7">
         <f>Q13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M14,0)</f>
-        <v>-9179</v>
+        <v>-10159</v>
       </c>
       <c r="R14" s="22">
         <f>IF(Demanda!M15=0,"",Q14/(Demanda!M15/DiasVenta))</f>
-        <v>-10.383484162895927</v>
+        <v>-11.4920814479638</v>
       </c>
       <c r="S14" s="7">
         <f>S13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N14,0)</f>
@@ -31084,7 +31087,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-22102</v>
+        <v>-22146</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31100,7 +31103,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-31038</v>
+        <v>-31082</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
@@ -31108,7 +31111,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13962</v>
+        <v>13918</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31120,11 +31123,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22962</v>
+        <v>22918</v>
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.1042352941176468</v>
+        <v>8.0887058823529401</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31132,19 +31135,19 @@
       </c>
       <c r="O15" s="7">
         <f>O14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L15,0)</f>
-        <v>-8539</v>
+        <v>-7603</v>
       </c>
       <c r="P15" s="22">
         <f>IF(Demanda!L16=0,"",O15/(Demanda!L16/DiasVenta))</f>
-        <v>-4.8845457145581079</v>
+        <v>-4.3491276575460001</v>
       </c>
       <c r="Q15" s="7">
         <f>Q14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M15,0)</f>
-        <v>-14483</v>
+        <v>-15463</v>
       </c>
       <c r="R15" s="22">
         <f>IF(Demanda!M16=0,"",Q15/(Demanda!M16/DiasVenta))</f>
-        <v>-16.383484162895929</v>
+        <v>-17.492081447963802</v>
       </c>
       <c r="S15" s="7">
         <f>S14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N15,0)</f>
@@ -31170,7 +31173,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-31038</v>
+        <v>-31082</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31186,7 +31189,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-39974</v>
+        <v>-40018</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
@@ -31194,7 +31197,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14026</v>
+        <v>13982</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31206,11 +31209,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23026</v>
+        <v>22982</v>
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.1268235294117641</v>
+        <v>8.1112941176470592</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31218,19 +31221,19 @@
       </c>
       <c r="O16" s="7">
         <f>O15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L16,0)</f>
-        <v>-10964</v>
+        <v>-10028</v>
       </c>
       <c r="P16" s="22">
         <f>IF(Demanda!L17=0,"",O16/(Demanda!L17/DiasVenta))</f>
-        <v>-6.2717132233768709</v>
+        <v>-5.736295166364763</v>
       </c>
       <c r="Q16" s="7">
         <f>Q15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M16,0)</f>
-        <v>-19787</v>
+        <v>-20767</v>
       </c>
       <c r="R16" s="22">
         <f>IF(Demanda!M17=0,"",Q16/(Demanda!M17/DiasVenta))</f>
-        <v>-22.383484162895929</v>
+        <v>-23.492081447963802</v>
       </c>
       <c r="S16" s="7">
         <f>S15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N16,0)</f>
@@ -31256,7 +31259,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-39974</v>
+        <v>-40018</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31272,7 +31275,7 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-48910</v>
+        <v>-48954</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
@@ -31280,7 +31283,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14090</v>
+        <v>14046</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31292,11 +31295,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23090</v>
+        <v>23046</v>
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.1494117647058815</v>
+        <v>8.1338823529411766</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31304,19 +31307,19 @@
       </c>
       <c r="O17" s="7">
         <f>O16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L17,0)</f>
-        <v>-13389</v>
+        <v>-12453</v>
       </c>
       <c r="P17" s="22">
         <f>IF(Demanda!L18=0,"",O17/(Demanda!L18/DiasVenta))</f>
-        <v>-7.6588807321956329</v>
+        <v>-7.1234626751835251</v>
       </c>
       <c r="Q17" s="7">
         <f>Q16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M17,0)</f>
-        <v>-25091</v>
+        <v>-26071</v>
       </c>
       <c r="R17" s="22">
         <f>IF(Demanda!M18=0,"",Q17/(Demanda!M18/DiasVenta))</f>
-        <v>-28.383484162895929</v>
+        <v>-29.492081447963802</v>
       </c>
       <c r="S17" s="7">
         <f>S16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N17,0)</f>
@@ -31342,7 +31345,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-48910</v>
+        <v>-48954</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31358,7 +31361,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-57846</v>
+        <v>-57890</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
@@ -31366,7 +31369,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14154</v>
+        <v>14110</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31378,11 +31381,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23154</v>
+        <v>23110</v>
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.1719999999999988</v>
+        <v>8.1564705882352939</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31390,19 +31393,19 @@
       </c>
       <c r="O18" s="7">
         <f>O17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L18,0)</f>
-        <v>-15814</v>
+        <v>-14878</v>
       </c>
       <c r="P18" s="22">
         <f>IF(Demanda!L18=0,"",O18/(Demanda!L18/DiasVenta))</f>
-        <v>-9.046048241014395</v>
+        <v>-8.510630184002288</v>
       </c>
       <c r="Q18" s="7">
         <f>Q17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M18,0)</f>
-        <v>-30395</v>
+        <v>-31375</v>
       </c>
       <c r="R18" s="22">
         <f>IF(Demanda!M18=0,"",Q18/(Demanda!M18/DiasVenta))</f>
-        <v>-34.383484162895925</v>
+        <v>-35.492081447963798</v>
       </c>
       <c r="S18" s="7">
         <f>S17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N18,0)</f>
@@ -31620,7 +31623,7 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
@@ -31640,7 +31643,7 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.4007058823529412</v>
+        <v>8.7409411764705869</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
@@ -31648,7 +31651,7 @@
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 23.802 cajas - descargan 18 - vende 17.000 -&gt; ok</v>
+        <v>Sab 10/10: 24.766 cajas - descargan 19 - vende 17.000 -&gt; ok</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31658,7 +31661,7 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
@@ -31678,7 +31681,7 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>8.0039999999999996</v>
+        <v>7.9884705882352938</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
@@ -31686,7 +31689,7 @@
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 17.678 cajas - descargan 11 - vende 17.000 -&gt; cargar 5 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 17.634 cajas - descargan 10 - vende 17.000 -&gt; cargar 5 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31696,7 +31699,7 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>18642</v>
+        <v>18598</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
@@ -31716,7 +31719,7 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>7.9912941176470582</v>
+        <v>7.9757647058823524</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
@@ -31724,7 +31727,7 @@
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 18.642 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 18.598 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31734,7 +31737,7 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>13706</v>
+        <v>13662</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
@@ -31754,7 +31757,7 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>8.0138823529411756</v>
+        <v>7.9983529411764698</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
@@ -31762,7 +31765,7 @@
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 13.706 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 13.662 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31772,7 +31775,7 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
@@ -31792,7 +31795,7 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.0364705882352929</v>
+        <v>8.020941176470588</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
@@ -31800,7 +31803,7 @@
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 13.770 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 13.726 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31810,7 +31813,7 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>13834</v>
+        <v>13790</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
@@ -31830,7 +31833,7 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.0590588235294121</v>
+        <v>8.0435294117647054</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
@@ -31838,7 +31841,7 @@
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 13.834 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 13.790 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31848,7 +31851,7 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>13898</v>
+        <v>13854</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
@@ -31868,7 +31871,7 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.0816470588235294</v>
+        <v>8.0661176470588227</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
@@ -31876,7 +31879,7 @@
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 13.898 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 13.854 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31886,7 +31889,7 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>13962</v>
+        <v>13918</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
@@ -31906,7 +31909,7 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.1042352941176468</v>
+        <v>8.0887058823529401</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
@@ -31914,7 +31917,7 @@
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 13.962 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 13.918 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31924,7 +31927,7 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>14026</v>
+        <v>13982</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
@@ -31944,7 +31947,7 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.1268235294117641</v>
+        <v>8.1112941176470592</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
@@ -31952,7 +31955,7 @@
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 14.026 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 13.982 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -31962,7 +31965,7 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>14090</v>
+        <v>14046</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
@@ -31982,7 +31985,7 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.1494117647058815</v>
+        <v>8.1338823529411766</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
@@ -31990,7 +31993,7 @@
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 14.090 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 14.046 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32000,7 +32003,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>14154</v>
+        <v>14110</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
@@ -32020,7 +32023,7 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.1719999999999988</v>
+        <v>8.1564705882352939</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
@@ -32028,7 +32031,7 @@
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 14.154 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 14.110 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -32101,12 +32104,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -32124,7 +32127,7 @@
         <v>173</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>251</v>
@@ -32133,12 +32136,12 @@
         <v>178</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B6" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32159,7 +32162,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B7" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32201,7 +32204,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B9" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32235,7 +32238,7 @@
         <v>173</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>251</v>
@@ -32244,41 +32247,41 @@
         <v>178</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>10524</v>
+        <v>12468</v>
       </c>
       <c r="C13" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>6.0200209743540851</v>
+        <v>7.1320430927638476</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(B13="","",IF(B13&lt;0,"FALTA",IF(C13&lt;2,"CRITICO",IF(C13&lt;CoberturaObjetivo,"JUSTO",IF(C13&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>JUSTO</v>
+        <v>OK</v>
       </c>
       <c r="E13" t="str">
         <f ca="1">IF(D13="FALTA","se queda sin fruta: cargar ya",IF(D13="CRITICO","cargar esta semana, sin falta",IF(D13="JUSTO","priorizar este origen en los pedidos",IF(D13="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v>priorizar este origen en los pedidos</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>12845</v>
+        <v>11865</v>
       </c>
       <c r="C14" s="22">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>14.53054298642534</v>
+        <v>13.421945701357465</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(B14="","",IF(B14&lt;0,"FALTA",IF(C14&lt;2,"CRITICO",IF(C14&lt;CoberturaObjetivo,"JUSTO",IF(C14&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32312,15 +32315,15 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="39" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.4007058823529412</v>
+        <v>8.7409411764705869</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32346,7 +32349,7 @@
         <v>173</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>251</v>
@@ -32355,20 +32358,20 @@
         <v>178</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>6011</v>
+        <v>6947</v>
       </c>
       <c r="C20" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>3.4384593383544666</v>
+        <v>3.9738773953665745</v>
       </c>
       <c r="D20" t="str">
         <f ca="1">IF(B20="","",IF(B20&lt;0,"FALTA",IF(C20&lt;2,"CRITICO",IF(C20&lt;CoberturaObjetivo,"JUSTO",IF(C20&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32381,15 +32384,15 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>12441</v>
+        <v>11461</v>
       </c>
       <c r="C21" s="22">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>14.073529411764707</v>
+        <v>12.964932126696832</v>
       </c>
       <c r="D21" t="str">
         <f ca="1">IF(B21="","",IF(B21&lt;0,"FALTA",IF(C21&lt;2,"CRITICO",IF(C21&lt;CoberturaObjetivo,"JUSTO",IF(C21&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32423,15 +32426,15 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>8.0039999999999996</v>
+        <v>7.9884705882352938</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32444,7 +32447,7 @@
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -32494,7 +32497,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 18.790 (plan: 23.802).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 18.790 (plan: 24.766).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32811,7 +32814,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>17904</v>
+        <v>18868</v>
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
@@ -32819,7 +32822,7 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>27102</v>
+        <v>28066</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32827,7 +32830,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
@@ -32835,7 +32838,7 @@
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>20502</v>
+        <v>21466</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
@@ -32855,15 +32858,15 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>20862</v>
+        <v>21826</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>22802</v>
+        <v>23766</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>23802</v>
+        <v>24766</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -32877,7 +32880,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>10876</v>
+        <v>9868</v>
       </c>
       <c r="D9" s="7">
         <f>Proyeccion!F9</f>
@@ -32885,7 +32888,7 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>22678</v>
+        <v>22634</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
@@ -32893,7 +32896,7 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17678</v>
+        <v>17634</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
@@ -32901,7 +32904,7 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14678</v>
+        <v>14634</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
@@ -32909,11 +32912,11 @@
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>15888</v>
+        <v>15844</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>21678</v>
+        <v>21634</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -32921,15 +32924,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14738</v>
+        <v>14694</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>16678</v>
+        <v>16634</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>17678</v>
+        <v>17634</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -32951,7 +32954,7 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>20342</v>
+        <v>20298</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
@@ -32959,7 +32962,7 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18642</v>
+        <v>18598</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
@@ -32967,7 +32970,7 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16942</v>
+        <v>16898</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
@@ -32979,7 +32982,7 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18642</v>
+        <v>18598</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
@@ -32987,15 +32990,15 @@
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15702</v>
+        <v>15658</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17642</v>
+        <v>17598</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18642</v>
+        <v>18598</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33017,7 +33020,7 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16106</v>
+        <v>16062</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
@@ -33025,7 +33028,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13706</v>
+        <v>13662</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
@@ -33033,7 +33036,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12306</v>
+        <v>12262</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
@@ -33045,7 +33048,7 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13706</v>
+        <v>13662</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
@@ -33053,15 +33056,15 @@
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10766</v>
+        <v>10722</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12706</v>
+        <v>12662</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13706</v>
+        <v>13662</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33083,7 +33086,7 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15870</v>
+        <v>15826</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -33091,7 +33094,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -33099,7 +33102,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12670</v>
+        <v>12626</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
@@ -33111,7 +33114,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -33119,15 +33122,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10830</v>
+        <v>10786</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12770</v>
+        <v>12726</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13770</v>
+        <v>13726</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33149,7 +33152,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15634</v>
+        <v>15590</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -33157,7 +33160,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13834</v>
+        <v>13790</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
@@ -33165,7 +33168,7 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12034</v>
+        <v>11990</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
@@ -33177,7 +33180,7 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13834</v>
+        <v>13790</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
@@ -33185,15 +33188,15 @@
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10894</v>
+        <v>10850</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12834</v>
+        <v>12790</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13834</v>
+        <v>13790</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33215,7 +33218,7 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15398</v>
+        <v>15354</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
@@ -33223,7 +33226,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13898</v>
+        <v>13854</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
@@ -33231,7 +33234,7 @@
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12398</v>
+        <v>12354</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -33243,7 +33246,7 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13898</v>
+        <v>13854</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
@@ -33251,15 +33254,15 @@
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10958</v>
+        <v>10914</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12898</v>
+        <v>12854</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13898</v>
+        <v>13854</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33281,7 +33284,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16162</v>
+        <v>16118</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -33289,7 +33292,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13962</v>
+        <v>13918</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -33297,7 +33300,7 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12762</v>
+        <v>12718</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -33309,7 +33312,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13962</v>
+        <v>13918</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -33317,15 +33320,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11022</v>
+        <v>10978</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12962</v>
+        <v>12918</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13962</v>
+        <v>13918</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33347,7 +33350,7 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15926</v>
+        <v>15882</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
@@ -33355,7 +33358,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14026</v>
+        <v>13982</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -33363,7 +33366,7 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12126</v>
+        <v>12082</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
@@ -33375,7 +33378,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14026</v>
+        <v>13982</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -33383,15 +33386,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11086</v>
+        <v>11042</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13026</v>
+        <v>12982</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14026</v>
+        <v>13982</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33413,7 +33416,7 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15690</v>
+        <v>15646</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
@@ -33421,7 +33424,7 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14090</v>
+        <v>14046</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -33429,7 +33432,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12490</v>
+        <v>12446</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -33441,7 +33444,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14090</v>
+        <v>14046</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -33449,15 +33452,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11150</v>
+        <v>11106</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13090</v>
+        <v>13046</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14090</v>
+        <v>14046</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33479,7 +33482,7 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15454</v>
+        <v>15410</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
@@ -33487,7 +33490,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14154</v>
+        <v>14110</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -33495,7 +33498,7 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12854</v>
+        <v>12810</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
@@ -33507,7 +33510,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14154</v>
+        <v>14110</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -33515,15 +33518,15 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11214</v>
+        <v>11170</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13154</v>
+        <v>13110</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14154</v>
+        <v>14110</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36283C1A-FBB3-4A4B-8CB7-9A1043A13AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9CEF13-A5C3-44BB-ADF2-072D89D470EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 12:30 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 12:33 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C6" s="7">
         <f>Proyeccion!E6</f>
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7">
         <f>Demanda!H7</f>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H6" s="7">
         <f ca="1">Proyeccion!L6</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="I6" s="7" t="str">
         <f t="shared" ref="I6:I18" si="3">IF(CapFisica="","",CapFisica)</f>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C7" s="7">
         <f>Proyeccion!E7</f>
-        <v>10946</v>
+        <v>11926</v>
       </c>
       <c r="D7" s="7">
         <f>Demanda!H8</f>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>320</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.62637237396953238</v>
+        <v>0.61492559579308548</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>322</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.35368309083311172</v>
+        <v>0.36549434975571549</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>1.9944535197355926E-2</v>
+        <v>1.9580054451199046E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>375479.83999999973</v>
+        <v>382339.83999999973</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>326</v>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="1"/>
@@ -10100,8 +10100,8 @@
         <v>46292</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" ref="M5:M68" si="5">IF(L5="","",L5-WEEKDAY(L5,2)+1)</f>
-        <v>46286</v>
+        <f t="shared" ref="M5:M68" si="5">IF(L5="","",IF(WEEKDAY(L5,2)=7,L5+1,L5-WEEKDAY(L5,2)+1))</f>
+        <v>46293</v>
       </c>
       <c r="N5">
         <f t="shared" ref="N5:N68" si="6">IF(L5="","",IF(L5&gt;FechaConteo,1,0)*IF(I5="Supuesto",SupPY,IF(I5="Supuesto BR",SupBR,1)))</f>
@@ -10123,8 +10123,8 @@
         <v>46292</v>
       </c>
       <c r="S5" s="5">
-        <f t="shared" ref="S5:S68" si="10">IF(R5="","",R5-WEEKDAY(R5,2)+1)</f>
-        <v>46286</v>
+        <f t="shared" ref="S5:S68" si="10">IF(R5="","",IF(WEEKDAY(R5,2)=7,R5+1,R5-WEEKDAY(R5,2)+1))</f>
+        <v>46293</v>
       </c>
       <c r="T5" s="7">
         <f t="shared" ref="T5:T68" ca="1" si="11">IF(B5="","",IF(AND(B5&lt;=FechaHoy,J5="",I5&lt;&gt;"Supuesto",I5&lt;&gt;"Simulado"),H5,0))</f>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="S13" s="5">
         <f t="shared" si="10"/>
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="T13" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="S31" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="T31" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="S32" s="5">
         <f t="shared" si="10"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="T32" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14964,7 +14964,7 @@
         <v>46328</v>
       </c>
       <c r="M69" s="5">
-        <f t="shared" ref="M69:M132" si="18">IF(L69="","",L69-WEEKDAY(L69,2)+1)</f>
+        <f t="shared" ref="M69:M132" si="18">IF(L69="","",IF(WEEKDAY(L69,2)=7,L69+1,L69-WEEKDAY(L69,2)+1))</f>
         <v>46328</v>
       </c>
       <c r="N69">
@@ -14987,7 +14987,7 @@
         <v>46331</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" ref="S69:S132" si="23">IF(R69="","",R69-WEEKDAY(R69,2)+1)</f>
+        <f t="shared" ref="S69:S132" si="23">IF(R69="","",IF(WEEKDAY(R69,2)=7,R69+1,R69-WEEKDAY(R69,2)+1))</f>
         <v>46328</v>
       </c>
       <c r="T69" s="7">
@@ -19788,7 +19788,7 @@
         <v/>
       </c>
       <c r="M133" s="5" t="str">
-        <f t="shared" ref="M133:M196" si="31">IF(L133="","",L133-WEEKDAY(L133,2)+1)</f>
+        <f t="shared" ref="M133:M196" si="31">IF(L133="","",IF(WEEKDAY(L133,2)=7,L133+1,L133-WEEKDAY(L133,2)+1))</f>
         <v/>
       </c>
       <c r="N133" t="str">
@@ -19809,7 +19809,7 @@
         <v/>
       </c>
       <c r="S133" s="5" t="str">
-        <f t="shared" ref="S133:S196" si="36">IF(R133="","",R133-WEEKDAY(R133,2)+1)</f>
+        <f t="shared" ref="S133:S196" si="36">IF(R133="","",IF(WEEKDAY(R133,2)=7,R133+1,R133-WEEKDAY(R133,2)+1))</f>
         <v/>
       </c>
       <c r="T133" s="7" t="str">
@@ -23756,7 +23756,7 @@
         <v/>
       </c>
       <c r="M197" s="5" t="str">
-        <f t="shared" ref="M197:M260" si="44">IF(L197="","",L197-WEEKDAY(L197,2)+1)</f>
+        <f t="shared" ref="M197:M260" si="44">IF(L197="","",IF(WEEKDAY(L197,2)=7,L197+1,L197-WEEKDAY(L197,2)+1))</f>
         <v/>
       </c>
       <c r="N197" t="str">
@@ -23777,7 +23777,7 @@
         <v/>
       </c>
       <c r="S197" s="5" t="str">
-        <f t="shared" ref="S197:S260" si="49">IF(R197="","",R197-WEEKDAY(R197,2)+1)</f>
+        <f t="shared" ref="S197:S260" si="49">IF(R197="","",IF(WEEKDAY(R197,2)=7,R197+1,R197-WEEKDAY(R197,2)+1))</f>
         <v/>
       </c>
       <c r="T197" s="7" t="str">
@@ -27724,7 +27724,7 @@
         <v/>
       </c>
       <c r="M261" s="5" t="str">
-        <f t="shared" ref="M261:M324" si="57">IF(L261="","",L261-WEEKDAY(L261,2)+1)</f>
+        <f t="shared" ref="M261:M324" si="57">IF(L261="","",IF(WEEKDAY(L261,2)=7,L261+1,L261-WEEKDAY(L261,2)+1))</f>
         <v/>
       </c>
       <c r="N261" t="str">
@@ -27745,7 +27745,7 @@
         <v/>
       </c>
       <c r="S261" s="5" t="str">
-        <f t="shared" ref="S261:S324" si="62">IF(R261="","",R261-WEEKDAY(R261,2)+1)</f>
+        <f t="shared" ref="S261:S324" si="62">IF(R261="","",IF(WEEKDAY(R261,2)=7,R261+1,R261-WEEKDAY(R261,2)+1))</f>
         <v/>
       </c>
       <c r="T261" s="7" t="str">
@@ -30317,11 +30317,11 @@
       </c>
       <c r="D6" s="7">
         <f t="shared" ref="D6:D18" si="1">COUNTIFS(CgSemana,A6,CgCuenta,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" ref="E6:E18" si="2">SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1)</f>
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="F6" s="7">
         <f>ROUND(Demanda!H6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="G6" s="7">
         <f t="shared" ref="G6:G18" si="3">C6+E6-F6</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="H6" s="7">
         <f>0</f>
@@ -30337,7 +30337,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ref="I6:I18" si="4">G6+H6</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="J6" s="21">
         <f t="shared" ref="J6:J18" si="5">B6-MAX(LagBR,LagPY)-AtrasoDias</f>
@@ -30349,11 +30349,11 @@
       </c>
       <c r="L6" s="7">
         <f t="shared" ref="L6:L18" ca="1" si="7">I6+K6*CajasProm</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="M6" s="22">
         <f ca="1">IF(Demanda!H7=0,"",L6/(Demanda!H7/DiasVenta))</f>
-        <v>10.482000000000001</v>
+        <v>10.114500000000001</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" ref="N6:N18" ca="1" si="8">IF(I6&lt;0,"FALTA",IF(K6&gt;0,"CARGAR "&amp;K6,IF(I6&lt;MinimoSabado,"BAJO MINIMO (limite pasado)",IF(AND(M6&lt;&gt;"",M6&gt;VidaVerde),"EXCESO (merma)","OK"))))</f>
@@ -30369,11 +30369,11 @@
       </c>
       <c r="Q6" s="7">
         <f>ConteoPY+SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
-        <v>14653</v>
+        <v>13673</v>
       </c>
       <c r="R6" s="22">
         <f>IF(Demanda!M7=0,"",Q6/(Demanda!M7/DiasVenta))</f>
-        <v>13.946383248730964</v>
+        <v>13.013642131979694</v>
       </c>
       <c r="S6" s="7">
         <f>ConteoBO+SUMIFS(CgCajas,CgSemana,A6,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N6*MAX(0,MIN(DiasVenta,B6-FechaConteo))/DiasVenta,0)</f>
@@ -30399,15 +30399,15 @@
       </c>
       <c r="C7" s="7">
         <f t="shared" ref="C7:C18" si="10">G6</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="7">
         <f t="shared" si="2"/>
-        <v>10946</v>
+        <v>11926</v>
       </c>
       <c r="F7" s="7">
         <f>ROUND(Demanda!H7,0)</f>
@@ -32497,7 +32497,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 18.866 cajas (4.032 menos que el plan) y el 10/10 en 18.790 (plan: 24.766).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.830 (plan: 24.766).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="C6" s="7">
         <f>Proyeccion!E6</f>
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7">
         <f>Proyeccion!F6</f>
@@ -32690,7 +32690,7 @@
       </c>
       <c r="E6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*0.9,0)</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="F6">
         <f ca="1">IF(AND(E6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-E6)/CajasProm,0),0)</f>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="G6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*1,0)</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="H6">
         <f ca="1">IF(AND(G6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-G6)/CajasProm,0),0)</f>
@@ -32706,7 +32706,7 @@
       </c>
       <c r="I6" s="7">
         <f>ConteoTotal+C6-ROUND(D6*1.1,0)</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="J6">
         <f ca="1">IF(AND(I6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-I6)/CajasProm,0),0)</f>
@@ -32714,11 +32714,11 @@
       </c>
       <c r="K6" s="7">
         <f t="shared" ref="K6:K18" si="0">SUMIFS(CgCajas,CgSemanaP90,A6,CgCuenta,1)</f>
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7">
         <f>ConteoTotal+K6-D6</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="M6">
         <f ca="1">IF(AND(L6&lt;MinimoSabado,Proyeccion!J6&gt;=FechaHoy),ROUNDUP((MinimoSabado-L6)/CajasProm,0),0)</f>
@@ -32726,15 +32726,15 @@
       </c>
       <c r="N6" s="7">
         <f t="shared" ref="N6:N18" ca="1" si="1">G6-IF(A6&gt;=FechaHoy-WEEKDAY(FechaHoy,2)+8,3*CajasPY,0)</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" ref="O6:O18" ca="1" si="2">G6-IF(A6&gt;=FechaHoy-WEEKDAY(FechaHoy,2)+8,1000,0)</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P18" ca="1" si="3">G6-SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+8),CgSemana,"&lt;="&amp;MIN(A6,FechaHoy-WEEKDAY(FechaHoy,2)+15))</f>
-        <v>27952</v>
+        <v>26972</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -32748,7 +32748,7 @@
       </c>
       <c r="C7" s="7">
         <f>Proyeccion!E7</f>
-        <v>10946</v>
+        <v>11926</v>
       </c>
       <c r="D7" s="7">
         <f>Proyeccion!F7</f>
@@ -32784,7 +32784,7 @@
       </c>
       <c r="L7" s="7">
         <f t="shared" ref="L7:L18" ca="1" si="7">(L6+M6*CajasProm)+K7-D7</f>
-        <v>18866</v>
+        <v>17886</v>
       </c>
       <c r="M7">
         <f ca="1">IF(AND(L7&lt;MinimoSabado,Proyeccion!J7&gt;=FechaHoy),ROUNDUP((MinimoSabado-L7)/CajasProm,0),0)</f>
@@ -32846,15 +32846,15 @@
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
-        <v>16924</v>
+        <v>15944</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18790</v>
+        <v>16830</v>
       </c>
       <c r="M8">
         <f ca="1">IF(AND(L8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-L8)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -32912,15 +32912,15 @@
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>15844</v>
+        <v>17804</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>21634</v>
+        <v>23634</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -32982,11 +32982,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>18598</v>
+        <v>19598</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9CEF13-A5C3-44BB-ADF2-072D89D470EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167D7F55-B319-458B-A1CC-28D37EA6A334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="681">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 12:33 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 12:39 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -127,7 +127,7 @@
     <t>Proyectar el stock de banana al cierre de cada sabado, saber cuantos camiones cargar y hasta que dia, y probar escenarios (venta distinta a comienzo/fin de mes, atraso en frontera, camiones de mas o de menos).</t>
   </si>
   <si>
-    <t>Sigue las reglas de Almar: el sabado cierra la semana; lo que descarga el lunes suma a la semana siguiente; Paraguay carga domingo-lunes-martes y entra en la semana; los pedidos a Paraguay cierran el miercoles y a Brasil el jueves; minimo 22.500 cajas al cierre del sabado (Bolivia incluida).</t>
+    <t>Sigue las reglas de Almar: el sabado cierra la semana; lo que descarga el lunes suma a la semana siguiente; Paraguay carga domingo-lunes-martes y entra en la semana; los pedidos a Paraguay cierran el miercoles y a Brasil el jueves; minimo 25.000 cajas al cierre del sabado contando los tres origenes (desde el 01/10/2026, verano; antes 22.500).</t>
   </si>
   <si>
     <t>Y la practica de las multinacionales de fruta (S&amp;OP semanal): un solo plan de demanda, proyeccion de inventario por semana con dias de cobertura, stock minimo explicito, recomendacion de pedido con fecha limite por lead time, escenarios, KPIs y tablero de proveedores.</t>
@@ -211,7 +211,7 @@
     <t>ORIGEN DE LOS DATOS</t>
   </si>
   <si>
-    <t>plan_compras.json (paso 5j de actualizar_precios.ps1): Plan de Cargas de Aloha, cargas dictadas por Gonzalo (plan_compras.xlsx), supuestos PY, ventas_plan, conteo por camara. Precios: precios_cepea.json (Cepea + cargas 2026).</t>
+    <t>plan_compras.json (paso 5j de actualizar_precios.ps1): Plan de Cargas de Aloha, cargas dictadas por Gonzalo (plan_compras.xlsx), supuestos PY y BO, ventas_plan, conteo por camara. Precios: precios_cepea.json (Cepea + cargas 2026).</t>
   </si>
   <si>
     <t>Para refrescar los datos: volver a correr el script que arma esta planilla (plan_compras\generar_plan_xlsx.ps1) o pegar a mano las cargas nuevas en la hoja Cargas.</t>
@@ -244,7 +244,7 @@
     <t>Minimo al cierre del sabado (cajas)</t>
   </si>
   <si>
-    <t>Gonzalo 27/09/2026: "de una semana a otra unas 22/23 mil cajas cerrando el sabado", Bolivia incluida. Equivale a ~7-8 dias de venta (fruta que todavia no maduro: gas + camara).</t>
+    <t>Viene del JSON (plan_compras.xlsx &gt; supuestos &gt; minimo_cajas_sabado). 01/10/2026: 25.000 contando Brasil + Paraguay + Bolivia ("comienza el calor en Uruguay, levanta las ventas, quieren mantener 25 mil cajas al cierre del sabado"). Antes, 27/09: 22.500 ("de una semana a otra unas 22/23 mil cajas cerrando el sabado"). Equivale a ~8-9 dias de venta.</t>
   </si>
   <si>
     <t>Cobertura objetivo (dias de venta)</t>
@@ -787,6 +787,15 @@
     <t>nota 30/09: Milciades 2, lunes</t>
   </si>
   <si>
+    <t>Bolivia (supuesto)</t>
+  </si>
+  <si>
+    <t>Supuesto</t>
+  </si>
+  <si>
+    <t>supuesto: 1 camion BO por semana, descarga el lunes (Gonzalo 01/10)</t>
+  </si>
+  <si>
     <t>nota 30/09: tersa; transportista supuesto = semana anterior</t>
   </si>
   <si>
@@ -814,9 +823,6 @@
     <t>Paraguay (supuesto)</t>
   </si>
   <si>
-    <t>Supuesto</t>
-  </si>
-  <si>
     <t>supuesto: 5 camiones PY por semana, cargan dom-lun-mar (Gonzalo 27/09)</t>
   </si>
   <si>
@@ -1156,7 +1162,7 @@
     <t>Stock inicial + recepciones - demanda = stock final, por semana, contra un stock de seguridad explicito; recomendacion de pedido con fecha limite por lead time.</t>
   </si>
   <si>
-    <t>Hoja Proyeccion: cierre del sabado, minimo 22.500, camiones a cargar y fecha limite (sabado - lead time).</t>
+    <t>Hoja Proyeccion: cierre del sabado, minimo 25.000, camiones a cargar y fecha limite (sabado - lead time).</t>
   </si>
   <si>
     <t>Stock de seguridad dinamico (perecederos)</t>
@@ -1165,7 +1171,7 @@
     <t>Sube y baja con la venta (mas antes del fin de semana / comienzo de mes), acotado por la vida util: mas stock = mas merma.</t>
   </si>
   <si>
-    <t>Minimo en cajas (22.500) o por dias de venta (7): Parametros. La cobertura objetivo pinta la proyeccion.</t>
+    <t>Minimo en cajas (25.000 desde el 01/10/2026) o por dias de venta (7): Parametros. La cobertura objetivo pinta la proyeccion.</t>
   </si>
   <si>
     <t>Dias de cobertura (DOS / days on hand)</t>
@@ -1732,7 +1738,7 @@
     <t>Parametros, Demanda, KPIs, MercadoPY</t>
   </si>
   <si>
-    <t>Reglas fijas: el sabado cierra la semana; lo que descarga el lunes suma a la siguiente; Paraguay carga domingo-lunes-martes (entra en la semana); Brasil cierra pedidos jueves y Paraguay miercoles; minimo 22.500 cajas al sabado, Bolivia incluida.</t>
+    <t>Reglas fijas: el sabado cierra la semana; lo que descarga el lunes suma a la siguiente; Paraguay carga domingo-lunes-martes (entra en la semana); Brasil cierra pedidos jueves y Paraguay miercoles; minimo 25.000 cajas al sabado contando los tres origenes (desde el 01/10/2026).</t>
   </si>
   <si>
     <t>Semaforo semanal</t>
@@ -1954,7 +1960,7 @@
     <t>Stock de seguridad / minimo</t>
   </si>
   <si>
-    <t>Stock que se quiere tener al cierre para absorber atrasos y picos de venta. Aca: 22.500 cajas al sabado (o 7 dias de venta).</t>
+    <t>Stock que se quiere tener al cierre para absorber atrasos y picos de venta. Aca: 25.000 cajas al sabado desde el 01/10/2026 (antes 22.500), o 7 dias de venta.</t>
   </si>
   <si>
     <t>Lead time</t>
@@ -3904,12 +3910,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45">
@@ -3920,28 +3926,28 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>178</v>
@@ -4070,7 +4076,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>24766</v>
+        <v>25766</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4096,7 +4102,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>9868</v>
+        <v>10918</v>
       </c>
       <c r="D9" s="7">
         <f>Demanda!H10</f>
@@ -4116,7 +4122,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>22634</v>
+        <v>25684</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4142,7 +4148,7 @@
       </c>
       <c r="C10" s="7">
         <f>Proyeccion!E10</f>
-        <v>12964</v>
+        <v>14014</v>
       </c>
       <c r="D10" s="7">
         <f>Demanda!H11</f>
@@ -4162,7 +4168,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>22598</v>
+        <v>25698</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4188,7 +4194,7 @@
       </c>
       <c r="C11" s="7">
         <f>Proyeccion!E11</f>
-        <v>8064</v>
+        <v>9114</v>
       </c>
       <c r="D11" s="7">
         <f>Demanda!H12</f>
@@ -4208,7 +4214,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>22662</v>
+        <v>25812</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>22726</v>
+        <v>25876</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4300,7 +4306,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>22790</v>
+        <v>25940</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4346,7 +4352,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>22854</v>
+        <v>25004</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4392,7 +4398,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>22918</v>
+        <v>25068</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4438,7 +4444,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>22982</v>
+        <v>25132</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4484,7 +4490,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>23046</v>
+        <v>25196</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4530,7 +4536,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>23110</v>
+        <v>25260</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4547,7 +4553,7 @@
     </row>
     <row r="20" spans="1:12" ht="63.95" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -4594,184 +4600,184 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B5" s="12">
         <f>ConteoTotal</f>
         <v>26972</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" s="24">
         <f>ConteoTotal/(INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))/DiasVenta)</f>
         <v>10.114500000000001</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B7" s="12">
         <f ca="1">IFERROR(INDEX(PrStock,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>22898</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B8" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30">
       <c r="A10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.1967058823529406</v>
+        <v>8.8275882352941188</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B11" s="25">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30">
       <c r="A13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B13" s="24">
         <f>ConteoTotal/INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))</f>
         <v>1.6857500000000001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30">
       <c r="A14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B14" s="12">
         <f>ConteoBR*CostoBR+ConteoPY*CostoPY+ConteoBO*CostoBO</f>
         <v>196107.57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30">
       <c r="A15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B15" s="12">
         <f ca="1">SUM(CgPipeline)</f>
         <v>10946</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B16" s="26">
         <f>PrecioBR_BRL-(CepeaKg*KgCaja+ServiciosCaja)</f>
         <v>-7.0899999999999963</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="PY")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"PY",Proveedores!D5:D60),"")</f>
         <v>0.48076923076923078</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B18" s="27">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="BR")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"BR",Proveedores!D5:D60),"")</f>
@@ -4783,35 +4789,35 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30">
       <c r="A20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.61492559579308548</v>
+        <v>0.59175250331981477</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.36549434975571549</v>
+        <v>0.35172092021677492</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4819,11 +4825,11 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>1.9580054451199046E-2</v>
+        <v>5.6526576463410257E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4831,206 +4837,206 @@
     </row>
     <row r="23" spans="1:3" ht="30">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>382339.83999999973</v>
+        <v>405019.83999999979</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45">
       <c r="A24" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B24" s="25">
         <f>COUNTIFS(CgEstado,"Supuesto*",CgCuenta,1)</f>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B25" s="28">
         <f>IFERROR(AVERAGE(Proveedores!R5:R60),"")</f>
         <v>-9.5789473684210517E-4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
       <c r="A26" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B26" s="27">
         <f>IFERROR(AVERAGE(CgOTIF),"sin descargas reales todavia")</f>
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B27" s="25">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
         <v>32</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30">
       <c r="A28" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B28" s="29" t="str">
         <f>IFERROR(SUMPRODUCT((Demanda!O6:O18&lt;&gt;"")*ABS(Demanda!P6:P18))/COUNTIF(Demanda!O6:O18,"&lt;&gt;"),"sin venta real cargada")</f>
         <v>sin venta real cargada</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30">
       <c r="A30" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="45">
       <c r="A31" s="30" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45">
       <c r="A32" s="30" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45">
       <c r="A33" s="30" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30">
       <c r="A34" s="30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30">
       <c r="A35" s="30" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="30">
       <c r="A36" s="30" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="45">
       <c r="A37" s="30" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45">
       <c r="A38" s="30" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30">
       <c r="A39" s="30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30">
       <c r="A40" s="30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30">
       <c r="A41" s="30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5062,12 +5068,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="90">
@@ -5075,64 +5081,64 @@
         <v>173</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -5167,10 +5173,10 @@
         <v>1008</v>
       </c>
       <c r="K5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M5" s="10">
         <v>37.75</v>
@@ -5187,19 +5193,19 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R5" s="32">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="S5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="T5" s="22">
         <v>1.2</v>
       </c>
       <c r="U5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -5207,7 +5213,7 @@
         <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>212</v>
@@ -5234,10 +5240,10 @@
         <v>1008</v>
       </c>
       <c r="K6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M6" s="10">
         <v>37</v>
@@ -5254,19 +5260,19 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="R6" s="32">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="S6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T6" s="22">
         <v>1.6</v>
       </c>
       <c r="U6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -5301,10 +5307,10 @@
         <v>936</v>
       </c>
       <c r="K7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M7" s="10">
         <v>38.64</v>
@@ -5321,19 +5327,19 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="R7" s="32">
         <v>-1.4E-3</v>
       </c>
       <c r="S7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T7" s="22">
         <v>2.5</v>
       </c>
       <c r="U7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -5341,7 +5347,7 @@
         <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>214</v>
@@ -5368,10 +5374,10 @@
         <v>1008</v>
       </c>
       <c r="K8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M8" s="10">
         <v>41.63</v>
@@ -5388,19 +5394,19 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="R8" s="32">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="T8" s="22">
         <v>0.6</v>
       </c>
       <c r="U8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -5408,7 +5414,7 @@
         <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>205</v>
@@ -5435,10 +5441,10 @@
         <v>1008</v>
       </c>
       <c r="K9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M9" s="10">
         <v>40.74</v>
@@ -5455,19 +5461,19 @@
         <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R9" s="32">
         <v>-7.7999999999999996E-3</v>
       </c>
       <c r="S9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T9" s="22">
         <v>0.4</v>
       </c>
       <c r="U9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -5502,10 +5508,10 @@
         <v>1008</v>
       </c>
       <c r="K10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M10" s="10">
         <v>40.65</v>
@@ -5522,19 +5528,19 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="R10" s="32">
         <v>-4.0000000000000002E-4</v>
       </c>
       <c r="S10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="T10" s="22">
         <v>1</v>
       </c>
       <c r="U10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -5542,7 +5548,7 @@
         <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>220</v>
@@ -5569,10 +5575,10 @@
         <v>1008</v>
       </c>
       <c r="K11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M11" s="10">
         <v>42.33</v>
@@ -5595,7 +5601,7 @@
         <v>3</v>
       </c>
       <c r="U11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -5603,7 +5609,7 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>221</v>
@@ -5630,10 +5636,10 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M12" s="10">
         <v>42.16</v>
@@ -5650,19 +5656,19 @@
         <v>3</v>
       </c>
       <c r="Q12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="R12" s="32">
         <v>-1E-4</v>
       </c>
       <c r="S12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="T12" s="22">
         <v>0.4</v>
       </c>
       <c r="U12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -5670,10 +5676,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -5697,10 +5703,10 @@
         <v>1008</v>
       </c>
       <c r="K13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M13" s="10">
         <v>37.64</v>
@@ -5717,7 +5723,7 @@
         <v>3</v>
       </c>
       <c r="U13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -5725,10 +5731,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -5752,10 +5758,10 @@
         <v>1008</v>
       </c>
       <c r="K14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M14" s="10">
         <v>37.799999999999997</v>
@@ -5772,7 +5778,7 @@
         <v>3</v>
       </c>
       <c r="U14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -5780,10 +5786,10 @@
         <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -5807,10 +5813,10 @@
         <v>1008</v>
       </c>
       <c r="K15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M15" s="10">
         <v>41.14</v>
@@ -5827,19 +5833,19 @@
         <v>3</v>
       </c>
       <c r="Q15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="R15" s="32">
         <v>-1.8E-3</v>
       </c>
       <c r="S15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="T15" s="22">
         <v>0.3</v>
       </c>
       <c r="U15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -5847,10 +5853,10 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -5874,10 +5880,10 @@
         <v>980</v>
       </c>
       <c r="K16" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L16" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
@@ -5888,22 +5894,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="R16" s="32">
         <v>-1E-3</v>
       </c>
       <c r="S16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T16" s="22">
         <v>2</v>
       </c>
       <c r="U16" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -5938,10 +5944,10 @@
         <v>980</v>
       </c>
       <c r="K17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="0"/>
@@ -5952,22 +5958,22 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q17" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="R17" s="32">
         <v>-3.8999999999999998E-3</v>
       </c>
       <c r="S17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T17" s="22">
         <v>1.8</v>
       </c>
       <c r="U17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -6002,10 +6008,10 @@
         <v>980</v>
       </c>
       <c r="K18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
@@ -6016,22 +6022,22 @@
         <v>2</v>
       </c>
       <c r="P18" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q18" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="R18" s="32">
         <v>1E-4</v>
       </c>
       <c r="S18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T18" s="22">
         <v>0.6</v>
       </c>
       <c r="U18" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -6066,10 +6072,10 @@
         <v>980</v>
       </c>
       <c r="K19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="0"/>
@@ -6080,22 +6086,22 @@
         <v>2</v>
       </c>
       <c r="P19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q19" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R19" s="32">
         <v>-1.5E-3</v>
       </c>
       <c r="S19" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="T19" s="22">
         <v>0.5</v>
       </c>
       <c r="U19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -6103,7 +6109,7 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>194</v>
@@ -6130,10 +6136,10 @@
         <v>1050</v>
       </c>
       <c r="K20" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L20" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="0"/>
@@ -6144,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q20" t="s">
         <v>3</v>
@@ -6153,7 +6159,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -6161,7 +6167,7 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>194</v>
@@ -6188,10 +6194,10 @@
         <v>1050</v>
       </c>
       <c r="K21" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L21" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="0"/>
@@ -6202,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q21" t="s">
         <v>3</v>
@@ -6246,7 +6252,7 @@
         <v>3</v>
       </c>
       <c r="L22" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="0"/>
@@ -6257,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q22" t="s">
         <v>3</v>
@@ -6266,7 +6272,7 @@
         <v>3</v>
       </c>
       <c r="U22" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -6274,10 +6280,10 @@
         <v>58</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D23" s="33">
         <v>0</v>
@@ -6308,20 +6314,20 @@
         <v>0</v>
       </c>
       <c r="P23" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="R23" s="36">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="S23" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="T23" s="33"/>
       <c r="U23" s="33" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -6329,10 +6335,10 @@
         <v>58</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D24" s="33">
         <v>0</v>
@@ -6363,20 +6369,20 @@
         <v>0</v>
       </c>
       <c r="P24" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="R24" s="36">
         <v>-8.0000000000000004E-4</v>
       </c>
       <c r="S24" s="33" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="T24" s="33"/>
       <c r="U24" s="33" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -6384,10 +6390,10 @@
         <v>58</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D25" s="33">
         <v>0</v>
@@ -6418,20 +6424,20 @@
         <v>0</v>
       </c>
       <c r="P25" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R25" s="36">
         <v>0</v>
       </c>
       <c r="S25" s="33" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="T25" s="33"/>
       <c r="U25" s="33" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -6439,10 +6445,10 @@
         <v>58</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D26" s="33">
         <v>0</v>
@@ -6471,20 +6477,20 @@
         <v>0</v>
       </c>
       <c r="P26" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="R26" s="36">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="S26" s="33" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="T26" s="33"/>
       <c r="U26" s="33" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -6492,10 +6498,10 @@
         <v>59</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D27" s="33">
         <v>0</v>
@@ -6511,7 +6517,7 @@
         <v>972</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -6524,20 +6530,20 @@
         <v>0</v>
       </c>
       <c r="P27" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="R27" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="S27" s="33" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="T27" s="33"/>
       <c r="U27" s="33" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -6545,10 +6551,10 @@
         <v>59</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D28" s="33">
         <v>0</v>
@@ -6577,20 +6583,20 @@
         <v>0</v>
       </c>
       <c r="P28" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="R28" s="36">
         <v>-1.4E-3</v>
       </c>
       <c r="S28" s="33" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="T28" s="33"/>
       <c r="U28" s="33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -6598,10 +6604,10 @@
         <v>59</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D29" s="33">
         <v>0</v>
@@ -6630,25 +6636,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="33" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="R29" s="36">
         <v>-1E-3</v>
       </c>
       <c r="S29" s="33" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T29" s="33"/>
       <c r="U29" s="33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="48.95" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
@@ -6694,40 +6700,40 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21">
       <c r="A1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30">
       <c r="A4" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C5" s="18">
         <v>0.18</v>
@@ -6739,15 +6745,15 @@
         <v>8600</v>
       </c>
       <c r="F5" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C6" s="18">
         <v>9.5000000000000001E-2</v>
@@ -6759,12 +6765,12 @@
         <v>4200</v>
       </c>
       <c r="F6" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -6784,7 +6790,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -6804,7 +6810,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -6824,7 +6830,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -6839,15 +6845,15 @@
         <v>2250</v>
       </c>
       <c r="F10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C11" s="18">
         <v>4.2000000000000003E-2</v>
@@ -6859,15 +6865,15 @@
         <v>2100</v>
       </c>
       <c r="F11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C12" s="18">
         <v>0.04</v>
@@ -6879,12 +6885,12 @@
         <v>1750</v>
       </c>
       <c r="F12" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -6904,7 +6910,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -6924,7 +6930,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -6944,7 +6950,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -6964,7 +6970,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -6984,24 +6990,24 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C18" s="18">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C19" s="18">
         <v>2.5999999999999999E-2</v>
@@ -7012,7 +7018,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -7021,12 +7027,12 @@
         <v>2.4E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -7040,7 +7046,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -7054,7 +7060,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -7068,7 +7074,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -7083,21 +7089,21 @@
         <v>940</v>
       </c>
       <c r="F24" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45">
       <c r="A26" s="11" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>61</v>
@@ -7105,10 +7111,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B27" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C27" s="18">
         <v>0.22</v>
@@ -7117,15 +7123,15 @@
         <v>10350</v>
       </c>
       <c r="E27" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B28" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C28" s="18">
         <v>0.121</v>
@@ -7134,15 +7140,15 @@
         <v>4200</v>
       </c>
       <c r="E28" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B29" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C29" s="18">
         <v>7.0999999999999994E-2</v>
@@ -7151,15 +7157,15 @@
         <v>2100</v>
       </c>
       <c r="E29" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B30" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C30" s="18">
         <v>6.9000000000000006E-2</v>
@@ -7173,10 +7179,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C31" s="18">
         <v>6.3E-2</v>
@@ -7190,10 +7196,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B32" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C32" s="18">
         <v>5.1999999999999998E-2</v>
@@ -7207,10 +7213,10 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C33" s="18">
         <v>4.7E-2</v>
@@ -7224,10 +7230,10 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B34" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C34" s="18">
         <v>3.6999999999999998E-2</v>
@@ -7241,10 +7247,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B35" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C35" s="18">
         <v>3.5000000000000003E-2</v>
@@ -7258,10 +7264,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B36" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C36" s="18">
         <v>3.4000000000000002E-2</v>
@@ -7275,10 +7281,10 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B37" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C37" s="18">
         <v>3.1E-2</v>
@@ -7292,10 +7298,10 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B38" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C38" s="18">
         <v>0.03</v>
@@ -7309,10 +7315,10 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B39" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C39" s="18">
         <v>2.4E-2</v>
@@ -7323,10 +7329,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B40" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C40" s="18">
         <v>2.3E-2</v>
@@ -7337,10 +7343,10 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B41" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C41" s="18">
         <v>2.1000000000000001E-2</v>
@@ -7351,10 +7357,10 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B42" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C42" s="18">
         <v>1.7999999999999999E-2</v>
@@ -7365,10 +7371,10 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B43" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C43" s="18">
         <v>8.9999999999999993E-3</v>
@@ -7382,7 +7388,7 @@
     </row>
     <row r="45" spans="1:12" ht="63.95" customHeight="1">
       <c r="A45" s="44" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
@@ -7415,164 +7421,164 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30">
       <c r="A6" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30">
       <c r="A17" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30">
       <c r="A18" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30">
       <c r="A20" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>3</v>
@@ -7580,138 +7586,138 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -7752,12 +7758,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -7765,101 +7771,101 @@
         <v>172</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45">
       <c r="A5" s="37" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30">
       <c r="A6" s="37" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="45">
       <c r="A7" s="37" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30">
       <c r="A8" s="37" t="s">
+        <v>527</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>512</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>523</v>
-      </c>
       <c r="E8" s="15" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30">
       <c r="A9" s="37" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30">
@@ -7867,38 +7873,38 @@
         <v>160</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30">
       <c r="A11" s="37" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48.95" customHeight="1">
       <c r="A13" s="44" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -7970,7 +7976,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="8">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="C5" t="s">
         <v>44</v>
@@ -8521,7 +8527,7 @@
       </c>
       <c r="E52" t="str">
         <f ca="1">"Contra el minimo de Gonzalo ("&amp;FIXED(MinimoSabado,0)&amp;"): "&amp;IF(MinSugerido&gt;MinimoSabado,"la formula pide "&amp;FIXED(MinSugerido-MinimoSabado,0)&amp;" cajas mas","la formula pide "&amp;FIXED(MinimoSabado-MinSugerido,0)&amp;" cajas menos")&amp;". El que manda en la planilla es el de la fila 5."</f>
-        <v>Contra el minimo de Gonzalo (22.500): la formula pide 619 cajas mas. El que manda en la planilla es el de la fila 5.</v>
+        <v>Contra el minimo de Gonzalo (25.000): la formula pide 1.881 cajas menos. El que manda en la planilla es el de la fila 5.</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30">
@@ -11820,36 +11826,36 @@
         <v>mar</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>213</v>
+        <v>3</v>
       </c>
       <c r="G28" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H28" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="4"/>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="M28" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="N28">
         <f t="shared" si="6"/>
@@ -11857,18 +11863,18 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="9"/>
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="S28" s="5">
         <f t="shared" si="10"/>
@@ -11899,10 +11905,10 @@
         <v>58</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G29" s="8">
         <v>1008</v>
@@ -11940,7 +11946,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="9"/>
@@ -11975,7 +11981,7 @@
         <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>210</v>
@@ -12016,7 +12022,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
@@ -12048,20 +12054,20 @@
         <v>mar</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="G31" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H31" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>199</v>
@@ -12069,11 +12075,11 @@
       <c r="J31" s="6"/>
       <c r="K31">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="4"/>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="M31" s="5">
         <f t="shared" si="5"/>
@@ -12085,18 +12091,18 @@
       </c>
       <c r="O31" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="9"/>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="S31" s="5">
         <f t="shared" si="10"/>
@@ -12127,7 +12133,7 @@
         <v>59</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>3</v>
@@ -12168,7 +12174,7 @@
         <v>6860</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
@@ -12193,27 +12199,27 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>mar</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="G33" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H33" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>199</v>
@@ -12221,7 +12227,7 @@
       <c r="J33" s="6"/>
       <c r="K33">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="4"/>
@@ -12237,18 +12243,18 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P33" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="9"/>
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="S33" s="5">
         <f t="shared" si="10"/>
@@ -12279,17 +12285,17 @@
         <v>58</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G34" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>199</v>
@@ -12317,10 +12323,10 @@
       </c>
       <c r="P34" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
@@ -12355,17 +12361,17 @@
         <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G35" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H35" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>199</v>
@@ -12393,10 +12399,10 @@
       </c>
       <c r="P35" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
@@ -12421,20 +12427,20 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G36" s="8">
         <v>1008</v>
@@ -12453,11 +12459,11 @@
       </c>
       <c r="L36" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="M36" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N36">
         <f t="shared" si="6"/>
@@ -12472,11 +12478,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="R36" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="S36" s="5">
         <f t="shared" si="10"/>
@@ -12507,10 +12513,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G37" s="8">
         <v>1008</v>
@@ -12548,7 +12554,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
@@ -12583,10 +12589,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G38" s="8">
         <v>1008</v>
@@ -12624,7 +12630,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="9"/>
@@ -12659,7 +12665,7 @@
         <v>58</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>206</v>
@@ -12700,7 +12706,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R39" s="5">
         <f t="shared" si="9"/>
@@ -12725,27 +12731,27 @@
         <v>36</v>
       </c>
       <c r="B40" s="6">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="1"/>
-        <v>sáb</v>
+        <v>vie</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="G40" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>199</v>
@@ -12757,7 +12763,7 @@
       </c>
       <c r="L40" s="5">
         <f t="shared" si="4"/>
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="M40" s="5">
         <f t="shared" si="5"/>
@@ -12773,14 +12779,14 @@
       </c>
       <c r="P40" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="S40" s="5">
         <f t="shared" si="10"/>
@@ -12801,39 +12807,39 @@
         <v>37</v>
       </c>
       <c r="B41" s="6">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>sáb</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="G41" s="8">
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="4"/>
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="5"/>
@@ -12845,18 +12851,18 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P41" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>6636.24</v>
       </c>
       <c r="Q41" s="9" t="s">
         <v>235</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="S41" s="5">
         <f t="shared" si="10"/>
@@ -12887,7 +12893,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>3</v>
@@ -12900,7 +12906,7 @@
         <v>980</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42">
@@ -12928,7 +12934,7 @@
         <v>6860</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="9"/>
@@ -12963,7 +12969,7 @@
         <v>59</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>3</v>
@@ -12976,7 +12982,7 @@
         <v>980</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43">
@@ -13004,7 +13010,7 @@
         <v>6860</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R43" s="5">
         <f t="shared" si="9"/>
@@ -13039,7 +13045,7 @@
         <v>59</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>3</v>
@@ -13052,7 +13058,7 @@
         <v>980</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44">
@@ -13080,7 +13086,7 @@
         <v>6860</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R44" s="5">
         <f t="shared" si="9"/>
@@ -13115,7 +13121,7 @@
         <v>59</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>3</v>
@@ -13128,7 +13134,7 @@
         <v>980</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45">
@@ -13156,7 +13162,7 @@
         <v>6860</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R45" s="5">
         <f t="shared" si="9"/>
@@ -13181,14 +13187,14 @@
         <v>42</v>
       </c>
       <c r="B46" s="6">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>236</v>
@@ -13197,27 +13203,27 @@
         <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H46" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="M46" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="N46">
         <f t="shared" si="6"/>
@@ -13225,22 +13231,22 @@
       </c>
       <c r="O46" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="S46" s="5">
         <f t="shared" si="10"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="T46" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13257,35 +13263,35 @@
         <v>43</v>
       </c>
       <c r="B47" s="6">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mar</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H47" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" si="4"/>
@@ -13301,18 +13307,18 @@
       </c>
       <c r="O47" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="S47" s="5">
         <f t="shared" si="10"/>
@@ -13343,7 +13349,7 @@
         <v>58</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
@@ -13356,7 +13362,7 @@
         <v>1008</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
@@ -13384,7 +13390,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
@@ -13419,7 +13425,7 @@
         <v>58</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>3</v>
@@ -13432,7 +13438,7 @@
         <v>1008</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49">
@@ -13460,7 +13466,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R49" s="5">
         <f t="shared" si="9"/>
@@ -13495,7 +13501,7 @@
         <v>58</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>3</v>
@@ -13508,7 +13514,7 @@
         <v>1008</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50">
@@ -13536,7 +13542,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R50" s="5">
         <f t="shared" si="9"/>
@@ -13571,7 +13577,7 @@
         <v>58</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>3</v>
@@ -13584,7 +13590,7 @@
         <v>1008</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51">
@@ -13612,7 +13618,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R51" s="5">
         <f t="shared" si="9"/>
@@ -13647,7 +13653,7 @@
         <v>58</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>3</v>
@@ -13660,7 +13666,7 @@
         <v>1008</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52">
@@ -13688,7 +13694,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R52" s="5">
         <f t="shared" si="9"/>
@@ -13723,7 +13729,7 @@
         <v>58</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>3</v>
@@ -13736,7 +13742,7 @@
         <v>1008</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53">
@@ -13764,7 +13770,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R53" s="5">
         <f t="shared" si="9"/>
@@ -13789,39 +13795,39 @@
         <v>50</v>
       </c>
       <c r="B54" s="6">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G54" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H54" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" si="4"/>
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="M54" s="5">
         <f t="shared" si="5"/>
@@ -13833,18 +13839,18 @@
       </c>
       <c r="O54" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P54" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="S54" s="5">
         <f t="shared" si="10"/>
@@ -13865,39 +13871,39 @@
         <v>51</v>
       </c>
       <c r="B55" s="6">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G55" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H55" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" s="5">
         <f t="shared" si="4"/>
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="M55" s="5">
         <f t="shared" si="5"/>
@@ -13909,18 +13915,18 @@
       </c>
       <c r="O55" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P55" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="R55" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="S55" s="5">
         <f t="shared" si="10"/>
@@ -13951,7 +13957,7 @@
         <v>59</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>3</v>
@@ -13964,7 +13970,7 @@
         <v>980</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56">
@@ -13992,7 +13998,7 @@
         <v>6860</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="9"/>
@@ -14027,7 +14033,7 @@
         <v>59</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>3</v>
@@ -14040,7 +14046,7 @@
         <v>980</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57">
@@ -14068,7 +14074,7 @@
         <v>6860</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R57" s="5">
         <f t="shared" si="9"/>
@@ -14103,7 +14109,7 @@
         <v>59</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>3</v>
@@ -14116,7 +14122,7 @@
         <v>980</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58">
@@ -14144,7 +14150,7 @@
         <v>6860</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="9"/>
@@ -14169,14 +14175,14 @@
         <v>55</v>
       </c>
       <c r="B59" s="6">
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>236</v>
@@ -14185,27 +14191,27 @@
         <v>3</v>
       </c>
       <c r="G59" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H59" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L59" s="5">
         <f t="shared" si="4"/>
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="M59" s="5">
         <f t="shared" si="5"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="N59">
         <f t="shared" si="6"/>
@@ -14213,22 +14219,22 @@
       </c>
       <c r="O59" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P59" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R59" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46319</v>
       </c>
       <c r="S59" s="5">
         <f t="shared" si="10"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="T59" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14245,14 +14251,14 @@
         <v>56</v>
       </c>
       <c r="B60" s="6">
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>236</v>
@@ -14261,27 +14267,27 @@
         <v>3</v>
       </c>
       <c r="G60" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H60" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" si="4"/>
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="M60" s="5">
         <f t="shared" si="5"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="N60">
         <f t="shared" si="6"/>
@@ -14289,22 +14295,22 @@
       </c>
       <c r="O60" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P60" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R60" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46319</v>
       </c>
       <c r="S60" s="5">
         <f t="shared" si="10"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="T60" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14321,35 +14327,35 @@
         <v>57</v>
       </c>
       <c r="B61" s="6">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mar</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G61" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="4"/>
@@ -14365,18 +14371,18 @@
       </c>
       <c r="O61" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P61" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="S61" s="5">
         <f t="shared" si="10"/>
@@ -14407,7 +14413,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
@@ -14420,7 +14426,7 @@
         <v>1008</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
@@ -14448,7 +14454,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
@@ -14483,7 +14489,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>3</v>
@@ -14496,7 +14502,7 @@
         <v>1008</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63">
@@ -14524,7 +14530,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R63" s="5">
         <f t="shared" si="9"/>
@@ -14559,7 +14565,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>3</v>
@@ -14572,7 +14578,7 @@
         <v>1008</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64">
@@ -14600,7 +14606,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q64" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R64" s="5">
         <f t="shared" si="9"/>
@@ -14635,7 +14641,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>3</v>
@@ -14648,7 +14654,7 @@
         <v>1008</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65">
@@ -14676,7 +14682,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R65" s="5">
         <f t="shared" si="9"/>
@@ -14711,7 +14717,7 @@
         <v>58</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>3</v>
@@ -14724,7 +14730,7 @@
         <v>1008</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66">
@@ -14752,7 +14758,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R66" s="5">
         <f t="shared" si="9"/>
@@ -14777,7 +14783,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="6">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="1"/>
@@ -14787,7 +14793,7 @@
         <v>58</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>3</v>
@@ -14800,7 +14806,7 @@
         <v>1008</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67">
@@ -14809,11 +14815,11 @@
       </c>
       <c r="L67" s="5">
         <f t="shared" si="4"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="M67" s="5">
         <f t="shared" si="5"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="N67">
         <f t="shared" si="6"/>
@@ -14828,15 +14834,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R67" s="5">
         <f t="shared" si="9"/>
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="S67" s="5">
         <f t="shared" si="10"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="T67" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14853,7 +14859,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="6">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="1"/>
@@ -14863,7 +14869,7 @@
         <v>58</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>3</v>
@@ -14876,7 +14882,7 @@
         <v>1008</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68">
@@ -14885,11 +14891,11 @@
       </c>
       <c r="L68" s="5">
         <f t="shared" si="4"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="M68" s="5">
         <f t="shared" si="5"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="N68">
         <f t="shared" si="6"/>
@@ -14904,15 +14910,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R68" s="5">
         <f t="shared" si="9"/>
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="S68" s="5">
         <f t="shared" si="10"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="T68" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14929,7 +14935,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="6">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" ref="C69:C132" si="14">IF(B69="","",TEXT(B69,"ddd"))</f>
@@ -14939,7 +14945,7 @@
         <v>58</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>3</v>
@@ -14952,7 +14958,7 @@
         <v>1008</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69">
@@ -14961,11 +14967,11 @@
       </c>
       <c r="L69" s="5">
         <f t="shared" ref="L69:L132" si="17">IF(B69="","",IF(J69&lt;&gt;"",J69,B69+K69))</f>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="M69" s="5">
         <f t="shared" ref="M69:M132" si="18">IF(L69="","",IF(WEEKDAY(L69,2)=7,L69+1,L69-WEEKDAY(L69,2)+1))</f>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="N69">
         <f t="shared" ref="N69:N132" si="19">IF(L69="","",IF(L69&gt;FechaConteo,1,0)*IF(I69="Supuesto",SupPY,IF(I69="Supuesto BR",SupBR,1)))</f>
@@ -14980,15 +14986,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R69" s="5">
         <f t="shared" ref="R69:R132" si="22">IF(B69="","",IF(J69&lt;&gt;"",J69,B69+IFERROR(INDEX(LagsP90,MATCH(D69,Origenes,0)),K69)))</f>
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="S69" s="5">
         <f t="shared" ref="S69:S132" si="23">IF(R69="","",IF(WEEKDAY(R69,2)=7,R69+1,R69-WEEKDAY(R69,2)+1))</f>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="T69" s="7">
         <f t="shared" ref="T69:T132" ca="1" si="24">IF(B69="","",IF(AND(B69&lt;=FechaHoy,J69="",I69&lt;&gt;"Supuesto",I69&lt;&gt;"Simulado"),H69,0))</f>
@@ -15015,7 +15021,7 @@
         <v>58</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>3</v>
@@ -15028,7 +15034,7 @@
         <v>1008</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70">
@@ -15056,7 +15062,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
@@ -15091,7 +15097,7 @@
         <v>58</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>3</v>
@@ -15104,7 +15110,7 @@
         <v>1008</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71">
@@ -15132,7 +15138,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R71" s="5">
         <f t="shared" si="22"/>
@@ -15167,7 +15173,7 @@
         <v>58</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>3</v>
@@ -15180,7 +15186,7 @@
         <v>1008</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72">
@@ -15208,7 +15214,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R72" s="5">
         <f t="shared" si="22"/>
@@ -15243,7 +15249,7 @@
         <v>58</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>3</v>
@@ -15256,7 +15262,7 @@
         <v>1008</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73">
@@ -15284,7 +15290,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R73" s="5">
         <f t="shared" si="22"/>
@@ -15319,7 +15325,7 @@
         <v>58</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>3</v>
@@ -15332,7 +15338,7 @@
         <v>1008</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74">
@@ -15360,7 +15366,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R74" s="5">
         <f t="shared" si="22"/>
@@ -15385,7 +15391,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="6">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="14"/>
@@ -15395,7 +15401,7 @@
         <v>58</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>3</v>
@@ -15408,7 +15414,7 @@
         <v>1008</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75">
@@ -15417,11 +15423,11 @@
       </c>
       <c r="L75" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="M75" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="N75">
         <f t="shared" si="19"/>
@@ -15436,15 +15442,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R75" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="S75" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="T75" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15461,7 +15467,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="6">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="14"/>
@@ -15471,7 +15477,7 @@
         <v>58</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>3</v>
@@ -15484,7 +15490,7 @@
         <v>1008</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76">
@@ -15493,11 +15499,11 @@
       </c>
       <c r="L76" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="M76" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="N76">
         <f t="shared" si="19"/>
@@ -15512,15 +15518,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R76" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="S76" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="T76" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15537,7 +15543,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="6">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="14"/>
@@ -15547,7 +15553,7 @@
         <v>58</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>3</v>
@@ -15560,7 +15566,7 @@
         <v>1008</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77">
@@ -15569,11 +15575,11 @@
       </c>
       <c r="L77" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="M77" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="N77">
         <f t="shared" si="19"/>
@@ -15588,15 +15594,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q77" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R77" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="S77" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="T77" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15623,7 +15629,7 @@
         <v>58</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>3</v>
@@ -15636,7 +15642,7 @@
         <v>1008</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78">
@@ -15664,7 +15670,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
@@ -15699,7 +15705,7 @@
         <v>58</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>3</v>
@@ -15712,7 +15718,7 @@
         <v>1008</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79">
@@ -15740,7 +15746,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R79" s="5">
         <f t="shared" si="22"/>
@@ -15775,7 +15781,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>3</v>
@@ -15788,7 +15794,7 @@
         <v>1008</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80">
@@ -15816,7 +15822,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R80" s="5">
         <f t="shared" si="22"/>
@@ -15851,7 +15857,7 @@
         <v>58</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>3</v>
@@ -15864,7 +15870,7 @@
         <v>1008</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81">
@@ -15892,7 +15898,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R81" s="5">
         <f t="shared" si="22"/>
@@ -15927,7 +15933,7 @@
         <v>58</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>3</v>
@@ -15940,7 +15946,7 @@
         <v>1008</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82">
@@ -15968,7 +15974,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R82" s="5">
         <f t="shared" si="22"/>
@@ -15993,7 +15999,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="6">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="14"/>
@@ -16003,7 +16009,7 @@
         <v>58</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>3</v>
@@ -16016,7 +16022,7 @@
         <v>1008</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83">
@@ -16025,11 +16031,11 @@
       </c>
       <c r="L83" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="M83" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="N83">
         <f t="shared" si="19"/>
@@ -16044,15 +16050,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q83" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R83" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="S83" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="T83" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16069,7 +16075,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="6">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="14"/>
@@ -16079,7 +16085,7 @@
         <v>58</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>3</v>
@@ -16092,7 +16098,7 @@
         <v>1008</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84">
@@ -16101,11 +16107,11 @@
       </c>
       <c r="L84" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="M84" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="N84">
         <f t="shared" si="19"/>
@@ -16120,15 +16126,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R84" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="S84" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="T84" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16145,7 +16151,7 @@
         <v>81</v>
       </c>
       <c r="B85" s="6">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="14"/>
@@ -16155,7 +16161,7 @@
         <v>58</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>3</v>
@@ -16168,7 +16174,7 @@
         <v>1008</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85">
@@ -16177,11 +16183,11 @@
       </c>
       <c r="L85" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="M85" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="N85">
         <f t="shared" si="19"/>
@@ -16196,15 +16202,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R85" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="S85" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="T85" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16231,7 +16237,7 @@
         <v>58</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>3</v>
@@ -16244,7 +16250,7 @@
         <v>1008</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86">
@@ -16272,7 +16278,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
@@ -16307,7 +16313,7 @@
         <v>58</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>3</v>
@@ -16320,7 +16326,7 @@
         <v>1008</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87">
@@ -16348,7 +16354,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R87" s="5">
         <f t="shared" si="22"/>
@@ -16383,7 +16389,7 @@
         <v>58</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>3</v>
@@ -16396,7 +16402,7 @@
         <v>1008</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88">
@@ -16424,7 +16430,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q88" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R88" s="5">
         <f t="shared" si="22"/>
@@ -16459,7 +16465,7 @@
         <v>58</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>3</v>
@@ -16472,7 +16478,7 @@
         <v>1008</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89">
@@ -16500,7 +16506,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q89" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R89" s="5">
         <f t="shared" si="22"/>
@@ -16535,7 +16541,7 @@
         <v>58</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>3</v>
@@ -16548,7 +16554,7 @@
         <v>1008</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90">
@@ -16576,7 +16582,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q90" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R90" s="5">
         <f t="shared" si="22"/>
@@ -16601,7 +16607,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="6">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="14"/>
@@ -16611,7 +16617,7 @@
         <v>58</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>3</v>
@@ -16624,7 +16630,7 @@
         <v>1008</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91">
@@ -16633,11 +16639,11 @@
       </c>
       <c r="L91" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="M91" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="N91">
         <f t="shared" si="19"/>
@@ -16652,15 +16658,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R91" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="S91" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="T91" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16677,7 +16683,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="6">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="14"/>
@@ -16687,7 +16693,7 @@
         <v>58</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>3</v>
@@ -16700,7 +16706,7 @@
         <v>1008</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92">
@@ -16709,11 +16715,11 @@
       </c>
       <c r="L92" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="M92" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="N92">
         <f t="shared" si="19"/>
@@ -16728,15 +16734,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R92" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="S92" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="T92" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16753,7 +16759,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="6">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="14"/>
@@ -16763,7 +16769,7 @@
         <v>58</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>3</v>
@@ -16776,7 +16782,7 @@
         <v>1008</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93">
@@ -16785,11 +16791,11 @@
       </c>
       <c r="L93" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="M93" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="N93">
         <f t="shared" si="19"/>
@@ -16804,15 +16810,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q93" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R93" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="S93" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="T93" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16839,7 +16845,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>3</v>
@@ -16852,7 +16858,7 @@
         <v>1008</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94">
@@ -16880,7 +16886,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
@@ -16915,7 +16921,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>3</v>
@@ -16928,7 +16934,7 @@
         <v>1008</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95">
@@ -16956,7 +16962,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R95" s="5">
         <f t="shared" si="22"/>
@@ -16991,7 +16997,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>3</v>
@@ -17004,7 +17010,7 @@
         <v>1008</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96">
@@ -17032,7 +17038,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q96" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R96" s="5">
         <f t="shared" si="22"/>
@@ -17067,7 +17073,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>3</v>
@@ -17080,7 +17086,7 @@
         <v>1008</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97">
@@ -17108,7 +17114,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R97" s="5">
         <f t="shared" si="22"/>
@@ -17143,7 +17149,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>3</v>
@@ -17156,7 +17162,7 @@
         <v>1008</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98">
@@ -17184,7 +17190,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R98" s="5">
         <f t="shared" si="22"/>
@@ -17209,7 +17215,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="6">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="14"/>
@@ -17219,7 +17225,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>3</v>
@@ -17232,7 +17238,7 @@
         <v>1008</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99">
@@ -17241,11 +17247,11 @@
       </c>
       <c r="L99" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="M99" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="N99">
         <f t="shared" si="19"/>
@@ -17260,15 +17266,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q99" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R99" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46352</v>
       </c>
       <c r="S99" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="T99" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17285,7 +17291,7 @@
         <v>96</v>
       </c>
       <c r="B100" s="6">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="14"/>
@@ -17295,7 +17301,7 @@
         <v>58</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>3</v>
@@ -17308,7 +17314,7 @@
         <v>1008</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100">
@@ -17317,11 +17323,11 @@
       </c>
       <c r="L100" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="M100" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="N100">
         <f t="shared" si="19"/>
@@ -17336,15 +17342,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q100" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R100" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46352</v>
       </c>
       <c r="S100" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="T100" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17361,7 +17367,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="6">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="14"/>
@@ -17371,7 +17377,7 @@
         <v>58</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>3</v>
@@ -17384,7 +17390,7 @@
         <v>1008</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101">
@@ -17393,11 +17399,11 @@
       </c>
       <c r="L101" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="M101" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="N101">
         <f t="shared" si="19"/>
@@ -17412,15 +17418,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R101" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46352</v>
       </c>
       <c r="S101" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="T101" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17447,7 +17453,7 @@
         <v>58</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>3</v>
@@ -17460,7 +17466,7 @@
         <v>1008</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102">
@@ -17488,7 +17494,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q102" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
@@ -17523,7 +17529,7 @@
         <v>58</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>3</v>
@@ -17536,7 +17542,7 @@
         <v>1008</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103">
@@ -17564,7 +17570,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R103" s="5">
         <f t="shared" si="22"/>
@@ -17599,7 +17605,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>3</v>
@@ -17612,7 +17618,7 @@
         <v>1008</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104">
@@ -17640,7 +17646,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q104" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R104" s="5">
         <f t="shared" si="22"/>
@@ -17675,7 +17681,7 @@
         <v>58</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>3</v>
@@ -17688,7 +17694,7 @@
         <v>1008</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105">
@@ -17716,7 +17722,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q105" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R105" s="5">
         <f t="shared" si="22"/>
@@ -17751,7 +17757,7 @@
         <v>58</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
@@ -17764,7 +17770,7 @@
         <v>1008</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106">
@@ -17792,7 +17798,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q106" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R106" s="5">
         <f t="shared" si="22"/>
@@ -17817,7 +17823,7 @@
         <v>103</v>
       </c>
       <c r="B107" s="6">
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="14"/>
@@ -17827,7 +17833,7 @@
         <v>58</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>3</v>
@@ -17840,7 +17846,7 @@
         <v>1008</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107">
@@ -17849,11 +17855,11 @@
       </c>
       <c r="L107" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="M107" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="N107">
         <f t="shared" si="19"/>
@@ -17868,15 +17874,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q107" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R107" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46359</v>
       </c>
       <c r="S107" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="T107" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17893,7 +17899,7 @@
         <v>104</v>
       </c>
       <c r="B108" s="6">
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="14"/>
@@ -17903,7 +17909,7 @@
         <v>58</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>3</v>
@@ -17916,7 +17922,7 @@
         <v>1008</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108">
@@ -17925,11 +17931,11 @@
       </c>
       <c r="L108" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="M108" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="N108">
         <f t="shared" si="19"/>
@@ -17944,15 +17950,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q108" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R108" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46359</v>
       </c>
       <c r="S108" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="T108" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17969,7 +17975,7 @@
         <v>105</v>
       </c>
       <c r="B109" s="6">
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="14"/>
@@ -17979,7 +17985,7 @@
         <v>58</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>3</v>
@@ -17992,7 +17998,7 @@
         <v>1008</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109">
@@ -18001,11 +18007,11 @@
       </c>
       <c r="L109" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="M109" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="N109">
         <f t="shared" si="19"/>
@@ -18020,15 +18026,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q109" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R109" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46359</v>
       </c>
       <c r="S109" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="T109" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18055,7 +18061,7 @@
         <v>58</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>3</v>
@@ -18068,7 +18074,7 @@
         <v>1008</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110">
@@ -18096,7 +18102,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q110" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
@@ -18131,7 +18137,7 @@
         <v>58</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>3</v>
@@ -18144,7 +18150,7 @@
         <v>1008</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111">
@@ -18172,7 +18178,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q111" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R111" s="5">
         <f t="shared" si="22"/>
@@ -18207,7 +18213,7 @@
         <v>58</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>3</v>
@@ -18220,7 +18226,7 @@
         <v>1008</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112">
@@ -18248,7 +18254,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q112" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R112" s="5">
         <f t="shared" si="22"/>
@@ -18283,7 +18289,7 @@
         <v>58</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>3</v>
@@ -18296,7 +18302,7 @@
         <v>1008</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113">
@@ -18324,7 +18330,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q113" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R113" s="5">
         <f t="shared" si="22"/>
@@ -18359,7 +18365,7 @@
         <v>58</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>3</v>
@@ -18372,7 +18378,7 @@
         <v>1008</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114">
@@ -18400,7 +18406,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q114" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R114" s="5">
         <f t="shared" si="22"/>
@@ -18425,7 +18431,7 @@
         <v>111</v>
       </c>
       <c r="B115" s="6">
-        <v>46367</v>
+        <v>46360</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="14"/>
@@ -18435,7 +18441,7 @@
         <v>58</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>3</v>
@@ -18448,7 +18454,7 @@
         <v>1008</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115">
@@ -18457,11 +18463,11 @@
       </c>
       <c r="L115" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="M115" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="N115">
         <f t="shared" si="19"/>
@@ -18476,15 +18482,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R115" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46366</v>
       </c>
       <c r="S115" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="T115" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18501,7 +18507,7 @@
         <v>112</v>
       </c>
       <c r="B116" s="6">
-        <v>46367</v>
+        <v>46360</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="14"/>
@@ -18511,7 +18517,7 @@
         <v>58</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>3</v>
@@ -18524,7 +18530,7 @@
         <v>1008</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116">
@@ -18533,11 +18539,11 @@
       </c>
       <c r="L116" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="M116" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="N116">
         <f t="shared" si="19"/>
@@ -18552,15 +18558,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q116" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R116" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46366</v>
       </c>
       <c r="S116" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="T116" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18577,7 +18583,7 @@
         <v>113</v>
       </c>
       <c r="B117" s="6">
-        <v>46367</v>
+        <v>46360</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="14"/>
@@ -18587,7 +18593,7 @@
         <v>58</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>3</v>
@@ -18600,7 +18606,7 @@
         <v>1008</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117">
@@ -18609,11 +18615,11 @@
       </c>
       <c r="L117" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="M117" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="N117">
         <f t="shared" si="19"/>
@@ -18628,15 +18634,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q117" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R117" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46366</v>
       </c>
       <c r="S117" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="T117" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18663,7 +18669,7 @@
         <v>58</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>3</v>
@@ -18676,7 +18682,7 @@
         <v>1008</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118">
@@ -18704,7 +18710,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q118" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
@@ -18739,7 +18745,7 @@
         <v>58</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>3</v>
@@ -18752,7 +18758,7 @@
         <v>1008</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119">
@@ -18780,7 +18786,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q119" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R119" s="5">
         <f t="shared" si="22"/>
@@ -18815,7 +18821,7 @@
         <v>58</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>3</v>
@@ -18828,7 +18834,7 @@
         <v>1008</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120">
@@ -18856,7 +18862,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q120" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R120" s="5">
         <f t="shared" si="22"/>
@@ -18891,7 +18897,7 @@
         <v>58</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>3</v>
@@ -18904,7 +18910,7 @@
         <v>1008</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121">
@@ -18932,7 +18938,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q121" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R121" s="5">
         <f t="shared" si="22"/>
@@ -18967,7 +18973,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>3</v>
@@ -18980,7 +18986,7 @@
         <v>1008</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122">
@@ -19008,7 +19014,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q122" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R122" s="5">
         <f t="shared" si="22"/>
@@ -19033,7 +19039,7 @@
         <v>119</v>
       </c>
       <c r="B123" s="6">
-        <v>46374</v>
+        <v>46367</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="14"/>
@@ -19043,7 +19049,7 @@
         <v>58</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>3</v>
@@ -19056,7 +19062,7 @@
         <v>1008</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123">
@@ -19065,11 +19071,11 @@
       </c>
       <c r="L123" s="5">
         <f t="shared" si="17"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="M123" s="5">
         <f t="shared" si="18"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="N123">
         <f t="shared" si="19"/>
@@ -19084,15 +19090,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q123" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R123" s="5">
         <f t="shared" si="22"/>
-        <v>46380</v>
+        <v>46373</v>
       </c>
       <c r="S123" s="5">
         <f t="shared" si="23"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="T123" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19109,7 +19115,7 @@
         <v>120</v>
       </c>
       <c r="B124" s="6">
-        <v>46374</v>
+        <v>46367</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="14"/>
@@ -19119,7 +19125,7 @@
         <v>58</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>3</v>
@@ -19132,7 +19138,7 @@
         <v>1008</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124">
@@ -19141,11 +19147,11 @@
       </c>
       <c r="L124" s="5">
         <f t="shared" si="17"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="M124" s="5">
         <f t="shared" si="18"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="N124">
         <f t="shared" si="19"/>
@@ -19160,15 +19166,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q124" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R124" s="5">
         <f t="shared" si="22"/>
-        <v>46380</v>
+        <v>46373</v>
       </c>
       <c r="S124" s="5">
         <f t="shared" si="23"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="T124" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19185,7 +19191,7 @@
         <v>121</v>
       </c>
       <c r="B125" s="6">
-        <v>46374</v>
+        <v>46367</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="14"/>
@@ -19195,7 +19201,7 @@
         <v>58</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>3</v>
@@ -19208,7 +19214,7 @@
         <v>1008</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125">
@@ -19217,11 +19223,11 @@
       </c>
       <c r="L125" s="5">
         <f t="shared" si="17"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="M125" s="5">
         <f t="shared" si="18"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="N125">
         <f t="shared" si="19"/>
@@ -19236,15 +19242,15 @@
         <v>7146.72</v>
       </c>
       <c r="Q125" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R125" s="5">
         <f t="shared" si="22"/>
-        <v>46380</v>
+        <v>46373</v>
       </c>
       <c r="S125" s="5">
         <f t="shared" si="23"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="T125" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19271,7 +19277,7 @@
         <v>58</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>3</v>
@@ -19284,7 +19290,7 @@
         <v>1008</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126">
@@ -19312,7 +19318,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q126" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
@@ -19347,7 +19353,7 @@
         <v>58</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>3</v>
@@ -19360,7 +19366,7 @@
         <v>1008</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J127" s="6"/>
       <c r="K127">
@@ -19388,7 +19394,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q127" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R127" s="5">
         <f t="shared" si="22"/>
@@ -19423,7 +19429,7 @@
         <v>58</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>3</v>
@@ -19436,7 +19442,7 @@
         <v>1008</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J128" s="6"/>
       <c r="K128">
@@ -19464,7 +19470,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q128" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R128" s="5">
         <f t="shared" si="22"/>
@@ -19499,7 +19505,7 @@
         <v>58</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>3</v>
@@ -19512,7 +19518,7 @@
         <v>1008</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J129" s="6"/>
       <c r="K129">
@@ -19540,7 +19546,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q129" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R129" s="5">
         <f t="shared" si="22"/>
@@ -19575,7 +19581,7 @@
         <v>58</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>3</v>
@@ -19588,7 +19594,7 @@
         <v>1008</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J130" s="6"/>
       <c r="K130">
@@ -19616,7 +19622,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q130" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R130" s="5">
         <f t="shared" si="22"/>
@@ -19636,61 +19642,75 @@
       </c>
     </row>
     <row r="131" spans="1:21">
-      <c r="A131" t="str">
+      <c r="A131">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="B131" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="B131" s="6">
+        <v>46374</v>
+      </c>
       <c r="C131" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="7" t="str">
+        <v>vie</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G131" s="8">
+        <v>1008</v>
+      </c>
+      <c r="H131" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I131" s="9"/>
+        <v>1008</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="J131" s="6"/>
-      <c r="K131" t="str">
+      <c r="K131">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L131" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L131" s="5">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="M131" s="5" t="str">
+        <v>46377</v>
+      </c>
+      <c r="M131" s="5">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N131" t="str">
+        <v>46377</v>
+      </c>
+      <c r="N131">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="O131" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O131" s="10">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="P131" s="7" t="str">
+        <v>7.09</v>
+      </c>
+      <c r="P131" s="7">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Q131" s="9"/>
-      <c r="R131" s="5" t="str">
+        <v>7146.72</v>
+      </c>
+      <c r="Q131" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="R131" s="5">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="S131" s="5" t="str">
+        <v>46380</v>
+      </c>
+      <c r="S131" s="5">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="T131" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v/>
+        <v>46377</v>
+      </c>
+      <c r="T131" s="7">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
       </c>
       <c r="U131" t="str">
         <f t="shared" si="25"/>
@@ -19698,61 +19718,75 @@
       </c>
     </row>
     <row r="132" spans="1:21">
-      <c r="A132" t="str">
+      <c r="A132">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="B132" s="6"/>
+        <v>128</v>
+      </c>
+      <c r="B132" s="6">
+        <v>46374</v>
+      </c>
       <c r="C132" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="7" t="str">
+        <v>vie</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="8">
+        <v>1008</v>
+      </c>
+      <c r="H132" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I132" s="9"/>
+        <v>1008</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="J132" s="6"/>
-      <c r="K132" t="str">
+      <c r="K132">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="L132" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L132" s="5">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="M132" s="5" t="str">
+        <v>46377</v>
+      </c>
+      <c r="M132" s="5">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N132" t="str">
+        <v>46377</v>
+      </c>
+      <c r="N132">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="O132" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O132" s="10">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="P132" s="7" t="str">
+        <v>7.09</v>
+      </c>
+      <c r="P132" s="7">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Q132" s="9"/>
-      <c r="R132" s="5" t="str">
+        <v>7146.72</v>
+      </c>
+      <c r="Q132" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="R132" s="5">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="S132" s="5" t="str">
+        <v>46380</v>
+      </c>
+      <c r="S132" s="5">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="T132" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v/>
+        <v>46377</v>
+      </c>
+      <c r="T132" s="7">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
       </c>
       <c r="U132" t="str">
         <f t="shared" si="25"/>
@@ -19760,61 +19794,75 @@
       </c>
     </row>
     <row r="133" spans="1:21">
-      <c r="A133" t="str">
+      <c r="A133">
         <f t="shared" ref="A133:A196" si="26">IF(B133="","",ROW()-4)</f>
-        <v/>
-      </c>
-      <c r="B133" s="6"/>
+        <v>129</v>
+      </c>
+      <c r="B133" s="6">
+        <v>46374</v>
+      </c>
       <c r="C133" t="str">
         <f t="shared" ref="C133:C196" si="27">IF(B133="","",TEXT(B133,"ddd"))</f>
-        <v/>
-      </c>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="7" t="str">
+        <v>vie</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G133" s="8">
+        <v>1008</v>
+      </c>
+      <c r="H133" s="7">
         <f t="shared" ref="H133:H196" si="28">IF(B133="","",IF(G133&lt;&gt;"",G133,IFERROR(INDEX(CajasOrigen,MATCH(D133,Origenes,0)),CajasProm)))</f>
-        <v/>
-      </c>
-      <c r="I133" s="9"/>
+        <v>1008</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="J133" s="6"/>
-      <c r="K133" t="str">
+      <c r="K133">
         <f t="shared" ref="K133:K196" si="29">IF(B133="","",IFERROR(INDEX(Lags,MATCH(D133,Origenes,0)),LagBR)+IF(J133&lt;&gt;"",0,AtrasoDias))</f>
-        <v/>
-      </c>
-      <c r="L133" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L133" s="5">
         <f t="shared" ref="L133:L196" si="30">IF(B133="","",IF(J133&lt;&gt;"",J133,B133+K133))</f>
-        <v/>
-      </c>
-      <c r="M133" s="5" t="str">
+        <v>46377</v>
+      </c>
+      <c r="M133" s="5">
         <f t="shared" ref="M133:M196" si="31">IF(L133="","",IF(WEEKDAY(L133,2)=7,L133+1,L133-WEEKDAY(L133,2)+1))</f>
-        <v/>
-      </c>
-      <c r="N133" t="str">
+        <v>46377</v>
+      </c>
+      <c r="N133">
         <f t="shared" ref="N133:N196" si="32">IF(L133="","",IF(L133&gt;FechaConteo,1,0)*IF(I133="Supuesto",SupPY,IF(I133="Supuesto BR",SupBR,1)))</f>
-        <v/>
-      </c>
-      <c r="O133" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O133" s="10">
         <f t="shared" ref="O133:O196" si="33">IF(D133="","",IFERROR(INDEX(CostoOrigen,MATCH(D133,Origenes,0)),0))</f>
-        <v/>
-      </c>
-      <c r="P133" s="7" t="str">
+        <v>7.09</v>
+      </c>
+      <c r="P133" s="7">
         <f t="shared" ref="P133:P196" si="34">IF(H133="","",H133*O133)</f>
-        <v/>
-      </c>
-      <c r="Q133" s="9"/>
-      <c r="R133" s="5" t="str">
+        <v>7146.72</v>
+      </c>
+      <c r="Q133" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="R133" s="5">
         <f t="shared" ref="R133:R196" si="35">IF(B133="","",IF(J133&lt;&gt;"",J133,B133+IFERROR(INDEX(LagsP90,MATCH(D133,Origenes,0)),K133)))</f>
-        <v/>
-      </c>
-      <c r="S133" s="5" t="str">
+        <v>46380</v>
+      </c>
+      <c r="S133" s="5">
         <f t="shared" ref="S133:S196" si="36">IF(R133="","",IF(WEEKDAY(R133,2)=7,R133+1,R133-WEEKDAY(R133,2)+1))</f>
-        <v/>
-      </c>
-      <c r="T133" s="7" t="str">
-        <f t="shared" ref="T133:T196" si="37">IF(B133="","",IF(AND(B133&lt;=FechaHoy,J133="",I133&lt;&gt;"Supuesto",I133&lt;&gt;"Simulado"),H133,0))</f>
-        <v/>
+        <v>46377</v>
+      </c>
+      <c r="T133" s="7">
+        <f t="shared" ref="T133:T196" ca="1" si="37">IF(B133="","",IF(AND(B133&lt;=FechaHoy,J133="",I133&lt;&gt;"Supuesto",I133&lt;&gt;"Simulado"),H133,0))</f>
+        <v>0</v>
       </c>
       <c r="U133" t="str">
         <f t="shared" ref="U133:U196" si="38">IF(J133="","",IF(J133-B133&lt;=K133+1,1,0))</f>
@@ -30229,12 +30277,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="75">
@@ -30245,61 +30293,61 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>178</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -30443,7 +30491,7 @@
       </c>
       <c r="N7" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>OK</v>
+        <v>BAJO MINIMO (limite pasado)</v>
       </c>
       <c r="O7" s="7">
         <f>O6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L7,0)</f>
@@ -30517,19 +30565,19 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>24766</v>
+        <v>25766</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.7409411764705869</v>
+        <v>9.0938823529411756</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
@@ -30575,11 +30623,11 @@
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="2"/>
-        <v>9868</v>
+        <v>10918</v>
       </c>
       <c r="F9" s="7">
         <f>ROUND(Demanda!H9,0)</f>
@@ -30587,15 +30635,15 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>17634</v>
+        <v>18684</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>17634</v>
+        <v>19684</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30603,19 +30651,19 @@
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22634</v>
+        <v>25684</v>
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>7.9884705882352938</v>
+        <v>9.0649411764705885</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 5</v>
+        <v>CARGAR 6</v>
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
@@ -30635,11 +30683,11 @@
       </c>
       <c r="S9" s="7">
         <f>S8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N9,0)</f>
-        <v>-774</v>
+        <v>276</v>
       </c>
       <c r="T9" s="22">
         <f>IF(Demanda!N10=0,"",S9/(Demanda!N10/DiasVenta))</f>
-        <v>-3.847555923777962</v>
+        <v>1.371996685998343</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="9"/>
@@ -30657,15 +30705,15 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>17634</v>
+        <v>18684</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" si="2"/>
-        <v>12964</v>
+        <v>14014</v>
       </c>
       <c r="F10" s="7">
         <f>ROUND(Demanda!H10,0)</f>
@@ -30673,15 +30721,15 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>13598</v>
+        <v>15698</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18598</v>
+        <v>22698</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30689,19 +30737,19 @@
       </c>
       <c r="K10" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22598</v>
+        <v>25698</v>
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>7.9757647058823524</v>
+        <v>9.0698823529411765</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 4</v>
+        <v>CARGAR 3</v>
       </c>
       <c r="O10" s="7">
         <f>O9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L10,0)</f>
@@ -30721,11 +30769,11 @@
       </c>
       <c r="S10" s="7">
         <f>S9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N10,0)</f>
-        <v>-1981</v>
+        <v>119</v>
       </c>
       <c r="T10" s="22">
         <f>IF(Demanda!N11=0,"",S10/(Demanda!N11/DiasVenta))</f>
-        <v>-9.8475559237779624</v>
+        <v>0.59154929577464788</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="9"/>
@@ -30743,15 +30791,15 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>13598</v>
+        <v>15698</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" si="2"/>
-        <v>8064</v>
+        <v>9114</v>
       </c>
       <c r="F11" s="7">
         <f>ROUND(Demanda!H11,0)</f>
@@ -30759,15 +30807,15 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>4662</v>
+        <v>7812</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13662</v>
+        <v>17812</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30775,19 +30823,19 @@
       </c>
       <c r="K11" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22662</v>
+        <v>25812</v>
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>7.9983529411764698</v>
+        <v>9.1101176470588232</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="O11" s="7">
         <f>O10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L11,0)</f>
@@ -30807,11 +30855,11 @@
       </c>
       <c r="S11" s="7">
         <f>S10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N11,0)</f>
-        <v>-3188</v>
+        <v>-38</v>
       </c>
       <c r="T11" s="22">
         <f>IF(Demanda!N12=0,"",S11/(Demanda!N12/DiasVenta))</f>
-        <v>-15.847555923777962</v>
+        <v>-0.18889809444904723</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="9"/>
@@ -30829,7 +30877,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>4662</v>
+        <v>7812</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30845,7 +30893,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-4274</v>
+        <v>-1124</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
@@ -30853,7 +30901,7 @@
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13726</v>
+        <v>16876</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30865,11 +30913,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22726</v>
+        <v>25876</v>
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.020941176470588</v>
+        <v>9.1327058823529406</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30893,11 +30941,11 @@
       </c>
       <c r="S12" s="7">
         <f>S11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N12,0)</f>
-        <v>-4395</v>
+        <v>-1245</v>
       </c>
       <c r="T12" s="22">
         <f>IF(Demanda!N13=0,"",S12/(Demanda!N13/DiasVenta))</f>
-        <v>-21.847555923777964</v>
+        <v>-6.1888980944490477</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="9"/>
@@ -30915,7 +30963,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-4274</v>
+        <v>-1124</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30931,7 +30979,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-13210</v>
+        <v>-10060</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
@@ -30939,7 +30987,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13790</v>
+        <v>16940</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -30951,11 +30999,11 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22790</v>
+        <v>25940</v>
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.0435294117647054</v>
+        <v>9.1552941176470579</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30979,11 +31027,11 @@
       </c>
       <c r="S13" s="7">
         <f>S12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N13,0)</f>
-        <v>-5602</v>
+        <v>-2452</v>
       </c>
       <c r="T13" s="22">
         <f>IF(Demanda!N14=0,"",S13/(Demanda!N14/DiasVenta))</f>
-        <v>-27.847555923777964</v>
+        <v>-12.188898094449048</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="9"/>
@@ -31001,7 +31049,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-13210</v>
+        <v>-10060</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31017,7 +31065,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-22146</v>
+        <v>-18996</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
@@ -31025,7 +31073,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13854</v>
+        <v>17004</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31033,19 +31081,19 @@
       </c>
       <c r="K14" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22854</v>
+        <v>25004</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.0661176470588227</v>
+        <v>8.8249411764705883</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="O14" s="7">
         <f>O13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L14,0)</f>
@@ -31065,11 +31113,11 @@
       </c>
       <c r="S14" s="7">
         <f>S13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N14,0)</f>
-        <v>-6809</v>
+        <v>-3659</v>
       </c>
       <c r="T14" s="22">
         <f>IF(Demanda!N15=0,"",S14/(Demanda!N15/DiasVenta))</f>
-        <v>-33.847555923777961</v>
+        <v>-18.188898094449048</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="9"/>
@@ -31087,7 +31135,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-22146</v>
+        <v>-18996</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31103,15 +31151,15 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-31082</v>
+        <v>-27932</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>45000</v>
+        <v>44000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13918</v>
+        <v>16068</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31123,11 +31171,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22918</v>
+        <v>25068</v>
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.0887058823529401</v>
+        <v>8.8475294117647056</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31151,11 +31199,11 @@
       </c>
       <c r="S15" s="7">
         <f>S14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N15,0)</f>
-        <v>-8016</v>
+        <v>-4866</v>
       </c>
       <c r="T15" s="22">
         <f>IF(Demanda!N16=0,"",S15/(Demanda!N16/DiasVenta))</f>
-        <v>-39.847555923777961</v>
+        <v>-24.188898094449048</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="9"/>
@@ -31173,7 +31221,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-31082</v>
+        <v>-27932</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31189,15 +31237,15 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-40018</v>
+        <v>-36868</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>54000</v>
+        <v>53000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>13982</v>
+        <v>16132</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31209,11 +31257,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22982</v>
+        <v>25132</v>
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.1112941176470592</v>
+        <v>8.870117647058823</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31237,11 +31285,11 @@
       </c>
       <c r="S16" s="7">
         <f>S15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N16,0)</f>
-        <v>-9223</v>
+        <v>-6073</v>
       </c>
       <c r="T16" s="22">
         <f>IF(Demanda!N17=0,"",S16/(Demanda!N17/DiasVenta))</f>
-        <v>-45.847555923777961</v>
+        <v>-30.188898094449048</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="9"/>
@@ -31259,7 +31307,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-40018</v>
+        <v>-36868</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31275,15 +31323,15 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-48954</v>
+        <v>-45804</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>63000</v>
+        <v>62000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14046</v>
+        <v>16196</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31295,11 +31343,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23046</v>
+        <v>25196</v>
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.1338823529411766</v>
+        <v>8.8927058823529403</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31323,11 +31371,11 @@
       </c>
       <c r="S17" s="7">
         <f>S16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N17,0)</f>
-        <v>-10430</v>
+        <v>-7280</v>
       </c>
       <c r="T17" s="22">
         <f>IF(Demanda!N18=0,"",S17/(Demanda!N18/DiasVenta))</f>
-        <v>-51.847555923777968</v>
+        <v>-36.188898094449051</v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="9"/>
@@ -31345,7 +31393,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-48954</v>
+        <v>-45804</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31361,15 +31409,15 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-57890</v>
+        <v>-54740</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>72000</v>
+        <v>71000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>14110</v>
+        <v>16260</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31381,11 +31429,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23110</v>
+        <v>25260</v>
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.1564705882352939</v>
+        <v>8.9152941176470577</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31409,11 +31457,11 @@
       </c>
       <c r="S18" s="7">
         <f>S17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N18,0)</f>
-        <v>-11637</v>
+        <v>-8487</v>
       </c>
       <c r="T18" s="22">
         <f>IF(Demanda!N18=0,"",S18/(Demanda!N18/DiasVenta))</f>
-        <v>-57.847555923777968</v>
+        <v>-42.188898094449051</v>
       </c>
       <c r="U18" t="str">
         <f t="shared" si="9"/>
@@ -31503,41 +31551,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45">
       <c r="A5" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>178</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -31627,7 +31675,7 @@
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31635,7 +31683,7 @@
       </c>
       <c r="E8" t="str">
         <f ca="1">IF(A8="","",IF(C8&gt;0,Proyeccion!U8,"-"))</f>
-        <v>-</v>
+        <v>Bolivia</v>
       </c>
       <c r="F8" t="str">
         <f ca="1">IF(A8="","","PY mie "&amp;TEXT(Proyeccion!A8-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A8-4,"dd/mm"))</f>
@@ -31643,15 +31691,15 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.7409411764705869</v>
+        <v>9.0938823529411756</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 24.766 cajas - descargan 19 - vende 17.000 -&gt; ok</v>
+        <v>Sab 10/10: 24.766 cajas - descargan 19 - vende 17.000 -&gt; cargar 1 mas hasta el 06/10 (Bolivia; BR hasta el 07/10)</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31661,11 +31709,11 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>17634</v>
+        <v>19684</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="str">
         <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31681,15 +31729,15 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>7.9884705882352938</v>
+        <v>9.0649411764705885</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
-        <v>CARGAR 5</v>
+        <v>CARGAR 6</v>
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 17.634 cajas - descargan 10 - vende 17.000 -&gt; cargar 5 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 19.684 cajas - descargan 11 - vende 17.000 -&gt; cargar 6 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31699,11 +31747,11 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>18598</v>
+        <v>22698</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="str">
         <f ca="1">IF(A10="","","BR "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B10-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B10-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31719,15 +31767,15 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>7.9757647058823524</v>
+        <v>9.0698823529411765</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
-        <v>CARGAR 4</v>
+        <v>CARGAR 3</v>
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 18.598 cajas - descargan 13 - vende 17.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 22.698 cajas - descargan 14 - vende 17.000 -&gt; cargar 3 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31737,11 +31785,11 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>13662</v>
+        <v>17812</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="str">
         <f ca="1">IF(A11="","","BR "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B11-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B11-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31757,15 +31805,15 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>7.9983529411764698</v>
+        <v>9.1101176470588232</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 13.662 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 17.812 cajas - descargan 9 - vende 17.000 -&gt; cargar 8 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31775,7 +31823,7 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>13726</v>
+        <v>16876</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
@@ -31795,7 +31843,7 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.020941176470588</v>
+        <v>9.1327058823529406</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
@@ -31803,7 +31851,7 @@
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 13.726 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 16.876 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31813,7 +31861,7 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>13790</v>
+        <v>16940</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
@@ -31833,7 +31881,7 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.0435294117647054</v>
+        <v>9.1552941176470579</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
@@ -31841,7 +31889,7 @@
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 13.790 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 16.940 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31851,11 +31899,11 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>13854</v>
+        <v>17004</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(A14="","","BR "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B14-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B14-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31871,15 +31919,15 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.0661176470588227</v>
+        <v>8.8249411764705883</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 13.854 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 17.004 cajas - descargan 8 - vende 17.000 -&gt; cargar 8 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31889,7 +31937,7 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>13918</v>
+        <v>16068</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
@@ -31909,7 +31957,7 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.0887058823529401</v>
+        <v>8.8475294117647056</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
@@ -31917,7 +31965,7 @@
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 13.918 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 16.068 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31927,7 +31975,7 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>13982</v>
+        <v>16132</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
@@ -31947,7 +31995,7 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.1112941176470592</v>
+        <v>8.870117647058823</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
@@ -31955,7 +32003,7 @@
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 13.982 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 16.132 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -31965,7 +32013,7 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>14046</v>
+        <v>16196</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
@@ -31985,7 +32033,7 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.1338823529411766</v>
+        <v>8.8927058823529403</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
@@ -31993,7 +32041,7 @@
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 14.046 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 16.196 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32003,7 +32051,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>14110</v>
+        <v>16260</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
@@ -32023,7 +32071,7 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.1564705882352939</v>
+        <v>8.9152941176470577</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
@@ -32031,12 +32079,12 @@
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 14.110 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 16.260 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -32052,7 +32100,7 @@
     </row>
     <row r="21" spans="1:12" ht="33.950000000000003" customHeight="1">
       <c r="A21" s="44" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B21" s="44"/>
       <c r="C21" s="44"/>
@@ -32104,12 +32152,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -32127,21 +32175,21 @@
         <v>173</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B6" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32162,7 +32210,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B7" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32204,7 +32252,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B9" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32216,11 +32264,11 @@
       </c>
       <c r="D9" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>OK</v>
+        <v>BAJO MINIMO (limite pasado)</v>
       </c>
       <c r="E9" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>ok, cierra sobre 22.500</v>
+        <v>ok, cierra sobre 25.000</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -32238,21 +32286,21 @@
         <v>173</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32273,7 +32321,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32315,7 +32363,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="39" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32323,15 +32371,15 @@
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.7409411764705869</v>
+        <v>9.0938823529411756</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>ok, cierra sobre 22.500</v>
+        <v>cargar 1 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -32349,21 +32397,21 @@
         <v>173</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32384,7 +32432,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32409,45 +32457,45 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>-774</v>
+        <v>276</v>
       </c>
       <c r="C22" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>-3.847555923777962</v>
+        <v>1.371996685998343</v>
       </c>
       <c r="D22" t="str">
         <f ca="1">IF(B22="","",IF(B22&lt;0,"FALTA",IF(C22&lt;2,"CRITICO",IF(C22&lt;CoberturaObjetivo,"JUSTO",IF(C22&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>FALTA</v>
+        <v>CRITICO</v>
       </c>
       <c r="E22" t="str">
         <f ca="1">IF(D22="FALTA","se queda sin fruta: cargar ya",IF(D22="CRITICO","cargar esta semana, sin falta",IF(D22="JUSTO","priorizar este origen en los pedidos",IF(D22="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v>se queda sin fruta: cargar ya</v>
+        <v>cargar esta semana, sin falta</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>17634</v>
+        <v>19684</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>7.9884705882352938</v>
+        <v>9.0649411764705885</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>CARGAR 5</v>
+        <v>CARGAR 6</v>
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 5 camion(es) mas hasta el mar 13/10 para cerrar en 22.500</v>
+        <v>cargar 6 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -32457,7 +32505,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="45" t="str">
         <f ca="1">IF(COUNTIFS(CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1))=0,"Bolivia: no hay ningun camion en camino ni dictado. Tarda 6 dias: para que entre el sabado que viene tiene que cargar antes del "&amp;TEXT(FechaHoy-WEEKDAY(FechaHoy,2)+1+12-LagBO,"ddd dd/mm"),"Bolivia: "&amp;COUNTIFS(CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1))&amp;" camion(es) en el plan")</f>
-        <v>Bolivia: 1 camion(es) en el plan</v>
+        <v>Bolivia: 4 camion(es) en el plan</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -32613,12 +32661,12 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="45">
@@ -32629,46 +32677,46 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -32834,7 +32882,7 @@
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
@@ -32842,7 +32890,7 @@
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -32854,7 +32902,7 @@
       </c>
       <c r="M8">
         <f ca="1">IF(AND(L8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-L8)/CajasProm,0),0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -32880,7 +32928,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>9868</v>
+        <v>10918</v>
       </c>
       <c r="D9" s="7">
         <f>Proyeccion!F9</f>
@@ -32888,23 +32936,23 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>22634</v>
+        <v>23684</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17634</v>
+        <v>19684</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14634</v>
+        <v>17684</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
@@ -32912,11 +32960,11 @@
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>17804</v>
+        <v>18854</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>23634</v>
+        <v>27684</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -32924,15 +32972,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14694</v>
+        <v>16744</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>16634</v>
+        <v>18684</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>17634</v>
+        <v>18634</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -32946,7 +32994,7 @@
       </c>
       <c r="C10" s="7">
         <f>Proyeccion!E10</f>
-        <v>12964</v>
+        <v>14014</v>
       </c>
       <c r="D10" s="7">
         <f>Proyeccion!F10</f>
@@ -32954,51 +33002,51 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>20298</v>
+        <v>24398</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18598</v>
+        <v>22698</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16898</v>
+        <v>20998</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
-        <v>12964</v>
+        <v>14014</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>19598</v>
+        <v>24698</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15658</v>
+        <v>19758</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17598</v>
+        <v>21698</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18598</v>
+        <v>21648</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33012,7 +33060,7 @@
       </c>
       <c r="C11" s="7">
         <f>Proyeccion!E11</f>
-        <v>8064</v>
+        <v>9114</v>
       </c>
       <c r="D11" s="7">
         <f>Proyeccion!F11</f>
@@ -33020,51 +33068,51 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16062</v>
+        <v>19212</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13662</v>
+        <v>17812</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12262</v>
+        <v>16412</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="0"/>
-        <v>8064</v>
+        <v>9114</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13662</v>
+        <v>17812</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10722</v>
+        <v>14872</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12662</v>
+        <v>16812</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13662</v>
+        <v>16762</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33086,15 +33134,15 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15826</v>
+        <v>17976</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13726</v>
+        <v>16876</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -33102,11 +33150,11 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12626</v>
+        <v>14776</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" si="0"/>
@@ -33114,7 +33162,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13726</v>
+        <v>16876</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -33122,15 +33170,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10786</v>
+        <v>13936</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12726</v>
+        <v>15876</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13726</v>
+        <v>15826</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33152,7 +33200,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15590</v>
+        <v>18740</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -33160,7 +33208,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13790</v>
+        <v>16940</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
@@ -33168,11 +33216,11 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>11990</v>
+        <v>15140</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K13" s="7">
         <f t="shared" si="0"/>
@@ -33180,7 +33228,7 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13790</v>
+        <v>16940</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
@@ -33188,15 +33236,15 @@
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10850</v>
+        <v>14000</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12790</v>
+        <v>15940</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13790</v>
+        <v>15890</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33218,23 +33266,23 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15354</v>
+        <v>18504</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13854</v>
+        <v>17004</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12354</v>
+        <v>14504</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -33246,23 +33294,23 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13854</v>
+        <v>17004</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10914</v>
+        <v>14064</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12854</v>
+        <v>16004</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13854</v>
+        <v>15954</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33284,7 +33332,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16118</v>
+        <v>18268</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -33292,7 +33340,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13918</v>
+        <v>16068</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -33300,11 +33348,11 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12718</v>
+        <v>14868</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="0"/>
@@ -33312,7 +33360,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13918</v>
+        <v>16068</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -33320,15 +33368,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>10978</v>
+        <v>13128</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12918</v>
+        <v>15068</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13918</v>
+        <v>15018</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33350,7 +33398,7 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15882</v>
+        <v>18032</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
@@ -33358,7 +33406,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13982</v>
+        <v>16132</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -33366,11 +33414,11 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12082</v>
+        <v>15232</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" si="0"/>
@@ -33378,7 +33426,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>13982</v>
+        <v>16132</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -33386,15 +33434,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11042</v>
+        <v>13192</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>12982</v>
+        <v>15132</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13982</v>
+        <v>15082</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33416,15 +33464,15 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15646</v>
+        <v>17796</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14046</v>
+        <v>16196</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -33432,7 +33480,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12446</v>
+        <v>14596</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -33444,7 +33492,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14046</v>
+        <v>16196</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -33452,15 +33500,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11106</v>
+        <v>13256</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13046</v>
+        <v>15196</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14046</v>
+        <v>15146</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33482,15 +33530,15 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>15410</v>
+        <v>18560</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14110</v>
+        <v>16260</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -33498,11 +33546,11 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>12810</v>
+        <v>14960</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K18" s="7">
         <f t="shared" si="0"/>
@@ -33510,7 +33558,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>14110</v>
+        <v>16260</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -33518,20 +33566,20 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11170</v>
+        <v>13320</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>13110</v>
+        <v>15260</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14110</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167D7F55-B319-458B-A1CC-28D37EA6A334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0102A0E-9300-4D41-A032-F8B9C2C29FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 12:39 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 12:49 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -583,7 +583,7 @@
     <t>Gonzalo 27/09: se pide vender 16.000; Bolivia 1 carga, el resto PY y BR</t>
   </si>
   <si>
-    <t>SUPUESTO = semana anterior (confirmar)</t>
+    <t>SUPUESTO 18.000 (Gonzalo 01/10: "si sube es a 18 mil la venta, no mas"; verano)</t>
   </si>
   <si>
     <t>sin fila en ventas_plan: copia de la semana del 19/10 (SUPUESTO)</t>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="D7" s="7">
         <f>Demanda!H8</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E7" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E8" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D9" s="7">
         <f>Demanda!H10</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E9" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D10" s="7">
         <f>Demanda!H11</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E10" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D11" s="7">
         <f>Demanda!H12</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E11" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D12" s="7">
         <f>Demanda!H13</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E12" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D13" s="7">
         <f>Demanda!H14</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E13" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D14" s="7">
         <f>Demanda!H15</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E14" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D15" s="7">
         <f>Demanda!H16</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E15" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D16" s="7">
         <f>Demanda!H17</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E16" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D17" s="7">
         <f>Demanda!H18</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E17" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D18" s="7">
         <f>Demanda!H18</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E18" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>303</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.8275882352941188</v>
+        <v>8.3371666666666666</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>305</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>309</v>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="B52" s="7">
         <f ca="1">SSsugerido+ROUND(INDEX(DemVenta,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,DemSemana,0))/DiasVenta*DiasMadurar,0)</f>
-        <v>23119</v>
+        <v>24286</v>
       </c>
       <c r="E52" t="str">
         <f ca="1">"Contra el minimo de Gonzalo ("&amp;FIXED(MinimoSabado,0)&amp;"): "&amp;IF(MinSugerido&gt;MinimoSabado,"la formula pide "&amp;FIXED(MinSugerido-MinimoSabado,0)&amp;" cajas mas","la formula pide "&amp;FIXED(MinimoSabado-MinSugerido,0)&amp;" cajas menos")&amp;". El que manda en la planilla es el de la fila 5."</f>
-        <v>Contra el minimo de Gonzalo (25.000): la formula pide 1.881 cajas menos. El que manda en la planilla es el de la fila 5.</v>
+        <v>Contra el minimo de Gonzalo (25.000): la formula pide 714 cajas menos. El que manda en la planilla es el de la fila 5.</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30">
@@ -8849,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="3"/>
@@ -8858,7 +8858,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I8" s="19">
         <v>0.61699999999999999</v>
@@ -8872,15 +8872,15 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M8" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="20" t="str">
@@ -8908,7 +8908,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F9" s="10">
         <f t="shared" si="3"/>
@@ -8917,7 +8917,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I9" s="19">
         <v>0.61699999999999999</v>
@@ -8931,15 +8931,15 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="20" t="str">
@@ -8967,7 +8967,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="3"/>
@@ -8976,7 +8976,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I10" s="19">
         <v>0.61699999999999999</v>
@@ -8990,15 +8990,15 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M10" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="20" t="str">
@@ -9026,7 +9026,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F11" s="10">
         <f t="shared" si="3"/>
@@ -9035,7 +9035,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I11" s="19">
         <v>0.61699999999999999</v>
@@ -9049,15 +9049,15 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="20" t="str">
@@ -9085,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" si="3"/>
@@ -9094,7 +9094,7 @@
       <c r="G12" s="8"/>
       <c r="H12" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I12" s="19">
         <v>0.61699999999999999</v>
@@ -9108,15 +9108,15 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M12" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N12" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="20" t="str">
@@ -9144,7 +9144,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="3"/>
@@ -9153,7 +9153,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I13" s="19">
         <v>0.61699999999999999</v>
@@ -9167,15 +9167,15 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M13" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N13" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="20" t="str">
@@ -9203,7 +9203,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="3"/>
@@ -9212,7 +9212,7 @@
       <c r="G14" s="8"/>
       <c r="H14" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I14" s="19">
         <v>0.61699999999999999</v>
@@ -9226,15 +9226,15 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M14" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N14" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="20" t="str">
@@ -9262,7 +9262,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="3"/>
@@ -9271,7 +9271,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I15" s="19">
         <v>0.61699999999999999</v>
@@ -9285,15 +9285,15 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M15" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N15" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="20" t="str">
@@ -9321,7 +9321,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F16" s="10">
         <f t="shared" si="3"/>
@@ -9330,7 +9330,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I16" s="19">
         <v>0.61699999999999999</v>
@@ -9344,15 +9344,15 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M16" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N16" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="20" t="str">
@@ -9380,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F17" s="10">
         <f t="shared" si="3"/>
@@ -9389,7 +9389,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I17" s="19">
         <v>0.61699999999999999</v>
@@ -9403,15 +9403,15 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M17" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="20" t="str">
@@ -9439,7 +9439,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="8">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="F18" s="10">
         <f t="shared" si="3"/>
@@ -9448,7 +9448,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="12">
         <f t="shared" si="4"/>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I18" s="19">
         <v>0.61699999999999999</v>
@@ -9462,15 +9462,15 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="6"/>
-        <v>10489</v>
+        <v>11106</v>
       </c>
       <c r="M18" s="7">
         <f t="shared" si="7"/>
-        <v>5304</v>
+        <v>5616</v>
       </c>
       <c r="N18" s="7">
         <f t="shared" si="8"/>
-        <v>1207</v>
+        <v>1278</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="20" t="str">
@@ -30487,7 +30487,7 @@
       </c>
       <c r="M7" s="22">
         <f ca="1">IF(Demanda!H8=0,"",L7/(Demanda!H8/DiasVenta))</f>
-        <v>8.0816470588235294</v>
+        <v>7.6326666666666663</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="P7" s="22">
         <f>IF(Demanda!L8=0,"",O7/(Demanda!L8/DiasVenta))</f>
-        <v>5.1419582419677754</v>
+        <v>4.8562938951917882</v>
       </c>
       <c r="Q7" s="7">
         <f>Q6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M7,0)</f>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="R7" s="22">
         <f>IF(Demanda!M8=0,"",Q7/(Demanda!M8/DiasVenta))</f>
-        <v>13.878959276018099</v>
+        <v>13.107905982905983</v>
       </c>
       <c r="S7" s="7">
         <f>S6+SUMIFS(CgCajas,CgSemana,A7,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N7,0)</f>
@@ -30515,7 +30515,7 @@
       </c>
       <c r="T7" s="22">
         <f>IF(Demanda!N8=0,"",S7/(Demanda!N8/DiasVenta))</f>
-        <v>8.1524440762220394</v>
+        <v>7.699530516431925</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="9"/>
@@ -30545,11 +30545,11 @@
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30557,7 +30557,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30565,7 +30565,7 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30573,35 +30573,35 @@
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>9.0938823529411756</v>
+        <v>8.5886666666666667</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 1</v>
+        <v>CARGAR 2</v>
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
-        <v>12468</v>
+        <v>11851</v>
       </c>
       <c r="P8" s="22">
         <f>IF(Demanda!L9=0,"",O8/(Demanda!L9/DiasVenta))</f>
-        <v>7.1320430927638476</v>
+        <v>6.4024851431658565</v>
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
-        <v>11865</v>
+        <v>11553</v>
       </c>
       <c r="R8" s="22">
         <f>IF(Demanda!M9=0,"",Q8/(Demanda!M9/DiasVenta))</f>
-        <v>13.421945701357465</v>
+        <v>12.342948717948717</v>
       </c>
       <c r="S8" s="7">
         <f>S7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N8,0)</f>
-        <v>433</v>
+        <v>362</v>
       </c>
       <c r="T8" s="22">
         <f>IF(Demanda!N9=0,"",S8/(Demanda!N9/DiasVenta))</f>
-        <v>2.152444076222038</v>
+        <v>1.699530516431925</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="9"/>
@@ -30619,7 +30619,7 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
@@ -30631,19 +30631,19 @@
       </c>
       <c r="F9" s="7">
         <f>ROUND(Demanda!H9,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>18684</v>
+        <v>16684</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>19684</v>
+        <v>18684</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30659,35 +30659,35 @@
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>9.0649411764705885</v>
+        <v>8.5613333333333337</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 6</v>
+        <v>CARGAR 7</v>
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
-        <v>6947</v>
+        <v>5713</v>
       </c>
       <c r="P9" s="22">
         <f>IF(Demanda!L10=0,"",O9/(Demanda!L10/DiasVenta))</f>
-        <v>3.9738773953665745</v>
+        <v>3.0864397622906536</v>
       </c>
       <c r="Q9" s="7">
         <f>Q8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M9,0)</f>
-        <v>11461</v>
+        <v>10837</v>
       </c>
       <c r="R9" s="22">
         <f>IF(Demanda!M10=0,"",Q9/(Demanda!M10/DiasVenta))</f>
-        <v>12.964932126696832</v>
+        <v>11.577991452991453</v>
       </c>
       <c r="S9" s="7">
         <f>S8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N9,0)</f>
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="T9" s="22">
         <f>IF(Demanda!N10=0,"",S9/(Demanda!N10/DiasVenta))</f>
-        <v>1.371996685998343</v>
+        <v>0.62910798122065725</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="9"/>
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>18684</v>
+        <v>16684</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -30717,19 +30717,19 @@
       </c>
       <c r="F10" s="7">
         <f>ROUND(Demanda!H10,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>15698</v>
+        <v>12698</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>22698</v>
+        <v>21698</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K10" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30745,35 +30745,35 @@
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>9.0698823529411765</v>
+        <v>8.5660000000000007</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 3</v>
+        <v>CARGAR 4</v>
       </c>
       <c r="O10" s="7">
         <f>O9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L10,0)</f>
-        <v>4522</v>
+        <v>2671</v>
       </c>
       <c r="P10" s="22">
         <f>IF(Demanda!L11=0,"",O10/(Demanda!L11/DiasVenta))</f>
-        <v>2.586709886547812</v>
+        <v>1.4430037817396002</v>
       </c>
       <c r="Q10" s="7">
         <f>Q9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M10,0)</f>
-        <v>11057</v>
+        <v>10121</v>
       </c>
       <c r="R10" s="22">
         <f>IF(Demanda!M11=0,"",Q10/(Demanda!M11/DiasVenta))</f>
-        <v>12.5079185520362</v>
+        <v>10.813034188034187</v>
       </c>
       <c r="S10" s="7">
         <f>S9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N10,0)</f>
-        <v>119</v>
+        <v>-94</v>
       </c>
       <c r="T10" s="22">
         <f>IF(Demanda!N11=0,"",S10/(Demanda!N11/DiasVenta))</f>
-        <v>0.59154929577464788</v>
+        <v>-0.44131455399061031</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="9"/>
@@ -30791,7 +30791,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>15698</v>
+        <v>12698</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -30803,19 +30803,19 @@
       </c>
       <c r="F11" s="7">
         <f>ROUND(Demanda!H11,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>7812</v>
+        <v>3812</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>17812</v>
+        <v>16812</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30823,7 +30823,7 @@
       </c>
       <c r="K11" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30831,35 +30831,35 @@
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>9.1101176470588232</v>
+        <v>8.6039999999999992</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 8</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="O11" s="7">
         <f>O10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L11,0)</f>
-        <v>2097</v>
+        <v>-371</v>
       </c>
       <c r="P11" s="22">
         <f>IF(Demanda!L12=0,"",O11/(Demanda!L12/DiasVenta))</f>
-        <v>1.1995423777290495</v>
+        <v>-0.20043219881145327</v>
       </c>
       <c r="Q11" s="7">
         <f>Q10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M11,0)</f>
-        <v>5753</v>
+        <v>4505</v>
       </c>
       <c r="R11" s="22">
         <f>IF(Demanda!M12=0,"",Q11/(Demanda!M12/DiasVenta))</f>
-        <v>6.5079185520361991</v>
+        <v>4.8130341880341883</v>
       </c>
       <c r="S11" s="7">
         <f>S10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N11,0)</f>
-        <v>-38</v>
+        <v>-322</v>
       </c>
       <c r="T11" s="22">
         <f>IF(Demanda!N12=0,"",S11/(Demanda!N12/DiasVenta))</f>
-        <v>-0.18889809444904723</v>
+        <v>-1.511737089201878</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="9"/>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>7812</v>
+        <v>3812</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30889,19 +30889,19 @@
       </c>
       <c r="F12" s="7">
         <f>ROUND(Demanda!H12,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-1124</v>
+        <v>-6124</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16876</v>
+        <v>15876</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30909,7 +30909,7 @@
       </c>
       <c r="K12" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30917,35 +30917,35 @@
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>9.1327058823529406</v>
+        <v>8.6253333333333337</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O12" s="7">
         <f>O11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L12,0)</f>
-        <v>-328</v>
+        <v>-3413</v>
       </c>
       <c r="P12" s="22">
         <f>IF(Demanda!L13=0,"",O12/(Demanda!L13/DiasVenta))</f>
-        <v>-0.18762513108971302</v>
+        <v>-1.8438681793625067</v>
       </c>
       <c r="Q12" s="7">
         <f>Q11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M12,0)</f>
-        <v>449</v>
+        <v>-1111</v>
       </c>
       <c r="R12" s="22">
         <f>IF(Demanda!M13=0,"",Q12/(Demanda!M13/DiasVenta))</f>
-        <v>0.50791855203619907</v>
+        <v>-1.186965811965812</v>
       </c>
       <c r="S12" s="7">
         <f>S11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N12,0)</f>
-        <v>-1245</v>
+        <v>-1600</v>
       </c>
       <c r="T12" s="22">
         <f>IF(Demanda!N13=0,"",S12/(Demanda!N13/DiasVenta))</f>
-        <v>-6.1888980944490477</v>
+        <v>-7.511737089201878</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="9"/>
@@ -30963,7 +30963,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-1124</v>
+        <v>-6124</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30975,19 +30975,19 @@
       </c>
       <c r="F13" s="7">
         <f>ROUND(Demanda!H13,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-10060</v>
+        <v>-16060</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
-        <v>27000</v>
+        <v>32000</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16940</v>
+        <v>15940</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="K13" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31003,35 +31003,35 @@
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>9.1552941176470579</v>
+        <v>8.6466666666666665</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O13" s="7">
         <f>O12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L13,0)</f>
-        <v>-2753</v>
+        <v>-6455</v>
       </c>
       <c r="P13" s="22">
         <f>IF(Demanda!L14=0,"",O13/(Demanda!L14/DiasVenta))</f>
-        <v>-1.5747926399084755</v>
+        <v>-3.4873041599135601</v>
       </c>
       <c r="Q13" s="7">
         <f>Q12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M13,0)</f>
-        <v>-4855</v>
+        <v>-6727</v>
       </c>
       <c r="R13" s="22">
         <f>IF(Demanda!M14=0,"",Q13/(Demanda!M14/DiasVenta))</f>
-        <v>-5.4920814479638009</v>
+        <v>-7.1869658119658117</v>
       </c>
       <c r="S13" s="7">
         <f>S12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N13,0)</f>
-        <v>-2452</v>
+        <v>-2878</v>
       </c>
       <c r="T13" s="22">
         <f>IF(Demanda!N14=0,"",S13/(Demanda!N14/DiasVenta))</f>
-        <v>-12.188898094449048</v>
+        <v>-13.511737089201878</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="9"/>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-10060</v>
+        <v>-16060</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31061,19 +31061,19 @@
       </c>
       <c r="F14" s="7">
         <f>ROUND(Demanda!H14,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-18996</v>
+        <v>-25996</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
-        <v>36000</v>
+        <v>42000</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>17004</v>
+        <v>16004</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31081,7 +31081,7 @@
       </c>
       <c r="K14" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31089,35 +31089,35 @@
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.8249411764705883</v>
+        <v>8.3346666666666671</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 8</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="O14" s="7">
         <f>O13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L14,0)</f>
-        <v>-5178</v>
+        <v>-9497</v>
       </c>
       <c r="P14" s="22">
         <f>IF(Demanda!L15=0,"",O14/(Demanda!L15/DiasVenta))</f>
-        <v>-2.961960148727238</v>
+        <v>-5.1307401404646136</v>
       </c>
       <c r="Q14" s="7">
         <f>Q13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M14,0)</f>
-        <v>-10159</v>
+        <v>-12343</v>
       </c>
       <c r="R14" s="22">
         <f>IF(Demanda!M15=0,"",Q14/(Demanda!M15/DiasVenta))</f>
-        <v>-11.4920814479638</v>
+        <v>-13.186965811965813</v>
       </c>
       <c r="S14" s="7">
         <f>S13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N14,0)</f>
-        <v>-3659</v>
+        <v>-4156</v>
       </c>
       <c r="T14" s="22">
         <f>IF(Demanda!N15=0,"",S14/(Demanda!N15/DiasVenta))</f>
-        <v>-18.188898094449048</v>
+        <v>-19.511737089201876</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="9"/>
@@ -31135,7 +31135,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-18996</v>
+        <v>-25996</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31147,19 +31147,19 @@
       </c>
       <c r="F15" s="7">
         <f>ROUND(Demanda!H15,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-27932</v>
+        <v>-35932</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>44000</v>
+        <v>51000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16068</v>
+        <v>15068</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31167,7 +31167,7 @@
       </c>
       <c r="K15" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31175,35 +31175,35 @@
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.8475294117647056</v>
+        <v>8.3559999999999999</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O15" s="7">
         <f>O14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L15,0)</f>
-        <v>-7603</v>
+        <v>-12539</v>
       </c>
       <c r="P15" s="22">
         <f>IF(Demanda!L16=0,"",O15/(Demanda!L16/DiasVenta))</f>
-        <v>-4.3491276575460001</v>
+        <v>-6.7741761210156675</v>
       </c>
       <c r="Q15" s="7">
         <f>Q14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M15,0)</f>
-        <v>-15463</v>
+        <v>-17959</v>
       </c>
       <c r="R15" s="22">
         <f>IF(Demanda!M16=0,"",Q15/(Demanda!M16/DiasVenta))</f>
-        <v>-17.492081447963802</v>
+        <v>-19.186965811965813</v>
       </c>
       <c r="S15" s="7">
         <f>S14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N15,0)</f>
-        <v>-4866</v>
+        <v>-5434</v>
       </c>
       <c r="T15" s="22">
         <f>IF(Demanda!N16=0,"",S15/(Demanda!N16/DiasVenta))</f>
-        <v>-24.188898094449048</v>
+        <v>-25.511737089201876</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="9"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-27932</v>
+        <v>-35932</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31233,19 +31233,19 @@
       </c>
       <c r="F16" s="7">
         <f>ROUND(Demanda!H16,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-36868</v>
+        <v>-45868</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>53000</v>
+        <v>61000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16132</v>
+        <v>15132</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31253,7 +31253,7 @@
       </c>
       <c r="K16" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31261,35 +31261,35 @@
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.870117647058823</v>
+        <v>8.3773333333333326</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O16" s="7">
         <f>O15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L16,0)</f>
-        <v>-10028</v>
+        <v>-15581</v>
       </c>
       <c r="P16" s="22">
         <f>IF(Demanda!L17=0,"",O16/(Demanda!L17/DiasVenta))</f>
-        <v>-5.736295166364763</v>
+        <v>-8.4176121015667213</v>
       </c>
       <c r="Q16" s="7">
         <f>Q15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M16,0)</f>
-        <v>-20767</v>
+        <v>-23575</v>
       </c>
       <c r="R16" s="22">
         <f>IF(Demanda!M17=0,"",Q16/(Demanda!M17/DiasVenta))</f>
-        <v>-23.492081447963802</v>
+        <v>-25.186965811965813</v>
       </c>
       <c r="S16" s="7">
         <f>S15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N16,0)</f>
-        <v>-6073</v>
+        <v>-6712</v>
       </c>
       <c r="T16" s="22">
         <f>IF(Demanda!N17=0,"",S16/(Demanda!N17/DiasVenta))</f>
-        <v>-30.188898094449048</v>
+        <v>-31.511737089201876</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="9"/>
@@ -31307,7 +31307,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-36868</v>
+        <v>-45868</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31319,19 +31319,19 @@
       </c>
       <c r="F17" s="7">
         <f>ROUND(Demanda!H17,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-45804</v>
+        <v>-55804</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>62000</v>
+        <v>71000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16196</v>
+        <v>15196</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="K17" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31347,35 +31347,35 @@
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.8927058823529403</v>
+        <v>8.3986666666666672</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O17" s="7">
         <f>O16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L17,0)</f>
-        <v>-12453</v>
+        <v>-18623</v>
       </c>
       <c r="P17" s="22">
         <f>IF(Demanda!L18=0,"",O17/(Demanda!L18/DiasVenta))</f>
-        <v>-7.1234626751835251</v>
+        <v>-10.061048082117773</v>
       </c>
       <c r="Q17" s="7">
         <f>Q16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M17,0)</f>
-        <v>-26071</v>
+        <v>-29191</v>
       </c>
       <c r="R17" s="22">
         <f>IF(Demanda!M18=0,"",Q17/(Demanda!M18/DiasVenta))</f>
-        <v>-29.492081447963802</v>
+        <v>-31.186965811965813</v>
       </c>
       <c r="S17" s="7">
         <f>S16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N17,0)</f>
-        <v>-7280</v>
+        <v>-7990</v>
       </c>
       <c r="T17" s="22">
         <f>IF(Demanda!N18=0,"",S17/(Demanda!N18/DiasVenta))</f>
-        <v>-36.188898094449051</v>
+        <v>-37.51173708920188</v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="9"/>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-45804</v>
+        <v>-55804</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31405,19 +31405,19 @@
       </c>
       <c r="F18" s="7">
         <f>ROUND(Demanda!H18,0)</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-54740</v>
+        <v>-65740</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>71000</v>
+        <v>81000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16260</v>
+        <v>15260</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31425,7 +31425,7 @@
       </c>
       <c r="K18" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -31433,35 +31433,35 @@
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.9152941176470577</v>
+        <v>8.42</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O18" s="7">
         <f>O17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L18,0)</f>
-        <v>-14878</v>
+        <v>-21665</v>
       </c>
       <c r="P18" s="22">
         <f>IF(Demanda!L18=0,"",O18/(Demanda!L18/DiasVenta))</f>
-        <v>-8.510630184002288</v>
+        <v>-11.704484062668827</v>
       </c>
       <c r="Q18" s="7">
         <f>Q17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M18,0)</f>
-        <v>-31375</v>
+        <v>-34807</v>
       </c>
       <c r="R18" s="22">
         <f>IF(Demanda!M18=0,"",Q18/(Demanda!M18/DiasVenta))</f>
-        <v>-35.492081447963798</v>
+        <v>-37.186965811965813</v>
       </c>
       <c r="S18" s="7">
         <f>S17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N18,0)</f>
-        <v>-8487</v>
+        <v>-9268</v>
       </c>
       <c r="T18" s="22">
         <f>IF(Demanda!N18=0,"",S18/(Demanda!N18/DiasVenta))</f>
-        <v>-42.188898094449051</v>
+        <v>-43.51173708920188</v>
       </c>
       <c r="U18" t="str">
         <f t="shared" si="9"/>
@@ -31671,11 +31671,11 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31691,15 +31691,15 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>9.0938823529411756</v>
+        <v>8.5886666666666667</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
-        <v>CARGAR 1</v>
+        <v>CARGAR 2</v>
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 24.766 cajas - descargan 19 - vende 17.000 -&gt; cargar 1 mas hasta el 06/10 (Bolivia; BR hasta el 07/10)</v>
+        <v>Sab 10/10: 23.766 cajas - descargan 19 - vende 18.000 -&gt; cargar 2 mas hasta el 06/10 (Bolivia; BR hasta el 07/10)</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31709,11 +31709,11 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>19684</v>
+        <v>18684</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="str">
         <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31729,15 +31729,15 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>9.0649411764705885</v>
+        <v>8.5613333333333337</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
-        <v>CARGAR 6</v>
+        <v>CARGAR 7</v>
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 19.684 cajas - descargan 11 - vende 17.000 -&gt; cargar 6 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 18.684 cajas - descargan 11 - vende 18.000 -&gt; cargar 7 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31747,11 +31747,11 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>22698</v>
+        <v>21698</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="str">
         <f ca="1">IF(A10="","","BR "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B10-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B10-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31767,15 +31767,15 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>9.0698823529411765</v>
+        <v>8.5660000000000007</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
-        <v>CARGAR 3</v>
+        <v>CARGAR 4</v>
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 22.698 cajas - descargan 14 - vende 17.000 -&gt; cargar 3 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 21.698 cajas - descargan 14 - vende 18.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31785,11 +31785,11 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>17812</v>
+        <v>16812</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="str">
         <f ca="1">IF(A11="","","BR "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B11-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B11-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31805,15 +31805,15 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>9.1101176470588232</v>
+        <v>8.6039999999999992</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
-        <v>CARGAR 8</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 17.812 cajas - descargan 9 - vende 17.000 -&gt; cargar 8 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 16.812 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31823,11 +31823,11 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>16876</v>
+        <v>15876</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="str">
         <f ca="1">IF(A12="","","BR "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B12-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B12-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31843,15 +31843,15 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>9.1327058823529406</v>
+        <v>8.6253333333333337</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 16.876 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 15.876 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31861,11 +31861,11 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>16940</v>
+        <v>15940</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(A13="","","BR "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B13-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B13-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31881,15 +31881,15 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>9.1552941176470579</v>
+        <v>8.6466666666666665</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 16.940 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 15.940 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31899,11 +31899,11 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>17004</v>
+        <v>16004</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(A14="","","BR "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B14-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B14-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31919,15 +31919,15 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.8249411764705883</v>
+        <v>8.3346666666666671</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
-        <v>CARGAR 8</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 17.004 cajas - descargan 8 - vende 17.000 -&gt; cargar 8 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 16.004 cajas - descargan 8 - vende 18.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31937,11 +31937,11 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>16068</v>
+        <v>15068</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="str">
         <f ca="1">IF(A15="","","BR "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B15-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B15-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31957,15 +31957,15 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.8475294117647056</v>
+        <v>8.3559999999999999</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 16.068 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 15.068 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31975,11 +31975,11 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>16132</v>
+        <v>15132</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="str">
         <f ca="1">IF(A16="","","BR "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B16-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B16-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31995,15 +31995,15 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.870117647058823</v>
+        <v>8.3773333333333326</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 16.132 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 15.132 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -32013,11 +32013,11 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>16196</v>
+        <v>15196</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="str">
         <f ca="1">IF(A17="","","BR "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B17-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B17-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -32033,15 +32033,15 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.8927058823529403</v>
+        <v>8.3986666666666672</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 16.196 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 15.196 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32051,11 +32051,11 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>16260</v>
+        <v>15260</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="str">
         <f ca="1">IF(A18="","","BR "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B18-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B18-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -32071,15 +32071,15 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.9152941176470577</v>
+        <v>8.42</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 16.260 cajas - descargan 8 - vende 17.000 -&gt; cargar 9 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 15.260 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="C6" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>5.1419582419677754</v>
+        <v>4.8562938951917882</v>
       </c>
       <c r="D6" t="str">
         <f ca="1">IF(B6="","",IF(B6&lt;0,"FALTA",IF(C6&lt;2,"CRITICO",IF(C6&lt;CoberturaObjetivo,"JUSTO",IF(C6&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32218,7 +32218,7 @@
       </c>
       <c r="C7" s="22">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>13.878959276018099</v>
+        <v>13.107905982905983</v>
       </c>
       <c r="D7" t="str">
         <f ca="1">IF(B7="","",IF(B7&lt;0,"FALTA",IF(C7&lt;2,"CRITICO",IF(C7&lt;CoberturaObjetivo,"JUSTO",IF(C7&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32239,7 +32239,7 @@
       </c>
       <c r="C8" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>8.1524440762220394</v>
+        <v>7.699530516431925</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(B8="","",IF(B8&lt;0,"FALTA",IF(C8&lt;2,"CRITICO",IF(C8&lt;CoberturaObjetivo,"JUSTO",IF(C8&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32260,7 +32260,7 @@
       </c>
       <c r="C9" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
-        <v>8.0816470588235294</v>
+        <v>7.6326666666666663</v>
       </c>
       <c r="D9" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32304,19 +32304,19 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>12468</v>
+        <v>11851</v>
       </c>
       <c r="C13" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>7.1320430927638476</v>
+        <v>6.4024851431658565</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(B13="","",IF(B13&lt;0,"FALTA",IF(C13&lt;2,"CRITICO",IF(C13&lt;CoberturaObjetivo,"JUSTO",IF(C13&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>OK</v>
+        <v>JUSTO</v>
       </c>
       <c r="E13" t="str">
         <f ca="1">IF(D13="FALTA","se queda sin fruta: cargar ya",IF(D13="CRITICO","cargar esta semana, sin falta",IF(D13="JUSTO","priorizar este origen en los pedidos",IF(D13="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v/>
+        <v>priorizar este origen en los pedidos</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -32325,11 +32325,11 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>11865</v>
+        <v>11553</v>
       </c>
       <c r="C14" s="22">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>13.421945701357465</v>
+        <v>12.342948717948717</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(B14="","",IF(B14&lt;0,"FALTA",IF(C14&lt;2,"CRITICO",IF(C14&lt;CoberturaObjetivo,"JUSTO",IF(C14&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32346,19 +32346,19 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>433</v>
+        <v>362</v>
       </c>
       <c r="C15" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>2.152444076222038</v>
+        <v>1.699530516431925</v>
       </c>
       <c r="D15" t="str">
         <f ca="1">IF(B15="","",IF(B15&lt;0,"FALTA",IF(C15&lt;2,"CRITICO",IF(C15&lt;CoberturaObjetivo,"JUSTO",IF(C15&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>JUSTO</v>
+        <v>CRITICO</v>
       </c>
       <c r="E15" t="str">
         <f ca="1">IF(D15="FALTA","se queda sin fruta: cargar ya",IF(D15="CRITICO","cargar esta semana, sin falta",IF(D15="JUSTO","priorizar este origen en los pedidos",IF(D15="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v>priorizar este origen en los pedidos</v>
+        <v>cargar esta semana, sin falta</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -32367,19 +32367,19 @@
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>9.0938823529411756</v>
+        <v>8.5886666666666667</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>CARGAR 1</v>
+        <v>CARGAR 2</v>
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 1 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
+        <v>cargar 2 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -32415,11 +32415,11 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>6947</v>
+        <v>5713</v>
       </c>
       <c r="C20" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>3.9738773953665745</v>
+        <v>3.0864397622906536</v>
       </c>
       <c r="D20" t="str">
         <f ca="1">IF(B20="","",IF(B20&lt;0,"FALTA",IF(C20&lt;2,"CRITICO",IF(C20&lt;CoberturaObjetivo,"JUSTO",IF(C20&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32436,11 +32436,11 @@
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>11461</v>
+        <v>10837</v>
       </c>
       <c r="C21" s="22">
         <f ca="1">IFERROR(INDEX(PrPYd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>12.964932126696832</v>
+        <v>11.577991452991453</v>
       </c>
       <c r="D21" t="str">
         <f ca="1">IF(B21="","",IF(B21&lt;0,"FALTA",IF(C21&lt;2,"CRITICO",IF(C21&lt;CoberturaObjetivo,"JUSTO",IF(C21&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32457,11 +32457,11 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="C22" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>1.371996685998343</v>
+        <v>0.62910798122065725</v>
       </c>
       <c r="D22" t="str">
         <f ca="1">IF(B22="","",IF(B22&lt;0,"FALTA",IF(C22&lt;2,"CRITICO",IF(C22&lt;CoberturaObjetivo,"JUSTO",IF(C22&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32478,19 +32478,19 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>19684</v>
+        <v>18684</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>9.0649411764705885</v>
+        <v>8.5613333333333337</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>CARGAR 6</v>
+        <v>CARGAR 7</v>
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 6 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
+        <v>cargar 7 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
@@ -32545,7 +32545,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.830 (plan: 24.766).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 15.830 (plan: 23.766).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32866,11 +32866,11 @@
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>28066</v>
+        <v>27166</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32878,19 +32878,19 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24766</v>
+        <v>23766</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>21466</v>
+        <v>20366</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -32898,23 +32898,23 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16830</v>
+        <v>15830</v>
       </c>
       <c r="M8">
         <f ca="1">IF(AND(L8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-L8)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>21826</v>
+        <v>20826</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>23766</v>
+        <v>22766</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>24766</v>
+        <v>23766</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -32932,31 +32932,31 @@
       </c>
       <c r="D9" s="7">
         <f>Proyeccion!F9</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>23684</v>
+        <v>21884</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>19684</v>
+        <v>18684</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>17684</v>
+        <v>16484</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
@@ -32964,7 +32964,7 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>27684</v>
+        <v>26684</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -32972,15 +32972,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>16744</v>
+        <v>15744</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>18684</v>
+        <v>17684</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>18634</v>
+        <v>17634</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -32998,31 +32998,31 @@
       </c>
       <c r="D10" s="7">
         <f>Proyeccion!F10</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>24398</v>
+        <v>23698</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22698</v>
+        <v>21698</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>20998</v>
+        <v>19698</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
@@ -33030,23 +33030,23 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>24698</v>
+        <v>22698</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>19758</v>
+        <v>18758</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>21698</v>
+        <v>20698</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>21648</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33064,31 +33064,31 @@
       </c>
       <c r="D11" s="7">
         <f>Proyeccion!F11</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>19212</v>
+        <v>18612</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17812</v>
+        <v>16812</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16412</v>
+        <v>15012</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="0"/>
@@ -33096,23 +33096,23 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>17812</v>
+        <v>16812</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14872</v>
+        <v>13872</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>16812</v>
+        <v>15812</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>16762</v>
+        <v>15762</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33130,11 +33130,11 @@
       </c>
       <c r="D12" s="7">
         <f>Proyeccion!F12</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17976</v>
+        <v>17476</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -33142,19 +33142,19 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16876</v>
+        <v>15876</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14776</v>
+        <v>13276</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" si="0"/>
@@ -33162,23 +33162,23 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16876</v>
+        <v>15876</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13936</v>
+        <v>12936</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15876</v>
+        <v>14876</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15826</v>
+        <v>14826</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33196,31 +33196,31 @@
       </c>
       <c r="D13" s="7">
         <f>Proyeccion!F13</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18740</v>
+        <v>17340</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16940</v>
+        <v>15940</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>15140</v>
+        <v>13540</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K13" s="7">
         <f t="shared" si="0"/>
@@ -33228,23 +33228,23 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16940</v>
+        <v>15940</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15940</v>
+        <v>14940</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15890</v>
+        <v>14890</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33262,31 +33262,31 @@
       </c>
       <c r="D14" s="7">
         <f>Proyeccion!F14</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18504</v>
+        <v>17204</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17004</v>
+        <v>16004</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14504</v>
+        <v>13804</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="7">
         <f t="shared" si="0"/>
@@ -33294,23 +33294,23 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>17004</v>
+        <v>16004</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14064</v>
+        <v>13064</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>16004</v>
+        <v>15004</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15954</v>
+        <v>14954</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33328,27 +33328,27 @@
       </c>
       <c r="D15" s="7">
         <f>Proyeccion!F15</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18268</v>
+        <v>17068</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16068</v>
+        <v>15068</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14868</v>
+        <v>14068</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -33360,23 +33360,23 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16068</v>
+        <v>15068</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13128</v>
+        <v>12128</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15068</v>
+        <v>14068</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15018</v>
+        <v>14018</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33394,31 +33394,31 @@
       </c>
       <c r="D16" s="7">
         <f>Proyeccion!F16</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18032</v>
+        <v>16932</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16132</v>
+        <v>15132</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>15232</v>
+        <v>13332</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" si="0"/>
@@ -33426,23 +33426,23 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16132</v>
+        <v>15132</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13192</v>
+        <v>12192</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15132</v>
+        <v>14132</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15082</v>
+        <v>14082</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33460,7 +33460,7 @@
       </c>
       <c r="D17" s="7">
         <f>Proyeccion!F17</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
@@ -33472,19 +33472,19 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16196</v>
+        <v>15196</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14596</v>
+        <v>13596</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
@@ -33492,23 +33492,23 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16196</v>
+        <v>15196</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13256</v>
+        <v>12256</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15196</v>
+        <v>14196</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15146</v>
+        <v>14146</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33526,31 +33526,31 @@
       </c>
       <c r="D18" s="7">
         <f>Proyeccion!F18</f>
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18560</v>
+        <v>17660</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16260</v>
+        <v>15260</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14960</v>
+        <v>13860</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="7">
         <f t="shared" si="0"/>
@@ -33558,23 +33558,23 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16260</v>
+        <v>15260</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13320</v>
+        <v>12320</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15260</v>
+        <v>14260</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15210</v>
+        <v>14210</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0102A0E-9300-4D41-A032-F8B9C2C29FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935BD00B-2EF7-4EC9-9B16-04B00CF42E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="681">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 12:49 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 12:52 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -727,6 +727,15 @@
     <t>nota 25/09: Milciades 1, nota completa 25/09: lunes confirmado</t>
   </si>
   <si>
+    <t>Bolivia (supuesto)</t>
+  </si>
+  <si>
+    <t>Supuesto</t>
+  </si>
+  <si>
+    <t>supuesto: 1 camion BO por semana, descarga el lunes (Gonzalo 01/10)</t>
+  </si>
+  <si>
     <t>Ivo zimer</t>
   </si>
   <si>
@@ -785,15 +794,6 @@
   </si>
   <si>
     <t>nota 30/09: Milciades 2, lunes</t>
-  </si>
-  <si>
-    <t>Bolivia (supuesto)</t>
-  </si>
-  <si>
-    <t>Supuesto</t>
-  </si>
-  <si>
-    <t>supuesto: 1 camion BO por semana, descarga el lunes (Gonzalo 01/10)</t>
   </si>
   <si>
     <t>nota 30/09: tersa; transportista supuesto = semana anterior</t>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>18868</v>
+        <v>19918</v>
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>25766</v>
+        <v>25816</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>25684</v>
+        <v>25734</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>25698</v>
+        <v>25748</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>25812</v>
+        <v>25862</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>25876</v>
+        <v>25926</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>25940</v>
+        <v>25990</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>25004</v>
+        <v>25054</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>25068</v>
+        <v>25118</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>25132</v>
+        <v>25182</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>25196</v>
+        <v>25246</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>25260</v>
+        <v>25310</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>303</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.3371666666666666</v>
+        <v>8.3496666666666659</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>305</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>309</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>322</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.59175250331981477</v>
+        <v>0.58080879244751304</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>324</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.35172092021677492</v>
+        <v>0.34521628857263631</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>5.6526576463410257E-2</v>
+        <v>7.3974918979850646E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>405019.83999999979</v>
+        <v>416359.83999999973</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>328</v>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="B24" s="25">
         <f>COUNTIFS(CgEstado,"Supuesto*",CgCuenta,1)</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>330</v>
@@ -5149,7 +5149,7 @@
         <v>197</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -5216,7 +5216,7 @@
         <v>401</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -5283,7 +5283,7 @@
         <v>196</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -5350,7 +5350,7 @@
         <v>411</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5417,7 +5417,7 @@
         <v>416</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -5481,10 +5481,10 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -5551,7 +5551,7 @@
         <v>424</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -5612,7 +5612,7 @@
         <v>427</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -6409,7 +6409,7 @@
         <v>1008</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L25" s="33"/>
       <c r="M25" s="35">
@@ -7498,7 +7498,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>627</v>
@@ -10610,36 +10610,36 @@
         <v>mar</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>205</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="G12" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="4"/>
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="M12" s="5">
         <f t="shared" si="5"/>
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="N12">
         <f t="shared" si="6"/>
@@ -10647,18 +10647,18 @@
       </c>
       <c r="O12" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>207</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="9"/>
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="10"/>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="T12" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="12"/>
@@ -10686,20 +10686,20 @@
         <v>mar</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>3</v>
+        <v>209</v>
       </c>
       <c r="G13" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>199</v>
@@ -10707,11 +10707,11 @@
       <c r="J13" s="6"/>
       <c r="K13">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="4"/>
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="M13" s="5">
         <f t="shared" si="5"/>
@@ -10723,18 +10723,18 @@
       </c>
       <c r="O13" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="9"/>
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="S13" s="5">
         <f t="shared" si="10"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="T13" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="12"/>
@@ -10755,27 +10755,27 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>mar</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H14" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>199</v>
@@ -10783,7 +10783,7 @@
       <c r="J14" s="6"/>
       <c r="K14">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="4"/>
@@ -10799,18 +10799,18 @@
       </c>
       <c r="O14" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q14" s="9" t="s">
         <v>211</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="9"/>
-        <v>46301</v>
+        <v>46299</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="10"/>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="T14" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="12"/>
@@ -10882,7 +10882,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="9"/>
@@ -10917,10 +10917,10 @@
         <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G16" s="8">
         <v>1008</v>
@@ -10958,7 +10958,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R16" s="5">
         <f t="shared" si="9"/>
@@ -10983,20 +10983,20 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G17" s="8">
         <v>1008</v>
@@ -11015,11 +11015,11 @@
       </c>
       <c r="L17" s="5">
         <f t="shared" si="4"/>
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="M17" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="N17">
         <f t="shared" si="6"/>
@@ -11034,11 +11034,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R17" s="5">
         <f t="shared" si="9"/>
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="S17" s="5">
         <f t="shared" si="10"/>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="T17" s="7">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="12"/>
@@ -11069,17 +11069,17 @@
         <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G18" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>199</v>
@@ -11107,10 +11107,10 @@
       </c>
       <c r="P18" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R18" s="5">
         <f t="shared" si="9"/>
@@ -11145,17 +11145,17 @@
         <v>58</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G19" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>199</v>
@@ -11183,10 +11183,10 @@
       </c>
       <c r="P19" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="9"/>
@@ -11221,10 +11221,10 @@
         <v>58</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G20" s="8">
         <v>1008</v>
@@ -11262,7 +11262,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R20" s="5">
         <f t="shared" si="9"/>
@@ -11297,10 +11297,10 @@
         <v>58</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G21" s="8">
         <v>1008</v>
@@ -11338,7 +11338,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R21" s="5">
         <f t="shared" si="9"/>
@@ -11373,10 +11373,10 @@
         <v>58</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G22" s="8">
         <v>1008</v>
@@ -11414,7 +11414,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R22" s="5">
         <f t="shared" si="9"/>
@@ -11449,10 +11449,10 @@
         <v>58</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G23" s="8">
         <v>1008</v>
@@ -11490,7 +11490,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R23" s="5">
         <f t="shared" si="9"/>
@@ -11525,10 +11525,10 @@
         <v>58</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G24" s="8">
         <v>1008</v>
@@ -11566,7 +11566,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="R24" s="5">
         <f t="shared" si="9"/>
@@ -11591,27 +11591,27 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>3</v>
+        <v>213</v>
       </c>
       <c r="G25" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H25" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>199</v>
@@ -11619,11 +11619,11 @@
       <c r="J25" s="6"/>
       <c r="K25">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="4"/>
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="M25" s="5">
         <f t="shared" si="5"/>
@@ -11635,18 +11635,18 @@
       </c>
       <c r="O25" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P25" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" si="9"/>
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="S25" s="5">
         <f t="shared" si="10"/>
@@ -11677,7 +11677,7 @@
         <v>59</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>3</v>
@@ -11718,7 +11718,7 @@
         <v>6860</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="9"/>
@@ -11753,7 +11753,7 @@
         <v>59</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>3</v>
@@ -11794,7 +11794,7 @@
         <v>6860</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R27" s="5">
         <f t="shared" si="9"/>
@@ -11819,43 +11819,43 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>lun</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="8">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="H28" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="M28" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N28">
         <f t="shared" si="6"/>
@@ -11863,22 +11863,22 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>6860</v>
       </c>
       <c r="Q28" s="9" t="s">
         <v>227</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="9"/>
-        <v>46309</v>
+        <v>46305</v>
       </c>
       <c r="S28" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="T28" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -11902,36 +11902,36 @@
         <v>mar</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>213</v>
+        <v>3</v>
       </c>
       <c r="G29" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H29" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="4"/>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="M29" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="N29">
         <f t="shared" si="6"/>
@@ -11939,18 +11939,18 @@
       </c>
       <c r="O29" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="9"/>
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="S29" s="5">
         <f t="shared" si="10"/>
@@ -11981,10 +11981,10 @@
         <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G30" s="8">
         <v>1008</v>
@@ -12022,7 +12022,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="9"/>
@@ -12057,10 +12057,10 @@
         <v>58</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G31" s="8">
         <v>1008</v>
@@ -12098,7 +12098,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="9"/>
@@ -12130,20 +12130,20 @@
         <v>mar</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>3</v>
+        <v>213</v>
       </c>
       <c r="G32" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H32" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>199</v>
@@ -12151,11 +12151,11 @@
       <c r="J32" s="6"/>
       <c r="K32">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="4"/>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="M32" s="5">
         <f t="shared" si="5"/>
@@ -12167,18 +12167,18 @@
       </c>
       <c r="O32" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P32" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="9"/>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="S32" s="5">
         <f t="shared" si="10"/>
@@ -12209,7 +12209,7 @@
         <v>59</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>3</v>
@@ -12250,7 +12250,7 @@
         <v>6860</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="9"/>
@@ -12275,27 +12275,27 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>mar</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="G34" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>199</v>
@@ -12303,7 +12303,7 @@
       <c r="J34" s="6"/>
       <c r="K34">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="4"/>
@@ -12319,18 +12319,18 @@
       </c>
       <c r="O34" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P34" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R34" s="5">
         <f t="shared" si="9"/>
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="S34" s="5">
         <f t="shared" si="10"/>
@@ -12361,17 +12361,17 @@
         <v>58</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G35" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H35" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>199</v>
@@ -12399,10 +12399,10 @@
       </c>
       <c r="P35" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R35" s="5">
         <f t="shared" si="9"/>
@@ -12437,17 +12437,17 @@
         <v>58</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G36" s="8">
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>936</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>199</v>
@@ -12475,10 +12475,10 @@
       </c>
       <c r="P36" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6636.24</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R36" s="5">
         <f t="shared" si="9"/>
@@ -12503,20 +12503,20 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G37" s="8">
         <v>1008</v>
@@ -12535,11 +12535,11 @@
       </c>
       <c r="L37" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="M37" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N37">
         <f t="shared" si="6"/>
@@ -12554,11 +12554,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="S37" s="5">
         <f t="shared" si="10"/>
@@ -12589,10 +12589,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G38" s="8">
         <v>1008</v>
@@ -12665,10 +12665,10 @@
         <v>58</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G39" s="8">
         <v>1008</v>
@@ -12741,10 +12741,10 @@
         <v>58</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G40" s="8">
         <v>1008</v>
@@ -12807,27 +12807,27 @@
         <v>37</v>
       </c>
       <c r="B41" s="6">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="1"/>
-        <v>sáb</v>
+        <v>vie</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G41" s="8">
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>1008</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>199</v>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="L41" s="5">
         <f t="shared" si="4"/>
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="5"/>
@@ -12855,14 +12855,14 @@
       </c>
       <c r="P41" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>7146.72</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="S41" s="5">
         <f t="shared" si="10"/>
@@ -12883,39 +12883,39 @@
         <v>38</v>
       </c>
       <c r="B42" s="6">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>sáb</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>3</v>
+        <v>221</v>
       </c>
       <c r="G42" s="8">
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="H42" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>936</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="4"/>
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="M42" s="5">
         <f t="shared" si="5"/>
@@ -12927,18 +12927,18 @@
       </c>
       <c r="O42" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P42" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>6636.24</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="S42" s="5">
         <f t="shared" si="10"/>
@@ -12982,7 +12982,7 @@
         <v>980</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43">
@@ -13058,7 +13058,7 @@
         <v>980</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44">
@@ -13134,7 +13134,7 @@
         <v>980</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45">
@@ -13210,7 +13210,7 @@
         <v>980</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46">
@@ -13263,43 +13263,43 @@
         <v>43</v>
       </c>
       <c r="B47" s="6">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>lun</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="8">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="H47" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="M47" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="N47">
         <f t="shared" si="6"/>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="O47" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>6860</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="S47" s="5">
         <f t="shared" si="10"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="T47" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13339,35 +13339,35 @@
         <v>44</v>
       </c>
       <c r="B48" s="6">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mar</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H48" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L48" s="5">
         <f t="shared" si="4"/>
@@ -13383,18 +13383,18 @@
       </c>
       <c r="O48" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P48" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="S48" s="5">
         <f t="shared" si="10"/>
@@ -13947,39 +13947,39 @@
         <v>52</v>
       </c>
       <c r="B56" s="6">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>vie</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="8">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="H56" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="4"/>
-        <v>46318</v>
+        <v>46314</v>
       </c>
       <c r="M56" s="5">
         <f t="shared" si="5"/>
@@ -13991,18 +13991,18 @@
       </c>
       <c r="O56" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="P56" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>7146.72</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="S56" s="5">
         <f t="shared" si="10"/>
@@ -14046,7 +14046,7 @@
         <v>980</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57">
@@ -14122,7 +14122,7 @@
         <v>980</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58">
@@ -14198,7 +14198,7 @@
         <v>980</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59">
@@ -14274,7 +14274,7 @@
         <v>980</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60">
@@ -14327,43 +14327,43 @@
         <v>57</v>
       </c>
       <c r="B61" s="6">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>lun</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G61" s="8">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="4"/>
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="M61" s="5">
         <f t="shared" si="5"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="N61">
         <f t="shared" si="6"/>
@@ -14371,22 +14371,22 @@
       </c>
       <c r="O61" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="P61" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>6860</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="9"/>
-        <v>46323</v>
+        <v>46319</v>
       </c>
       <c r="S61" s="5">
         <f t="shared" si="10"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="T61" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14403,35 +14403,35 @@
         <v>58</v>
       </c>
       <c r="B62" s="6">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mar</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="8">
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="H62" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1050</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="4"/>
@@ -14447,18 +14447,18 @@
       </c>
       <c r="O62" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>10.8</v>
       </c>
       <c r="P62" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>11340</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="S62" s="5">
         <f t="shared" si="10"/>
@@ -15011,7 +15011,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="6">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="14"/>
@@ -15043,11 +15043,11 @@
       </c>
       <c r="L70" s="5">
         <f t="shared" si="17"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="M70" s="5">
         <f t="shared" si="18"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="N70">
         <f t="shared" si="19"/>
@@ -15066,11 +15066,11 @@
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="S70" s="5">
         <f t="shared" si="23"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="T70" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15619,7 +15619,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="6">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="14"/>
@@ -15651,11 +15651,11 @@
       </c>
       <c r="L78" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="M78" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="N78">
         <f t="shared" si="19"/>
@@ -15674,11 +15674,11 @@
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="S78" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="T78" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16227,7 +16227,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="6">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="14"/>
@@ -16259,11 +16259,11 @@
       </c>
       <c r="L86" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="M86" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="N86">
         <f t="shared" si="19"/>
@@ -16282,11 +16282,11 @@
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="S86" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="T86" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16835,7 +16835,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="6">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="14"/>
@@ -16867,11 +16867,11 @@
       </c>
       <c r="L94" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="M94" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="N94">
         <f t="shared" si="19"/>
@@ -16890,11 +16890,11 @@
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="S94" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="T94" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17443,7 +17443,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="6">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="14"/>
@@ -17475,11 +17475,11 @@
       </c>
       <c r="L102" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="M102" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="N102">
         <f t="shared" si="19"/>
@@ -17498,11 +17498,11 @@
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46352</v>
       </c>
       <c r="S102" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46349</v>
       </c>
       <c r="T102" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18051,7 +18051,7 @@
         <v>106</v>
       </c>
       <c r="B110" s="6">
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="14"/>
@@ -18083,11 +18083,11 @@
       </c>
       <c r="L110" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="M110" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="N110">
         <f t="shared" si="19"/>
@@ -18106,11 +18106,11 @@
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46359</v>
       </c>
       <c r="S110" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="T110" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18659,7 +18659,7 @@
         <v>114</v>
       </c>
       <c r="B118" s="6">
-        <v>46367</v>
+        <v>46360</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="14"/>
@@ -18691,11 +18691,11 @@
       </c>
       <c r="L118" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="M118" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="N118">
         <f t="shared" si="19"/>
@@ -18714,11 +18714,11 @@
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46366</v>
       </c>
       <c r="S118" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46363</v>
       </c>
       <c r="T118" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19267,7 +19267,7 @@
         <v>122</v>
       </c>
       <c r="B126" s="6">
-        <v>46374</v>
+        <v>46367</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="14"/>
@@ -19299,11 +19299,11 @@
       </c>
       <c r="L126" s="5">
         <f t="shared" si="17"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="M126" s="5">
         <f t="shared" si="18"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="N126">
         <f t="shared" si="19"/>
@@ -19322,11 +19322,11 @@
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
-        <v>46380</v>
+        <v>46373</v>
       </c>
       <c r="S126" s="5">
         <f t="shared" si="23"/>
-        <v>46377</v>
+        <v>46370</v>
       </c>
       <c r="T126" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19870,61 +19870,75 @@
       </c>
     </row>
     <row r="134" spans="1:21">
-      <c r="A134" t="str">
+      <c r="A134">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="B134" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="B134" s="6">
+        <v>46374</v>
+      </c>
       <c r="C134" t="str">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="7" t="str">
+        <v>vie</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G134" s="8">
+        <v>1008</v>
+      </c>
+      <c r="H134" s="7">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="I134" s="9"/>
+        <v>1008</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="J134" s="6"/>
-      <c r="K134" t="str">
+      <c r="K134">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="L134" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="L134" s="5">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="M134" s="5" t="str">
+        <v>46377</v>
+      </c>
+      <c r="M134" s="5">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N134" t="str">
+        <v>46377</v>
+      </c>
+      <c r="N134">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O134" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O134" s="10">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="P134" s="7" t="str">
+        <v>7.09</v>
+      </c>
+      <c r="P134" s="7">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q134" s="9"/>
-      <c r="R134" s="5" t="str">
+        <v>7146.72</v>
+      </c>
+      <c r="Q134" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="R134" s="5">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="S134" s="5" t="str">
+        <v>46380</v>
+      </c>
+      <c r="S134" s="5">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="T134" s="7" t="str">
-        <f t="shared" si="37"/>
-        <v/>
+        <v>46377</v>
+      </c>
+      <c r="T134" s="7">
+        <f t="shared" ca="1" si="37"/>
+        <v>0</v>
       </c>
       <c r="U134" t="str">
         <f t="shared" si="38"/>
@@ -30537,11 +30551,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="2"/>
-        <v>18868</v>
+        <v>19918</v>
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
@@ -30549,7 +30563,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30557,7 +30571,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30565,19 +30579,19 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25766</v>
+        <v>25816</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.5886666666666667</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 2</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
@@ -30597,15 +30611,15 @@
       </c>
       <c r="S8" s="7">
         <f>S7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N8,0)</f>
-        <v>362</v>
+        <v>1412</v>
       </c>
       <c r="T8" s="22">
         <f>IF(Demanda!N9=0,"",S8/(Demanda!N9/DiasVenta))</f>
-        <v>1.699530516431925</v>
+        <v>6.629107981220657</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="9"/>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -30619,7 +30633,7 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
@@ -30635,15 +30649,15 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>16684</v>
+        <v>17734</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18684</v>
+        <v>18734</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30655,11 +30669,11 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25684</v>
+        <v>25734</v>
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>8.5613333333333337</v>
+        <v>8.5779999999999994</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30683,15 +30697,15 @@
       </c>
       <c r="S9" s="7">
         <f>S8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N9,0)</f>
-        <v>134</v>
+        <v>1184</v>
       </c>
       <c r="T9" s="22">
         <f>IF(Demanda!N10=0,"",S9/(Demanda!N10/DiasVenta))</f>
-        <v>0.62910798122065725</v>
+        <v>5.55868544600939</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="9"/>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -30705,7 +30719,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>16684</v>
+        <v>17734</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -30721,15 +30735,15 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>12698</v>
+        <v>13748</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>21698</v>
+        <v>21748</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30741,11 +30755,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25698</v>
+        <v>25748</v>
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>8.5660000000000007</v>
+        <v>8.5826666666666664</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30769,15 +30783,15 @@
       </c>
       <c r="S10" s="7">
         <f>S9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N10,0)</f>
-        <v>-94</v>
+        <v>956</v>
       </c>
       <c r="T10" s="22">
         <f>IF(Demanda!N11=0,"",S10/(Demanda!N11/DiasVenta))</f>
-        <v>-0.44131455399061031</v>
+        <v>4.488262910798122</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="9"/>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -30791,7 +30805,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>12698</v>
+        <v>13748</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -30807,15 +30821,15 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>3812</v>
+        <v>4862</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16812</v>
+        <v>16862</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30827,11 +30841,11 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25812</v>
+        <v>25862</v>
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>8.6039999999999992</v>
+        <v>8.6206666666666667</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30855,15 +30869,15 @@
       </c>
       <c r="S11" s="7">
         <f>S10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N11,0)</f>
-        <v>-322</v>
+        <v>728</v>
       </c>
       <c r="T11" s="22">
         <f>IF(Demanda!N12=0,"",S11/(Demanda!N12/DiasVenta))</f>
-        <v>-1.511737089201878</v>
+        <v>3.4178403755868545</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="9"/>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -30877,7 +30891,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>3812</v>
+        <v>4862</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30893,15 +30907,15 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-6124</v>
+        <v>-5074</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15876</v>
+        <v>15926</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30913,11 +30927,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25876</v>
+        <v>25926</v>
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.6253333333333337</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30941,11 +30955,11 @@
       </c>
       <c r="S12" s="7">
         <f>S11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N12,0)</f>
-        <v>-1600</v>
+        <v>-550</v>
       </c>
       <c r="T12" s="22">
         <f>IF(Demanda!N13=0,"",S12/(Demanda!N13/DiasVenta))</f>
-        <v>-7.511737089201878</v>
+        <v>-2.5821596244131455</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="9"/>
@@ -30963,7 +30977,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-6124</v>
+        <v>-5074</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30979,15 +30993,15 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-16060</v>
+        <v>-15010</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15940</v>
+        <v>15990</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -30999,11 +31013,11 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25940</v>
+        <v>25990</v>
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.6466666666666665</v>
+        <v>8.663333333333334</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31027,11 +31041,11 @@
       </c>
       <c r="S13" s="7">
         <f>S12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N13,0)</f>
-        <v>-2878</v>
+        <v>-1828</v>
       </c>
       <c r="T13" s="22">
         <f>IF(Demanda!N14=0,"",S13/(Demanda!N14/DiasVenta))</f>
-        <v>-13.511737089201878</v>
+        <v>-8.5821596244131459</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="9"/>
@@ -31049,7 +31063,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-16060</v>
+        <v>-15010</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31065,15 +31079,15 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-25996</v>
+        <v>-24946</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
-        <v>42000</v>
+        <v>41000</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16004</v>
+        <v>16054</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31085,11 +31099,11 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25004</v>
+        <v>25054</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.3346666666666671</v>
+        <v>8.3513333333333328</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31113,11 +31127,11 @@
       </c>
       <c r="S14" s="7">
         <f>S13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N14,0)</f>
-        <v>-4156</v>
+        <v>-3106</v>
       </c>
       <c r="T14" s="22">
         <f>IF(Demanda!N15=0,"",S14/(Demanda!N15/DiasVenta))</f>
-        <v>-19.511737089201876</v>
+        <v>-14.582159624413146</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="9"/>
@@ -31135,7 +31149,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-25996</v>
+        <v>-24946</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31151,15 +31165,15 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-35932</v>
+        <v>-34882</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>51000</v>
+        <v>50000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15068</v>
+        <v>15118</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31171,11 +31185,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25068</v>
+        <v>25118</v>
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.3559999999999999</v>
+        <v>8.3726666666666674</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31199,11 +31213,11 @@
       </c>
       <c r="S15" s="7">
         <f>S14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N15,0)</f>
-        <v>-5434</v>
+        <v>-4384</v>
       </c>
       <c r="T15" s="22">
         <f>IF(Demanda!N16=0,"",S15/(Demanda!N16/DiasVenta))</f>
-        <v>-25.511737089201876</v>
+        <v>-20.582159624413144</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="9"/>
@@ -31221,7 +31235,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-35932</v>
+        <v>-34882</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31237,15 +31251,15 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-45868</v>
+        <v>-44818</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>61000</v>
+        <v>60000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15132</v>
+        <v>15182</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31257,11 +31271,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25132</v>
+        <v>25182</v>
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.3773333333333326</v>
+        <v>8.3940000000000001</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31285,11 +31299,11 @@
       </c>
       <c r="S16" s="7">
         <f>S15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N16,0)</f>
-        <v>-6712</v>
+        <v>-5662</v>
       </c>
       <c r="T16" s="22">
         <f>IF(Demanda!N17=0,"",S16/(Demanda!N17/DiasVenta))</f>
-        <v>-31.511737089201876</v>
+        <v>-26.582159624413144</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="9"/>
@@ -31307,7 +31321,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-45868</v>
+        <v>-44818</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31323,15 +31337,15 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-55804</v>
+        <v>-54754</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>71000</v>
+        <v>70000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15196</v>
+        <v>15246</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31343,11 +31357,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25196</v>
+        <v>25246</v>
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.3986666666666672</v>
+        <v>8.4153333333333329</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31371,11 +31385,11 @@
       </c>
       <c r="S17" s="7">
         <f>S16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N17,0)</f>
-        <v>-7990</v>
+        <v>-6940</v>
       </c>
       <c r="T17" s="22">
         <f>IF(Demanda!N18=0,"",S17/(Demanda!N18/DiasVenta))</f>
-        <v>-37.51173708920188</v>
+        <v>-32.582159624413144</v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="9"/>
@@ -31393,7 +31407,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-55804</v>
+        <v>-54754</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31409,15 +31423,15 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-65740</v>
+        <v>-64690</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>81000</v>
+        <v>80000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15260</v>
+        <v>15310</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31429,11 +31443,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25260</v>
+        <v>25310</v>
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.42</v>
+        <v>8.4366666666666674</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31457,11 +31471,11 @@
       </c>
       <c r="S18" s="7">
         <f>S17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BO")-ROUND(Demanda!N18,0)</f>
-        <v>-9268</v>
+        <v>-8218</v>
       </c>
       <c r="T18" s="22">
         <f>IF(Demanda!N18=0,"",S18/(Demanda!N18/DiasVenta))</f>
-        <v>-43.51173708920188</v>
+        <v>-38.582159624413144</v>
       </c>
       <c r="U18" t="str">
         <f t="shared" si="9"/>
@@ -31671,11 +31685,11 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31683,7 +31697,7 @@
       </c>
       <c r="E8" t="str">
         <f ca="1">IF(A8="","",IF(C8&gt;0,Proyeccion!U8,"-"))</f>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
       <c r="F8" t="str">
         <f ca="1">IF(A8="","","PY mie "&amp;TEXT(Proyeccion!A8-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A8-4,"dd/mm"))</f>
@@ -31691,15 +31705,15 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.5886666666666667</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
-        <v>CARGAR 2</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 23.766 cajas - descargan 19 - vende 18.000 -&gt; cargar 2 mas hasta el 06/10 (Bolivia; BR hasta el 07/10)</v>
+        <v>Sab 10/10: 24.816 cajas - descargan 20 - vende 18.000 -&gt; cargar 1 mas hasta el 06/10 (Brasil; BR hasta el 07/10)</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31709,7 +31723,7 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>18684</v>
+        <v>18734</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
@@ -31721,7 +31735,7 @@
       </c>
       <c r="E9" t="str">
         <f ca="1">IF(A9="","",IF(C9&gt;0,Proyeccion!U9,"-"))</f>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
       <c r="F9" t="str">
         <f ca="1">IF(A9="","","PY mie "&amp;TEXT(Proyeccion!A9-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A9-4,"dd/mm"))</f>
@@ -31729,7 +31743,7 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>8.5613333333333337</v>
+        <v>8.5779999999999994</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
@@ -31737,7 +31751,7 @@
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 18.684 cajas - descargan 11 - vende 18.000 -&gt; cargar 7 mas hasta el 13/10 (Bolivia; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 18.734 cajas - descargan 11 - vende 18.000 -&gt; cargar 7 mas hasta el 13/10 (Brasil; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31747,7 +31761,7 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>21698</v>
+        <v>21748</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
@@ -31759,7 +31773,7 @@
       </c>
       <c r="E10" t="str">
         <f ca="1">IF(A10="","",IF(C10&gt;0,Proyeccion!U10,"-"))</f>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
       <c r="F10" t="str">
         <f ca="1">IF(A10="","","PY mie "&amp;TEXT(Proyeccion!A10-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A10-4,"dd/mm"))</f>
@@ -31767,7 +31781,7 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>8.5660000000000007</v>
+        <v>8.5826666666666664</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
@@ -31775,7 +31789,7 @@
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 21.698 cajas - descargan 14 - vende 18.000 -&gt; cargar 4 mas hasta el 20/10 (Bolivia; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 21.748 cajas - descargan 14 - vende 18.000 -&gt; cargar 4 mas hasta el 20/10 (Brasil; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31785,7 +31799,7 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>16812</v>
+        <v>16862</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
@@ -31797,7 +31811,7 @@
       </c>
       <c r="E11" t="str">
         <f ca="1">IF(A11="","",IF(C11&gt;0,Proyeccion!U11,"-"))</f>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
       <c r="F11" t="str">
         <f ca="1">IF(A11="","","PY mie "&amp;TEXT(Proyeccion!A11-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A11-4,"dd/mm"))</f>
@@ -31805,7 +31819,7 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>8.6039999999999992</v>
+        <v>8.6206666666666667</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
@@ -31813,7 +31827,7 @@
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 16.812 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 27/10 (Bolivia; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 16.862 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 27/10 (Brasil; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31823,7 +31837,7 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>15876</v>
+        <v>15926</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
@@ -31843,7 +31857,7 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.6253333333333337</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
@@ -31851,7 +31865,7 @@
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 15.876 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 15.926 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31861,7 +31875,7 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>15940</v>
+        <v>15990</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
@@ -31881,7 +31895,7 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.6466666666666665</v>
+        <v>8.663333333333334</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
@@ -31889,7 +31903,7 @@
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 15.940 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 15.990 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31899,7 +31913,7 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>16004</v>
+        <v>16054</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
@@ -31919,7 +31933,7 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.3346666666666671</v>
+        <v>8.3513333333333328</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
@@ -31927,7 +31941,7 @@
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 16.004 cajas - descargan 8 - vende 18.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 16.054 cajas - descargan 8 - vende 18.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31937,7 +31951,7 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>15068</v>
+        <v>15118</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
@@ -31957,7 +31971,7 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.3559999999999999</v>
+        <v>8.3726666666666674</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
@@ -31965,7 +31979,7 @@
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 15.068 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 15.118 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31975,7 +31989,7 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>15132</v>
+        <v>15182</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
@@ -31995,7 +32009,7 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.3773333333333326</v>
+        <v>8.3940000000000001</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
@@ -32003,7 +32017,7 @@
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 15.132 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 15.182 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -32013,7 +32027,7 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>15196</v>
+        <v>15246</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
@@ -32033,7 +32047,7 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.3986666666666672</v>
+        <v>8.4153333333333329</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
@@ -32041,7 +32055,7 @@
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 15.196 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 15.246 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32051,7 +32065,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>15260</v>
+        <v>15310</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
@@ -32071,7 +32085,7 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.42</v>
+        <v>8.4366666666666674</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
@@ -32079,7 +32093,7 @@
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 15.260 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 15.310 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -32346,19 +32360,19 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>362</v>
+        <v>1412</v>
       </c>
       <c r="C15" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>1.699530516431925</v>
+        <v>6.629107981220657</v>
       </c>
       <c r="D15" t="str">
         <f ca="1">IF(B15="","",IF(B15&lt;0,"FALTA",IF(C15&lt;2,"CRITICO",IF(C15&lt;CoberturaObjetivo,"JUSTO",IF(C15&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>CRITICO</v>
+        <v>JUSTO</v>
       </c>
       <c r="E15" t="str">
         <f ca="1">IF(D15="FALTA","se queda sin fruta: cargar ya",IF(D15="CRITICO","cargar esta semana, sin falta",IF(D15="JUSTO","priorizar este origen en los pedidos",IF(D15="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v>cargar esta semana, sin falta</v>
+        <v>priorizar este origen en los pedidos</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -32367,19 +32381,19 @@
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.5886666666666667</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>CARGAR 2</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 2 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
+        <v>cargar 1 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -32457,19 +32471,19 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IFERROR(INDEX(PrBO,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>134</v>
+        <v>1184</v>
       </c>
       <c r="C22" s="22">
         <f ca="1">IFERROR(INDEX(PrBOd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>0.62910798122065725</v>
+        <v>5.55868544600939</v>
       </c>
       <c r="D22" t="str">
         <f ca="1">IF(B22="","",IF(B22&lt;0,"FALTA",IF(C22&lt;2,"CRITICO",IF(C22&lt;CoberturaObjetivo,"JUSTO",IF(C22&gt;VidaVerde,"EXCESO","OK")))))</f>
-        <v>CRITICO</v>
+        <v>JUSTO</v>
       </c>
       <c r="E22" t="str">
         <f ca="1">IF(D22="FALTA","se queda sin fruta: cargar ya",IF(D22="CRITICO","cargar esta semana, sin falta",IF(D22="JUSTO","priorizar este origen en los pedidos",IF(D22="EXCESO","frenar cargas: riesgo de merma",""))))</f>
-        <v>cargar esta semana, sin falta</v>
+        <v>priorizar este origen en los pedidos</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -32478,11 +32492,11 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>18684</v>
+        <v>18734</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>8.5613333333333337</v>
+        <v>8.5779999999999994</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32505,7 +32519,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="45" t="str">
         <f ca="1">IF(COUNTIFS(CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1))=0,"Bolivia: no hay ningun camion en camino ni dictado. Tarda 6 dias: para que entre el sabado que viene tiene que cargar antes del "&amp;TEXT(FechaHoy-WEEKDAY(FechaHoy,2)+1+12-LagBO,"ddd dd/mm"),"Bolivia: "&amp;COUNTIFS(CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1))&amp;" camion(es) en el plan")</f>
-        <v>Bolivia: 4 camion(es) en el plan</v>
+        <v>Bolivia: 5 camion(es) en el plan</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -32515,7 +32529,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="45" t="str">
         <f ca="1">"Paraguay: "&amp;COUNTIFS(CgEstado,"Supuesto",CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+14))&amp;" camiones SUPUESTOS en las proximas 2 semanas (todavia no dictados). El plan es firme cuando se dictan."</f>
-        <v>Paraguay: 0 camiones SUPUESTOS en las proximas 2 semanas (todavia no dictados). El plan es firme cuando se dictan.</v>
+        <v>Paraguay: 1 camiones SUPUESTOS en las proximas 2 semanas (todavia no dictados). El plan es firme cuando se dictan.</v>
       </c>
       <c r="B27" s="46"/>
       <c r="C27" s="46"/>
@@ -32545,7 +32559,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 15.830 (plan: 23.766).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.880 (plan: 24.816).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32862,7 +32876,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>18868</v>
+        <v>19918</v>
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
@@ -32870,7 +32884,7 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>27166</v>
+        <v>28216</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32878,39 +32892,39 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23766</v>
+        <v>24816</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>20366</v>
+        <v>21416</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
-        <v>15944</v>
+        <v>16994</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15830</v>
+        <v>16880</v>
       </c>
       <c r="M8">
         <f ca="1">IF(AND(L8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-L8)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>20826</v>
+        <v>21876</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>22766</v>
+        <v>23816</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
@@ -32936,15 +32950,15 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>21884</v>
+        <v>22934</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18684</v>
+        <v>18734</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
@@ -32952,7 +32966,7 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16484</v>
+        <v>16534</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
@@ -32964,7 +32978,7 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>26684</v>
+        <v>26734</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -32972,15 +32986,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15744</v>
+        <v>15794</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17684</v>
+        <v>17734</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>17634</v>
+        <v>16634</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -33002,7 +33016,7 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>23698</v>
+        <v>23748</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
@@ -33010,7 +33024,7 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>21698</v>
+        <v>21748</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
@@ -33018,7 +33032,7 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>19698</v>
+        <v>19748</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
@@ -33030,7 +33044,7 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22698</v>
+        <v>22748</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
@@ -33038,15 +33052,15 @@
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>18758</v>
+        <v>18808</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>20698</v>
+        <v>20748</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>20648</v>
+        <v>19648</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33068,7 +33082,7 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18612</v>
+        <v>18662</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
@@ -33076,7 +33090,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16812</v>
+        <v>16862</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
@@ -33084,7 +33098,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>15012</v>
+        <v>15062</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
@@ -33096,7 +33110,7 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16812</v>
+        <v>16862</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
@@ -33104,15 +33118,15 @@
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13872</v>
+        <v>13922</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15812</v>
+        <v>15862</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>15762</v>
+        <v>14762</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33134,7 +33148,7 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17476</v>
+        <v>17526</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -33142,7 +33156,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15876</v>
+        <v>15926</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -33150,7 +33164,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13276</v>
+        <v>13326</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
@@ -33162,7 +33176,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15876</v>
+        <v>15926</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -33170,15 +33184,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12936</v>
+        <v>12986</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14876</v>
+        <v>14926</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14826</v>
+        <v>13826</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33200,7 +33214,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17340</v>
+        <v>17390</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -33208,7 +33222,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15940</v>
+        <v>15990</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
@@ -33216,7 +33230,7 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13540</v>
+        <v>13590</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
@@ -33228,7 +33242,7 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15940</v>
+        <v>15990</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
@@ -33236,15 +33250,15 @@
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13000</v>
+        <v>13050</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14940</v>
+        <v>14990</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14890</v>
+        <v>13890</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33266,7 +33280,7 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17204</v>
+        <v>17254</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
@@ -33274,7 +33288,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16004</v>
+        <v>16054</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
@@ -33282,7 +33296,7 @@
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13804</v>
+        <v>13854</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -33294,7 +33308,7 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16004</v>
+        <v>16054</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
@@ -33302,15 +33316,15 @@
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13064</v>
+        <v>13114</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15004</v>
+        <v>15054</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14954</v>
+        <v>13954</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33332,7 +33346,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17068</v>
+        <v>17118</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -33340,7 +33354,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15068</v>
+        <v>15118</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -33348,7 +33362,7 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14068</v>
+        <v>14118</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -33360,7 +33374,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15068</v>
+        <v>15118</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -33368,15 +33382,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12128</v>
+        <v>12178</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14068</v>
+        <v>14118</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14018</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33398,7 +33412,7 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16932</v>
+        <v>16982</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
@@ -33406,7 +33420,7 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15132</v>
+        <v>15182</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -33414,7 +33428,7 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13332</v>
+        <v>13382</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
@@ -33426,7 +33440,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15132</v>
+        <v>15182</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -33434,15 +33448,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12192</v>
+        <v>12242</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14132</v>
+        <v>14182</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14082</v>
+        <v>13082</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33464,7 +33478,7 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17796</v>
+        <v>17846</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
@@ -33472,7 +33486,7 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15196</v>
+        <v>15246</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -33480,7 +33494,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13596</v>
+        <v>13646</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -33492,7 +33506,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15196</v>
+        <v>15246</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -33500,15 +33514,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12256</v>
+        <v>12306</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14196</v>
+        <v>14246</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14146</v>
+        <v>13146</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33530,7 +33544,7 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17660</v>
+        <v>17710</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
@@ -33538,7 +33552,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15260</v>
+        <v>15310</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -33546,7 +33560,7 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13860</v>
+        <v>13910</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
@@ -33558,7 +33572,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15260</v>
+        <v>15310</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -33566,15 +33580,15 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12320</v>
+        <v>12370</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14260</v>
+        <v>14310</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14210</v>
+        <v>13210</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935BD00B-2EF7-4EC9-9B16-04B00CF42E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F346E5D6-36FE-4E2A-ABFB-9222F388B35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="681">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 12:52 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 18:41 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -814,10 +814,10 @@
     <t>nota 01/10: cuarta (antes martes, sacada el 30/09); transportista supuesto</t>
   </si>
   <si>
+    <t>nota 01/10 (v3): cuarta (antes sexta); transportista supuesto = semana anterior</t>
+  </si>
+  <si>
     <t>nota 30/09: sexta; transportista supuesto = semana anterior</t>
-  </si>
-  <si>
-    <t>nota 30/09: sabado (descarga martes 13, suma a la semana siguiente); transportista supuesto = semana anterior</t>
   </si>
   <si>
     <t>Paraguay (supuesto)</t>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>19918</v>
+        <v>20926</v>
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>25816</v>
+        <v>25824</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>10918</v>
+        <v>8974</v>
       </c>
       <c r="D9" s="7">
         <f>Demanda!H10</f>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">Proyeccion!L9</f>
-        <v>25734</v>
+        <v>25798</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="H10" s="7">
         <f ca="1">Proyeccion!L10</f>
-        <v>25748</v>
+        <v>25812</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="H11" s="7">
         <f ca="1">Proyeccion!L11</f>
-        <v>25862</v>
+        <v>25926</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H12" s="7">
         <f ca="1">Proyeccion!L12</f>
-        <v>25926</v>
+        <v>25990</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="H13" s="7">
         <f ca="1">Proyeccion!L13</f>
-        <v>25990</v>
+        <v>25054</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H14" s="7">
         <f ca="1">Proyeccion!L14</f>
-        <v>25054</v>
+        <v>25118</v>
       </c>
       <c r="I14" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H15" s="7">
         <f ca="1">Proyeccion!L15</f>
-        <v>25118</v>
+        <v>25182</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H16" s="7">
         <f ca="1">Proyeccion!L16</f>
-        <v>25182</v>
+        <v>25246</v>
       </c>
       <c r="I16" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H17" s="7">
         <f ca="1">Proyeccion!L17</f>
-        <v>25246</v>
+        <v>25310</v>
       </c>
       <c r="I17" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="H18" s="7">
         <f ca="1">Proyeccion!L18</f>
-        <v>25310</v>
+        <v>25374</v>
       </c>
       <c r="I18" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>303</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.3496666666666659</v>
+        <v>8.3610000000000007</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>305</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B11" s="25">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>307</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>309</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>322</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.58080879244751304</v>
+        <v>0.57378223495702008</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>324</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>0.34521628857263631</v>
+        <v>0.35100286532951291</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
-        <v>7.3974918979850646E-2</v>
+        <v>7.5214899713467051E-2</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>416359.83999999973</v>
+        <v>409723.59999999974</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>328</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B27" s="25">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>336</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="s">
         <v>3</v>
@@ -12513,10 +12513,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G37" s="8">
         <v>1008</v>
@@ -12554,7 +12554,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
@@ -12579,20 +12579,20 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>mié</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="G38" s="8">
         <v>1008</v>
@@ -12611,11 +12611,11 @@
       </c>
       <c r="L38" s="5">
         <f t="shared" si="4"/>
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="M38" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="N38">
         <f t="shared" si="6"/>
@@ -12630,11 +12630,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="9"/>
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="S38" s="5">
         <f t="shared" si="10"/>
@@ -12665,10 +12665,10 @@
         <v>58</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G39" s="8">
         <v>1008</v>
@@ -12706,7 +12706,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R39" s="5">
         <f t="shared" si="9"/>
@@ -12782,7 +12782,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
@@ -12858,7 +12858,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
@@ -12883,39 +12883,39 @@
         <v>38</v>
       </c>
       <c r="B42" s="6">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="1"/>
-        <v>sáb</v>
+        <v>lun</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>221</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8">
-        <v>936</v>
+        <v>980</v>
       </c>
       <c r="H42" s="7">
         <f t="shared" si="2"/>
-        <v>936</v>
+        <v>980</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="4"/>
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="M42" s="5">
         <f t="shared" si="5"/>
@@ -12927,18 +12927,18 @@
       </c>
       <c r="O42" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P42" s="7">
         <f t="shared" si="8"/>
-        <v>6636.24</v>
+        <v>6860</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="9"/>
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="S42" s="5">
         <f t="shared" si="10"/>
@@ -13263,27 +13263,27 @@
         <v>43</v>
       </c>
       <c r="B47" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>mar</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="8">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="H47" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>206</v>
@@ -13291,15 +13291,15 @@
       <c r="J47" s="6"/>
       <c r="K47">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" si="4"/>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="M47" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="N47">
         <f t="shared" si="6"/>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="O47" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>11340</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="S47" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="T47" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13339,35 +13339,35 @@
         <v>44</v>
       </c>
       <c r="B48" s="6">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>vie</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="8">
-        <v>1050</v>
+        <v>1008</v>
       </c>
       <c r="H48" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>1008</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5">
         <f t="shared" si="4"/>
@@ -13383,18 +13383,18 @@
       </c>
       <c r="O48" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7.09</v>
       </c>
       <c r="P48" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>7146.72</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="S48" s="5">
         <f t="shared" si="10"/>
@@ -13947,39 +13947,39 @@
         <v>52</v>
       </c>
       <c r="B56" s="6">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="1"/>
-        <v>vie</v>
+        <v>lun</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="8">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="H56" s="7">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M56" s="5">
         <f t="shared" si="5"/>
@@ -13991,18 +13991,18 @@
       </c>
       <c r="O56" s="10">
         <f t="shared" si="7"/>
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="P56" s="7">
         <f t="shared" si="8"/>
-        <v>7146.72</v>
+        <v>6860</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="9"/>
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="S56" s="5">
         <f t="shared" si="10"/>
@@ -14327,27 +14327,27 @@
         <v>57</v>
       </c>
       <c r="B61" s="6">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>mar</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G61" s="8">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="I61" s="9" t="s">
         <v>206</v>
@@ -14355,15 +14355,15 @@
       <c r="J61" s="6"/>
       <c r="K61">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="4"/>
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="M61" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="N61">
         <f t="shared" si="6"/>
@@ -14371,22 +14371,22 @@
       </c>
       <c r="O61" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="P61" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>11340</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="9"/>
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="S61" s="5">
         <f t="shared" si="10"/>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="T61" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -14403,35 +14403,35 @@
         <v>58</v>
       </c>
       <c r="B62" s="6">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="1"/>
-        <v>mar</v>
+        <v>vie</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="8">
-        <v>1050</v>
+        <v>1008</v>
       </c>
       <c r="H62" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>1008</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="4"/>
@@ -14447,18 +14447,18 @@
       </c>
       <c r="O62" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7.09</v>
       </c>
       <c r="P62" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>7146.72</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="S62" s="5">
         <f t="shared" si="10"/>
@@ -15011,7 +15011,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="6">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="14"/>
@@ -15043,11 +15043,11 @@
       </c>
       <c r="L70" s="5">
         <f t="shared" si="17"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="M70" s="5">
         <f t="shared" si="18"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="N70">
         <f t="shared" si="19"/>
@@ -15066,11 +15066,11 @@
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
-        <v>46324</v>
+        <v>46331</v>
       </c>
       <c r="S70" s="5">
         <f t="shared" si="23"/>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="T70" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -15619,7 +15619,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="6">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="14"/>
@@ -15651,11 +15651,11 @@
       </c>
       <c r="L78" s="5">
         <f t="shared" si="17"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="M78" s="5">
         <f t="shared" si="18"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="N78">
         <f t="shared" si="19"/>
@@ -15674,11 +15674,11 @@
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
-        <v>46331</v>
+        <v>46338</v>
       </c>
       <c r="S78" s="5">
         <f t="shared" si="23"/>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="T78" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16227,7 +16227,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="6">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="14"/>
@@ -16259,11 +16259,11 @@
       </c>
       <c r="L86" s="5">
         <f t="shared" si="17"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="M86" s="5">
         <f t="shared" si="18"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="N86">
         <f t="shared" si="19"/>
@@ -16282,11 +16282,11 @@
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
-        <v>46338</v>
+        <v>46345</v>
       </c>
       <c r="S86" s="5">
         <f t="shared" si="23"/>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="T86" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -16835,7 +16835,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="6">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="14"/>
@@ -16867,11 +16867,11 @@
       </c>
       <c r="L94" s="5">
         <f t="shared" si="17"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="M94" s="5">
         <f t="shared" si="18"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="N94">
         <f t="shared" si="19"/>
@@ -16890,11 +16890,11 @@
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
-        <v>46345</v>
+        <v>46352</v>
       </c>
       <c r="S94" s="5">
         <f t="shared" si="23"/>
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="T94" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -17443,7 +17443,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="6">
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="14"/>
@@ -17475,11 +17475,11 @@
       </c>
       <c r="L102" s="5">
         <f t="shared" si="17"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="M102" s="5">
         <f t="shared" si="18"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="N102">
         <f t="shared" si="19"/>
@@ -17498,11 +17498,11 @@
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
-        <v>46352</v>
+        <v>46359</v>
       </c>
       <c r="S102" s="5">
         <f t="shared" si="23"/>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="T102" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18051,7 +18051,7 @@
         <v>106</v>
       </c>
       <c r="B110" s="6">
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="14"/>
@@ -18083,11 +18083,11 @@
       </c>
       <c r="L110" s="5">
         <f t="shared" si="17"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="M110" s="5">
         <f t="shared" si="18"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="N110">
         <f t="shared" si="19"/>
@@ -18106,11 +18106,11 @@
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
-        <v>46359</v>
+        <v>46366</v>
       </c>
       <c r="S110" s="5">
         <f t="shared" si="23"/>
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="T110" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -18659,7 +18659,7 @@
         <v>114</v>
       </c>
       <c r="B118" s="6">
-        <v>46360</v>
+        <v>46367</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="14"/>
@@ -18691,11 +18691,11 @@
       </c>
       <c r="L118" s="5">
         <f t="shared" si="17"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="M118" s="5">
         <f t="shared" si="18"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="N118">
         <f t="shared" si="19"/>
@@ -18714,11 +18714,11 @@
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
-        <v>46366</v>
+        <v>46373</v>
       </c>
       <c r="S118" s="5">
         <f t="shared" si="23"/>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="T118" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19267,7 +19267,7 @@
         <v>122</v>
       </c>
       <c r="B126" s="6">
-        <v>46367</v>
+        <v>46374</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="14"/>
@@ -19299,11 +19299,11 @@
       </c>
       <c r="L126" s="5">
         <f t="shared" si="17"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="M126" s="5">
         <f t="shared" si="18"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="N126">
         <f t="shared" si="19"/>
@@ -19322,11 +19322,11 @@
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
-        <v>46373</v>
+        <v>46380</v>
       </c>
       <c r="S126" s="5">
         <f t="shared" si="23"/>
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="T126" s="7">
         <f t="shared" ca="1" si="24"/>
@@ -19870,75 +19870,61 @@
       </c>
     </row>
     <row r="134" spans="1:21">
-      <c r="A134">
+      <c r="A134" t="str">
         <f t="shared" si="26"/>
-        <v>130</v>
-      </c>
-      <c r="B134" s="6">
-        <v>46374</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B134" s="6"/>
       <c r="C134" t="str">
         <f t="shared" si="27"/>
-        <v>vie</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E134" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G134" s="8">
-        <v>1008</v>
-      </c>
-      <c r="H134" s="7">
+        <v/>
+      </c>
+      <c r="D134" s="9"/>
+      <c r="E134" s="9"/>
+      <c r="F134" s="9"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="7" t="str">
         <f t="shared" si="28"/>
-        <v>1008</v>
-      </c>
-      <c r="I134" s="9" t="s">
-        <v>239</v>
-      </c>
+        <v/>
+      </c>
+      <c r="I134" s="9"/>
       <c r="J134" s="6"/>
-      <c r="K134">
+      <c r="K134" t="str">
         <f t="shared" si="29"/>
-        <v>3</v>
-      </c>
-      <c r="L134" s="5">
+        <v/>
+      </c>
+      <c r="L134" s="5" t="str">
         <f t="shared" si="30"/>
-        <v>46377</v>
-      </c>
-      <c r="M134" s="5">
+        <v/>
+      </c>
+      <c r="M134" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>46377</v>
-      </c>
-      <c r="N134">
+        <v/>
+      </c>
+      <c r="N134" t="str">
         <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="O134" s="10">
+        <v/>
+      </c>
+      <c r="O134" s="10" t="str">
         <f t="shared" si="33"/>
-        <v>7.09</v>
-      </c>
-      <c r="P134" s="7">
+        <v/>
+      </c>
+      <c r="P134" s="7" t="str">
         <f t="shared" si="34"/>
-        <v>7146.72</v>
-      </c>
-      <c r="Q134" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="R134" s="5">
+        <v/>
+      </c>
+      <c r="Q134" s="9"/>
+      <c r="R134" s="5" t="str">
         <f t="shared" si="35"/>
-        <v>46380</v>
-      </c>
-      <c r="S134" s="5">
+        <v/>
+      </c>
+      <c r="S134" s="5" t="str">
         <f t="shared" si="36"/>
-        <v>46377</v>
-      </c>
-      <c r="T134" s="7">
-        <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="T134" s="7" t="str">
+        <f t="shared" si="37"/>
+        <v/>
       </c>
       <c r="U134" t="str">
         <f t="shared" si="38"/>
@@ -30551,11 +30537,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="2"/>
-        <v>19918</v>
+        <v>20926</v>
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
@@ -30563,7 +30549,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30571,7 +30557,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30579,27 +30565,27 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25816</v>
+        <v>25824</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.6053333333333342</v>
+        <v>8.6080000000000005</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
-        <v>11851</v>
+        <v>12859</v>
       </c>
       <c r="P8" s="22">
         <f>IF(Demanda!L9=0,"",O8/(Demanda!L9/DiasVenta))</f>
-        <v>6.4024851431658565</v>
+        <v>6.9470556455969747</v>
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
@@ -30619,7 +30605,7 @@
       </c>
       <c r="U8" t="str">
         <f t="shared" si="9"/>
-        <v>Brasil</v>
+        <v>Bolivia</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -30633,15 +30619,15 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="2"/>
-        <v>10918</v>
+        <v>8974</v>
       </c>
       <c r="F9" s="7">
         <f>ROUND(Demanda!H9,0)</f>
@@ -30649,15 +30635,15 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>17734</v>
+        <v>16798</v>
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>18734</v>
+        <v>16798</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30665,27 +30651,27 @@
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25734</v>
+        <v>25798</v>
       </c>
       <c r="M9" s="22">
         <f ca="1">IF(Demanda!H10=0,"",L9/(Demanda!H10/DiasVenta))</f>
-        <v>8.5779999999999994</v>
+        <v>8.5993333333333339</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 7</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
-        <v>5713</v>
+        <v>4777</v>
       </c>
       <c r="P9" s="22">
         <f>IF(Demanda!L10=0,"",O9/(Demanda!L10/DiasVenta))</f>
-        <v>3.0864397622906536</v>
+        <v>2.5807671528903295</v>
       </c>
       <c r="Q9" s="7">
         <f>Q8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M9,0)</f>
@@ -30719,7 +30705,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" si="10"/>
-        <v>17734</v>
+        <v>16798</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
@@ -30735,15 +30721,15 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>13748</v>
+        <v>12812</v>
       </c>
       <c r="H10" s="7">
         <f ca="1">SUM($K$6:K9)*CajasProm</f>
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>21748</v>
+        <v>21812</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="5"/>
@@ -30755,11 +30741,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25748</v>
+        <v>25812</v>
       </c>
       <c r="M10" s="22">
         <f ca="1">IF(Demanda!H11=0,"",L10/(Demanda!H11/DiasVenta))</f>
-        <v>8.5826666666666664</v>
+        <v>8.6039999999999992</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30767,11 +30753,11 @@
       </c>
       <c r="O10" s="7">
         <f>O9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L10,0)</f>
-        <v>2671</v>
+        <v>1735</v>
       </c>
       <c r="P10" s="22">
         <f>IF(Demanda!L11=0,"",O10/(Demanda!L11/DiasVenta))</f>
-        <v>1.4430037817396002</v>
+        <v>0.9373311723392761</v>
       </c>
       <c r="Q10" s="7">
         <f>Q9+SUMIFS(CgCajas,CgSemana,A10,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M10,0)</f>
@@ -30805,7 +30791,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" si="10"/>
-        <v>13748</v>
+        <v>12812</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="1"/>
@@ -30821,15 +30807,15 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>4862</v>
+        <v>3926</v>
       </c>
       <c r="H11" s="7">
         <f ca="1">SUM($K$6:K10)*CajasProm</f>
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16862</v>
+        <v>16926</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="5"/>
@@ -30841,11 +30827,11 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25862</v>
+        <v>25926</v>
       </c>
       <c r="M11" s="22">
         <f ca="1">IF(Demanda!H12=0,"",L11/(Demanda!H12/DiasVenta))</f>
-        <v>8.6206666666666667</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30853,11 +30839,11 @@
       </c>
       <c r="O11" s="7">
         <f>O10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L11,0)</f>
-        <v>-371</v>
+        <v>-1307</v>
       </c>
       <c r="P11" s="22">
         <f>IF(Demanda!L12=0,"",O11/(Demanda!L12/DiasVenta))</f>
-        <v>-0.20043219881145327</v>
+        <v>-0.70610480821177746</v>
       </c>
       <c r="Q11" s="7">
         <f>Q10+SUMIFS(CgCajas,CgSemana,A11,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M11,0)</f>
@@ -30891,7 +30877,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" si="10"/>
-        <v>4862</v>
+        <v>3926</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
@@ -30907,15 +30893,15 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>-5074</v>
+        <v>-6010</v>
       </c>
       <c r="H12" s="7">
         <f ca="1">SUM($K$6:K11)*CajasProm</f>
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15926</v>
+        <v>15990</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="5"/>
@@ -30927,11 +30913,11 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25926</v>
+        <v>25990</v>
       </c>
       <c r="M12" s="22">
         <f ca="1">IF(Demanda!H13=0,"",L12/(Demanda!H13/DiasVenta))</f>
-        <v>8.6419999999999995</v>
+        <v>8.663333333333334</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -30939,11 +30925,11 @@
       </c>
       <c r="O12" s="7">
         <f>O11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L12,0)</f>
-        <v>-3413</v>
+        <v>-4349</v>
       </c>
       <c r="P12" s="22">
         <f>IF(Demanda!L13=0,"",O12/(Demanda!L13/DiasVenta))</f>
-        <v>-1.8438681793625067</v>
+        <v>-2.3495407887628308</v>
       </c>
       <c r="Q12" s="7">
         <f>Q11+SUMIFS(CgCajas,CgSemana,A12,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M12,0)</f>
@@ -30977,7 +30963,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" si="10"/>
-        <v>-5074</v>
+        <v>-6010</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
@@ -30993,15 +30979,15 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="3"/>
-        <v>-15010</v>
+        <v>-15946</v>
       </c>
       <c r="H13" s="7">
         <f ca="1">SUM($K$6:K12)*CajasProm</f>
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15990</v>
+        <v>16054</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="5"/>
@@ -31009,27 +30995,27 @@
       </c>
       <c r="K13" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25990</v>
+        <v>25054</v>
       </c>
       <c r="M13" s="22">
         <f ca="1">IF(Demanda!H14=0,"",L13/(Demanda!H14/DiasVenta))</f>
-        <v>8.663333333333334</v>
+        <v>8.3513333333333328</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 10</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="O13" s="7">
         <f>O12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L13,0)</f>
-        <v>-6455</v>
+        <v>-7391</v>
       </c>
       <c r="P13" s="22">
         <f>IF(Demanda!L14=0,"",O13/(Demanda!L14/DiasVenta))</f>
-        <v>-3.4873041599135601</v>
+        <v>-3.9929767693138842</v>
       </c>
       <c r="Q13" s="7">
         <f>Q12+SUMIFS(CgCajas,CgSemana,A13,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M13,0)</f>
@@ -31063,7 +31049,7 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" si="10"/>
-        <v>-15010</v>
+        <v>-15946</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
@@ -31079,7 +31065,7 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" si="3"/>
-        <v>-24946</v>
+        <v>-25882</v>
       </c>
       <c r="H14" s="7">
         <f ca="1">SUM($K$6:K13)*CajasProm</f>
@@ -31087,7 +31073,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16054</v>
+        <v>15118</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
@@ -31095,27 +31081,27 @@
       </c>
       <c r="K14" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25054</v>
+        <v>25118</v>
       </c>
       <c r="M14" s="22">
         <f ca="1">IF(Demanda!H15=0,"",L14/(Demanda!H15/DiasVenta))</f>
-        <v>8.3513333333333328</v>
+        <v>8.3726666666666674</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="O14" s="7">
         <f>O13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L14,0)</f>
-        <v>-9497</v>
+        <v>-10433</v>
       </c>
       <c r="P14" s="22">
         <f>IF(Demanda!L15=0,"",O14/(Demanda!L15/DiasVenta))</f>
-        <v>-5.1307401404646136</v>
+        <v>-5.6364127498649381</v>
       </c>
       <c r="Q14" s="7">
         <f>Q13+SUMIFS(CgCajas,CgSemana,A14,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M14,0)</f>
@@ -31149,7 +31135,7 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" si="10"/>
-        <v>-24946</v>
+        <v>-25882</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
@@ -31165,15 +31151,15 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="3"/>
-        <v>-34882</v>
+        <v>-35818</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">SUM($K$6:K14)*CajasProm</f>
-        <v>50000</v>
+        <v>51000</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15118</v>
+        <v>15182</v>
       </c>
       <c r="J15" s="21">
         <f t="shared" si="5"/>
@@ -31185,11 +31171,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25118</v>
+        <v>25182</v>
       </c>
       <c r="M15" s="22">
         <f ca="1">IF(Demanda!H16=0,"",L15/(Demanda!H16/DiasVenta))</f>
-        <v>8.3726666666666674</v>
+        <v>8.3940000000000001</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31197,11 +31183,11 @@
       </c>
       <c r="O15" s="7">
         <f>O14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L15,0)</f>
-        <v>-12539</v>
+        <v>-13475</v>
       </c>
       <c r="P15" s="22">
         <f>IF(Demanda!L16=0,"",O15/(Demanda!L16/DiasVenta))</f>
-        <v>-6.7741761210156675</v>
+        <v>-7.2798487304159911</v>
       </c>
       <c r="Q15" s="7">
         <f>Q14+SUMIFS(CgCajas,CgSemana,A15,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M15,0)</f>
@@ -31235,7 +31221,7 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" si="10"/>
-        <v>-34882</v>
+        <v>-35818</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
@@ -31251,15 +31237,15 @@
       </c>
       <c r="G16" s="7">
         <f t="shared" si="3"/>
-        <v>-44818</v>
+        <v>-45754</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">SUM($K$6:K15)*CajasProm</f>
-        <v>60000</v>
+        <v>61000</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15182</v>
+        <v>15246</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="5"/>
@@ -31271,11 +31257,11 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25182</v>
+        <v>25246</v>
       </c>
       <c r="M16" s="22">
         <f ca="1">IF(Demanda!H17=0,"",L16/(Demanda!H17/DiasVenta))</f>
-        <v>8.3940000000000001</v>
+        <v>8.4153333333333329</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31283,11 +31269,11 @@
       </c>
       <c r="O16" s="7">
         <f>O15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L16,0)</f>
-        <v>-15581</v>
+        <v>-16517</v>
       </c>
       <c r="P16" s="22">
         <f>IF(Demanda!L17=0,"",O16/(Demanda!L17/DiasVenta))</f>
-        <v>-8.4176121015667213</v>
+        <v>-8.9232847109670441</v>
       </c>
       <c r="Q16" s="7">
         <f>Q15+SUMIFS(CgCajas,CgSemana,A16,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M16,0)</f>
@@ -31321,7 +31307,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" si="10"/>
-        <v>-44818</v>
+        <v>-45754</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
@@ -31337,15 +31323,15 @@
       </c>
       <c r="G17" s="7">
         <f t="shared" si="3"/>
-        <v>-54754</v>
+        <v>-55690</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">SUM($K$6:K16)*CajasProm</f>
-        <v>70000</v>
+        <v>71000</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15246</v>
+        <v>15310</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="5"/>
@@ -31357,11 +31343,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25246</v>
+        <v>25310</v>
       </c>
       <c r="M17" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L17/(Demanda!H18/DiasVenta))</f>
-        <v>8.4153333333333329</v>
+        <v>8.4366666666666674</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31369,11 +31355,11 @@
       </c>
       <c r="O17" s="7">
         <f>O16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L17,0)</f>
-        <v>-18623</v>
+        <v>-19559</v>
       </c>
       <c r="P17" s="22">
         <f>IF(Demanda!L18=0,"",O17/(Demanda!L18/DiasVenta))</f>
-        <v>-10.061048082117773</v>
+        <v>-10.566720691518098</v>
       </c>
       <c r="Q17" s="7">
         <f>Q16+SUMIFS(CgCajas,CgSemana,A17,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M17,0)</f>
@@ -31407,7 +31393,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" si="10"/>
-        <v>-54754</v>
+        <v>-55690</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
@@ -31423,15 +31409,15 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" si="3"/>
-        <v>-64690</v>
+        <v>-65626</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">SUM($K$6:K17)*CajasProm</f>
-        <v>80000</v>
+        <v>81000</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>15310</v>
+        <v>15374</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="5"/>
@@ -31443,11 +31429,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25310</v>
+        <v>25374</v>
       </c>
       <c r="M18" s="22">
         <f ca="1">IF(Demanda!H18=0,"",L18/(Demanda!H18/DiasVenta))</f>
-        <v>8.4366666666666674</v>
+        <v>8.4580000000000002</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -31455,11 +31441,11 @@
       </c>
       <c r="O18" s="7">
         <f>O17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L18,0)</f>
-        <v>-21665</v>
+        <v>-22601</v>
       </c>
       <c r="P18" s="22">
         <f>IF(Demanda!L18=0,"",O18/(Demanda!L18/DiasVenta))</f>
-        <v>-11.704484062668827</v>
+        <v>-12.210156672069152</v>
       </c>
       <c r="Q18" s="7">
         <f>Q17+SUMIFS(CgCajas,CgSemana,A18,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M18,0)</f>
@@ -31685,11 +31671,11 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31697,7 +31683,7 @@
       </c>
       <c r="E8" t="str">
         <f ca="1">IF(A8="","",IF(C8&gt;0,Proyeccion!U8,"-"))</f>
-        <v>Brasil</v>
+        <v>-</v>
       </c>
       <c r="F8" t="str">
         <f ca="1">IF(A8="","","PY mie "&amp;TEXT(Proyeccion!A8-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A8-4,"dd/mm"))</f>
@@ -31705,15 +31691,15 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.6053333333333342</v>
+        <v>8.6080000000000005</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 24.816 cajas - descargan 20 - vende 18.000 -&gt; cargar 1 mas hasta el 06/10 (Brasil; BR hasta el 07/10)</v>
+        <v>Sab 10/10: 25.824 cajas - descargan 21 - vende 18.000 -&gt; ok</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31723,11 +31709,11 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>18734</v>
+        <v>16798</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" t="str">
         <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31743,15 +31729,15 @@
       </c>
       <c r="G9" s="22">
         <f ca="1">IF(A9="","",Proyeccion!M9)</f>
-        <v>8.5779999999999994</v>
+        <v>8.5993333333333339</v>
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
-        <v>CARGAR 7</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 18.734 cajas - descargan 11 - vende 18.000 -&gt; cargar 7 mas hasta el 13/10 (Brasil; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 16.798 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 13/10 (Brasil; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -31761,7 +31747,7 @@
       </c>
       <c r="B10" s="7">
         <f ca="1">IF(A10="","",Proyeccion!I10)</f>
-        <v>21748</v>
+        <v>21812</v>
       </c>
       <c r="C10" s="3">
         <f ca="1">IF(A10="","",Proyeccion!K10)</f>
@@ -31781,7 +31767,7 @@
       </c>
       <c r="G10" s="22">
         <f ca="1">IF(A10="","",Proyeccion!M10)</f>
-        <v>8.5826666666666664</v>
+        <v>8.6039999999999992</v>
       </c>
       <c r="H10" t="str">
         <f ca="1">IF(A10="","",Proyeccion!N10)</f>
@@ -31789,7 +31775,7 @@
       </c>
       <c r="I10" t="str">
         <f ca="1">IF(A10="","","Sab "&amp;TEXT(A10,"dd/mm")&amp;": "&amp;FIXED(B10,0)&amp;" cajas - descargan "&amp;Proyeccion!D10&amp;" - vende "&amp;FIXED(Proyeccion!F10,0)&amp;IF(C10&gt;0," -&gt; cargar "&amp;C10&amp;" mas hasta el "&amp;TEXT(Proyeccion!J10,"dd/mm")&amp;" ("&amp;E10&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B10-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 24/10: 21.748 cajas - descargan 14 - vende 18.000 -&gt; cargar 4 mas hasta el 20/10 (Brasil; BR hasta el 21/10)</v>
+        <v>Sab 24/10: 21.812 cajas - descargan 14 - vende 18.000 -&gt; cargar 4 mas hasta el 20/10 (Brasil; BR hasta el 21/10)</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -31799,7 +31785,7 @@
       </c>
       <c r="B11" s="7">
         <f ca="1">IF(A11="","",Proyeccion!I11)</f>
-        <v>16862</v>
+        <v>16926</v>
       </c>
       <c r="C11" s="3">
         <f ca="1">IF(A11="","",Proyeccion!K11)</f>
@@ -31819,7 +31805,7 @@
       </c>
       <c r="G11" s="22">
         <f ca="1">IF(A11="","",Proyeccion!M11)</f>
-        <v>8.6206666666666667</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="H11" t="str">
         <f ca="1">IF(A11="","",Proyeccion!N11)</f>
@@ -31827,7 +31813,7 @@
       </c>
       <c r="I11" t="str">
         <f ca="1">IF(A11="","","Sab "&amp;TEXT(A11,"dd/mm")&amp;": "&amp;FIXED(B11,0)&amp;" cajas - descargan "&amp;Proyeccion!D11&amp;" - vende "&amp;FIXED(Proyeccion!F11,0)&amp;IF(C11&gt;0," -&gt; cargar "&amp;C11&amp;" mas hasta el "&amp;TEXT(Proyeccion!J11,"dd/mm")&amp;" ("&amp;E11&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B11-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 31/10: 16.862 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 27/10 (Brasil; BR hasta el 28/10)</v>
+        <v>Sab 31/10: 16.926 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 27/10 (Brasil; BR hasta el 28/10)</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -31837,7 +31823,7 @@
       </c>
       <c r="B12" s="7">
         <f ca="1">IF(A12="","",Proyeccion!I12)</f>
-        <v>15926</v>
+        <v>15990</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">IF(A12="","",Proyeccion!K12)</f>
@@ -31857,7 +31843,7 @@
       </c>
       <c r="G12" s="22">
         <f ca="1">IF(A12="","",Proyeccion!M12)</f>
-        <v>8.6419999999999995</v>
+        <v>8.663333333333334</v>
       </c>
       <c r="H12" t="str">
         <f ca="1">IF(A12="","",Proyeccion!N12)</f>
@@ -31865,7 +31851,7 @@
       </c>
       <c r="I12" t="str">
         <f ca="1">IF(A12="","","Sab "&amp;TEXT(A12,"dd/mm")&amp;": "&amp;FIXED(B12,0)&amp;" cajas - descargan "&amp;Proyeccion!D12&amp;" - vende "&amp;FIXED(Proyeccion!F12,0)&amp;IF(C12&gt;0," -&gt; cargar "&amp;C12&amp;" mas hasta el "&amp;TEXT(Proyeccion!J12,"dd/mm")&amp;" ("&amp;E12&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B12-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 07/11: 15.926 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
+        <v>Sab 07/11: 15.990 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 03/11 (Bolivia; BR hasta el 04/11)</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -31875,11 +31861,11 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IF(A13="","",Proyeccion!I13)</f>
-        <v>15990</v>
+        <v>16054</v>
       </c>
       <c r="C13" s="3">
         <f ca="1">IF(A13="","",Proyeccion!K13)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(A13="","","BR "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B13-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B13-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31895,15 +31881,15 @@
       </c>
       <c r="G13" s="22">
         <f ca="1">IF(A13="","",Proyeccion!M13)</f>
-        <v>8.663333333333334</v>
+        <v>8.3513333333333328</v>
       </c>
       <c r="H13" t="str">
         <f ca="1">IF(A13="","",Proyeccion!N13)</f>
-        <v>CARGAR 10</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="I13" t="str">
         <f ca="1">IF(A13="","","Sab "&amp;TEXT(A13,"dd/mm")&amp;": "&amp;FIXED(B13,0)&amp;" cajas - descargan "&amp;Proyeccion!D13&amp;" - vende "&amp;FIXED(Proyeccion!F13,0)&amp;IF(C13&gt;0," -&gt; cargar "&amp;C13&amp;" mas hasta el "&amp;TEXT(Proyeccion!J13,"dd/mm")&amp;" ("&amp;E13&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B13-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 14/11: 15.990 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
+        <v>Sab 14/11: 16.054 cajas - descargan 8 - vende 18.000 -&gt; cargar 9 mas hasta el 10/11 (Bolivia; BR hasta el 11/11)</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -31913,11 +31899,11 @@
       </c>
       <c r="B14" s="7">
         <f ca="1">IF(A14="","",Proyeccion!I14)</f>
-        <v>16054</v>
+        <v>15118</v>
       </c>
       <c r="C14" s="3">
         <f ca="1">IF(A14="","",Proyeccion!K14)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="str">
         <f ca="1">IF(A14="","","BR "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B14-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B14-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31933,15 +31919,15 @@
       </c>
       <c r="G14" s="22">
         <f ca="1">IF(A14="","",Proyeccion!M14)</f>
-        <v>8.3513333333333328</v>
+        <v>8.3726666666666674</v>
       </c>
       <c r="H14" t="str">
         <f ca="1">IF(A14="","",Proyeccion!N14)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 10</v>
       </c>
       <c r="I14" t="str">
         <f ca="1">IF(A14="","","Sab "&amp;TEXT(A14,"dd/mm")&amp;": "&amp;FIXED(B14,0)&amp;" cajas - descargan "&amp;Proyeccion!D14&amp;" - vende "&amp;FIXED(Proyeccion!F14,0)&amp;IF(C14&gt;0," -&gt; cargar "&amp;C14&amp;" mas hasta el "&amp;TEXT(Proyeccion!J14,"dd/mm")&amp;" ("&amp;E14&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B14-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 21/11: 16.054 cajas - descargan 8 - vende 18.000 -&gt; cargar 9 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
+        <v>Sab 21/11: 15.118 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 17/11 (Bolivia; BR hasta el 18/11)</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -31951,7 +31937,7 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(A15="","",Proyeccion!I15)</f>
-        <v>15118</v>
+        <v>15182</v>
       </c>
       <c r="C15" s="3">
         <f ca="1">IF(A15="","",Proyeccion!K15)</f>
@@ -31971,7 +31957,7 @@
       </c>
       <c r="G15" s="22">
         <f ca="1">IF(A15="","",Proyeccion!M15)</f>
-        <v>8.3726666666666674</v>
+        <v>8.3940000000000001</v>
       </c>
       <c r="H15" t="str">
         <f ca="1">IF(A15="","",Proyeccion!N15)</f>
@@ -31979,7 +31965,7 @@
       </c>
       <c r="I15" t="str">
         <f ca="1">IF(A15="","","Sab "&amp;TEXT(A15,"dd/mm")&amp;": "&amp;FIXED(B15,0)&amp;" cajas - descargan "&amp;Proyeccion!D15&amp;" - vende "&amp;FIXED(Proyeccion!F15,0)&amp;IF(C15&gt;0," -&gt; cargar "&amp;C15&amp;" mas hasta el "&amp;TEXT(Proyeccion!J15,"dd/mm")&amp;" ("&amp;E15&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B15-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 28/11: 15.118 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
+        <v>Sab 28/11: 15.182 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 24/11 (Bolivia; BR hasta el 25/11)</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -31989,7 +31975,7 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(A16="","",Proyeccion!I16)</f>
-        <v>15182</v>
+        <v>15246</v>
       </c>
       <c r="C16" s="3">
         <f ca="1">IF(A16="","",Proyeccion!K16)</f>
@@ -32009,7 +31995,7 @@
       </c>
       <c r="G16" s="22">
         <f ca="1">IF(A16="","",Proyeccion!M16)</f>
-        <v>8.3940000000000001</v>
+        <v>8.4153333333333329</v>
       </c>
       <c r="H16" t="str">
         <f ca="1">IF(A16="","",Proyeccion!N16)</f>
@@ -32017,7 +32003,7 @@
       </c>
       <c r="I16" t="str">
         <f ca="1">IF(A16="","","Sab "&amp;TEXT(A16,"dd/mm")&amp;": "&amp;FIXED(B16,0)&amp;" cajas - descargan "&amp;Proyeccion!D16&amp;" - vende "&amp;FIXED(Proyeccion!F16,0)&amp;IF(C16&gt;0," -&gt; cargar "&amp;C16&amp;" mas hasta el "&amp;TEXT(Proyeccion!J16,"dd/mm")&amp;" ("&amp;E16&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B16-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 05/12: 15.182 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
+        <v>Sab 05/12: 15.246 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 01/12 (Bolivia; BR hasta el 02/12)</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -32027,7 +32013,7 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(A17="","",Proyeccion!I17)</f>
-        <v>15246</v>
+        <v>15310</v>
       </c>
       <c r="C17" s="3">
         <f ca="1">IF(A17="","",Proyeccion!K17)</f>
@@ -32047,7 +32033,7 @@
       </c>
       <c r="G17" s="22">
         <f ca="1">IF(A17="","",Proyeccion!M17)</f>
-        <v>8.4153333333333329</v>
+        <v>8.4366666666666674</v>
       </c>
       <c r="H17" t="str">
         <f ca="1">IF(A17="","",Proyeccion!N17)</f>
@@ -32055,7 +32041,7 @@
       </c>
       <c r="I17" t="str">
         <f ca="1">IF(A17="","","Sab "&amp;TEXT(A17,"dd/mm")&amp;": "&amp;FIXED(B17,0)&amp;" cajas - descargan "&amp;Proyeccion!D17&amp;" - vende "&amp;FIXED(Proyeccion!F17,0)&amp;IF(C17&gt;0," -&gt; cargar "&amp;C17&amp;" mas hasta el "&amp;TEXT(Proyeccion!J17,"dd/mm")&amp;" ("&amp;E17&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B17-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 12/12: 15.246 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
+        <v>Sab 12/12: 15.310 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 08/12 (Bolivia; BR hasta el 09/12)</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -32065,7 +32051,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(A18="","",Proyeccion!I18)</f>
-        <v>15310</v>
+        <v>15374</v>
       </c>
       <c r="C18" s="3">
         <f ca="1">IF(A18="","",Proyeccion!K18)</f>
@@ -32085,7 +32071,7 @@
       </c>
       <c r="G18" s="22">
         <f ca="1">IF(A18="","",Proyeccion!M18)</f>
-        <v>8.4366666666666674</v>
+        <v>8.4580000000000002</v>
       </c>
       <c r="H18" t="str">
         <f ca="1">IF(A18="","",Proyeccion!N18)</f>
@@ -32093,7 +32079,7 @@
       </c>
       <c r="I18" t="str">
         <f ca="1">IF(A18="","","Sab "&amp;TEXT(A18,"dd/mm")&amp;": "&amp;FIXED(B18,0)&amp;" cajas - descargan "&amp;Proyeccion!D18&amp;" - vende "&amp;FIXED(Proyeccion!F18,0)&amp;IF(C18&gt;0," -&gt; cargar "&amp;C18&amp;" mas hasta el "&amp;TEXT(Proyeccion!J18,"dd/mm")&amp;" ("&amp;E18&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B18-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 19/12: 15.310 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
+        <v>Sab 19/12: 15.374 cajas - descargan 8 - vende 18.000 -&gt; cargar 10 mas hasta el 15/12 (Bolivia; BR hasta el 16/12)</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -32318,11 +32304,11 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>11851</v>
+        <v>12859</v>
       </c>
       <c r="C13" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>6.4024851431658565</v>
+        <v>6.9470556455969747</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(B13="","",IF(B13&lt;0,"FALTA",IF(C13&lt;2,"CRITICO",IF(C13&lt;CoberturaObjetivo,"JUSTO",IF(C13&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32381,19 +32367,19 @@
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.6053333333333342</v>
+        <v>8.6080000000000005</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>CARGAR 1</v>
+        <v>OK</v>
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 1 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
+        <v>ok, cierra sobre 25.000</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -32429,11 +32415,11 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>5713</v>
+        <v>4777</v>
       </c>
       <c r="C20" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>3.0864397622906536</v>
+        <v>2.5807671528903295</v>
       </c>
       <c r="D20" t="str">
         <f ca="1">IF(B20="","",IF(B20&lt;0,"FALTA",IF(C20&lt;2,"CRITICO",IF(C20&lt;CoberturaObjetivo,"JUSTO",IF(C20&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32492,19 +32478,19 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>18734</v>
+        <v>16798</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>8.5779999999999994</v>
+        <v>8.5993333333333339</v>
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>CARGAR 7</v>
+        <v>CARGAR 9</v>
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 7 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
+        <v>cargar 9 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
@@ -32549,7 +32535,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="45" t="str">
         <f>"Dictados que Aloha aun no tiene: "&amp;COUNTIFS(CgEstado,"Dictado",CgCuenta,1)&amp;" camiones. Pasan a Aloha cuando se cargan en el sistema."</f>
-        <v>Dictados que Aloha aun no tiene: 32 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
+        <v>Dictados que Aloha aun no tiene: 31 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
       </c>
       <c r="B29" s="46"/>
       <c r="C29" s="46"/>
@@ -32559,7 +32545,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.880 (plan: 24.816).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.880 (plan: 25.824).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32876,7 +32862,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>19918</v>
+        <v>20926</v>
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
@@ -32884,7 +32870,7 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>28216</v>
+        <v>29224</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32892,19 +32878,19 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24816</v>
+        <v>25824</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>21416</v>
+        <v>22424</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -32920,15 +32906,15 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>21876</v>
+        <v>22884</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>23816</v>
+        <v>24824</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>23766</v>
+        <v>24774</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -32942,7 +32928,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>10918</v>
+        <v>8974</v>
       </c>
       <c r="D9" s="7">
         <f>Proyeccion!F9</f>
@@ -32950,35 +32936,35 @@
       </c>
       <c r="E9" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>22934</v>
+        <v>21998</v>
       </c>
       <c r="F9">
         <f ca="1">IF(AND(E9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-E9)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18734</v>
+        <v>16798</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>16534</v>
+        <v>14598</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>18854</v>
+        <v>17918</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>26734</v>
+        <v>25798</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
@@ -32986,15 +32972,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>15794</v>
+        <v>13858</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>17734</v>
+        <v>15798</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>16634</v>
+        <v>14698</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -33016,7 +33002,7 @@
       </c>
       <c r="E10" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>23748</v>
+        <v>23812</v>
       </c>
       <c r="F10">
         <f ca="1">IF(AND(E10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-E10)/CajasProm,0),0)</f>
@@ -33024,7 +33010,7 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>21748</v>
+        <v>21812</v>
       </c>
       <c r="H10">
         <f ca="1">IF(AND(G10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-G10)/CajasProm,0),0)</f>
@@ -33032,7 +33018,7 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>19748</v>
+        <v>19812</v>
       </c>
       <c r="J10">
         <f ca="1">IF(AND(I10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-I10)/CajasProm,0),0)</f>
@@ -33044,23 +33030,23 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>22748</v>
+        <v>21812</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>18808</v>
+        <v>18872</v>
       </c>
       <c r="O10" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>20748</v>
+        <v>20812</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>19648</v>
+        <v>19712</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -33082,7 +33068,7 @@
       </c>
       <c r="E11" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>18662</v>
+        <v>18726</v>
       </c>
       <c r="F11">
         <f ca="1">IF(AND(E11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-E11)/CajasProm,0),0)</f>
@@ -33090,7 +33076,7 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16862</v>
+        <v>16926</v>
       </c>
       <c r="H11">
         <f ca="1">IF(AND(G11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-G11)/CajasProm,0),0)</f>
@@ -33098,7 +33084,7 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>15062</v>
+        <v>15126</v>
       </c>
       <c r="J11">
         <f ca="1">IF(AND(I11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-I11)/CajasProm,0),0)</f>
@@ -33110,7 +33096,7 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16862</v>
+        <v>16926</v>
       </c>
       <c r="M11">
         <f ca="1">IF(AND(L11&lt;MinimoSabado,Proyeccion!J11&gt;=FechaHoy),ROUNDUP((MinimoSabado-L11)/CajasProm,0),0)</f>
@@ -33118,15 +33104,15 @@
       </c>
       <c r="N11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13922</v>
+        <v>13986</v>
       </c>
       <c r="O11" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15862</v>
+        <v>15926</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14762</v>
+        <v>14826</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -33148,7 +33134,7 @@
       </c>
       <c r="E12" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17526</v>
+        <v>17590</v>
       </c>
       <c r="F12">
         <f ca="1">IF(AND(E12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-E12)/CajasProm,0),0)</f>
@@ -33156,7 +33142,7 @@
       </c>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15926</v>
+        <v>15990</v>
       </c>
       <c r="H12">
         <f ca="1">IF(AND(G12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-G12)/CajasProm,0),0)</f>
@@ -33164,7 +33150,7 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13326</v>
+        <v>13390</v>
       </c>
       <c r="J12">
         <f ca="1">IF(AND(I12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-I12)/CajasProm,0),0)</f>
@@ -33176,7 +33162,7 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15926</v>
+        <v>15990</v>
       </c>
       <c r="M12">
         <f ca="1">IF(AND(L12&lt;MinimoSabado,Proyeccion!J12&gt;=FechaHoy),ROUNDUP((MinimoSabado-L12)/CajasProm,0),0)</f>
@@ -33184,15 +33170,15 @@
       </c>
       <c r="N12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12986</v>
+        <v>13050</v>
       </c>
       <c r="O12" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14926</v>
+        <v>14990</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13826</v>
+        <v>13890</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -33214,7 +33200,7 @@
       </c>
       <c r="E13" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17390</v>
+        <v>17454</v>
       </c>
       <c r="F13">
         <f ca="1">IF(AND(E13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-E13)/CajasProm,0),0)</f>
@@ -33222,15 +33208,15 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15990</v>
+        <v>16054</v>
       </c>
       <c r="H13">
         <f ca="1">IF(AND(G13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-G13)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13590</v>
+        <v>13654</v>
       </c>
       <c r="J13">
         <f ca="1">IF(AND(I13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-I13)/CajasProm,0),0)</f>
@@ -33242,23 +33228,23 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15990</v>
+        <v>16054</v>
       </c>
       <c r="M13">
         <f ca="1">IF(AND(L13&lt;MinimoSabado,Proyeccion!J13&gt;=FechaHoy),ROUNDUP((MinimoSabado-L13)/CajasProm,0),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13050</v>
+        <v>13114</v>
       </c>
       <c r="O13" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14990</v>
+        <v>15054</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13890</v>
+        <v>13954</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -33280,7 +33266,7 @@
       </c>
       <c r="E14" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17254</v>
+        <v>17318</v>
       </c>
       <c r="F14">
         <f ca="1">IF(AND(E14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-E14)/CajasProm,0),0)</f>
@@ -33288,15 +33274,15 @@
       </c>
       <c r="G14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16054</v>
+        <v>15118</v>
       </c>
       <c r="H14">
         <f ca="1">IF(AND(G14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-G14)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13854</v>
+        <v>13918</v>
       </c>
       <c r="J14">
         <f ca="1">IF(AND(I14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-I14)/CajasProm,0),0)</f>
@@ -33308,23 +33294,23 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>16054</v>
+        <v>15118</v>
       </c>
       <c r="M14">
         <f ca="1">IF(AND(L14&lt;MinimoSabado,Proyeccion!J14&gt;=FechaHoy),ROUNDUP((MinimoSabado-L14)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13114</v>
+        <v>12178</v>
       </c>
       <c r="O14" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15054</v>
+        <v>14118</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13954</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -33346,7 +33332,7 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17118</v>
+        <v>17182</v>
       </c>
       <c r="F15">
         <f ca="1">IF(AND(E15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-E15)/CajasProm,0),0)</f>
@@ -33354,7 +33340,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15118</v>
+        <v>15182</v>
       </c>
       <c r="H15">
         <f ca="1">IF(AND(G15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-G15)/CajasProm,0),0)</f>
@@ -33362,7 +33348,7 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14118</v>
+        <v>14182</v>
       </c>
       <c r="J15">
         <f ca="1">IF(AND(I15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-I15)/CajasProm,0),0)</f>
@@ -33374,7 +33360,7 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15118</v>
+        <v>15182</v>
       </c>
       <c r="M15">
         <f ca="1">IF(AND(L15&lt;MinimoSabado,Proyeccion!J15&gt;=FechaHoy),ROUNDUP((MinimoSabado-L15)/CajasProm,0),0)</f>
@@ -33382,15 +33368,15 @@
       </c>
       <c r="N15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12178</v>
+        <v>12242</v>
       </c>
       <c r="O15" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14118</v>
+        <v>14182</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13018</v>
+        <v>13082</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -33412,15 +33398,15 @@
       </c>
       <c r="E16" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>16982</v>
+        <v>17046</v>
       </c>
       <c r="F16">
         <f ca="1">IF(AND(E16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-E16)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15182</v>
+        <v>15246</v>
       </c>
       <c r="H16">
         <f ca="1">IF(AND(G16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-G16)/CajasProm,0),0)</f>
@@ -33428,7 +33414,7 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13382</v>
+        <v>13446</v>
       </c>
       <c r="J16">
         <f ca="1">IF(AND(I16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-I16)/CajasProm,0),0)</f>
@@ -33440,7 +33426,7 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15182</v>
+        <v>15246</v>
       </c>
       <c r="M16">
         <f ca="1">IF(AND(L16&lt;MinimoSabado,Proyeccion!J16&gt;=FechaHoy),ROUNDUP((MinimoSabado-L16)/CajasProm,0),0)</f>
@@ -33448,15 +33434,15 @@
       </c>
       <c r="N16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12242</v>
+        <v>12306</v>
       </c>
       <c r="O16" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14182</v>
+        <v>14246</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13082</v>
+        <v>13146</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -33478,15 +33464,15 @@
       </c>
       <c r="E17" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17846</v>
+        <v>16910</v>
       </c>
       <c r="F17">
         <f ca="1">IF(AND(E17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-E17)/CajasProm,0),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15246</v>
+        <v>15310</v>
       </c>
       <c r="H17">
         <f ca="1">IF(AND(G17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-G17)/CajasProm,0),0)</f>
@@ -33494,7 +33480,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13646</v>
+        <v>13710</v>
       </c>
       <c r="J17">
         <f ca="1">IF(AND(I17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-I17)/CajasProm,0),0)</f>
@@ -33506,7 +33492,7 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15246</v>
+        <v>15310</v>
       </c>
       <c r="M17">
         <f ca="1">IF(AND(L17&lt;MinimoSabado,Proyeccion!J17&gt;=FechaHoy),ROUNDUP((MinimoSabado-L17)/CajasProm,0),0)</f>
@@ -33514,15 +33500,15 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12306</v>
+        <v>12370</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14246</v>
+        <v>14310</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13146</v>
+        <v>13210</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -33544,7 +33530,7 @@
       </c>
       <c r="E18" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>17710</v>
+        <v>17774</v>
       </c>
       <c r="F18">
         <f ca="1">IF(AND(E18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-E18)/CajasProm,0),0)</f>
@@ -33552,7 +33538,7 @@
       </c>
       <c r="G18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15310</v>
+        <v>15374</v>
       </c>
       <c r="H18">
         <f ca="1">IF(AND(G18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-G18)/CajasProm,0),0)</f>
@@ -33560,7 +33546,7 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>13910</v>
+        <v>13974</v>
       </c>
       <c r="J18">
         <f ca="1">IF(AND(I18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-I18)/CajasProm,0),0)</f>
@@ -33572,7 +33558,7 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>15310</v>
+        <v>15374</v>
       </c>
       <c r="M18">
         <f ca="1">IF(AND(L18&lt;MinimoSabado,Proyeccion!J18&gt;=FechaHoy),ROUNDUP((MinimoSabado-L18)/CajasProm,0),0)</f>
@@ -33580,15 +33566,15 @@
       </c>
       <c r="N18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12370</v>
+        <v>12434</v>
       </c>
       <c r="O18" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>14310</v>
+        <v>14374</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>13210</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F346E5D6-36FE-4E2A-ABFB-9222F388B35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817C7567-DC03-4B8B-B936-FA9FEF41E80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 18:41 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 18:45 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -814,10 +814,10 @@
     <t>nota 01/10: cuarta (antes martes, sacada el 30/09); transportista supuesto</t>
   </si>
   <si>
-    <t>nota 01/10 (v3): cuarta (antes sexta); transportista supuesto = semana anterior</t>
-  </si>
-  <si>
     <t>nota 30/09: sexta; transportista supuesto = semana anterior</t>
+  </si>
+  <si>
+    <t>nota 01/10 (v4): sexta (Gonzalo: "prefiero cerrar en casi 25 mil que casi 26 mil"); transportista supuesto = semana anterior</t>
   </si>
   <si>
     <t>Paraguay (supuesto)</t>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>20926</v>
+        <v>19918</v>
       </c>
       <c r="D8" s="7">
         <f>Demanda!H9</f>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="H8" s="7">
         <f ca="1">Proyeccion!L8</f>
-        <v>25824</v>
+        <v>25816</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" si="3"/>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>8974</v>
+        <v>9982</v>
       </c>
       <c r="D9" s="7">
         <f>Demanda!H10</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>303</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>8.3610000000000007</v>
+        <v>8.3603333333333332</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>305</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B11" s="25">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>307</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="s">
         <v>3</v>
@@ -12513,10 +12513,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G37" s="8">
         <v>1008</v>
@@ -12554,7 +12554,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="9"/>
@@ -12579,20 +12579,20 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="1"/>
-        <v>mié</v>
+        <v>vie</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G38" s="8">
         <v>1008</v>
@@ -12611,11 +12611,11 @@
       </c>
       <c r="L38" s="5">
         <f t="shared" si="4"/>
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="M38" s="5">
         <f t="shared" si="5"/>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="N38">
         <f t="shared" si="6"/>
@@ -12630,11 +12630,11 @@
         <v>7146.72</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="9"/>
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="S38" s="5">
         <f t="shared" si="10"/>
@@ -12665,10 +12665,10 @@
         <v>58</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G39" s="8">
         <v>1008</v>
@@ -12782,7 +12782,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="9"/>
@@ -12858,7 +12858,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="9"/>
@@ -30537,11 +30537,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="2"/>
-        <v>20926</v>
+        <v>19918</v>
       </c>
       <c r="F8" s="7">
         <f>ROUND(Demanda!H8,0)</f>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="H8" s="7">
         <f ca="1">SUM($K$6:K7)*CajasProm</f>
@@ -30557,7 +30557,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="5"/>
@@ -30565,27 +30565,27 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25824</v>
+        <v>25816</v>
       </c>
       <c r="M8" s="22">
         <f ca="1">IF(Demanda!H9=0,"",L8/(Demanda!H9/DiasVenta))</f>
-        <v>8.6080000000000005</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="O8" s="7">
         <f>O7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L8,0)</f>
-        <v>12859</v>
+        <v>11851</v>
       </c>
       <c r="P8" s="22">
         <f>IF(Demanda!L9=0,"",O8/(Demanda!L9/DiasVenta))</f>
-        <v>6.9470556455969747</v>
+        <v>6.4024851431658565</v>
       </c>
       <c r="Q8" s="7">
         <f>Q7+SUMIFS(CgCajas,CgSemana,A8,CgCuenta,1,CgOrigen,"PY")-ROUND(Demanda!M8,0)</f>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="U8" t="str">
         <f t="shared" si="9"/>
-        <v>Bolivia</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -30619,15 +30619,15 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" si="10"/>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="2"/>
-        <v>8974</v>
+        <v>9982</v>
       </c>
       <c r="F9" s="7">
         <f>ROUND(Demanda!H9,0)</f>
@@ -30639,11 +30639,11 @@
       </c>
       <c r="H9" s="7">
         <f ca="1">SUM($K$6:K8)*CajasProm</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>16798</v>
+        <v>17798</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="5"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="K9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
@@ -30663,7 +30663,7 @@
       </c>
       <c r="N9" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="O9" s="7">
         <f>O8+SUMIFS(CgCajas,CgSemana,A9,CgCuenta,1,CgOrigen,"BR")-ROUND(Demanda!L9,0)</f>
@@ -31671,11 +31671,11 @@
       </c>
       <c r="B8" s="7">
         <f ca="1">IF(A8="","",Proyeccion!I8)</f>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="C8" s="3">
         <f ca="1">IF(A8="","",Proyeccion!K8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
         <f ca="1">IF(A8="","","BR "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B8-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B8-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="E8" t="str">
         <f ca="1">IF(A8="","",IF(C8&gt;0,Proyeccion!U8,"-"))</f>
-        <v>-</v>
+        <v>Brasil</v>
       </c>
       <c r="F8" t="str">
         <f ca="1">IF(A8="","","PY mie "&amp;TEXT(Proyeccion!A8-5,"dd/mm")&amp;" / BR jue "&amp;TEXT(Proyeccion!A8-4,"dd/mm"))</f>
@@ -31691,15 +31691,15 @@
       </c>
       <c r="G8" s="22">
         <f ca="1">IF(A8="","",Proyeccion!M8)</f>
-        <v>8.6080000000000005</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="H8" t="str">
         <f ca="1">IF(A8="","",Proyeccion!N8)</f>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="I8" t="str">
         <f ca="1">IF(A8="","","Sab "&amp;TEXT(A8,"dd/mm")&amp;": "&amp;FIXED(B8,0)&amp;" cajas - descargan "&amp;Proyeccion!D8&amp;" - vende "&amp;FIXED(Proyeccion!F8,0)&amp;IF(C8&gt;0," -&gt; cargar "&amp;C8&amp;" mas hasta el "&amp;TEXT(Proyeccion!J8,"dd/mm")&amp;" ("&amp;E8&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B8-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 10/10: 25.824 cajas - descargan 21 - vende 18.000 -&gt; ok</v>
+        <v>Sab 10/10: 24.816 cajas - descargan 20 - vende 18.000 -&gt; cargar 1 mas hasta el 06/10 (Brasil; BR hasta el 07/10)</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -31709,11 +31709,11 @@
       </c>
       <c r="B9" s="7">
         <f ca="1">IF(A9="","",Proyeccion!I9)</f>
-        <v>16798</v>
+        <v>17798</v>
       </c>
       <c r="C9" s="3">
         <f ca="1">IF(A9="","",Proyeccion!K9)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <f ca="1">IF(A9="","","BR "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"ddd dd/mm")&amp;" · PY "&amp;TEXT(Proyeccion!B9-LagPY-AtrasoDias,"ddd dd/mm")&amp;" · BO "&amp;TEXT(Proyeccion!B9-LagBO-AtrasoDias,"ddd dd/mm"))</f>
@@ -31733,11 +31733,11 @@
       </c>
       <c r="H9" t="str">
         <f ca="1">IF(A9="","",Proyeccion!N9)</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="I9" t="str">
         <f ca="1">IF(A9="","","Sab "&amp;TEXT(A9,"dd/mm")&amp;": "&amp;FIXED(B9,0)&amp;" cajas - descargan "&amp;Proyeccion!D9&amp;" - vende "&amp;FIXED(Proyeccion!F9,0)&amp;IF(C9&gt;0," -&gt; cargar "&amp;C9&amp;" mas hasta el "&amp;TEXT(Proyeccion!J9,"dd/mm")&amp;" ("&amp;E9&amp;"; BR hasta el "&amp;TEXT(Proyeccion!B9-LagBR-AtrasoDias,"dd/mm")&amp;")"," -&gt; ok"))</f>
-        <v>Sab 17/10: 16.798 cajas - descargan 9 - vende 18.000 -&gt; cargar 9 mas hasta el 13/10 (Brasil; BR hasta el 14/10)</v>
+        <v>Sab 17/10: 17.798 cajas - descargan 10 - vende 18.000 -&gt; cargar 8 mas hasta el 13/10 (Brasil; BR hasta el 14/10)</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -32304,11 +32304,11 @@
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>12859</v>
+        <v>11851</v>
       </c>
       <c r="C13" s="22">
         <f ca="1">IFERROR(INDEX(PrBRd,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>6.9470556455969747</v>
+        <v>6.4024851431658565</v>
       </c>
       <c r="D13" t="str">
         <f ca="1">IF(B13="","",IF(B13&lt;0,"FALTA",IF(C13&lt;2,"CRITICO",IF(C13&lt;CoberturaObjetivo,"JUSTO",IF(C13&gt;VidaVerde,"EXCESO","OK")))))</f>
@@ -32367,19 +32367,19 @@
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="C16" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>8.6080000000000005</v>
+        <v>8.6053333333333342</v>
       </c>
       <c r="D16" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
-        <v>OK</v>
+        <v>CARGAR 1</v>
       </c>
       <c r="E16" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>ok, cierra sobre 25.000</v>
+        <v>cargar 1 camion(es) mas hasta el mar 06/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -32478,7 +32478,7 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>16798</v>
+        <v>17798</v>
       </c>
       <c r="C23" s="41">
         <f ca="1">IFERROR(INDEX(PrCobertura,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32486,11 +32486,11 @@
       </c>
       <c r="D23" s="42" t="str">
         <f ca="1">IFERROR(INDEX(PrEstado,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
-        <v>CARGAR 9</v>
+        <v>CARGAR 8</v>
       </c>
       <c r="E23" s="42" t="str">
         <f ca="1">IFERROR(IF(INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&gt;0,"cargar "&amp;INDEX(PrACargar,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0))&amp;" camion(es) mas hasta el "&amp;TEXT(INDEX(PrLimite,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"ddd dd/mm")&amp;" para cerrar en "&amp;FIXED(MinimoSabado,0),"ok, cierra sobre "&amp;FIXED(MinimoSabado,0)),"")</f>
-        <v>cargar 9 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
+        <v>cargar 8 camion(es) mas hasta el mar 13/10 para cerrar en 25.000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
@@ -32545,7 +32545,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="45" t="str">
         <f ca="1">IFERROR("Frontera lenta (P90): el sabado "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"dd/mm")&amp;" cerraria en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" cajas ("&amp;IF(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))&gt;INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0))-INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),0)&amp;" menos que el plan","igual o mas que el plan")&amp;") y el "&amp;TEXT(INDEX(PrSab,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"dd/mm")&amp;" en "&amp;FIXED(INDEX(Escenarios!L6:L18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;" (plan: "&amp;FIXED(INDEX(Escenarios!G6:G18,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),0)&amp;").","")</f>
-        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.880 (plan: 25.824).</v>
+        <v>Frontera lenta (P90): el sabado 03/10 cerraria en 17.886 cajas (5.012 menos que el plan) y el 10/10 en 16.880 (plan: 24.816).</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -32862,7 +32862,7 @@
       </c>
       <c r="C8" s="7">
         <f>Proyeccion!E8</f>
-        <v>20926</v>
+        <v>19918</v>
       </c>
       <c r="D8" s="7">
         <f>Proyeccion!F8</f>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="E8" s="7">
         <f t="shared" ca="1" si="4"/>
-        <v>29224</v>
+        <v>28216</v>
       </c>
       <c r="F8">
         <f ca="1">IF(AND(E8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-E8)/CajasProm,0),0)</f>
@@ -32878,19 +32878,19 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25824</v>
+        <v>24816</v>
       </c>
       <c r="H8">
         <f ca="1">IF(AND(G8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-G8)/CajasProm,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>22424</v>
+        <v>21416</v>
       </c>
       <c r="J8">
         <f ca="1">IF(AND(I8&lt;MinimoSabado,Proyeccion!J8&gt;=FechaHoy),ROUNDUP((MinimoSabado-I8)/CajasProm,0),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
@@ -32906,15 +32906,15 @@
       </c>
       <c r="N8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>22884</v>
+        <v>21876</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>24824</v>
+        <v>23816</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>24774</v>
+        <v>23766</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="C9" s="7">
         <f>Proyeccion!E9</f>
-        <v>8974</v>
+        <v>9982</v>
       </c>
       <c r="D9" s="7">
         <f>Proyeccion!F9</f>
@@ -32944,19 +32944,19 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16798</v>
+        <v>17798</v>
       </c>
       <c r="H9">
         <f ca="1">IF(AND(G9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-G9)/CajasProm,0),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="6"/>
-        <v>14598</v>
+        <v>15598</v>
       </c>
       <c r="J9">
         <f ca="1">IF(AND(I9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-I9)/CajasProm,0),0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
@@ -32972,15 +32972,15 @@
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13858</v>
+        <v>14858</v>
       </c>
       <c r="O9" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>15798</v>
+        <v>16798</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>14698</v>
+        <v>15698</v>
       </c>
     </row>
     <row r="10" spans="1:16">

--- a/plan_compras/Plan_Compras_Simulado.xlsx
+++ b/plan_compras/Plan_Compras_Simulado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PorongaEnLaNube\gonza_pepe\plan_compras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817C7567-DC03-4B8B-B936-FA9FEF41E80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9AA2A1-E5CA-45CB-8368-59E122E89E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,12 +110,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="682">
   <si>
     <t>PLAN DE COMPRAS SIMULADO - Almar S.R.L. (banana Brasil + Paraguay + Bolivia)</t>
   </si>
   <si>
-    <t>Generado el 01/10/2026 18:45 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
+    <t>Generado el 01/10/2026 18:52 a partir de plan_compras.json (conteo del 26/09/2026). Planilla de trabajo: se edita a mano, no la pisa el script.</t>
   </si>
   <si>
     <t>PARA QUE SIRVE</t>
@@ -826,6 +826,12 @@
     <t>supuesto: 5 camiones PY por semana, cargan dom-lun-mar (Gonzalo 27/09)</t>
   </si>
   <si>
+    <t>Paraguay GM</t>
+  </si>
+  <si>
+    <t>nota 01/10: Guido 1, martes 13 (reactivacion; sin cargar desde julio). Con 4 dias descarga el sabado 17.</t>
+  </si>
+  <si>
     <t>Brasil (supuesto)</t>
   </si>
   <si>
@@ -1583,9 +1589,6 @@
   </si>
   <si>
     <t>sin cargas desde junio; TT 4 dias</t>
-  </si>
-  <si>
-    <t>Paraguay GM</t>
   </si>
   <si>
     <t>Guido / Servi Fel</t>
@@ -3910,12 +3913,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45">
@@ -3926,28 +3929,28 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>178</v>
@@ -4553,7 +4556,7 @@
     </row>
     <row r="20" spans="1:12" ht="63.95" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -4600,184 +4603,184 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B5" s="12">
         <f>ConteoTotal</f>
         <v>26972</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B6" s="24">
         <f>ConteoTotal/(INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))/DiasVenta)</f>
         <v>10.114500000000001</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B7" s="12">
         <f ca="1">IFERROR(INDEX(PrStock,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>22898</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B8" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1,PrSemana,0)),"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B9" s="25">
         <f ca="1">IFERROR(INDEX(PrACargar,MATCH(FechaHoy-WEEKDAY(FechaHoy,2)+1+7,PrSemana,0)),"")</f>
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B10" s="24">
         <f ca="1">AVERAGEIFS(PrCobertura,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>8.3603333333333332</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30">
       <c r="A11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B11" s="25">
         <f ca="1">COUNTIFS(PrACargar,"&gt;0",PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B12" s="25">
         <f ca="1">SUMIFS(PrACargar,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B13" s="24">
         <f>ConteoTotal/INDEX(DemVenta,MATCH(FechaConteo-WEEKDAY(FechaConteo,2)+1+7,DemSemana,0))</f>
         <v>1.6857500000000001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30">
       <c r="A14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B14" s="12">
         <f>ConteoBR*CostoBR+ConteoPY*CostoPY+ConteoBO*CostoBO</f>
         <v>196107.57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30">
       <c r="A15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B15" s="12">
         <f ca="1">SUM(CgPipeline)</f>
         <v>10946</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B16" s="26">
         <f>PrecioBR_BRL-(CepeaKg*KgCaja+ServiciosCaja)</f>
         <v>-7.0899999999999963</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="PY")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"PY",Proveedores!D5:D60),"")</f>
         <v>0.48076923076923078</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B18" s="27">
         <f>IFERROR(SUMPRODUCT(MAX((Proveedores!A5:A60="BR")*Proveedores!D5:D60))/SUMIF(Proveedores!A5:A60,"BR",Proveedores!D5:D60),"")</f>
@@ -4789,31 +4792,31 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B19" s="24">
         <f ca="1">AVERAGEIFS(PrCamiones,PrSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),PrSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30">
       <c r="A20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B20" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BR",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
         <v>0.57378223495702008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B21" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"PY",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4825,7 +4828,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B22" s="27">
         <f ca="1">IFERROR(SUMIFS(CgCajas,CgOrigen,"BO",CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))/SUMIFS(CgCajas,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28)),0)</f>
@@ -4837,206 +4840,206 @@
     </row>
     <row r="23" spans="1:3" ht="30">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B23" s="12">
         <f ca="1">SUMIFS(CgCosto,CgCuenta,1,CgSemana,"&gt;="&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1),CgSemana,"&lt;"&amp;(FechaHoy-WEEKDAY(FechaHoy,2)+1+28))</f>
         <v>409723.59999999974</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45">
       <c r="A24" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B24" s="25">
         <f>COUNTIFS(CgEstado,"Supuesto*",CgCuenta,1)</f>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
       <c r="A25" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B25" s="28">
         <f>IFERROR(AVERAGE(Proveedores!R5:R60),"")</f>
         <v>-9.5789473684210517E-4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B26" s="27">
         <f>IFERROR(AVERAGE(CgOTIF),"sin descargas reales todavia")</f>
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B27" s="25">
         <f>COUNTIFS(CgEstado,"Dictado",CgCuenta,1)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B28" s="29" t="str">
         <f>IFERROR(SUMPRODUCT((Demanda!O6:O18&lt;&gt;"")*ABS(Demanda!P6:P18))/COUNTIF(Demanda!O6:O18,"&lt;&gt;"),"sin venta real cargada")</f>
         <v>sin venta real cargada</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30">
       <c r="A30" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="45">
       <c r="A31" s="30" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45">
       <c r="A32" s="30" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45">
       <c r="A33" s="30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30">
       <c r="A34" s="30" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30">
       <c r="A35" s="30" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="30">
       <c r="A36" s="30" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="45">
       <c r="A37" s="30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45">
       <c r="A38" s="30" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30">
       <c r="A39" s="30" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30">
       <c r="A40" s="30" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30">
       <c r="A41" s="30" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5068,12 +5071,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="90">
@@ -5081,64 +5084,64 @@
         <v>173</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -5173,10 +5176,10 @@
         <v>1008</v>
       </c>
       <c r="K5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M5" s="10">
         <v>37.75</v>
@@ -5193,19 +5196,19 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="R5" s="32">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="S5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T5" s="22">
         <v>1.2</v>
       </c>
       <c r="U5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -5213,7 +5216,7 @@
         <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>215</v>
@@ -5240,10 +5243,10 @@
         <v>1008</v>
       </c>
       <c r="K6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M6" s="10">
         <v>37</v>
@@ -5260,19 +5263,19 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="R6" s="32">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="S6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="T6" s="22">
         <v>1.6</v>
       </c>
       <c r="U6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -5307,10 +5310,10 @@
         <v>936</v>
       </c>
       <c r="K7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M7" s="10">
         <v>38.64</v>
@@ -5327,19 +5330,19 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="R7" s="32">
         <v>-1.4E-3</v>
       </c>
       <c r="S7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="T7" s="22">
         <v>2.5</v>
       </c>
       <c r="U7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -5347,7 +5350,7 @@
         <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>217</v>
@@ -5374,10 +5377,10 @@
         <v>1008</v>
       </c>
       <c r="K8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M8" s="10">
         <v>41.63</v>
@@ -5394,19 +5397,19 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R8" s="32">
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T8" s="22">
         <v>0.6</v>
       </c>
       <c r="U8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -5414,7 +5417,7 @@
         <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>208</v>
@@ -5441,10 +5444,10 @@
         <v>1008</v>
       </c>
       <c r="K9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M9" s="10">
         <v>40.74</v>
@@ -5461,19 +5464,19 @@
         <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="R9" s="32">
         <v>-7.7999999999999996E-3</v>
       </c>
       <c r="S9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="T9" s="22">
         <v>0.4</v>
       </c>
       <c r="U9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -5508,10 +5511,10 @@
         <v>1008</v>
       </c>
       <c r="K10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M10" s="10">
         <v>40.65</v>
@@ -5528,19 +5531,19 @@
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="R10" s="32">
         <v>-4.0000000000000002E-4</v>
       </c>
       <c r="S10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T10" s="22">
         <v>1</v>
       </c>
       <c r="U10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -5548,7 +5551,7 @@
         <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>223</v>
@@ -5575,10 +5578,10 @@
         <v>1008</v>
       </c>
       <c r="K11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M11" s="10">
         <v>42.33</v>
@@ -5601,7 +5604,7 @@
         <v>3</v>
       </c>
       <c r="U11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -5609,7 +5612,7 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>224</v>
@@ -5636,10 +5639,10 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M12" s="10">
         <v>42.16</v>
@@ -5656,19 +5659,19 @@
         <v>3</v>
       </c>
       <c r="Q12" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="R12" s="32">
         <v>-1E-4</v>
       </c>
       <c r="S12" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T12" s="22">
         <v>0.4</v>
       </c>
       <c r="U12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -5676,10 +5679,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -5703,10 +5706,10 @@
         <v>1008</v>
       </c>
       <c r="K13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M13" s="10">
         <v>37.64</v>
@@ -5723,7 +5726,7 @@
         <v>3</v>
       </c>
       <c r="U13" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -5731,10 +5734,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -5758,10 +5761,10 @@
         <v>1008</v>
       </c>
       <c r="K14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M14" s="10">
         <v>37.799999999999997</v>
@@ -5778,7 +5781,7 @@
         <v>3</v>
       </c>
       <c r="U14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -5786,10 +5789,10 @@
         <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -5813,10 +5816,10 @@
         <v>1008</v>
       </c>
       <c r="K15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M15" s="10">
         <v>41.14</v>
@@ -5833,19 +5836,19 @@
         <v>3</v>
       </c>
       <c r="Q15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="R15" s="32">
         <v>-1.8E-3</v>
       </c>
       <c r="S15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="T15" s="22">
         <v>0.3</v>
       </c>
       <c r="U15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -5853,10 +5856,10 @@
         <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -5880,10 +5883,10 @@
         <v>980</v>
       </c>
       <c r="K16" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
@@ -5894,22 +5897,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q16" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="R16" s="32">
         <v>-1E-3</v>
       </c>
       <c r="S16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="T16" s="22">
         <v>2</v>
       </c>
       <c r="U16" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -5944,10 +5947,10 @@
         <v>980</v>
       </c>
       <c r="K17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L17" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="0"/>
@@ -5958,22 +5961,22 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="R17" s="32">
         <v>-3.8999999999999998E-3</v>
       </c>
       <c r="S17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="T17" s="22">
         <v>1.8</v>
       </c>
       <c r="U17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -6008,10 +6011,10 @@
         <v>980</v>
       </c>
       <c r="K18" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
@@ -6022,22 +6025,22 @@
         <v>2</v>
       </c>
       <c r="P18" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q18" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="R18" s="32">
         <v>1E-4</v>
       </c>
       <c r="S18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T18" s="22">
         <v>0.6</v>
       </c>
       <c r="U18" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -6072,10 +6075,10 @@
         <v>980</v>
       </c>
       <c r="K19" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L19" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="0"/>
@@ -6086,22 +6089,22 @@
         <v>2</v>
       </c>
       <c r="P19" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="R19" s="32">
         <v>-1.5E-3</v>
       </c>
       <c r="S19" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="T19" s="22">
         <v>0.5</v>
       </c>
       <c r="U19" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -6109,7 +6112,7 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>194</v>
@@ -6136,10 +6139,10 @@
         <v>1050</v>
       </c>
       <c r="K20" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L20" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="0"/>
@@ -6150,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Q20" t="s">
         <v>3</v>
@@ -6159,7 +6162,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -6167,7 +6170,7 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>194</v>
@@ -6194,10 +6197,10 @@
         <v>1050</v>
       </c>
       <c r="K21" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L21" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="0"/>
@@ -6208,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Q21" t="s">
         <v>3</v>
@@ -6252,7 +6255,7 @@
         <v>3</v>
       </c>
       <c r="L22" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="0"/>
@@ -6263,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Q22" t="s">
         <v>3</v>
@@ -6272,7 +6275,7 @@
         <v>3</v>
       </c>
       <c r="U22" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -6280,10 +6283,10 @@
         <v>58</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D23" s="33">
         <v>0</v>
@@ -6314,20 +6317,20 @@
         <v>0</v>
       </c>
       <c r="P23" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="R23" s="36">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="S23" s="33" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="T23" s="33"/>
       <c r="U23" s="33" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -6335,10 +6338,10 @@
         <v>58</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D24" s="33">
         <v>0</v>
@@ -6369,20 +6372,20 @@
         <v>0</v>
       </c>
       <c r="P24" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R24" s="36">
         <v>-8.0000000000000004E-4</v>
       </c>
       <c r="S24" s="33" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="T24" s="33"/>
       <c r="U24" s="33" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -6390,10 +6393,10 @@
         <v>58</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D25" s="33">
         <v>0</v>
@@ -6424,20 +6427,20 @@
         <v>0</v>
       </c>
       <c r="P25" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="R25" s="36">
         <v>0</v>
       </c>
       <c r="S25" s="33" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="T25" s="33"/>
       <c r="U25" s="33" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -6445,10 +6448,10 @@
         <v>58</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D26" s="33">
         <v>0</v>
@@ -6477,20 +6480,20 @@
         <v>0</v>
       </c>
       <c r="P26" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R26" s="36">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="S26" s="33" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="T26" s="33"/>
       <c r="U26" s="33" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -6498,10 +6501,10 @@
         <v>59</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>491</v>
+        <v>238</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D27" s="33">
         <v>0</v>
@@ -6517,7 +6520,7 @@
         <v>972</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -6530,20 +6533,20 @@
         <v>0</v>
       </c>
       <c r="P27" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="R27" s="36">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="S27" s="33" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T27" s="33"/>
       <c r="U27" s="33" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -6551,10 +6554,10 @@
         <v>59</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D28" s="33">
         <v>0</v>
@@ -6583,20 +6586,20 @@
         <v>0</v>
       </c>
       <c r="P28" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="R28" s="36">
         <v>-1.4E-3</v>
       </c>
       <c r="S28" s="33" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="T28" s="33"/>
       <c r="U28" s="33" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -6604,10 +6607,10 @@
         <v>59</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D29" s="33">
         <v>0</v>
@@ -6636,25 +6639,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R29" s="36">
         <v>-1E-3</v>
       </c>
       <c r="S29" s="33" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="T29" s="33"/>
       <c r="U29" s="33" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="48.95" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
@@ -6700,40 +6703,40 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30">
       <c r="A4" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C5" s="18">
         <v>0.18</v>
@@ -6745,15 +6748,15 @@
         <v>8600</v>
       </c>
       <c r="F5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C6" s="18">
         <v>9.5000000000000001E-2</v>
@@ -6765,12 +6768,12 @@
         <v>4200</v>
       </c>
       <c r="F6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -6790,7 +6793,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -6810,7 +6813,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -6830,7 +6833,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -6845,15 +6848,15 @@
         <v>2250</v>
       </c>
       <c r="F10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C11" s="18">
         <v>4.2000000000000003E-2</v>
@@ -6865,15 +6868,15 @@
         <v>2100</v>
       </c>
       <c r="F11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C12" s="18">
         <v>0.04</v>
@@ -6885,12 +6888,12 @@
         <v>1750</v>
       </c>
       <c r="F12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -6910,7 +6913,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -6930,7 +6933,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -6950,7 +6953,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -6970,7 +6973,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -6990,24 +6993,24 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C18" s="18">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C19" s="18">
         <v>2.5999999999999999E-2</v>
@@ -7018,7 +7021,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -7027,12 +7030,12 @@
         <v>2.4E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -7046,7 +7049,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -7060,7 +7063,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -7074,7 +7077,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -7089,21 +7092,21 @@
         <v>940</v>
       </c>
       <c r="F24" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45">
       <c r="A26" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>61</v>
@@ -7111,10 +7114,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B27" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C27" s="18">
         <v>0.22</v>
@@ -7123,15 +7126,15 @@
         <v>10350</v>
       </c>
       <c r="E27" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B28" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C28" s="18">
         <v>0.121</v>
@@ -7140,15 +7143,15 @@
         <v>4200</v>
       </c>
       <c r="E28" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B29" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C29" s="18">
         <v>7.0999999999999994E-2</v>
@@ -7157,15 +7160,15 @@
         <v>2100</v>
       </c>
       <c r="E29" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B30" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C30" s="18">
         <v>6.9000000000000006E-2</v>
@@ -7179,10 +7182,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B31" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C31" s="18">
         <v>6.3E-2</v>
@@ -7196,10 +7199,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B32" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C32" s="18">
         <v>5.1999999999999998E-2</v>
@@ -7213,10 +7216,10 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B33" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C33" s="18">
         <v>4.7E-2</v>
@@ -7230,10 +7233,10 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B34" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C34" s="18">
         <v>3.6999999999999998E-2</v>
@@ -7247,10 +7250,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B35" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C35" s="18">
         <v>3.5000000000000003E-2</v>
@@ -7264,10 +7267,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B36" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C36" s="18">
         <v>3.4000000000000002E-2</v>
@@ -7281,10 +7284,10 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B37" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C37" s="18">
         <v>3.1E-2</v>
@@ -7298,10 +7301,10 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B38" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C38" s="18">
         <v>0.03</v>
@@ -7315,10 +7318,10 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B39" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C39" s="18">
         <v>2.4E-2</v>
@@ -7329,10 +7332,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B40" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C40" s="18">
         <v>2.3E-2</v>
@@ -7343,10 +7346,10 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B41" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C41" s="18">
         <v>2.1000000000000001E-2</v>
@@ -7357,10 +7360,10 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B42" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C42" s="18">
         <v>1.7999999999999999E-2</v>
@@ -7371,10 +7374,10 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B43" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C43" s="18">
         <v>8.9999999999999993E-3</v>
@@ -7388,7 +7391,7 @@
     </row>
     <row r="45" spans="1:12" ht="63.95" customHeight="1">
       <c r="A45" s="44" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
@@ -7421,79 +7424,79 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30">
       <c r="A6" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7501,84 +7504,84 @@
         <v>206</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30">
       <c r="A17" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30">
       <c r="A18" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30">
       <c r="A20" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>3</v>
@@ -7586,138 +7589,138 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -7758,12 +7761,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21">
       <c r="A1" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -7771,101 +7774,101 @@
         <v>172</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45">
       <c r="A5" s="37" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30">
       <c r="A6" s="37" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="45">
       <c r="A7" s="37" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30">
       <c r="A8" s="37" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30">
       <c r="A9" s="37" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30">
@@ -7873,38 +7876,38 @@
         <v>160</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30">
       <c r="A11" s="37" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48.95" customHeight="1">
       <c r="A13" s="44" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -13187,27 +13190,27 @@
         <v>42</v>
       </c>
       <c r="B46" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="1"/>
-        <v>lun</v>
+        <v>mar</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="H46" s="7">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>206</v>
@@ -13215,15 +13218,15 @@
       <c r="J46" s="6"/>
       <c r="K46">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="4"/>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="M46" s="5">
         <f t="shared" si="5"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="N46">
         <f t="shared" si="6"/>
@@ -13231,22 +13234,22 @@
       </c>
       <c r="O46" s="10">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="8"/>
-        <v>6860</v>
+        <v>11340</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="9"/>
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="S46" s="5">
         <f t="shared" si="10"/>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="T46" s="7">
         <f t="shared" ca="1" si="11"/>
@@ -13270,36 +13273,36 @@
         <v>mar</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="8">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="H47" s="7">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" si="4"/>
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="M47" s="5">
         <f t="shared" si="5"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="N47">
         <f t="shared" si="6"/>
@@ -13307,18 +13310,18 @@
       </c>
       <c r="O47" s="10">
         <f t="shared" si="7"/>
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="8"/>
-        <v>11340</v>
+        <v>6860</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="9"/>
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="S47" s="5">
         <f t="shared" si="10"/>
@@ -13349,7 +13352,7 @@
         <v>58</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>3</v>
@@ -13362,7 +13365,7 @@
         <v>1008</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48">
@@ -13390,7 +13393,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="9"/>
@@ -13425,7 +13428,7 @@
         <v>58</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>3</v>
@@ -13438,7 +13441,7 @@
         <v>1008</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49">
@@ -13466,7 +13469,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R49" s="5">
         <f t="shared" si="9"/>
@@ -13501,7 +13504,7 @@
         <v>58</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>3</v>
@@ -13514,7 +13517,7 @@
         <v>1008</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50">
@@ -13542,7 +13545,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R50" s="5">
         <f t="shared" si="9"/>
@@ -13577,7 +13580,7 @@
         <v>58</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>3</v>
@@ -13590,7 +13593,7 @@
         <v>1008</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51">
@@ -13618,7 +13621,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R51" s="5">
         <f t="shared" si="9"/>
@@ -13653,7 +13656,7 @@
         <v>58</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>3</v>
@@ -13666,7 +13669,7 @@
         <v>1008</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52">
@@ -13694,7 +13697,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R52" s="5">
         <f t="shared" si="9"/>
@@ -13729,7 +13732,7 @@
         <v>58</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>3</v>
@@ -13742,7 +13745,7 @@
         <v>1008</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53">
@@ -13770,7 +13773,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R53" s="5">
         <f t="shared" si="9"/>
@@ -13805,7 +13808,7 @@
         <v>58</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>3</v>
@@ -13818,7 +13821,7 @@
         <v>1008</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54">
@@ -13846,7 +13849,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="9"/>
@@ -13881,7 +13884,7 @@
         <v>58</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>3</v>
@@ -13894,7 +13897,7 @@
         <v>1008</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55">
@@ -13922,7 +13925,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R55" s="5">
         <f t="shared" si="9"/>
@@ -14413,7 +14416,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>3</v>
@@ -14426,7 +14429,7 @@
         <v>1008</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62">
@@ -14454,7 +14457,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="9"/>
@@ -14489,7 +14492,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>3</v>
@@ -14502,7 +14505,7 @@
         <v>1008</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63">
@@ -14530,7 +14533,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R63" s="5">
         <f t="shared" si="9"/>
@@ -14565,7 +14568,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>3</v>
@@ -14578,7 +14581,7 @@
         <v>1008</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64">
@@ -14606,7 +14609,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q64" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R64" s="5">
         <f t="shared" si="9"/>
@@ -14641,7 +14644,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>3</v>
@@ -14654,7 +14657,7 @@
         <v>1008</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65">
@@ -14682,7 +14685,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R65" s="5">
         <f t="shared" si="9"/>
@@ -14717,7 +14720,7 @@
         <v>58</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>3</v>
@@ -14730,7 +14733,7 @@
         <v>1008</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66">
@@ -14758,7 +14761,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R66" s="5">
         <f t="shared" si="9"/>
@@ -14793,7 +14796,7 @@
         <v>58</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>3</v>
@@ -14806,7 +14809,7 @@
         <v>1008</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67">
@@ -14834,7 +14837,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R67" s="5">
         <f t="shared" si="9"/>
@@ -14869,7 +14872,7 @@
         <v>58</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>3</v>
@@ -14882,7 +14885,7 @@
         <v>1008</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68">
@@ -14910,7 +14913,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R68" s="5">
         <f t="shared" si="9"/>
@@ -14945,7 +14948,7 @@
         <v>58</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>3</v>
@@ -14958,7 +14961,7 @@
         <v>1008</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69">
@@ -14986,7 +14989,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R69" s="5">
         <f t="shared" ref="R69:R132" si="22">IF(B69="","",IF(J69&lt;&gt;"",J69,B69+IFERROR(INDEX(LagsP90,MATCH(D69,Origenes,0)),K69)))</f>
@@ -15021,7 +15024,7 @@
         <v>58</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>3</v>
@@ -15034,7 +15037,7 @@
         <v>1008</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70">
@@ -15062,7 +15065,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R70" s="5">
         <f t="shared" si="22"/>
@@ -15097,7 +15100,7 @@
         <v>58</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>3</v>
@@ -15110,7 +15113,7 @@
         <v>1008</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71">
@@ -15138,7 +15141,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R71" s="5">
         <f t="shared" si="22"/>
@@ -15173,7 +15176,7 @@
         <v>58</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>3</v>
@@ -15186,7 +15189,7 @@
         <v>1008</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72">
@@ -15214,7 +15217,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R72" s="5">
         <f t="shared" si="22"/>
@@ -15249,7 +15252,7 @@
         <v>58</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>3</v>
@@ -15262,7 +15265,7 @@
         <v>1008</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73">
@@ -15290,7 +15293,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R73" s="5">
         <f t="shared" si="22"/>
@@ -15325,7 +15328,7 @@
         <v>58</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>3</v>
@@ -15338,7 +15341,7 @@
         <v>1008</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74">
@@ -15366,7 +15369,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R74" s="5">
         <f t="shared" si="22"/>
@@ -15401,7 +15404,7 @@
         <v>58</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>3</v>
@@ -15414,7 +15417,7 @@
         <v>1008</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75">
@@ -15442,7 +15445,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R75" s="5">
         <f t="shared" si="22"/>
@@ -15477,7 +15480,7 @@
         <v>58</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>3</v>
@@ -15490,7 +15493,7 @@
         <v>1008</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76">
@@ -15518,7 +15521,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R76" s="5">
         <f t="shared" si="22"/>
@@ -15553,7 +15556,7 @@
         <v>58</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>3</v>
@@ -15566,7 +15569,7 @@
         <v>1008</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77">
@@ -15594,7 +15597,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q77" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R77" s="5">
         <f t="shared" si="22"/>
@@ -15629,7 +15632,7 @@
         <v>58</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>3</v>
@@ -15642,7 +15645,7 @@
         <v>1008</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78">
@@ -15670,7 +15673,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R78" s="5">
         <f t="shared" si="22"/>
@@ -15705,7 +15708,7 @@
         <v>58</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>3</v>
@@ -15718,7 +15721,7 @@
         <v>1008</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79">
@@ -15746,7 +15749,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R79" s="5">
         <f t="shared" si="22"/>
@@ -15781,7 +15784,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>3</v>
@@ -15794,7 +15797,7 @@
         <v>1008</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80">
@@ -15822,7 +15825,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R80" s="5">
         <f t="shared" si="22"/>
@@ -15857,7 +15860,7 @@
         <v>58</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>3</v>
@@ -15870,7 +15873,7 @@
         <v>1008</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81">
@@ -15898,7 +15901,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R81" s="5">
         <f t="shared" si="22"/>
@@ -15933,7 +15936,7 @@
         <v>58</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>3</v>
@@ -15946,7 +15949,7 @@
         <v>1008</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82">
@@ -15974,7 +15977,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R82" s="5">
         <f t="shared" si="22"/>
@@ -16009,7 +16012,7 @@
         <v>58</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>3</v>
@@ -16022,7 +16025,7 @@
         <v>1008</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83">
@@ -16050,7 +16053,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q83" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R83" s="5">
         <f t="shared" si="22"/>
@@ -16085,7 +16088,7 @@
         <v>58</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>3</v>
@@ -16098,7 +16101,7 @@
         <v>1008</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84">
@@ -16126,7 +16129,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R84" s="5">
         <f t="shared" si="22"/>
@@ -16161,7 +16164,7 @@
         <v>58</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>3</v>
@@ -16174,7 +16177,7 @@
         <v>1008</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85">
@@ -16202,7 +16205,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R85" s="5">
         <f t="shared" si="22"/>
@@ -16237,7 +16240,7 @@
         <v>58</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>3</v>
@@ -16250,7 +16253,7 @@
         <v>1008</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86">
@@ -16278,7 +16281,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R86" s="5">
         <f t="shared" si="22"/>
@@ -16313,7 +16316,7 @@
         <v>58</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>3</v>
@@ -16326,7 +16329,7 @@
         <v>1008</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87">
@@ -16354,7 +16357,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R87" s="5">
         <f t="shared" si="22"/>
@@ -16389,7 +16392,7 @@
         <v>58</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>3</v>
@@ -16402,7 +16405,7 @@
         <v>1008</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88">
@@ -16430,7 +16433,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q88" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R88" s="5">
         <f t="shared" si="22"/>
@@ -16465,7 +16468,7 @@
         <v>58</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>3</v>
@@ -16478,7 +16481,7 @@
         <v>1008</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89">
@@ -16506,7 +16509,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q89" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R89" s="5">
         <f t="shared" si="22"/>
@@ -16541,7 +16544,7 @@
         <v>58</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>3</v>
@@ -16554,7 +16557,7 @@
         <v>1008</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90">
@@ -16582,7 +16585,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q90" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R90" s="5">
         <f t="shared" si="22"/>
@@ -16617,7 +16620,7 @@
         <v>58</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>3</v>
@@ -16630,7 +16633,7 @@
         <v>1008</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91">
@@ -16658,7 +16661,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R91" s="5">
         <f t="shared" si="22"/>
@@ -16693,7 +16696,7 @@
         <v>58</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>3</v>
@@ -16706,7 +16709,7 @@
         <v>1008</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92">
@@ -16734,7 +16737,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R92" s="5">
         <f t="shared" si="22"/>
@@ -16769,7 +16772,7 @@
         <v>58</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>3</v>
@@ -16782,7 +16785,7 @@
         <v>1008</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93">
@@ -16810,7 +16813,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q93" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R93" s="5">
         <f t="shared" si="22"/>
@@ -16845,7 +16848,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>3</v>
@@ -16858,7 +16861,7 @@
         <v>1008</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94">
@@ -16886,7 +16889,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R94" s="5">
         <f t="shared" si="22"/>
@@ -16921,7 +16924,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>3</v>
@@ -16934,7 +16937,7 @@
         <v>1008</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95">
@@ -16962,7 +16965,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R95" s="5">
         <f t="shared" si="22"/>
@@ -16997,7 +17000,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>3</v>
@@ -17010,7 +17013,7 @@
         <v>1008</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96">
@@ -17038,7 +17041,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q96" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R96" s="5">
         <f t="shared" si="22"/>
@@ -17073,7 +17076,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>3</v>
@@ -17086,7 +17089,7 @@
         <v>1008</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97">
@@ -17114,7 +17117,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R97" s="5">
         <f t="shared" si="22"/>
@@ -17149,7 +17152,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>3</v>
@@ -17162,7 +17165,7 @@
         <v>1008</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98">
@@ -17190,7 +17193,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R98" s="5">
         <f t="shared" si="22"/>
@@ -17225,7 +17228,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>3</v>
@@ -17238,7 +17241,7 @@
         <v>1008</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99">
@@ -17266,7 +17269,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q99" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R99" s="5">
         <f t="shared" si="22"/>
@@ -17301,7 +17304,7 @@
         <v>58</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>3</v>
@@ -17314,7 +17317,7 @@
         <v>1008</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100">
@@ -17342,7 +17345,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q100" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R100" s="5">
         <f t="shared" si="22"/>
@@ -17377,7 +17380,7 @@
         <v>58</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>3</v>
@@ -17390,7 +17393,7 @@
         <v>1008</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101">
@@ -17418,7 +17421,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R101" s="5">
         <f t="shared" si="22"/>
@@ -17453,7 +17456,7 @@
         <v>58</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>3</v>
@@ -17466,7 +17469,7 @@
         <v>1008</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102">
@@ -17494,7 +17497,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q102" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R102" s="5">
         <f t="shared" si="22"/>
@@ -17529,7 +17532,7 @@
         <v>58</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>3</v>
@@ -17542,7 +17545,7 @@
         <v>1008</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103">
@@ -17570,7 +17573,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R103" s="5">
         <f t="shared" si="22"/>
@@ -17605,7 +17608,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>3</v>
@@ -17618,7 +17621,7 @@
         <v>1008</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104">
@@ -17646,7 +17649,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q104" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R104" s="5">
         <f t="shared" si="22"/>
@@ -17681,7 +17684,7 @@
         <v>58</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>3</v>
@@ -17694,7 +17697,7 @@
         <v>1008</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105">
@@ -17722,7 +17725,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q105" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R105" s="5">
         <f t="shared" si="22"/>
@@ -17757,7 +17760,7 @@
         <v>58</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
@@ -17770,7 +17773,7 @@
         <v>1008</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106">
@@ -17798,7 +17801,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q106" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R106" s="5">
         <f t="shared" si="22"/>
@@ -17833,7 +17836,7 @@
         <v>58</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>3</v>
@@ -17846,7 +17849,7 @@
         <v>1008</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107">
@@ -17874,7 +17877,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q107" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R107" s="5">
         <f t="shared" si="22"/>
@@ -17909,7 +17912,7 @@
         <v>58</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>3</v>
@@ -17922,7 +17925,7 @@
         <v>1008</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108">
@@ -17950,7 +17953,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q108" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R108" s="5">
         <f t="shared" si="22"/>
@@ -17985,7 +17988,7 @@
         <v>58</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>3</v>
@@ -17998,7 +18001,7 @@
         <v>1008</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109">
@@ -18026,7 +18029,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q109" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R109" s="5">
         <f t="shared" si="22"/>
@@ -18061,7 +18064,7 @@
         <v>58</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>3</v>
@@ -18074,7 +18077,7 @@
         <v>1008</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110">
@@ -18102,7 +18105,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q110" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R110" s="5">
         <f t="shared" si="22"/>
@@ -18137,7 +18140,7 @@
         <v>58</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>3</v>
@@ -18150,7 +18153,7 @@
         <v>1008</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111">
@@ -18178,7 +18181,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q111" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R111" s="5">
         <f t="shared" si="22"/>
@@ -18213,7 +18216,7 @@
         <v>58</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>3</v>
@@ -18226,7 +18229,7 @@
         <v>1008</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112">
@@ -18254,7 +18257,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q112" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R112" s="5">
         <f t="shared" si="22"/>
@@ -18289,7 +18292,7 @@
         <v>58</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>3</v>
@@ -18302,7 +18305,7 @@
         <v>1008</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113">
@@ -18330,7 +18333,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q113" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R113" s="5">
         <f t="shared" si="22"/>
@@ -18365,7 +18368,7 @@
         <v>58</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>3</v>
@@ -18378,7 +18381,7 @@
         <v>1008</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114">
@@ -18406,7 +18409,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q114" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R114" s="5">
         <f t="shared" si="22"/>
@@ -18441,7 +18444,7 @@
         <v>58</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>3</v>
@@ -18454,7 +18457,7 @@
         <v>1008</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115">
@@ -18482,7 +18485,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R115" s="5">
         <f t="shared" si="22"/>
@@ -18517,7 +18520,7 @@
         <v>58</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>3</v>
@@ -18530,7 +18533,7 @@
         <v>1008</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116">
@@ -18558,7 +18561,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q116" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R116" s="5">
         <f t="shared" si="22"/>
@@ -18593,7 +18596,7 @@
         <v>58</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>3</v>
@@ -18606,7 +18609,7 @@
         <v>1008</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117">
@@ -18634,7 +18637,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q117" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R117" s="5">
         <f t="shared" si="22"/>
@@ -18669,7 +18672,7 @@
         <v>58</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>3</v>
@@ -18682,7 +18685,7 @@
         <v>1008</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118">
@@ -18710,7 +18713,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q118" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R118" s="5">
         <f t="shared" si="22"/>
@@ -18745,7 +18748,7 @@
         <v>58</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>3</v>
@@ -18758,7 +18761,7 @@
         <v>1008</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119">
@@ -18786,7 +18789,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q119" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R119" s="5">
         <f t="shared" si="22"/>
@@ -18821,7 +18824,7 @@
         <v>58</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>3</v>
@@ -18834,7 +18837,7 @@
         <v>1008</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120">
@@ -18862,7 +18865,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q120" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R120" s="5">
         <f t="shared" si="22"/>
@@ -18897,7 +18900,7 @@
         <v>58</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>3</v>
@@ -18910,7 +18913,7 @@
         <v>1008</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121">
@@ -18938,7 +18941,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q121" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R121" s="5">
         <f t="shared" si="22"/>
@@ -18973,7 +18976,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>3</v>
@@ -18986,7 +18989,7 @@
         <v>1008</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122">
@@ -19014,7 +19017,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q122" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R122" s="5">
         <f t="shared" si="22"/>
@@ -19049,7 +19052,7 @@
         <v>58</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>3</v>
@@ -19062,7 +19065,7 @@
         <v>1008</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123">
@@ -19090,7 +19093,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q123" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R123" s="5">
         <f t="shared" si="22"/>
@@ -19125,7 +19128,7 @@
         <v>58</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>3</v>
@@ -19138,7 +19141,7 @@
         <v>1008</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124">
@@ -19166,7 +19169,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q124" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R124" s="5">
         <f t="shared" si="22"/>
@@ -19201,7 +19204,7 @@
         <v>58</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>3</v>
@@ -19214,7 +19217,7 @@
         <v>1008</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125">
@@ -19242,7 +19245,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q125" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R125" s="5">
         <f t="shared" si="22"/>
@@ -19277,7 +19280,7 @@
         <v>58</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>3</v>
@@ -19290,7 +19293,7 @@
         <v>1008</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126">
@@ -19318,7 +19321,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q126" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R126" s="5">
         <f t="shared" si="22"/>
@@ -19353,7 +19356,7 @@
         <v>58</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>3</v>
@@ -19366,7 +19369,7 @@
         <v>1008</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J127" s="6"/>
       <c r="K127">
@@ -19394,7 +19397,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q127" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R127" s="5">
         <f t="shared" si="22"/>
@@ -19429,7 +19432,7 @@
         <v>58</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>3</v>
@@ -19442,7 +19445,7 @@
         <v>1008</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J128" s="6"/>
       <c r="K128">
@@ -19470,7 +19473,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q128" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R128" s="5">
         <f t="shared" si="22"/>
@@ -19505,7 +19508,7 @@
         <v>58</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>3</v>
@@ -19518,7 +19521,7 @@
         <v>1008</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J129" s="6"/>
       <c r="K129">
@@ -19546,7 +19549,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q129" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R129" s="5">
         <f t="shared" si="22"/>
@@ -19581,7 +19584,7 @@
         <v>58</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>3</v>
@@ -19594,7 +19597,7 @@
         <v>1008</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J130" s="6"/>
       <c r="K130">
@@ -19622,7 +19625,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q130" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R130" s="5">
         <f t="shared" si="22"/>
@@ -19657,7 +19660,7 @@
         <v>58</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>3</v>
@@ -19670,7 +19673,7 @@
         <v>1008</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J131" s="6"/>
       <c r="K131">
@@ -19698,7 +19701,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q131" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R131" s="5">
         <f t="shared" si="22"/>
@@ -19733,7 +19736,7 @@
         <v>58</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>3</v>
@@ -19746,7 +19749,7 @@
         <v>1008</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J132" s="6"/>
       <c r="K132">
@@ -19774,7 +19777,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q132" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R132" s="5">
         <f t="shared" si="22"/>
@@ -19809,7 +19812,7 @@
         <v>58</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>3</v>
@@ -19822,7 +19825,7 @@
         <v>1008</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J133" s="6"/>
       <c r="K133">
@@ -19850,7 +19853,7 @@
         <v>7146.72</v>
       </c>
       <c r="Q133" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R133" s="5">
         <f t="shared" ref="R133:R196" si="35">IF(B133="","",IF(J133&lt;&gt;"",J133,B133+IFERROR(INDEX(LagsP90,MATCH(D133,Origenes,0)),K133)))</f>
@@ -30277,12 +30280,12 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="75">
@@ -30293,61 +30296,61 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>178</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -31551,41 +31554,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45">
       <c r="A5" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>178</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -32084,7 +32087,7 @@
     </row>
     <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
@@ -32100,7 +32103,7 @@
     </row>
     <row r="21" spans="1:12" ht="33.950000000000003" customHeight="1">
       <c r="A21" s="44" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B21" s="44"/>
       <c r="C21" s="44"/>
@@ -32152,12 +32155,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -32175,21 +32178,21 @@
         <v>173</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B6" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32210,7 +32213,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B7" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32252,7 +32255,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B9" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+0),PrSemana,0)),"")</f>
@@ -32286,21 +32289,21 @@
         <v>173</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B13" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32321,7 +32324,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B14" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32363,7 +32366,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="39" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B16" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+7),PrSemana,0)),"")</f>
@@ -32397,21 +32400,21 @@
         <v>173</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>178</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B20" s="7">
         <f ca="1">IFERROR(INDEX(PrBR,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32432,7 +32435,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B21" s="7">
         <f ca="1">IFERROR(INDEX(PrPY,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32474,7 +32477,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B23" s="40">
         <f ca="1">IFERROR(INDEX(PrProy,MATCH((FechaHoy-WEEKDAY(FechaHoy,2)+1+14),PrSemana,0)),"")</f>
@@ -32495,7 +32498,7 @@
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -32535,7 +32538,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="45" t="str">
         <f>"Dictados que Aloha aun no tiene: "&amp;COUNTIFS(CgEstado,"Dictado",CgCuenta,1)&amp;" camiones. Pasan a Aloha cuando se cargan en el sistema."</f>
-        <v>Dictados que Aloha aun no tiene: 31 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
+        <v>Dictados que Aloha aun no tiene: 32 camiones. Pasan a Aloha cuando se cargan en el sistema.</v>
       </c>
       <c r="B29" s="46"/>
       <c r="C29" s="46"/>
@@ -32661,12 +32664,12 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="45">
@@ -32677,46 +32680,46 @@
         <v>160</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -32960,15 +32963,15 @@
       </c>
       <c r="K9" s="7">
         <f t="shared" si="0"/>
-        <v>17918</v>
+        <v>16938</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>25798</v>
+        <v>24818</v>
       </c>
       <c r="M9">
         <f ca="1">IF(AND(L9&lt;MinimoSabado,Proyeccion!J9&gt;=FechaHoy),ROUNDUP((MinimoSabado-L9)/CajasProm,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -33026,15 +33029,15 @@
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
-        <v>14014</v>
+        <v>14994</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>21812</v>
+        <v>22812</v>
       </c>
       <c r="M10">
         <f ca="1">IF(AND(L10&lt;MinimoSabado,Proyeccion!J10&gt;=FechaHoy),ROUNDUP((MinimoSabado-L10)/CajasProm,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -33579,7 +33582,7 @@
     </row>
     <row r="20" spans="1:16" ht="63.95" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
